--- a/Översikt KARLSKOGA.xlsx
+++ b/Översikt KARLSKOGA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE201"/>
+  <dimension ref="A1:AE200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45562</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>45958</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>45989</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>44510</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>46100</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>45989</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>44473</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>46066</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 60085-2021</t>
+          <t>A 63187-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1597,10 +1597,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44495</v>
+        <v>46010</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1612,20 +1612,25 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>3.6</v>
+        <v>1.3</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1640,18 +1645,130 @@
         <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
       </c>
       <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Talltita
+Bronshjon
+Korallblylav
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 63187-2025 artfynd.xlsx", "A 63187-2025")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 63187-2025 karta.png", "A 63187-2025")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 63187-2025 georefererad karta.tif", "A 63187-2025")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 63187-2025 FSC-klagomål.docx", "A 63187-2025")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 63187-2025 FSC-klagomål mail.docx", "A 63187-2025")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 63187-2025 tillsynsbegäran.docx", "A 63187-2025")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 63187-2025 tillsynsbegäran mail.docx", "A 63187-2025")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 63187-2025 prioriterade fågelarter.docx", "A 63187-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 60085-2021</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>44495</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>KARLSKOGA</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4</v>
+      </c>
+      <c r="T11" t="n">
         <v>5</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U11" t="n">
         <v>1</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Citronfingersvamp
 Mörk husmossa
@@ -1659,149 +1776,32 @@
 Västlig hakmossa</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 60085-2021 artfynd.xlsx", "A 60085-2021")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 60085-2021 karta.png", "A 60085-2021")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 60085-2021 georefererad karta.tif", "A 60085-2021")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 60085-2021 FSC-klagomål.docx", "A 60085-2021")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 60085-2021 FSC-klagomål mail.docx", "A 60085-2021")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 60085-2021 tillsynsbegäran.docx", "A 60085-2021")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 60085-2021 tillsynsbegäran mail.docx", "A 60085-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 63187-2025</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>46010</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>KARLSKOGA</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J11" t="n">
-        <v>2</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>4</v>
-      </c>
-      <c r="T11" t="n">
-        <v>4</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Talltita
-Bronshjon
-Korallblylav
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 63187-2025 artfynd.xlsx", "A 63187-2025")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 63187-2025 karta.png", "A 63187-2025")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 63187-2025 georefererad karta.tif", "A 63187-2025")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 63187-2025 FSC-klagomål.docx", "A 63187-2025")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 63187-2025 FSC-klagomål mail.docx", "A 63187-2025")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 63187-2025 tillsynsbegäran.docx", "A 63187-2025")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 63187-2025 tillsynsbegäran mail.docx", "A 63187-2025")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 63187-2025 prioriterade fågelarter.docx", "A 63187-2025")</f>
         <v/>
       </c>
     </row>
@@ -1825,7 +1825,7 @@
         <v>46136</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 18428-2026</t>
+          <t>A 63185-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1935,14 +1935,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46127</v>
+        <v>46010</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1960,10 +1960,10 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1972,615 +1972,615 @@
         <v>1</v>
       </c>
       <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>1</v>
       </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2</v>
-      </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>3</v>
       </c>
       <c r="T13" t="n">
+        <v>11</v>
+      </c>
+      <c r="U13" t="n">
+        <v>9</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Talltita
+Brudborste
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 63185-2025 artfynd.xlsx", "A 63185-2025")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 63185-2025 karta.png", "A 63185-2025")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 63185-2025 georefererad karta.tif", "A 63185-2025")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 63185-2025 FSC-klagomål.docx", "A 63185-2025")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 63185-2025 FSC-klagomål mail.docx", "A 63185-2025")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 63185-2025 tillsynsbegäran.docx", "A 63185-2025")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 63185-2025 tillsynsbegäran mail.docx", "A 63185-2025")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 63185-2025 prioriterade fågelarter.docx", "A 63185-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 18428-2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>46127</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>KARLSKOGA</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>6</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3</v>
+      </c>
+      <c r="T14" t="n">
         <v>17</v>
       </c>
-      <c r="U13" t="n">
+      <c r="U14" t="n">
         <v>17</v>
       </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Skuggblåslav
 Tjäder</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 18428-2026 artfynd.xlsx", "A 18428-2026")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 18428-2026 karta.png", "A 18428-2026")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 18428-2026 georefererad karta.tif", "A 18428-2026")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 18428-2026 FSC-klagomål.docx", "A 18428-2026")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 18428-2026 FSC-klagomål mail.docx", "A 18428-2026")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 18428-2026 tillsynsbegäran.docx", "A 18428-2026")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 18428-2026 tillsynsbegäran mail.docx", "A 18428-2026")</f>
         <v/>
       </c>
-      <c r="AE13">
+      <c r="AE14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 18428-2026 prioriterade fågelarter.docx", "A 18428-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 63185-2025</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 35696-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
-      <c r="D14" s="1" t="n">
+      <c r="D15" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>KARLSKOGA</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>4</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Grönpyrola
+Mattlummer
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 35696-2026 artfynd.xlsx", "A 35696-2026")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 35696-2026 karta.png", "A 35696-2026")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 35696-2026 georefererad karta.tif", "A 35696-2026")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 35696-2026 FSC-klagomål.docx", "A 35696-2026")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 35696-2026 FSC-klagomål mail.docx", "A 35696-2026")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 35696-2026 tillsynsbegäran.docx", "A 35696-2026")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 35696-2026 tillsynsbegäran mail.docx", "A 35696-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 20112-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>46136</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>KARLSKOGA</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="n">
+        <v>4</v>
+      </c>
+      <c r="U16" t="n">
+        <v>4</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett
+Spillkråka
+Tofsmes</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 20112-2026 artfynd.xlsx", "A 20112-2026")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 20112-2026 karta.png", "A 20112-2026")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 20112-2026 georefererad karta.tif", "A 20112-2026")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 20112-2026 FSC-klagomål.docx", "A 20112-2026")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 20112-2026 FSC-klagomål mail.docx", "A 20112-2026")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 20112-2026 tillsynsbegäran.docx", "A 20112-2026")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 20112-2026 tillsynsbegäran mail.docx", "A 20112-2026")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 20112-2026 prioriterade fågelarter.docx", "A 20112-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 20108-2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>46136</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>KARLSKOGA</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>5</v>
+      </c>
+      <c r="U17" t="n">
+        <v>5</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Talltita
+Vedticka</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 20108-2026 artfynd.xlsx", "A 20108-2026")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 20108-2026 karta.png", "A 20108-2026")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 20108-2026 georefererad karta.tif", "A 20108-2026")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 20108-2026 FSC-klagomål.docx", "A 20108-2026")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 20108-2026 FSC-klagomål mail.docx", "A 20108-2026")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 20108-2026 tillsynsbegäran.docx", "A 20108-2026")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 20108-2026 tillsynsbegäran mail.docx", "A 20108-2026")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 20108-2026 prioriterade fågelarter.docx", "A 20108-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>S 3545-2025</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
         <v>46010</v>
       </c>
-      <c r="E14" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>KARLSKOGA</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
+      <c r="E18" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>KARLSKOGA</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I14" t="n">
+      <c r="I18" t="n">
         <v>8.4</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J18" t="n">
         <v>2</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
         <v>1</v>
       </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
         <v>1</v>
       </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
         <v>3</v>
       </c>
-      <c r="T14" t="n">
+      <c r="T18" t="n">
         <v>11</v>
       </c>
-      <c r="U14" t="n">
+      <c r="U18" t="n">
         <v>9</v>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Talltita
 Brudborste
 Revlummer</t>
         </is>
       </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 63185-2025 artfynd.xlsx", "A 63185-2025")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 63185-2025 karta.png", "A 63185-2025")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 63185-2025 georefererad karta.tif", "A 63185-2025")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 63185-2025 FSC-klagomål.docx", "A 63185-2025")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 63185-2025 FSC-klagomål mail.docx", "A 63185-2025")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 63185-2025 tillsynsbegäran.docx", "A 63185-2025")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 63185-2025 tillsynsbegäran mail.docx", "A 63185-2025")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 63185-2025 prioriterade fågelarter.docx", "A 63185-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 35696-2026</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>KARLSKOGA</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3</v>
-      </c>
-      <c r="T15" t="n">
-        <v>4</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Grönpyrola
-Mattlummer
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 35696-2026 artfynd.xlsx", "A 35696-2026")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 35696-2026 karta.png", "A 35696-2026")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 35696-2026 georefererad karta.tif", "A 35696-2026")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 35696-2026 FSC-klagomål.docx", "A 35696-2026")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 35696-2026 FSC-klagomål mail.docx", "A 35696-2026")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 35696-2026 tillsynsbegäran.docx", "A 35696-2026")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 35696-2026 tillsynsbegäran mail.docx", "A 35696-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 20112-2026</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>46136</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>KARLSKOGA</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J16" t="n">
-        <v>3</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3</v>
-      </c>
-      <c r="T16" t="n">
-        <v>4</v>
-      </c>
-      <c r="U16" t="n">
-        <v>4</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett
-Spillkråka
-Tofsmes</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 20112-2026 artfynd.xlsx", "A 20112-2026")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 20112-2026 karta.png", "A 20112-2026")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 20112-2026 georefererad karta.tif", "A 20112-2026")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 20112-2026 FSC-klagomål.docx", "A 20112-2026")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 20112-2026 FSC-klagomål mail.docx", "A 20112-2026")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 20112-2026 tillsynsbegäran.docx", "A 20112-2026")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 20112-2026 tillsynsbegäran mail.docx", "A 20112-2026")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 20112-2026 prioriterade fågelarter.docx", "A 20112-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 20108-2026</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>46136</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>KARLSKOGA</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>5</v>
-      </c>
-      <c r="U17" t="n">
-        <v>5</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Talltita
-Vedticka</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 20108-2026 artfynd.xlsx", "A 20108-2026")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 20108-2026 karta.png", "A 20108-2026")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 20108-2026 georefererad karta.tif", "A 20108-2026")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 20108-2026 FSC-klagomål.docx", "A 20108-2026")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 20108-2026 FSC-klagomål mail.docx", "A 20108-2026")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 20108-2026 tillsynsbegäran.docx", "A 20108-2026")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 20108-2026 tillsynsbegäran mail.docx", "A 20108-2026")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 20108-2026 prioriterade fågelarter.docx", "A 20108-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>S 3545-2025</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>46010</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>KARLSKOGA</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>11</v>
-      </c>
-      <c r="U18" t="n">
-        <v>9</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Talltita
-Brudborste
-Revlummer</t>
-        </is>
-      </c>
       <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/S 3545-2025 artfynd.xlsx", "S 3545-2025")</f>
         <v/>
@@ -2634,7 +2634,7 @@
         <v>45553</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>44817</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 58091-2022</t>
+          <t>A 63188-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2852,10 +2852,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44900</v>
+        <v>46010</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2882,7 +2882,7 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2897,7 +2897,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2909,46 +2909,50 @@
         <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Hårklomossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 58091-2022 artfynd.xlsx", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 63188-2025 artfynd.xlsx", "A 63188-2025")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 58091-2022 karta.png", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 63188-2025 karta.png", "A 63188-2025")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 58091-2022 georefererad karta.tif", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 63188-2025 georefererad karta.tif", "A 63188-2025")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 58091-2022 FSC-klagomål.docx", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 63188-2025 FSC-klagomål.docx", "A 63188-2025")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 58091-2022 FSC-klagomål mail.docx", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 63188-2025 FSC-klagomål mail.docx", "A 63188-2025")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 58091-2022 tillsynsbegäran.docx", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 63188-2025 tillsynsbegäran.docx", "A 63188-2025")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 58091-2022 tillsynsbegäran mail.docx", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 63188-2025 tillsynsbegäran mail.docx", "A 63188-2025")</f>
+        <v/>
+      </c>
+      <c r="AE21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 63188-2025 prioriterade fågelarter.docx", "A 63188-2025")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 28566-2024</t>
+          <t>A 52377-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2962,10 +2966,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45478</v>
+        <v>45953</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2977,8 +2981,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -3018,42 +3027,42 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 28566-2024 artfynd.xlsx", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 52377-2025 artfynd.xlsx", "A 52377-2025")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 28566-2024 karta.png", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 52377-2025 karta.png", "A 52377-2025")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 28566-2024 georefererad karta.tif", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 52377-2025 georefererad karta.tif", "A 52377-2025")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 28566-2024 FSC-klagomål.docx", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 52377-2025 FSC-klagomål.docx", "A 52377-2025")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 28566-2024 FSC-klagomål mail.docx", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 52377-2025 FSC-klagomål mail.docx", "A 52377-2025")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 28566-2024 tillsynsbegäran.docx", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 52377-2025 tillsynsbegäran.docx", "A 52377-2025")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 28566-2024 tillsynsbegäran mail.docx", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 52377-2025 tillsynsbegäran mail.docx", "A 52377-2025")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 63188-2025</t>
+          <t>A 16784-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3067,10 +3076,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46010</v>
+        <v>46113</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3088,7 +3097,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.1</v>
+        <v>4.2</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -3097,7 +3106,7 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -3112,7 +3121,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -3124,50 +3133,46 @@
         <v>2</v>
       </c>
       <c r="U23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Hårklomossa</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 63188-2025 artfynd.xlsx", "A 63188-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 16784-2026 artfynd.xlsx", "A 16784-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 63188-2025 karta.png", "A 63188-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 16784-2026 karta.png", "A 16784-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 63188-2025 georefererad karta.tif", "A 63188-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 16784-2026 georefererad karta.tif", "A 16784-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 63188-2025 FSC-klagomål.docx", "A 63188-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 16784-2026 FSC-klagomål.docx", "A 16784-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 63188-2025 FSC-klagomål mail.docx", "A 63188-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 16784-2026 FSC-klagomål mail.docx", "A 16784-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 63188-2025 tillsynsbegäran.docx", "A 63188-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 16784-2026 tillsynsbegäran.docx", "A 16784-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 63188-2025 tillsynsbegäran mail.docx", "A 63188-2025")</f>
-        <v/>
-      </c>
-      <c r="AE23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 63188-2025 prioriterade fågelarter.docx", "A 63188-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 16784-2026 tillsynsbegäran mail.docx", "A 16784-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 52377-2025</t>
+          <t>A 18427-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3181,10 +3186,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45953</v>
+        <v>46127</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3202,7 +3207,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3242,42 +3247,46 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 52377-2025 artfynd.xlsx", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 18427-2026 artfynd.xlsx", "A 18427-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 52377-2025 karta.png", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 18427-2026 karta.png", "A 18427-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 52377-2025 georefererad karta.tif", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 18427-2026 georefererad karta.tif", "A 18427-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 52377-2025 FSC-klagomål.docx", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 18427-2026 FSC-klagomål.docx", "A 18427-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 52377-2025 FSC-klagomål mail.docx", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 18427-2026 FSC-klagomål mail.docx", "A 18427-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 52377-2025 tillsynsbegäran.docx", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 18427-2026 tillsynsbegäran.docx", "A 18427-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 52377-2025 tillsynsbegäran mail.docx", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 18427-2026 tillsynsbegäran mail.docx", "A 18427-2026")</f>
+        <v/>
+      </c>
+      <c r="AE24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 18427-2026 prioriterade fågelarter.docx", "A 18427-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 16784-2026</t>
+          <t>A 19233-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3291,10 +3300,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46113</v>
+        <v>46132</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3306,19 +3315,14 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>4.2</v>
+        <v>1.6</v>
       </c>
       <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
         <v>1</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -3345,49 +3349,49 @@
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Hårklomossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 16784-2026 artfynd.xlsx", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 19233-2026 artfynd.xlsx", "A 19233-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 16784-2026 karta.png", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 19233-2026 karta.png", "A 19233-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 16784-2026 georefererad karta.tif", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 19233-2026 georefererad karta.tif", "A 19233-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 16784-2026 FSC-klagomål.docx", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 19233-2026 FSC-klagomål.docx", "A 19233-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 16784-2026 FSC-klagomål mail.docx", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 19233-2026 FSC-klagomål mail.docx", "A 19233-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 16784-2026 tillsynsbegäran.docx", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 19233-2026 tillsynsbegäran.docx", "A 19233-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 16784-2026 tillsynsbegäran mail.docx", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 19233-2026 tillsynsbegäran mail.docx", "A 19233-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 18427-2026</t>
+          <t>A 21019-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3401,10 +3405,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46127</v>
+        <v>46145</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3422,7 +3426,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3</v>
+        <v>4.7</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3458,50 +3462,46 @@
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 18427-2026 artfynd.xlsx", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 21019-2026 artfynd.xlsx", "A 21019-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 18427-2026 karta.png", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 21019-2026 karta.png", "A 21019-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 18427-2026 georefererad karta.tif", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 21019-2026 georefererad karta.tif", "A 21019-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 18427-2026 FSC-klagomål.docx", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 21019-2026 FSC-klagomål.docx", "A 21019-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 18427-2026 FSC-klagomål mail.docx", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 21019-2026 FSC-klagomål mail.docx", "A 21019-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 18427-2026 tillsynsbegäran.docx", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 21019-2026 tillsynsbegäran.docx", "A 21019-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 18427-2026 tillsynsbegäran mail.docx", "A 18427-2026")</f>
-        <v/>
-      </c>
-      <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 18427-2026 prioriterade fågelarter.docx", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 21019-2026 tillsynsbegäran mail.docx", "A 21019-2026")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 19233-2026</t>
+          <t>A 25093-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3515,10 +3515,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46132</v>
+        <v>46175</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3530,8 +3530,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>1.6</v>
+        <v>4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3567,46 +3572,46 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 19233-2026 artfynd.xlsx", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 25093-2026 artfynd.xlsx", "A 25093-2026")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 19233-2026 karta.png", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 25093-2026 karta.png", "A 25093-2026")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 19233-2026 georefererad karta.tif", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 25093-2026 georefererad karta.tif", "A 25093-2026")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 19233-2026 FSC-klagomål.docx", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 25093-2026 FSC-klagomål.docx", "A 25093-2026")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 19233-2026 FSC-klagomål mail.docx", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 25093-2026 FSC-klagomål mail.docx", "A 25093-2026")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 19233-2026 tillsynsbegäran.docx", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 25093-2026 tillsynsbegäran.docx", "A 25093-2026")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 19233-2026 tillsynsbegäran mail.docx", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 25093-2026 tillsynsbegäran mail.docx", "A 25093-2026")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 21019-2026</t>
+          <t>A 30915-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3620,10 +3625,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46145</v>
+        <v>46213</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3637,11 +3642,11 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>4.7</v>
+        <v>8.9</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
@@ -3681,42 +3686,42 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 21019-2026 artfynd.xlsx", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 30915-2026 artfynd.xlsx", "A 30915-2026")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 21019-2026 karta.png", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 30915-2026 karta.png", "A 30915-2026")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 21019-2026 georefererad karta.tif", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 30915-2026 georefererad karta.tif", "A 30915-2026")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 21019-2026 FSC-klagomål.docx", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 30915-2026 FSC-klagomål.docx", "A 30915-2026")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 21019-2026 FSC-klagomål mail.docx", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 30915-2026 FSC-klagomål mail.docx", "A 30915-2026")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 21019-2026 tillsynsbegäran.docx", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 30915-2026 tillsynsbegäran.docx", "A 30915-2026")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 21019-2026 tillsynsbegäran mail.docx", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 30915-2026 tillsynsbegäran mail.docx", "A 30915-2026")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 28474-2023</t>
+          <t>A 35199-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3730,10 +3735,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45103</v>
+        <v>46260</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3745,8 +3750,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -3782,50 +3792,46 @@
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Blåhake</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 28474-2023 artfynd.xlsx", "A 28474-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 35199-2026 artfynd.xlsx", "A 35199-2026")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 28474-2023 karta.png", "A 28474-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 35199-2026 karta.png", "A 35199-2026")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 28474-2023 georefererad karta.tif", "A 28474-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 35199-2026 georefererad karta.tif", "A 35199-2026")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 28474-2023 FSC-klagomål.docx", "A 28474-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 35199-2026 FSC-klagomål.docx", "A 35199-2026")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 28474-2023 FSC-klagomål mail.docx", "A 28474-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 35199-2026 FSC-klagomål mail.docx", "A 35199-2026")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 28474-2023 tillsynsbegäran.docx", "A 28474-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 35199-2026 tillsynsbegäran.docx", "A 35199-2026")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 28474-2023 tillsynsbegäran mail.docx", "A 28474-2023")</f>
-        <v/>
-      </c>
-      <c r="AE29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 28474-2023 prioriterade fågelarter.docx", "A 28474-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 35199-2026 tillsynsbegäran mail.docx", "A 35199-2026")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 25093-2026</t>
+          <t>A 20110-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3839,10 +3845,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46175</v>
+        <v>46136</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3860,13 +3866,13 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -3900,42 +3906,42 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 25093-2026 artfynd.xlsx", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 20110-2026 artfynd.xlsx", "A 20110-2026")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 25093-2026 karta.png", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 20110-2026 karta.png", "A 20110-2026")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 25093-2026 georefererad karta.tif", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 20110-2026 georefererad karta.tif", "A 20110-2026")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 25093-2026 FSC-klagomål.docx", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 20110-2026 FSC-klagomål.docx", "A 20110-2026")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 25093-2026 FSC-klagomål mail.docx", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 20110-2026 FSC-klagomål mail.docx", "A 20110-2026")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 25093-2026 tillsynsbegäran.docx", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 20110-2026 tillsynsbegäran.docx", "A 20110-2026")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 25093-2026 tillsynsbegäran mail.docx", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 20110-2026 tillsynsbegäran mail.docx", "A 20110-2026")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 40528-2024</t>
+          <t>A 28474-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3949,10 +3955,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45555</v>
+        <v>45103</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3965,7 +3971,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.8</v>
+        <v>5.1</v>
       </c>
       <c r="J31" t="n">
         <v>1</v>
@@ -3974,7 +3980,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -3989,7 +3995,7 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -4005,42 +4011,46 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Blåhake</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 40528-2024 artfynd.xlsx", "A 40528-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 28474-2023 artfynd.xlsx", "A 28474-2023")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 40528-2024 karta.png", "A 40528-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 28474-2023 karta.png", "A 28474-2023")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 40528-2024 georefererad karta.tif", "A 40528-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 28474-2023 georefererad karta.tif", "A 28474-2023")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 40528-2024 FSC-klagomål.docx", "A 40528-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 28474-2023 FSC-klagomål.docx", "A 28474-2023")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 40528-2024 FSC-klagomål mail.docx", "A 40528-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 28474-2023 FSC-klagomål mail.docx", "A 28474-2023")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 40528-2024 tillsynsbegäran.docx", "A 40528-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 28474-2023 tillsynsbegäran.docx", "A 28474-2023")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 40528-2024 tillsynsbegäran mail.docx", "A 40528-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 28474-2023 tillsynsbegäran mail.docx", "A 28474-2023")</f>
+        <v/>
+      </c>
+      <c r="AE31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 28474-2023 prioriterade fågelarter.docx", "A 28474-2023")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 30915-2026</t>
+          <t>A 58091-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4054,10 +4064,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46213</v>
+        <v>44900</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4071,11 +4081,11 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>8.9</v>
+        <v>2.1</v>
       </c>
       <c r="J32" t="n">
         <v>1</v>
@@ -4108,49 +4118,49 @@
         <v>1</v>
       </c>
       <c r="T32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Hårklomossa</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 30915-2026 artfynd.xlsx", "A 30915-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 58091-2022 artfynd.xlsx", "A 58091-2022")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 30915-2026 karta.png", "A 30915-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 58091-2022 karta.png", "A 58091-2022")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 30915-2026 georefererad karta.tif", "A 30915-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 58091-2022 georefererad karta.tif", "A 58091-2022")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 30915-2026 FSC-klagomål.docx", "A 30915-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 58091-2022 FSC-klagomål.docx", "A 58091-2022")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 30915-2026 FSC-klagomål mail.docx", "A 30915-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 58091-2022 FSC-klagomål mail.docx", "A 58091-2022")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 30915-2026 tillsynsbegäran.docx", "A 30915-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 58091-2022 tillsynsbegäran.docx", "A 58091-2022")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 30915-2026 tillsynsbegäran mail.docx", "A 30915-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 58091-2022 tillsynsbegäran mail.docx", "A 58091-2022")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 35199-2026</t>
+          <t>A 28566-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4164,10 +4174,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46260</v>
+        <v>45478</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4179,13 +4189,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>5.6</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
         <v>1</v>
@@ -4194,7 +4199,7 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -4209,7 +4214,7 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -4221,46 +4226,46 @@
         <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 35199-2026 artfynd.xlsx", "A 35199-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 28566-2024 artfynd.xlsx", "A 28566-2024")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 35199-2026 karta.png", "A 35199-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 28566-2024 karta.png", "A 28566-2024")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 35199-2026 georefererad karta.tif", "A 35199-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 28566-2024 georefererad karta.tif", "A 28566-2024")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 35199-2026 FSC-klagomål.docx", "A 35199-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 28566-2024 FSC-klagomål.docx", "A 28566-2024")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 35199-2026 FSC-klagomål mail.docx", "A 35199-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 28566-2024 FSC-klagomål mail.docx", "A 28566-2024")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 35199-2026 tillsynsbegäran.docx", "A 35199-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 28566-2024 tillsynsbegäran.docx", "A 28566-2024")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 35199-2026 tillsynsbegäran mail.docx", "A 35199-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 28566-2024 tillsynsbegäran mail.docx", "A 28566-2024")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 20110-2026</t>
+          <t>A 40528-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4274,10 +4279,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46136</v>
+        <v>45555</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4289,13 +4294,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>5.4</v>
+        <v>2.8</v>
       </c>
       <c r="J34" t="n">
         <v>1</v>
@@ -4335,59 +4335,59 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 20110-2026 artfynd.xlsx", "A 20110-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 40528-2024 artfynd.xlsx", "A 40528-2024")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 20110-2026 karta.png", "A 20110-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 40528-2024 karta.png", "A 40528-2024")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 20110-2026 georefererad karta.tif", "A 20110-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 40528-2024 georefererad karta.tif", "A 40528-2024")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 20110-2026 FSC-klagomål.docx", "A 20110-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 40528-2024 FSC-klagomål.docx", "A 40528-2024")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 20110-2026 FSC-klagomål mail.docx", "A 20110-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 40528-2024 FSC-klagomål mail.docx", "A 40528-2024")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 20110-2026 tillsynsbegäran.docx", "A 20110-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 40528-2024 tillsynsbegäran.docx", "A 40528-2024")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 20110-2026 tillsynsbegäran mail.docx", "A 20110-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 40528-2024 tillsynsbegäran mail.docx", "A 40528-2024")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>S 6543-2021</t>
+          <t>A 72803-2021</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44453</v>
+        <v>44546</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4399,19 +4399,14 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -4435,52 +4430,20 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
       </c>
-      <c r="V35" s="2" t="inlineStr">
-        <is>
-          <t>Bårdlav</t>
-        </is>
-      </c>
-      <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/S 6543-2021 artfynd.xlsx", "S 6543-2021")</f>
-        <v/>
-      </c>
-      <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/S 6543-2021 karta.png", "S 6543-2021")</f>
-        <v/>
-      </c>
-      <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/S 6543-2021 georefererad karta.tif", "S 6543-2021")</f>
-        <v/>
-      </c>
-      <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/S 6543-2021 FSC-klagomål.docx", "S 6543-2021")</f>
-        <v/>
-      </c>
-      <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/S 6543-2021 FSC-klagomål mail.docx", "S 6543-2021")</f>
-        <v/>
-      </c>
-      <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/S 6543-2021 tillsynsbegäran.docx", "S 6543-2021")</f>
-        <v/>
-      </c>
-      <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/S 6543-2021 tillsynsbegäran mail.docx", "S 6543-2021")</f>
-        <v/>
-      </c>
+      <c r="V35" s="2" t="inlineStr"/>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 72803-2021</t>
+          <t>A 25548-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4494,10 +4457,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44546</v>
+        <v>44732</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4510,7 +4473,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4553,7 +4516,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 25548-2022</t>
+          <t>A 50991-2021</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4567,10 +4530,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44732</v>
+        <v>44460</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4583,7 +4546,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4626,7 +4589,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 50991-2021</t>
+          <t>A 64869-2021</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4640,10 +4603,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44460</v>
+        <v>44512</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4655,8 +4618,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>0.8</v>
+        <v>3.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4699,7 +4667,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 64869-2021</t>
+          <t>A 22861-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4713,10 +4681,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44512</v>
+        <v>44715</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4728,13 +4696,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>3.6</v>
+        <v>0.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4777,7 +4740,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 22861-2022</t>
+          <t>A 63671-2021</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4791,10 +4754,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44715</v>
+        <v>44508</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4806,8 +4769,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4850,7 +4818,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 63671-2021</t>
+          <t>A 56435-2021</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4864,10 +4832,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44508</v>
+        <v>44480</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4879,13 +4847,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4928,7 +4891,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 56435-2021</t>
+          <t>A 37582-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4942,10 +4905,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44480</v>
+        <v>44809</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4958,7 +4921,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -5001,7 +4964,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 37582-2022</t>
+          <t>A 38012-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5015,10 +4978,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44809</v>
+        <v>44811</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5031,7 +4994,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.8</v>
+        <v>3.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -5074,7 +5037,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 38012-2022</t>
+          <t>A 11081-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5084,14 +5047,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44811</v>
+        <v>44628</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5103,8 +5066,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>3.7</v>
+        <v>0.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5147,7 +5115,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 11081-2022</t>
+          <t>A 37584-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5157,14 +5125,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44628</v>
+        <v>44809</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5176,13 +5144,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>0.7</v>
+        <v>4.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5225,7 +5188,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 37584-2022</t>
+          <t>A 21612-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5239,10 +5202,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44809</v>
+        <v>44706</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5255,7 +5218,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>4.9</v>
+        <v>0.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5298,7 +5261,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 21612-2022</t>
+          <t>A 21622-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5315,7 +5278,7 @@
         <v>44706</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5328,7 +5291,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5371,7 +5334,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 21622-2022</t>
+          <t>A 39027-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5385,10 +5348,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44706</v>
+        <v>44817</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5400,8 +5363,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5444,7 +5412,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 39027-2022</t>
+          <t>A 58390-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5458,10 +5426,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44817</v>
+        <v>45633</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5473,13 +5441,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5522,7 +5485,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 8803-2025</t>
+          <t>A 35471-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5536,10 +5499,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45712</v>
+        <v>45531</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5552,7 +5515,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5595,7 +5558,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 35445-2024</t>
+          <t>A 4164-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5609,10 +5572,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45531</v>
+        <v>44588</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5624,8 +5587,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5668,7 +5636,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 39337-2022</t>
+          <t>A 9712-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5682,10 +5650,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44817</v>
+        <v>45362</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5697,8 +5665,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5741,7 +5714,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 56887-2022</t>
+          <t>A 42804-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5751,14 +5724,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44894</v>
+        <v>45182</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5770,8 +5743,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5814,7 +5792,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 20289-2024</t>
+          <t>A 9510-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5828,10 +5806,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45435</v>
+        <v>44981</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5843,13 +5821,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5892,7 +5865,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 38190-2024</t>
+          <t>A 1309-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5906,10 +5879,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45545</v>
+        <v>45303</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5922,7 +5895,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5965,7 +5938,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 9712-2024</t>
+          <t>A 64066-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5975,14 +5948,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45362</v>
+        <v>46013</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5994,13 +5967,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -6043,7 +6011,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 15256-2025</t>
+          <t>A 63628-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6057,10 +6025,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45744</v>
+        <v>46014</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6072,13 +6040,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>5.5</v>
+        <v>3.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6121,7 +6084,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 4058-2022</t>
+          <t>A 35444-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6135,10 +6098,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44588</v>
+        <v>45531</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6151,7 +6114,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6194,7 +6157,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 43075-2023</t>
+          <t>A 27498-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6208,10 +6171,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45182</v>
+        <v>45813</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6224,7 +6187,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6284,7 +6247,7 @@
         <v>44720</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6340,7 +6303,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 38196-2024</t>
+          <t>A 17815-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6354,10 +6317,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45545</v>
+        <v>45758</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6369,8 +6332,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6413,7 +6381,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 35444-2024</t>
+          <t>A 1788-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6427,10 +6395,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45531</v>
+        <v>46034</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6443,7 +6411,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6486,7 +6454,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 35471-2024</t>
+          <t>A 47201-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6500,10 +6468,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45531</v>
+        <v>45196</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6516,7 +6484,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6559,7 +6527,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 54680-2021</t>
+          <t>A 45664-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6573,10 +6541,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44473</v>
+        <v>45923</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6588,8 +6556,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>2.9</v>
+        <v>9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6632,7 +6605,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 30102-2025</t>
+          <t>A 61396-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6646,10 +6619,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45826</v>
+        <v>45264</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6662,7 +6635,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6705,7 +6678,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 53647-2023</t>
+          <t>A 2911-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6719,10 +6692,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45230</v>
+        <v>46038</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6735,7 +6708,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6795,7 +6768,7 @@
         <v>45454</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6851,7 +6824,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 58390-2024</t>
+          <t>A 53647-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6865,10 +6838,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45633</v>
+        <v>45230</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6881,7 +6854,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6924,7 +6897,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 31397-2025</t>
+          <t>A 30102-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6938,10 +6911,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45833</v>
+        <v>45826</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6954,7 +6927,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6997,7 +6970,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 32287-2025</t>
+          <t>A 54680-2021</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7011,10 +6984,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45835</v>
+        <v>44473</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7026,13 +6999,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>10.9</v>
+        <v>2.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7075,7 +7043,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 24255-2024</t>
+          <t>A 8259-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7089,10 +7057,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45457</v>
+        <v>45708</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7105,7 +7073,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7148,7 +7116,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 17815-2025</t>
+          <t>A 24116-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7162,10 +7130,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45758</v>
+        <v>45456</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7177,13 +7145,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7226,7 +7189,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 18768-2025</t>
+          <t>A 31397-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7240,10 +7203,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45764</v>
+        <v>45833</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7255,13 +7218,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7304,7 +7262,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 42803-2023</t>
+          <t>A 47222-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7314,14 +7272,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45182</v>
+        <v>45586</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7339,7 +7297,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.7</v>
+        <v>5.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7382,7 +7340,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 20086-2024</t>
+          <t>A 32287-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7392,14 +7350,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45434</v>
+        <v>45835</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7411,8 +7369,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>1.5</v>
+        <v>10.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7472,7 +7435,7 @@
         <v>45918</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7528,7 +7491,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 9917-2026</t>
+          <t>A 35930-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7542,10 +7505,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46073</v>
+        <v>45148</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7557,8 +7520,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>3.1</v>
+        <v>5.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7618,7 +7586,7 @@
         <v>45918</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7674,7 +7642,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 9510-2023</t>
+          <t>A 63863-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7688,10 +7656,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44981</v>
+        <v>45278</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7704,7 +7672,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7747,7 +7715,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 59025-2024</t>
+          <t>A 9917-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7761,10 +7729,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45636</v>
+        <v>46073</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7776,13 +7744,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7825,7 +7788,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 13501-2025</t>
+          <t>A 50958-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7839,10 +7802,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45736</v>
+        <v>45946</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7855,7 +7818,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3.2</v>
+        <v>0.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7898,7 +7861,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 47094-2023</t>
+          <t>A 59938-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7912,10 +7875,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45196</v>
+        <v>45257</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7928,7 +7891,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7971,7 +7934,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 13473-2026</t>
+          <t>A 52828-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7985,10 +7948,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46094</v>
+        <v>45610</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8001,7 +7964,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8044,7 +8007,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 50958-2025</t>
+          <t>A 24255-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8058,10 +8021,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45946</v>
+        <v>45457</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8074,7 +8037,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8117,7 +8080,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 14580-2026</t>
+          <t>A 15256-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8131,10 +8094,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46101</v>
+        <v>45744</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8152,7 +8115,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.6</v>
+        <v>5.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8195,7 +8158,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 31921-2022</t>
+          <t>A 24115-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8209,10 +8172,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44777</v>
+        <v>45456</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8225,7 +8188,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.4</v>
+        <v>8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8268,7 +8231,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 42804-2023</t>
+          <t>A 13473-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8278,14 +8241,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45182</v>
+        <v>46094</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8297,13 +8260,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8346,7 +8304,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 39030-2022</t>
+          <t>A 12897-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8360,10 +8318,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44817</v>
+        <v>46092</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8375,13 +8333,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8424,7 +8377,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 8244-2025</t>
+          <t>A 14580-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8438,10 +8391,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45708</v>
+        <v>46101</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8453,8 +8406,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8497,7 +8455,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 28100-2024</t>
+          <t>A 16783-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8511,10 +8469,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45476</v>
+        <v>46113</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8526,8 +8484,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8570,7 +8533,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 12897-2026</t>
+          <t>A 16787-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8584,10 +8547,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46092</v>
+        <v>46113</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8599,8 +8562,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8643,7 +8611,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 51344-2023</t>
+          <t>A 16782-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8657,10 +8625,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45219</v>
+        <v>46113</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8674,11 +8642,11 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8721,7 +8689,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 16782-2026</t>
+          <t>A 15058-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8735,10 +8703,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46113</v>
+        <v>46104</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8750,13 +8718,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I93" t="n">
-        <v>2.6</v>
+        <v>4.3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8799,7 +8762,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 16783-2026</t>
+          <t>A 15060-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8813,10 +8776,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46113</v>
+        <v>46104</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8828,13 +8791,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>1.7</v>
+        <v>11.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8877,7 +8835,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 16787-2026</t>
+          <t>A 55025-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8891,10 +8849,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46113</v>
+        <v>45967</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8906,13 +8864,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8955,7 +8908,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 55025-2025</t>
+          <t>A 17734-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8969,10 +8922,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45967</v>
+        <v>46122</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8984,8 +8937,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I96" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9028,7 +8986,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 15060-2026</t>
+          <t>A 18768-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9042,10 +9000,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46104</v>
+        <v>45764</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9057,8 +9015,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I97" t="n">
-        <v>11.5</v>
+        <v>0.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9101,7 +9064,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 15058-2026</t>
+          <t>A 4801-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9115,10 +9078,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46104</v>
+        <v>45328</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9131,7 +9094,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>4.3</v>
+        <v>0.9</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9174,7 +9137,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 17734-2026</t>
+          <t>A 4802-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9188,10 +9151,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46122</v>
+        <v>45328</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9203,13 +9166,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I99" t="n">
-        <v>3</v>
+        <v>0.9</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9252,7 +9210,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 20463-2025</t>
+          <t>A 19009-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9266,10 +9224,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45775</v>
+        <v>46130</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9287,7 +9245,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.9</v>
+        <v>6.3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9347,7 +9305,7 @@
         <v>46130</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9408,7 +9366,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 59522-2025</t>
+          <t>A 19010-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9418,14 +9376,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45989</v>
+        <v>46130</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9443,7 +9401,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9486,7 +9444,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 28471-2023</t>
+          <t>A 19008-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9500,10 +9458,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45103</v>
+        <v>46130</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9515,8 +9473,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9559,7 +9522,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 19010-2026</t>
+          <t>A 8990-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9573,10 +9536,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46130</v>
+        <v>44979</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9588,13 +9551,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I104" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9637,7 +9595,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 19009-2026</t>
+          <t>A 19663-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9651,10 +9609,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46130</v>
+        <v>46134</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9672,7 +9630,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>6.3</v>
+        <v>1.6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9715,7 +9673,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 19008-2026</t>
+          <t>A 42802-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9725,14 +9683,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46130</v>
+        <v>45182</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9750,7 +9708,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9793,7 +9751,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 16881-2023</t>
+          <t>A 59522-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9803,14 +9761,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45033</v>
+        <v>45989</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9824,11 +9782,11 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9871,7 +9829,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 19663-2026</t>
+          <t>A 6835-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9885,10 +9843,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46134</v>
+        <v>45700</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9900,13 +9858,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I108" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9949,7 +9902,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 60503-2025</t>
+          <t>A 28471-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9963,10 +9916,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45995</v>
+        <v>45103</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9979,7 +9932,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10022,7 +9975,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 60508-2025</t>
+          <t>A 22867-2022</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10036,10 +9989,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45995</v>
+        <v>44715</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10052,7 +10005,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10112,7 +10065,7 @@
         <v>45995</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10168,7 +10121,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 61396-2023</t>
+          <t>A 60508-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10182,10 +10135,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45264</v>
+        <v>45995</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10198,7 +10151,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10241,7 +10194,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 61788-2025</t>
+          <t>A 60503-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10255,10 +10208,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46002</v>
+        <v>45995</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10270,13 +10223,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10319,7 +10267,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 4164-2022</t>
+          <t>A 64060-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10333,10 +10281,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44588</v>
+        <v>45279</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10348,13 +10296,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I114" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10397,7 +10340,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 61271-2022</t>
+          <t>A 48707-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10411,10 +10354,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44909</v>
+        <v>45593</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10426,13 +10369,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I115" t="n">
-        <v>14.1</v>
+        <v>6</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10475,7 +10413,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 64066-2025</t>
+          <t>A 21210-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10485,14 +10423,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46013</v>
+        <v>45779</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10504,8 +10442,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I116" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10548,7 +10491,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 6835-2025</t>
+          <t>A 23717-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10562,10 +10505,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45700</v>
+        <v>45793</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10578,7 +10521,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10621,7 +10564,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 63628-2025</t>
+          <t>A 61788-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10635,10 +10578,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46014</v>
+        <v>46002</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10650,8 +10593,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I118" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10694,7 +10642,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 57422-2021</t>
+          <t>A 55832-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10708,10 +10656,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44483</v>
+        <v>45239</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10724,7 +10672,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10767,7 +10715,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 21210-2025</t>
+          <t>A 58388-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10781,10 +10729,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45779</v>
+        <v>45633</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10796,13 +10744,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I120" t="n">
-        <v>1.1</v>
+        <v>5.8</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10845,7 +10788,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 1788-2026</t>
+          <t>A 18978-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10859,10 +10802,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46034</v>
+        <v>45764</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10875,7 +10818,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>3.5</v>
+        <v>0.8</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10918,7 +10861,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 35060-2024</t>
+          <t>A 917-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10932,10 +10875,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45527</v>
+        <v>46030</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10947,13 +10890,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I122" t="n">
-        <v>0.6</v>
+        <v>3.7</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10996,7 +10934,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 23717-2025</t>
+          <t>A 31921-2022</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11010,10 +10948,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45793</v>
+        <v>44777</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11026,7 +10964,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -11069,7 +11007,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 2911-2026</t>
+          <t>A 43075-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11083,10 +11021,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46038</v>
+        <v>45182</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11099,7 +11037,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -11142,7 +11080,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 45664-2025</t>
+          <t>A 47196-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11156,10 +11094,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45923</v>
+        <v>45196</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11171,13 +11109,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I125" t="n">
-        <v>9</v>
+        <v>5.9</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11220,7 +11153,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 64060-2023</t>
+          <t>A 21253-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11234,10 +11167,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45279</v>
+        <v>46147</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11250,7 +11183,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.9</v>
+        <v>3.4</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11293,7 +11226,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 47222-2024</t>
+          <t>A 13454-2022</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11307,10 +11240,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45586</v>
+        <v>44645</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11322,13 +11255,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I127" t="n">
-        <v>5.3</v>
+        <v>1.7</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11371,7 +11299,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 14215-2024</t>
+          <t>A 21257-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11385,10 +11313,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45393</v>
+        <v>46147</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11400,13 +11328,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I128" t="n">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11449,7 +11372,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 917-2026</t>
+          <t>A 53618-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11463,10 +11386,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46030</v>
+        <v>45614</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11479,7 +11402,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>3.7</v>
+        <v>10.1</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11522,7 +11445,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 24116-2024</t>
+          <t>A 30961-2022</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11536,10 +11459,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45456</v>
+        <v>44768</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11551,8 +11474,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I130" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11595,7 +11523,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 55832-2023</t>
+          <t>A 3227-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11609,10 +11537,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45239</v>
+        <v>45679</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11625,7 +11553,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.5</v>
+        <v>4.5</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11668,7 +11596,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 10515-2023</t>
+          <t>A 42803-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11678,14 +11606,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44987</v>
+        <v>45182</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11697,8 +11625,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I132" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11741,7 +11674,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 33011-2023</t>
+          <t>A 23754-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11755,10 +11688,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45125</v>
+        <v>46164</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11770,8 +11703,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I133" t="n">
-        <v>0.8</v>
+        <v>12.2</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11814,7 +11752,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 21253-2026</t>
+          <t>A 4587-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11828,10 +11766,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46147</v>
+        <v>45687</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11844,7 +11782,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11887,7 +11825,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 48168-2024</t>
+          <t>A 8803-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11901,10 +11839,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45589</v>
+        <v>45712</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11917,7 +11855,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>5.5</v>
+        <v>1.5</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11960,7 +11898,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 21257-2026</t>
+          <t>A 4587-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11974,10 +11912,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46147</v>
+        <v>45687</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11990,7 +11928,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -12033,7 +11971,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 3227-2025</t>
+          <t>A 24666-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12047,10 +11985,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45679</v>
+        <v>46171</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12063,7 +12001,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>4.5</v>
+        <v>6.1</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -12106,7 +12044,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 13454-2022</t>
+          <t>A 25092-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12120,10 +12058,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44645</v>
+        <v>46175</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12135,8 +12073,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I138" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -12179,7 +12122,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 10743-2023</t>
+          <t>A 25098-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12189,14 +12132,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44988</v>
+        <v>46175</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12210,11 +12153,11 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I139" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12257,7 +12200,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 50611-2024</t>
+          <t>A 26608-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12271,10 +12214,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45601</v>
+        <v>46184</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12286,8 +12229,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I140" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12330,7 +12278,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 42802-2023</t>
+          <t>A 27120-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12340,14 +12288,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45182</v>
+        <v>46188</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12359,13 +12307,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I141" t="n">
-        <v>0.6</v>
+        <v>4.7</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12408,7 +12351,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 52829-2024</t>
+          <t>A 26819-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12422,10 +12365,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45610</v>
+        <v>46185</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12437,8 +12380,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I142" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12481,7 +12429,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 56313-2024</t>
+          <t>A 3239-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12495,10 +12443,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45624</v>
+        <v>46041</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12510,13 +12458,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I143" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12559,7 +12502,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 38382-2022</t>
+          <t>A 26820-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12573,10 +12516,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44812</v>
+        <v>46185</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12590,11 +12533,11 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I144" t="n">
-        <v>2.2</v>
+        <v>9.9</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12637,7 +12580,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 24115-2024</t>
+          <t>A 26821-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12651,10 +12594,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45456</v>
+        <v>46185</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12666,8 +12609,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I145" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12710,7 +12658,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 23754-2026</t>
+          <t>A 26822-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12724,10 +12672,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46164</v>
+        <v>46185</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12745,7 +12693,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>12.2</v>
+        <v>2.2</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12788,7 +12736,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 4587-2025</t>
+          <t>A 26824-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12802,10 +12750,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45687</v>
+        <v>46185</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12817,8 +12765,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I147" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12861,7 +12814,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 4587-2025</t>
+          <t>A 26825-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12875,10 +12828,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45687</v>
+        <v>46185</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12890,8 +12843,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I148" t="n">
-        <v>3.3</v>
+        <v>0.8</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12934,7 +12892,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 10404-2022</t>
+          <t>A 27392-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12948,10 +12906,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>44623</v>
+        <v>46189</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12963,8 +12921,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I149" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -13007,7 +12970,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 24666-2026</t>
+          <t>A 56313-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -13021,10 +12984,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46171</v>
+        <v>45624</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13036,8 +12999,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I150" t="n">
-        <v>6.1</v>
+        <v>2.2</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -13080,7 +13048,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 25098-2026</t>
+          <t>A 10743-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -13090,14 +13058,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46175</v>
+        <v>44988</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13111,11 +13079,11 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -13158,7 +13126,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 25092-2026</t>
+          <t>A 14215-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13172,10 +13140,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46175</v>
+        <v>45393</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13189,11 +13157,11 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1.9</v>
+        <v>4.2</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -13236,7 +13204,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 18955-2025</t>
+          <t>A 55191-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13250,10 +13218,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45764</v>
+        <v>45237</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13266,7 +13234,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>8.1</v>
+        <v>1.9</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -13309,7 +13277,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 22867-2022</t>
+          <t>A 59025-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13323,10 +13291,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>44715</v>
+        <v>45636</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13338,8 +13306,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I154" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13382,7 +13355,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 18978-2025</t>
+          <t>A 31378-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13396,10 +13369,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45764</v>
+        <v>46213</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13412,7 +13385,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>0.8</v>
+        <v>3.7</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13455,7 +13428,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 4801-2024</t>
+          <t>A 35094-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13469,10 +13442,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45328</v>
+        <v>46260</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13484,8 +13457,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I156" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13528,7 +13506,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 4802-2024</t>
+          <t>A 17243-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13542,10 +13520,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45328</v>
+        <v>45414</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13558,7 +13536,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>0.9</v>
+        <v>3.2</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13601,7 +13579,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 30961-2022</t>
+          <t>A 35699-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13611,14 +13589,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>44768</v>
+        <v>46265</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13632,11 +13610,11 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I158" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13679,7 +13657,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 55191-2023</t>
+          <t>A 36374-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13693,10 +13671,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45237</v>
+        <v>46268</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13708,8 +13686,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I159" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13752,7 +13735,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 26822-2026</t>
+          <t>A 35060-2024</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13766,10 +13749,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46185</v>
+        <v>45527</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13783,11 +13766,11 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I160" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13830,7 +13813,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 26819-2026</t>
+          <t>A 37089-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13844,10 +13827,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46185</v>
+        <v>46273</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13859,13 +13842,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I161" t="n">
-        <v>2.4</v>
+        <v>15.8</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13908,7 +13886,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 3239-2026</t>
+          <t>A 52826-2024</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13922,10 +13900,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46041</v>
+        <v>45610</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13938,7 +13916,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13981,7 +13959,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 26821-2026</t>
+          <t>A 52829-2024</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13995,10 +13973,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46185</v>
+        <v>45610</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14010,13 +13988,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I163" t="n">
-        <v>7.9</v>
+        <v>2</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -14059,7 +14032,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 26820-2026</t>
+          <t>A 11974-2025</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -14073,10 +14046,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46185</v>
+        <v>45728</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14088,13 +14061,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I164" t="n">
-        <v>9.9</v>
+        <v>1.4</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -14137,7 +14105,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 26608-2026</t>
+          <t>A 61271-2022</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -14151,10 +14119,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46184</v>
+        <v>44909</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14168,11 +14136,11 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.6</v>
+        <v>14.1</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -14215,7 +14183,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 26824-2026</t>
+          <t>A 48168-2024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -14229,10 +14197,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46185</v>
+        <v>45589</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14244,13 +14212,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I166" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -14293,7 +14256,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 26825-2026</t>
+          <t>A 18955-2025</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -14307,10 +14270,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46185</v>
+        <v>45764</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14322,13 +14285,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I167" t="n">
-        <v>0.8</v>
+        <v>8.1</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14371,7 +14329,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 27392-2026</t>
+          <t>A 50614-2024</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14385,10 +14343,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46189</v>
+        <v>45601</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14400,13 +14358,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I168" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14449,7 +14402,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 27120-2026</t>
+          <t>A 55182-2024</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14463,10 +14416,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46188</v>
+        <v>45618</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14479,7 +14432,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>4.7</v>
+        <v>11.4</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14522,7 +14475,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 13496-2025</t>
+          <t>A 4058-2022</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14536,10 +14489,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45736</v>
+        <v>44588</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14552,7 +14505,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>8.800000000000001</v>
+        <v>1.7</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14595,7 +14548,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 11974-2025</t>
+          <t>A 28100-2024</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14609,10 +14562,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45728</v>
+        <v>45476</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14625,7 +14578,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14668,7 +14621,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 63863-2023</t>
+          <t>A 1106-2024</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14682,10 +14635,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45278</v>
+        <v>45302</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14698,7 +14651,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14741,7 +14694,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 1309-2024</t>
+          <t>A 39030-2022</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14755,10 +14708,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45303</v>
+        <v>44817</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14770,8 +14723,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I173" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14814,7 +14772,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 52826-2024</t>
+          <t>A 38382-2022</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14828,10 +14786,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45610</v>
+        <v>44812</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14841,6 +14799,11 @@
       <c r="G174" t="inlineStr">
         <is>
           <t>KARLSKOGA</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I174" t="n">
@@ -14887,7 +14850,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 1106-2024</t>
+          <t>A 16881-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14901,10 +14864,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45302</v>
+        <v>45033</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14916,8 +14879,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I175" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14960,7 +14928,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 48707-2024</t>
+          <t>A 57422-2021</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14974,10 +14942,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45593</v>
+        <v>44483</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14990,7 +14958,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>6</v>
+        <v>1.2</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -15033,7 +15001,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 35470-2024</t>
+          <t>A 8244-2025</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -15047,10 +15015,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45531</v>
+        <v>45708</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15063,7 +15031,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -15106,7 +15074,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 8990-2023</t>
+          <t>A 38190-2024</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -15120,10 +15088,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>44979</v>
+        <v>45545</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15179,7 +15147,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 50614-2024</t>
+          <t>A 20463-2025</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -15193,10 +15161,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45601</v>
+        <v>45775</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15208,8 +15176,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I179" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -15252,7 +15225,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 55182-2024</t>
+          <t>A 35470-2024</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -15266,10 +15239,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45618</v>
+        <v>45531</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15282,7 +15255,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>11.4</v>
+        <v>0.5</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -15325,7 +15298,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 31378-2026</t>
+          <t>A 35445-2024</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15339,10 +15312,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46213</v>
+        <v>45531</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15355,7 +15328,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>3.7</v>
+        <v>0.5</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15398,7 +15371,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 52797-2021</t>
+          <t>A 47094-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15412,10 +15385,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>44467</v>
+        <v>45196</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15428,7 +15401,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15471,7 +15444,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 35094-2026</t>
+          <t>A 38196-2024</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15485,10 +15458,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46260</v>
+        <v>45545</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15500,13 +15473,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I183" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15549,7 +15517,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 8259-2025</t>
+          <t>A 50611-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15563,10 +15531,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45708</v>
+        <v>45601</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15579,7 +15547,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15622,7 +15590,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 53620-2024</t>
+          <t>A 20289-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15636,10 +15604,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45614</v>
+        <v>45435</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15649,6 +15617,11 @@
       <c r="G185" t="inlineStr">
         <is>
           <t>KARLSKOGA</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I185" t="n">
@@ -15695,7 +15668,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 35699-2026</t>
+          <t>A 52797-2021</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15705,14 +15678,14 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46265</v>
+        <v>44467</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15724,13 +15697,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I186" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15773,7 +15741,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 35930-2023</t>
+          <t>A 20086-2024</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15783,14 +15751,14 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45148</v>
+        <v>45434</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15802,13 +15770,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I187" t="n">
-        <v>5.2</v>
+        <v>1.5</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15851,7 +15814,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 36374-2026</t>
+          <t>A 13496-2025</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15865,10 +15828,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46268</v>
+        <v>45736</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15880,13 +15843,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I188" t="n">
-        <v>1.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15929,7 +15887,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 47196-2023</t>
+          <t>A 56887-2022</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15943,10 +15901,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45196</v>
+        <v>44894</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15959,7 +15917,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>5.9</v>
+        <v>1.8</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -16002,7 +15960,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 53618-2024</t>
+          <t>A 33011-2023</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -16016,10 +15974,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45614</v>
+        <v>45125</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16032,7 +15990,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>10.1</v>
+        <v>0.8</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -16075,7 +16033,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 58388-2024</t>
+          <t>A 51344-2023</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -16089,10 +16047,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45633</v>
+        <v>45219</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16104,8 +16062,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I191" t="n">
-        <v>5.8</v>
+        <v>4.5</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -16148,7 +16111,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 47201-2023</t>
+          <t>A 10515-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -16162,10 +16125,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45196</v>
+        <v>44987</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16178,7 +16141,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -16221,7 +16184,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 37089-2026</t>
+          <t>A 39337-2022</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -16235,10 +16198,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46273</v>
+        <v>44817</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16251,7 +16214,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>15.8</v>
+        <v>1.5</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -16294,7 +16257,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 52828-2024</t>
+          <t>A 53620-2024</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -16308,10 +16271,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45610</v>
+        <v>45614</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16324,7 +16287,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>8.300000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -16367,7 +16330,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 17243-2024</t>
+          <t>A 13501-2025</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16381,10 +16344,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45414</v>
+        <v>45736</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16440,7 +16403,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 59938-2023</t>
+          <t>A 10404-2022</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16454,10 +16417,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45257</v>
+        <v>44623</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16470,7 +16433,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16530,7 +16493,7 @@
         <v>45161</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16608,7 +16571,7 @@
         <v>45321</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16686,7 +16649,7 @@
         <v>45791</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16739,27 +16702,27 @@
       </c>
       <c r="V199" s="2" t="inlineStr"/>
     </row>
-    <row r="200" ht="15" customHeight="1">
+    <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 27498-2025</t>
+          <t>S 2960-2025</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45813</v>
+        <v>45953</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16771,8 +16734,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I200" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16811,84 +16779,6 @@
         <v>0</v>
       </c>
       <c r="V200" s="2" t="inlineStr"/>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>S 2960-2025</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D201" s="1" t="n">
-        <v>45953</v>
-      </c>
-      <c r="E201" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F201" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>KARLSKOGA</t>
-        </is>
-      </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I201" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J201" t="n">
-        <v>0</v>
-      </c>
-      <c r="K201" t="n">
-        <v>0</v>
-      </c>
-      <c r="L201" t="n">
-        <v>0</v>
-      </c>
-      <c r="M201" t="n">
-        <v>0</v>
-      </c>
-      <c r="N201" t="n">
-        <v>0</v>
-      </c>
-      <c r="O201" t="n">
-        <v>0</v>
-      </c>
-      <c r="P201" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q201" t="n">
-        <v>0</v>
-      </c>
-      <c r="R201" t="n">
-        <v>0</v>
-      </c>
-      <c r="S201" t="n">
-        <v>0</v>
-      </c>
-      <c r="T201" t="n">
-        <v>0</v>
-      </c>
-      <c r="U201" t="n">
-        <v>0</v>
-      </c>
-      <c r="V201" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt KARLSKOGA.xlsx
+++ b/Översikt KARLSKOGA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE200"/>
+  <dimension ref="A1:AE203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45562</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -625,7 +625,7 @@
         <v>15</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L2" t="n">
         <v>14</v>
@@ -649,13 +649,13 @@
         <v>3</v>
       </c>
       <c r="S2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="T2" t="n">
+        <v>258</v>
+      </c>
+      <c r="U2" t="n">
         <v>254</v>
-      </c>
-      <c r="U2" t="n">
-        <v>250</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
@@ -678,6 +678,7 @@
 Vedskivlav
 Stor revmossa
 Vedticka
+Vågbandad barkbock
 Hårklomossa
 Järpe
 Spillkråka
@@ -742,7 +743,7 @@
         <v>45958</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -872,7 +873,7 @@
         <v>45989</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1002,7 +1003,7 @@
         <v>44510</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1122,7 +1123,7 @@
         <v>46100</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1250,7 +1251,7 @@
         <v>45989</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1373,7 +1374,7 @@
         <v>44473</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1475,7 +1476,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 8803-2026</t>
+          <t>A 63187-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1489,10 +1490,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46066</v>
+        <v>46010</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1504,14 +1505,19 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I9" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L9" t="n">
         <v>1</v>
@@ -1538,12 +1544,232 @@
         <v>4</v>
       </c>
       <c r="T9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Talltita
+Bronshjon
+Korallblylav
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 63187-2025 artfynd.xlsx", "A 63187-2025")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 63187-2025 karta.png", "A 63187-2025")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 63187-2025 georefererad karta.tif", "A 63187-2025")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 63187-2025 FSC-klagomål.docx", "A 63187-2025")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 63187-2025 FSC-klagomål mail.docx", "A 63187-2025")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 63187-2025 tillsynsbegäran.docx", "A 63187-2025")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 63187-2025 tillsynsbegäran mail.docx", "A 63187-2025")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 63187-2025 prioriterade fågelarter.docx", "A 63187-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 60085-2021</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>44495</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>KARLSKOGA</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4</v>
+      </c>
+      <c r="T10" t="n">
+        <v>5</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Citronfingersvamp
+Mörk husmossa
+Svart trolldruva
+Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 60085-2021 artfynd.xlsx", "A 60085-2021")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 60085-2021 karta.png", "A 60085-2021")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 60085-2021 georefererad karta.tif", "A 60085-2021")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 60085-2021 FSC-klagomål.docx", "A 60085-2021")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 60085-2021 FSC-klagomål mail.docx", "A 60085-2021")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 60085-2021 tillsynsbegäran.docx", "A 60085-2021")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 60085-2021 tillsynsbegäran mail.docx", "A 60085-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 8803-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>46066</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>KARLSKOGA</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4</v>
+      </c>
+      <c r="T11" t="n">
         <v>8</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Dofttaggsvamp
 Platt fjädermossa
@@ -1551,257 +1777,32 @@
 Trubbfjädermossa</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 8803-2026 artfynd.xlsx", "A 8803-2026")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 8803-2026 karta.png", "A 8803-2026")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 8803-2026 georefererad karta.tif", "A 8803-2026")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 8803-2026 FSC-klagomål.docx", "A 8803-2026")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 8803-2026 FSC-klagomål mail.docx", "A 8803-2026")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 8803-2026 tillsynsbegäran.docx", "A 8803-2026")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 8803-2026 tillsynsbegäran mail.docx", "A 8803-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 63187-2025</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>46010</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>KARLSKOGA</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>4</v>
-      </c>
-      <c r="T10" t="n">
-        <v>4</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Talltita
-Bronshjon
-Korallblylav
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 63187-2025 artfynd.xlsx", "A 63187-2025")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 63187-2025 karta.png", "A 63187-2025")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 63187-2025 georefererad karta.tif", "A 63187-2025")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 63187-2025 FSC-klagomål.docx", "A 63187-2025")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 63187-2025 FSC-klagomål mail.docx", "A 63187-2025")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 63187-2025 tillsynsbegäran.docx", "A 63187-2025")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 63187-2025 tillsynsbegäran mail.docx", "A 63187-2025")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 63187-2025 prioriterade fågelarter.docx", "A 63187-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 60085-2021</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>44495</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>KARLSKOGA</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>3</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>4</v>
-      </c>
-      <c r="T11" t="n">
-        <v>5</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Citronfingersvamp
-Mörk husmossa
-Svart trolldruva
-Västlig hakmossa</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 60085-2021 artfynd.xlsx", "A 60085-2021")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 60085-2021 karta.png", "A 60085-2021")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 60085-2021 georefererad karta.tif", "A 60085-2021")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 60085-2021 FSC-klagomål.docx", "A 60085-2021")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 60085-2021 FSC-klagomål mail.docx", "A 60085-2021")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 60085-2021 tillsynsbegäran.docx", "A 60085-2021")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 60085-2021 tillsynsbegäran mail.docx", "A 60085-2021")</f>
         <v/>
       </c>
     </row>
@@ -1825,7 +1826,7 @@
         <v>46136</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1925,7 +1926,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 63185-2025</t>
+          <t>A 18428-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1935,14 +1936,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46010</v>
+        <v>46127</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1960,10 +1961,10 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>8.4</v>
+        <v>6</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1972,7 +1973,7 @@
         <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1984,173 +1985,173 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
+        <v>2</v>
+      </c>
+      <c r="R13" t="n">
         <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>3</v>
       </c>
       <c r="T13" t="n">
+        <v>17</v>
+      </c>
+      <c r="U13" t="n">
+        <v>17</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Skuggblåslav
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 18428-2026 artfynd.xlsx", "A 18428-2026")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 18428-2026 karta.png", "A 18428-2026")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 18428-2026 georefererad karta.tif", "A 18428-2026")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 18428-2026 FSC-klagomål.docx", "A 18428-2026")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 18428-2026 FSC-klagomål mail.docx", "A 18428-2026")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 18428-2026 tillsynsbegäran.docx", "A 18428-2026")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 18428-2026 tillsynsbegäran mail.docx", "A 18428-2026")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 18428-2026 prioriterade fågelarter.docx", "A 18428-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 63185-2025</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>46010</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>KARLSKOGA</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3</v>
+      </c>
+      <c r="T14" t="n">
         <v>11</v>
       </c>
-      <c r="U13" t="n">
+      <c r="U14" t="n">
         <v>9</v>
       </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Talltita
 Brudborste
 Revlummer</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 63185-2025 artfynd.xlsx", "A 63185-2025")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 63185-2025 karta.png", "A 63185-2025")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 63185-2025 georefererad karta.tif", "A 63185-2025")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 63185-2025 FSC-klagomål.docx", "A 63185-2025")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 63185-2025 FSC-klagomål mail.docx", "A 63185-2025")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 63185-2025 tillsynsbegäran.docx", "A 63185-2025")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 63185-2025 tillsynsbegäran mail.docx", "A 63185-2025")</f>
         <v/>
       </c>
-      <c r="AE13">
+      <c r="AE14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 63185-2025 prioriterade fågelarter.docx", "A 63185-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 18428-2026</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>46127</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>KARLSKOGA</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>6</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3</v>
-      </c>
-      <c r="T14" t="n">
-        <v>17</v>
-      </c>
-      <c r="U14" t="n">
-        <v>17</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Skuggblåslav
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 18428-2026 artfynd.xlsx", "A 18428-2026")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 18428-2026 karta.png", "A 18428-2026")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 18428-2026 georefererad karta.tif", "A 18428-2026")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 18428-2026 FSC-klagomål.docx", "A 18428-2026")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 18428-2026 FSC-klagomål mail.docx", "A 18428-2026")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 18428-2026 tillsynsbegäran.docx", "A 18428-2026")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 18428-2026 tillsynsbegäran mail.docx", "A 18428-2026")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 18428-2026 prioriterade fågelarter.docx", "A 18428-2026")</f>
         <v/>
       </c>
     </row>
@@ -2174,7 +2175,7 @@
         <v>46265</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2286,7 +2287,7 @@
         <v>46136</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2402,7 +2403,7 @@
         <v>46136</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2518,7 +2519,7 @@
         <v>46010</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2617,7 +2618,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 39936-2024</t>
+          <t>A 39025-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2631,10 +2632,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45553</v>
+        <v>44817</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2646,11 +2647,16 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>6.4</v>
+        <v>3.2</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -2680,165 +2686,160 @@
         <v>2</v>
       </c>
       <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Talltita
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 39025-2022 artfynd.xlsx", "A 39025-2022")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 39025-2022 karta.png", "A 39025-2022")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 39025-2022 georefererad karta.tif", "A 39025-2022")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 39025-2022 FSC-klagomål.docx", "A 39025-2022")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 39025-2022 FSC-klagomål mail.docx", "A 39025-2022")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 39025-2022 tillsynsbegäran.docx", "A 39025-2022")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 39025-2022 tillsynsbegäran mail.docx", "A 39025-2022")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 39025-2022 prioriterade fågelarter.docx", "A 39025-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 39936-2024</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>45553</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>KARLSKOGA</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2</v>
+      </c>
+      <c r="T20" t="n">
         <v>3</v>
       </c>
-      <c r="U19" t="n">
+      <c r="U20" t="n">
         <v>1</v>
       </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Storgröe
 Utter</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 39936-2024 artfynd.xlsx", "A 39936-2024")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 39936-2024 karta.png", "A 39936-2024")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 39936-2024 georefererad karta.tif", "A 39936-2024")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 39936-2024 FSC-klagomål.docx", "A 39936-2024")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 39936-2024 FSC-klagomål mail.docx", "A 39936-2024")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 39936-2024 tillsynsbegäran.docx", "A 39936-2024")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 39936-2024 tillsynsbegäran mail.docx", "A 39936-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 39025-2022</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>44817</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>KARLSKOGA</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Talltita
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 39025-2022 artfynd.xlsx", "A 39025-2022")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 39025-2022 karta.png", "A 39025-2022")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 39025-2022 georefererad karta.tif", "A 39025-2022")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 39025-2022 FSC-klagomål.docx", "A 39025-2022")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 39025-2022 FSC-klagomål mail.docx", "A 39025-2022")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 39025-2022 tillsynsbegäran.docx", "A 39025-2022")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 39025-2022 tillsynsbegäran mail.docx", "A 39025-2022")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 39025-2022 prioriterade fågelarter.docx", "A 39025-2022")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 63188-2025</t>
+          <t>A 58091-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2852,10 +2853,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46010</v>
+        <v>44900</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2873,7 +2874,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2882,7 +2883,7 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2897,7 +2898,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2909,50 +2910,46 @@
         <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Hårklomossa</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 63188-2025 artfynd.xlsx", "A 63188-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 58091-2022 artfynd.xlsx", "A 58091-2022")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 63188-2025 karta.png", "A 63188-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 58091-2022 karta.png", "A 58091-2022")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 63188-2025 georefererad karta.tif", "A 63188-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 58091-2022 georefererad karta.tif", "A 58091-2022")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 63188-2025 FSC-klagomål.docx", "A 63188-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 58091-2022 FSC-klagomål.docx", "A 58091-2022")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 63188-2025 FSC-klagomål mail.docx", "A 63188-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 58091-2022 FSC-klagomål mail.docx", "A 58091-2022")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 63188-2025 tillsynsbegäran.docx", "A 63188-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 58091-2022 tillsynsbegäran.docx", "A 58091-2022")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 63188-2025 tillsynsbegäran mail.docx", "A 63188-2025")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 63188-2025 prioriterade fågelarter.docx", "A 63188-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 58091-2022 tillsynsbegäran mail.docx", "A 58091-2022")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 52377-2025</t>
+          <t>A 28566-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2966,10 +2963,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45953</v>
+        <v>45478</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2981,13 +2978,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -3027,42 +3019,42 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 52377-2025 artfynd.xlsx", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 28566-2024 artfynd.xlsx", "A 28566-2024")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 52377-2025 karta.png", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 28566-2024 karta.png", "A 28566-2024")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 52377-2025 georefererad karta.tif", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 28566-2024 georefererad karta.tif", "A 28566-2024")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 52377-2025 FSC-klagomål.docx", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 28566-2024 FSC-klagomål.docx", "A 28566-2024")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 52377-2025 FSC-klagomål mail.docx", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 28566-2024 FSC-klagomål mail.docx", "A 28566-2024")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 52377-2025 tillsynsbegäran.docx", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 28566-2024 tillsynsbegäran.docx", "A 28566-2024")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 52377-2025 tillsynsbegäran mail.docx", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 28566-2024 tillsynsbegäran mail.docx", "A 28566-2024")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 16784-2026</t>
+          <t>A 63188-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3076,10 +3068,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46113</v>
+        <v>46010</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3097,7 +3089,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>4.2</v>
+        <v>1.1</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -3106,7 +3098,7 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -3121,7 +3113,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -3133,46 +3125,50 @@
         <v>2</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Hårklomossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 16784-2026 artfynd.xlsx", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 63188-2025 artfynd.xlsx", "A 63188-2025")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 16784-2026 karta.png", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 63188-2025 karta.png", "A 63188-2025")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 16784-2026 georefererad karta.tif", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 63188-2025 georefererad karta.tif", "A 63188-2025")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 16784-2026 FSC-klagomål.docx", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 63188-2025 FSC-klagomål.docx", "A 63188-2025")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 16784-2026 FSC-klagomål mail.docx", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 63188-2025 FSC-klagomål mail.docx", "A 63188-2025")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 16784-2026 tillsynsbegäran.docx", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 63188-2025 tillsynsbegäran.docx", "A 63188-2025")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 16784-2026 tillsynsbegäran mail.docx", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 63188-2025 tillsynsbegäran mail.docx", "A 63188-2025")</f>
+        <v/>
+      </c>
+      <c r="AE23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 63188-2025 prioriterade fågelarter.docx", "A 63188-2025")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 18427-2026</t>
+          <t>A 16784-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3186,10 +3182,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46127</v>
+        <v>46113</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3207,7 +3203,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3240,53 +3236,49 @@
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Hårklomossa</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 18427-2026 artfynd.xlsx", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 16784-2026 artfynd.xlsx", "A 16784-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 18427-2026 karta.png", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 16784-2026 karta.png", "A 16784-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 18427-2026 georefererad karta.tif", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 16784-2026 georefererad karta.tif", "A 16784-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 18427-2026 FSC-klagomål.docx", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 16784-2026 FSC-klagomål.docx", "A 16784-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 18427-2026 FSC-klagomål mail.docx", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 16784-2026 FSC-klagomål mail.docx", "A 16784-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 18427-2026 tillsynsbegäran.docx", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 16784-2026 tillsynsbegäran.docx", "A 16784-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 18427-2026 tillsynsbegäran mail.docx", "A 18427-2026")</f>
-        <v/>
-      </c>
-      <c r="AE24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 18427-2026 prioriterade fågelarter.docx", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 16784-2026 tillsynsbegäran mail.docx", "A 16784-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 19233-2026</t>
+          <t>A 40528-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3300,10 +3292,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46132</v>
+        <v>45555</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3316,13 +3308,13 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -3352,46 +3344,46 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 19233-2026 artfynd.xlsx", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 40528-2024 artfynd.xlsx", "A 40528-2024")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 19233-2026 karta.png", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 40528-2024 karta.png", "A 40528-2024")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 19233-2026 georefererad karta.tif", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 40528-2024 georefererad karta.tif", "A 40528-2024")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 19233-2026 FSC-klagomål.docx", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 40528-2024 FSC-klagomål.docx", "A 40528-2024")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 19233-2026 FSC-klagomål mail.docx", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 40528-2024 FSC-klagomål mail.docx", "A 40528-2024")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 19233-2026 tillsynsbegäran.docx", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 40528-2024 tillsynsbegäran.docx", "A 40528-2024")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 19233-2026 tillsynsbegäran mail.docx", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 40528-2024 tillsynsbegäran mail.docx", "A 40528-2024")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 21019-2026</t>
+          <t>A 18427-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3405,10 +3397,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46145</v>
+        <v>46127</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3426,7 +3418,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>4.7</v>
+        <v>3</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3462,46 +3454,50 @@
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 21019-2026 artfynd.xlsx", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 18427-2026 artfynd.xlsx", "A 18427-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 21019-2026 karta.png", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 18427-2026 karta.png", "A 18427-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 21019-2026 georefererad karta.tif", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 18427-2026 georefererad karta.tif", "A 18427-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 21019-2026 FSC-klagomål.docx", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 18427-2026 FSC-klagomål.docx", "A 18427-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 21019-2026 FSC-klagomål mail.docx", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 18427-2026 FSC-klagomål mail.docx", "A 18427-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 21019-2026 tillsynsbegäran.docx", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 18427-2026 tillsynsbegäran.docx", "A 18427-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 21019-2026 tillsynsbegäran mail.docx", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 18427-2026 tillsynsbegäran mail.docx", "A 18427-2026")</f>
+        <v/>
+      </c>
+      <c r="AE26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 18427-2026 prioriterade fågelarter.docx", "A 18427-2026")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 25093-2026</t>
+          <t>A 19233-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3515,10 +3511,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46175</v>
+        <v>46132</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3530,13 +3526,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>4</v>
+        <v>1.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3572,46 +3563,46 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 25093-2026 artfynd.xlsx", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 19233-2026 artfynd.xlsx", "A 19233-2026")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 25093-2026 karta.png", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 19233-2026 karta.png", "A 19233-2026")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 25093-2026 georefererad karta.tif", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 19233-2026 georefererad karta.tif", "A 19233-2026")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 25093-2026 FSC-klagomål.docx", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 19233-2026 FSC-klagomål.docx", "A 19233-2026")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 25093-2026 FSC-klagomål mail.docx", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 19233-2026 FSC-klagomål mail.docx", "A 19233-2026")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 25093-2026 tillsynsbegäran.docx", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 19233-2026 tillsynsbegäran.docx", "A 19233-2026")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 25093-2026 tillsynsbegäran mail.docx", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 19233-2026 tillsynsbegäran mail.docx", "A 19233-2026")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 30915-2026</t>
+          <t>A 52377-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3625,10 +3616,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46213</v>
+        <v>45953</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3642,11 +3633,11 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>8.9</v>
+        <v>2.6</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
@@ -3682,46 +3673,46 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 30915-2026 artfynd.xlsx", "A 30915-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 52377-2025 artfynd.xlsx", "A 52377-2025")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 30915-2026 karta.png", "A 30915-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 52377-2025 karta.png", "A 52377-2025")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 30915-2026 georefererad karta.tif", "A 30915-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 52377-2025 georefererad karta.tif", "A 52377-2025")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 30915-2026 FSC-klagomål.docx", "A 30915-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 52377-2025 FSC-klagomål.docx", "A 52377-2025")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 30915-2026 FSC-klagomål mail.docx", "A 30915-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 52377-2025 FSC-klagomål mail.docx", "A 52377-2025")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 30915-2026 tillsynsbegäran.docx", "A 30915-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 52377-2025 tillsynsbegäran.docx", "A 52377-2025")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 30915-2026 tillsynsbegäran mail.docx", "A 30915-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 52377-2025 tillsynsbegäran mail.docx", "A 52377-2025")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 35199-2026</t>
+          <t>A 21019-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3735,10 +3726,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46260</v>
+        <v>46145</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3752,11 +3743,11 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>5.6</v>
+        <v>4.7</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -3765,7 +3756,7 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -3780,7 +3771,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -3796,42 +3787,42 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 35199-2026 artfynd.xlsx", "A 35199-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 21019-2026 artfynd.xlsx", "A 21019-2026")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 35199-2026 karta.png", "A 35199-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 21019-2026 karta.png", "A 21019-2026")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 35199-2026 georefererad karta.tif", "A 35199-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 21019-2026 georefererad karta.tif", "A 21019-2026")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 35199-2026 FSC-klagomål.docx", "A 35199-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 21019-2026 FSC-klagomål.docx", "A 21019-2026")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 35199-2026 FSC-klagomål mail.docx", "A 35199-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 21019-2026 FSC-klagomål mail.docx", "A 21019-2026")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 35199-2026 tillsynsbegäran.docx", "A 35199-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 21019-2026 tillsynsbegäran.docx", "A 21019-2026")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 35199-2026 tillsynsbegäran mail.docx", "A 35199-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 21019-2026 tillsynsbegäran mail.docx", "A 21019-2026")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 20110-2026</t>
+          <t>A 25093-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3845,10 +3836,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46136</v>
+        <v>46175</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3866,13 +3857,13 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>5.4</v>
+        <v>4</v>
       </c>
       <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
         <v>1</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -3906,42 +3897,42 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 20110-2026 artfynd.xlsx", "A 20110-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 25093-2026 artfynd.xlsx", "A 25093-2026")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 20110-2026 karta.png", "A 20110-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 25093-2026 karta.png", "A 25093-2026")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 20110-2026 georefererad karta.tif", "A 20110-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 25093-2026 georefererad karta.tif", "A 25093-2026")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 20110-2026 FSC-klagomål.docx", "A 20110-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 25093-2026 FSC-klagomål.docx", "A 25093-2026")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 20110-2026 FSC-klagomål mail.docx", "A 20110-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 25093-2026 FSC-klagomål mail.docx", "A 25093-2026")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 20110-2026 tillsynsbegäran.docx", "A 20110-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 25093-2026 tillsynsbegäran.docx", "A 25093-2026")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 20110-2026 tillsynsbegäran mail.docx", "A 20110-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 25093-2026 tillsynsbegäran mail.docx", "A 25093-2026")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 28474-2023</t>
+          <t>A 30915-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3955,10 +3946,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45103</v>
+        <v>46213</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3970,8 +3961,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>5.1</v>
+        <v>8.9</v>
       </c>
       <c r="J31" t="n">
         <v>1</v>
@@ -3980,7 +3976,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -3995,7 +3991,7 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -4007,50 +4003,46 @@
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Blåhake</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 28474-2023 artfynd.xlsx", "A 28474-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 30915-2026 artfynd.xlsx", "A 30915-2026")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 28474-2023 karta.png", "A 28474-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 30915-2026 karta.png", "A 30915-2026")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 28474-2023 georefererad karta.tif", "A 28474-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 30915-2026 georefererad karta.tif", "A 30915-2026")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 28474-2023 FSC-klagomål.docx", "A 28474-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 30915-2026 FSC-klagomål.docx", "A 30915-2026")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 28474-2023 FSC-klagomål mail.docx", "A 28474-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 30915-2026 FSC-klagomål mail.docx", "A 30915-2026")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 28474-2023 tillsynsbegäran.docx", "A 28474-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 30915-2026 tillsynsbegäran.docx", "A 30915-2026")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 28474-2023 tillsynsbegäran mail.docx", "A 28474-2023")</f>
-        <v/>
-      </c>
-      <c r="AE31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 28474-2023 prioriterade fågelarter.docx", "A 28474-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 30915-2026 tillsynsbegäran mail.docx", "A 30915-2026")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 58091-2022</t>
+          <t>A 28474-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4064,10 +4056,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44900</v>
+        <v>45103</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4079,13 +4071,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>2.1</v>
+        <v>5.1</v>
       </c>
       <c r="J32" t="n">
         <v>1</v>
@@ -4094,7 +4081,7 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -4109,7 +4096,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -4118,49 +4105,53 @@
         <v>1</v>
       </c>
       <c r="T32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Hårklomossa</t>
+          <t>Blåhake</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 58091-2022 artfynd.xlsx", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 28474-2023 artfynd.xlsx", "A 28474-2023")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 58091-2022 karta.png", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 28474-2023 karta.png", "A 28474-2023")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 58091-2022 georefererad karta.tif", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 28474-2023 georefererad karta.tif", "A 28474-2023")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 58091-2022 FSC-klagomål.docx", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 28474-2023 FSC-klagomål.docx", "A 28474-2023")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 58091-2022 FSC-klagomål mail.docx", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 28474-2023 FSC-klagomål mail.docx", "A 28474-2023")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 58091-2022 tillsynsbegäran.docx", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 28474-2023 tillsynsbegäran.docx", "A 28474-2023")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 58091-2022 tillsynsbegäran mail.docx", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 28474-2023 tillsynsbegäran mail.docx", "A 28474-2023")</f>
+        <v/>
+      </c>
+      <c r="AE32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 28474-2023 prioriterade fågelarter.docx", "A 28474-2023")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 28566-2024</t>
+          <t>A 35199-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4174,10 +4165,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45478</v>
+        <v>46260</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4189,8 +4180,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>5.6</v>
       </c>
       <c r="J33" t="n">
         <v>1</v>
@@ -4199,7 +4195,7 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -4214,7 +4210,7 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -4226,46 +4222,46 @@
         <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 28566-2024 artfynd.xlsx", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 35199-2026 artfynd.xlsx", "A 35199-2026")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 28566-2024 karta.png", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 35199-2026 karta.png", "A 35199-2026")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 28566-2024 georefererad karta.tif", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 35199-2026 georefererad karta.tif", "A 35199-2026")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 28566-2024 FSC-klagomål.docx", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 35199-2026 FSC-klagomål.docx", "A 35199-2026")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 28566-2024 FSC-klagomål mail.docx", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 35199-2026 FSC-klagomål mail.docx", "A 35199-2026")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 28566-2024 tillsynsbegäran.docx", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 35199-2026 tillsynsbegäran.docx", "A 35199-2026")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 28566-2024 tillsynsbegäran mail.docx", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 35199-2026 tillsynsbegäran mail.docx", "A 35199-2026")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 40528-2024</t>
+          <t>A 20110-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4279,10 +4275,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45555</v>
+        <v>46136</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4294,8 +4290,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>2.8</v>
+        <v>5.4</v>
       </c>
       <c r="J34" t="n">
         <v>1</v>
@@ -4335,42 +4336,42 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 40528-2024 artfynd.xlsx", "A 40528-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 20110-2026 artfynd.xlsx", "A 20110-2026")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 40528-2024 karta.png", "A 40528-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 20110-2026 karta.png", "A 20110-2026")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 40528-2024 georefererad karta.tif", "A 40528-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 20110-2026 georefererad karta.tif", "A 20110-2026")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 40528-2024 FSC-klagomål.docx", "A 40528-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 20110-2026 FSC-klagomål.docx", "A 20110-2026")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 40528-2024 FSC-klagomål mail.docx", "A 40528-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 20110-2026 FSC-klagomål mail.docx", "A 20110-2026")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 40528-2024 tillsynsbegäran.docx", "A 40528-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 20110-2026 tillsynsbegäran.docx", "A 20110-2026")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 40528-2024 tillsynsbegäran mail.docx", "A 40528-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 20110-2026 tillsynsbegäran mail.docx", "A 20110-2026")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 72803-2021</t>
+          <t>A 38023-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4384,10 +4385,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44546</v>
+        <v>46280</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4399,12 +4400,17 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I35" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J35" t="n">
         <v>1</v>
       </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
@@ -4430,20 +4436,56 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
       </c>
-      <c r="V35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="W35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 38023-2026 artfynd.xlsx", "A 38023-2026")</f>
+        <v/>
+      </c>
+      <c r="X35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 38023-2026 karta.png", "A 38023-2026")</f>
+        <v/>
+      </c>
+      <c r="Y35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 38023-2026 georefererad karta.tif", "A 38023-2026")</f>
+        <v/>
+      </c>
+      <c r="AA35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 38023-2026 FSC-klagomål.docx", "A 38023-2026")</f>
+        <v/>
+      </c>
+      <c r="AB35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 38023-2026 FSC-klagomål mail.docx", "A 38023-2026")</f>
+        <v/>
+      </c>
+      <c r="AC35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 38023-2026 tillsynsbegäran.docx", "A 38023-2026")</f>
+        <v/>
+      </c>
+      <c r="AD35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 38023-2026 tillsynsbegäran mail.docx", "A 38023-2026")</f>
+        <v/>
+      </c>
+      <c r="AE35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 38023-2026 prioriterade fågelarter.docx", "A 38023-2026")</f>
+        <v/>
+      </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 25548-2022</t>
+          <t>A 72803-2021</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4457,10 +4499,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44732</v>
+        <v>44546</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4473,7 +4515,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4516,7 +4558,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 50991-2021</t>
+          <t>A 25548-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4530,10 +4572,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44460</v>
+        <v>44732</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4546,7 +4588,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4589,7 +4631,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 64869-2021</t>
+          <t>A 50991-2021</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4603,10 +4645,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44512</v>
+        <v>44460</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4618,13 +4660,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>3.6</v>
+        <v>0.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4684,7 +4721,7 @@
         <v>44715</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4740,7 +4777,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 63671-2021</t>
+          <t>A 64869-2021</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4754,10 +4791,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44508</v>
+        <v>44512</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4771,11 +4808,11 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>3.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4818,7 +4855,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 56435-2021</t>
+          <t>A 63671-2021</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4832,10 +4869,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44480</v>
+        <v>44508</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4847,8 +4884,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4891,7 +4933,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 37582-2022</t>
+          <t>A 56435-2021</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4905,10 +4947,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44809</v>
+        <v>44480</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4921,7 +4963,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4964,7 +5006,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 38012-2022</t>
+          <t>A 37582-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4978,10 +5020,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44811</v>
+        <v>44809</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4994,7 +5036,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.7</v>
+        <v>0.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -5037,7 +5079,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 11081-2022</t>
+          <t>A 38012-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5047,14 +5089,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44628</v>
+        <v>44811</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5066,13 +5108,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>0.7</v>
+        <v>3.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5115,7 +5152,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 37584-2022</t>
+          <t>A 11081-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5125,14 +5162,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44809</v>
+        <v>44628</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5144,8 +5181,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>4.9</v>
+        <v>0.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5188,7 +5230,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 21612-2022</t>
+          <t>A 35445-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5202,10 +5244,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44706</v>
+        <v>45531</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5218,7 +5260,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5261,7 +5303,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 21622-2022</t>
+          <t>A 39337-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5275,10 +5317,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44706</v>
+        <v>44817</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5291,7 +5333,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5334,7 +5376,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 39027-2022</t>
+          <t>A 18955-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5348,10 +5390,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44817</v>
+        <v>45764</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5363,13 +5405,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>1.8</v>
+        <v>8.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5412,7 +5449,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 58390-2024</t>
+          <t>A 37584-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5426,10 +5463,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45633</v>
+        <v>44809</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5442,7 +5479,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3</v>
+        <v>4.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5485,7 +5522,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 35471-2024</t>
+          <t>A 21612-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5499,10 +5536,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45531</v>
+        <v>44706</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5515,7 +5552,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5558,7 +5595,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 4164-2022</t>
+          <t>A 21622-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5572,10 +5609,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44588</v>
+        <v>44706</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5587,13 +5624,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5636,7 +5668,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 9712-2024</t>
+          <t>A 39027-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5650,10 +5682,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45362</v>
+        <v>44817</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5667,11 +5699,11 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5714,7 +5746,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 42804-2023</t>
+          <t>A 8803-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5724,14 +5756,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45182</v>
+        <v>45712</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5743,13 +5775,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5792,7 +5819,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 9510-2023</t>
+          <t>A 22867-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5806,10 +5833,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44981</v>
+        <v>44715</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5822,7 +5849,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5865,7 +5892,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 1309-2024</t>
+          <t>A 18978-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5879,10 +5906,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45303</v>
+        <v>45764</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5895,7 +5922,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>4</v>
+        <v>0.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5938,7 +5965,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 64066-2025</t>
+          <t>A 4801-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5948,14 +5975,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46013</v>
+        <v>45328</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5968,7 +5995,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -6011,7 +6038,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 63628-2025</t>
+          <t>A 4802-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6025,10 +6052,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46014</v>
+        <v>45328</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6041,7 +6068,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6084,7 +6111,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 35444-2024</t>
+          <t>A 30961-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6098,10 +6125,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45531</v>
+        <v>44768</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6113,8 +6140,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6157,7 +6189,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 27498-2025</t>
+          <t>A 55191-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6171,10 +6203,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45813</v>
+        <v>45237</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6187,7 +6219,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6230,7 +6262,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 23263-2022</t>
+          <t>A 56887-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6244,10 +6276,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44720</v>
+        <v>44894</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6260,7 +6292,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6303,7 +6335,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 17815-2025</t>
+          <t>A 38196-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6317,10 +6349,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45758</v>
+        <v>45545</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6332,13 +6364,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6381,7 +6408,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 1788-2026</t>
+          <t>A 24255-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6395,10 +6422,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46034</v>
+        <v>45457</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6411,7 +6438,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6454,7 +6481,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 47201-2023</t>
+          <t>A 13496-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6468,10 +6495,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45196</v>
+        <v>45736</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6484,7 +6511,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6527,7 +6554,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 45664-2025</t>
+          <t>A 17815-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6541,10 +6568,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45923</v>
+        <v>45758</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6562,7 +6589,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6605,7 +6632,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 61396-2023</t>
+          <t>A 11974-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6619,10 +6646,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45264</v>
+        <v>45728</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6635,7 +6662,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6678,7 +6705,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 2911-2026</t>
+          <t>A 20289-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6692,10 +6719,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46038</v>
+        <v>45435</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6707,8 +6734,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6751,7 +6783,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 23620-2024</t>
+          <t>A 13473-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6765,10 +6797,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45454</v>
+        <v>46094</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6781,7 +6813,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6824,7 +6856,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 53647-2023</t>
+          <t>A 38190-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6838,10 +6870,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45230</v>
+        <v>45545</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6854,7 +6886,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6897,7 +6929,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 30102-2025</t>
+          <t>A 63863-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6911,10 +6943,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45826</v>
+        <v>45278</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6927,7 +6959,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6970,7 +7002,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 54680-2021</t>
+          <t>A 14580-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6984,10 +7016,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44473</v>
+        <v>46101</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6999,8 +7031,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7043,7 +7080,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 8259-2025</t>
+          <t>A 9712-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7057,10 +7094,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45708</v>
+        <v>45362</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7072,8 +7109,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7116,7 +7158,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 24116-2024</t>
+          <t>A 12897-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7130,10 +7172,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45456</v>
+        <v>46092</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7146,7 +7188,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7189,7 +7231,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 31397-2025</t>
+          <t>A 4058-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7203,10 +7245,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45833</v>
+        <v>44588</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7219,7 +7261,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7262,7 +7304,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 47222-2024</t>
+          <t>A 15256-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7276,10 +7318,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45586</v>
+        <v>45744</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7297,7 +7339,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7340,7 +7382,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 32287-2025</t>
+          <t>A 1309-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7354,10 +7396,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45835</v>
+        <v>45303</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7369,13 +7411,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>10.9</v>
+        <v>4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7418,7 +7455,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 44946-2025</t>
+          <t>A 16782-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7432,10 +7469,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45918</v>
+        <v>46113</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7447,8 +7484,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7491,7 +7533,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 35930-2023</t>
+          <t>A 16783-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7505,10 +7547,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45148</v>
+        <v>46113</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7526,7 +7568,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>5.2</v>
+        <v>1.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7569,7 +7611,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 44949-2025</t>
+          <t>A 16787-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7583,10 +7625,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45918</v>
+        <v>46113</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7598,8 +7640,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7642,7 +7689,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 63863-2023</t>
+          <t>A 44946-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7656,10 +7703,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45278</v>
+        <v>45918</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7672,7 +7719,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7715,7 +7762,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 9917-2026</t>
+          <t>A 44949-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7729,10 +7776,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46073</v>
+        <v>45918</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7745,7 +7792,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3.1</v>
+        <v>0.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7788,7 +7835,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 50958-2025</t>
+          <t>A 43075-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7802,10 +7849,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45946</v>
+        <v>45182</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7818,7 +7865,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.4</v>
+        <v>3.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7861,7 +7908,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 59938-2023</t>
+          <t>A 23263-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7875,10 +7922,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45257</v>
+        <v>44720</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7891,7 +7938,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7934,7 +7981,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 52828-2024</t>
+          <t>A 15060-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7948,10 +7995,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45610</v>
+        <v>46104</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7964,7 +8011,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>8.300000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8007,7 +8054,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 24255-2024</t>
+          <t>A 15058-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8021,10 +8068,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45457</v>
+        <v>46104</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8037,7 +8084,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.4</v>
+        <v>4.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8080,7 +8127,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 15256-2025</t>
+          <t>A 17734-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8094,10 +8141,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45744</v>
+        <v>46122</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8115,7 +8162,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>5.5</v>
+        <v>3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8158,7 +8205,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 24115-2024</t>
+          <t>A 35444-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8172,10 +8219,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45456</v>
+        <v>45531</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8188,7 +8235,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>8</v>
+        <v>0.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8231,7 +8278,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 13473-2026</t>
+          <t>A 35471-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8245,10 +8292,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46094</v>
+        <v>45531</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8261,7 +8308,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8304,7 +8351,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 12897-2026</t>
+          <t>A 58390-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8318,10 +8365,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46092</v>
+        <v>45633</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8334,7 +8381,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.3</v>
+        <v>3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8377,7 +8424,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 14580-2026</t>
+          <t>A 19011-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8391,10 +8438,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46101</v>
+        <v>46130</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8412,7 +8459,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8455,7 +8502,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 16783-2026</t>
+          <t>A 19010-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8469,10 +8516,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46113</v>
+        <v>46130</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8490,7 +8537,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8533,7 +8580,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 16787-2026</t>
+          <t>A 52826-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8547,10 +8594,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46113</v>
+        <v>45610</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8562,13 +8609,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8611,7 +8653,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 16782-2026</t>
+          <t>A 19009-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8625,10 +8667,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46113</v>
+        <v>46130</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8646,7 +8688,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.6</v>
+        <v>6.3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8689,7 +8731,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 15058-2026</t>
+          <t>A 19008-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8703,10 +8745,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46104</v>
+        <v>46130</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8718,8 +8760,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I93" t="n">
-        <v>4.3</v>
+        <v>1.9</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8762,7 +8809,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 15060-2026</t>
+          <t>A 19663-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8776,10 +8823,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46104</v>
+        <v>46134</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8791,8 +8838,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>11.5</v>
+        <v>1.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8835,7 +8887,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 55025-2025</t>
+          <t>A 50958-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8849,10 +8901,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45967</v>
+        <v>45946</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8865,7 +8917,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8908,7 +8960,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 17734-2026</t>
+          <t>A 18768-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8922,10 +8974,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46122</v>
+        <v>45764</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8943,7 +8995,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8986,7 +9038,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 18768-2025</t>
+          <t>A 42803-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8996,14 +9048,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45764</v>
+        <v>45182</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9064,7 +9116,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 4801-2024</t>
+          <t>A 6835-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9078,10 +9130,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45328</v>
+        <v>45700</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9094,7 +9146,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.9</v>
+        <v>3</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9137,7 +9189,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 4802-2024</t>
+          <t>A 21210-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9151,10 +9203,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45328</v>
+        <v>45779</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9166,8 +9218,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9210,7 +9267,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 19009-2026</t>
+          <t>A 20086-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9220,14 +9277,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46130</v>
+        <v>45434</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9239,13 +9296,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>6.3</v>
+        <v>1.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9288,7 +9340,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 19011-2026</t>
+          <t>A 23717-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9302,10 +9354,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46130</v>
+        <v>45793</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9317,13 +9369,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9366,7 +9413,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 19010-2026</t>
+          <t>A 9510-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9380,10 +9427,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46130</v>
+        <v>44981</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9393,11 +9440,6 @@
       <c r="G102" t="inlineStr">
         <is>
           <t>KARLSKOGA</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I102" t="n">
@@ -9444,7 +9486,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 19008-2026</t>
+          <t>A 55025-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9458,10 +9500,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46130</v>
+        <v>45967</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9473,13 +9515,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I103" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9522,7 +9559,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 8990-2023</t>
+          <t>A 917-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9536,10 +9573,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44979</v>
+        <v>46030</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9552,7 +9589,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.1</v>
+        <v>3.7</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9595,7 +9632,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 19663-2026</t>
+          <t>A 1106-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9609,10 +9646,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46134</v>
+        <v>45302</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9624,13 +9661,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I105" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9673,7 +9705,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 42802-2023</t>
+          <t>A 48707-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9683,14 +9715,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45182</v>
+        <v>45593</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9702,13 +9734,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I106" t="n">
-        <v>0.6</v>
+        <v>6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9751,7 +9778,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 59522-2025</t>
+          <t>A 59025-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9761,14 +9788,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45989</v>
+        <v>45636</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9782,11 +9809,11 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9829,7 +9856,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 6835-2025</t>
+          <t>A 59522-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9839,14 +9866,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45700</v>
+        <v>45989</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9858,8 +9885,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I108" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9902,7 +9934,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 28471-2023</t>
+          <t>A 60503-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9916,10 +9948,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45103</v>
+        <v>45995</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9932,7 +9964,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9975,7 +10007,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 22867-2022</t>
+          <t>A 13501-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9989,10 +10021,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44715</v>
+        <v>45736</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10005,7 +10037,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.8</v>
+        <v>3.2</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10048,7 +10080,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 60506-2025</t>
+          <t>A 47094-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10062,10 +10094,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45995</v>
+        <v>45196</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10078,7 +10110,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10138,7 +10170,7 @@
         <v>45995</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10194,7 +10226,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 60503-2025</t>
+          <t>A 21253-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10208,10 +10240,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45995</v>
+        <v>46147</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10224,7 +10256,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10267,7 +10299,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 64060-2023</t>
+          <t>A 60506-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10281,10 +10313,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45279</v>
+        <v>45995</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10297,7 +10329,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10340,7 +10372,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 48707-2024</t>
+          <t>A 21257-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10354,10 +10386,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45593</v>
+        <v>46147</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10370,7 +10402,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>6</v>
+        <v>2.7</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10413,7 +10445,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 21210-2025</t>
+          <t>A 31921-2022</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10427,10 +10459,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45779</v>
+        <v>44777</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10442,13 +10474,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10491,7 +10518,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 23717-2025</t>
+          <t>A 42804-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10501,14 +10528,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45793</v>
+        <v>45182</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10520,8 +10547,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I117" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10564,7 +10596,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 61788-2025</t>
+          <t>A 39030-2022</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10578,10 +10610,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46002</v>
+        <v>44817</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10595,11 +10627,11 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10642,7 +10674,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 55832-2023</t>
+          <t>A 61788-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10656,10 +10688,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45239</v>
+        <v>46002</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10671,8 +10703,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I119" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10715,7 +10752,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 58388-2024</t>
+          <t>A 8244-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10729,10 +10766,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45633</v>
+        <v>45708</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10745,7 +10782,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>5.8</v>
+        <v>1.1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10788,7 +10825,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 18978-2025</t>
+          <t>A 28100-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10802,10 +10839,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45764</v>
+        <v>45476</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10818,7 +10855,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10861,7 +10898,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 917-2026</t>
+          <t>A 3227-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10875,10 +10912,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46030</v>
+        <v>45679</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10891,7 +10928,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10934,7 +10971,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 31921-2022</t>
+          <t>A 51344-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10948,10 +10985,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44777</v>
+        <v>45219</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10963,8 +11000,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I123" t="n">
-        <v>2.4</v>
+        <v>4.5</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -11007,7 +11049,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 43075-2023</t>
+          <t>A 64066-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11017,14 +11059,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45182</v>
+        <v>46013</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11037,7 +11079,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -11080,7 +11122,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 47196-2023</t>
+          <t>A 63628-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11094,10 +11136,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45196</v>
+        <v>46014</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11110,7 +11152,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>5.9</v>
+        <v>3.8</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11153,7 +11195,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 21253-2026</t>
+          <t>A 23754-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11167,10 +11209,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46147</v>
+        <v>46164</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11182,8 +11224,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I126" t="n">
-        <v>3.4</v>
+        <v>12.2</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11226,7 +11273,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 13454-2022</t>
+          <t>A 1788-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11240,10 +11287,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44645</v>
+        <v>46034</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11256,7 +11303,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11299,7 +11346,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 21257-2026</t>
+          <t>A 4587-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11313,10 +11360,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46147</v>
+        <v>45687</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11329,7 +11376,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11372,7 +11419,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 53618-2024</t>
+          <t>A 4587-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11386,10 +11433,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45614</v>
+        <v>45687</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11402,7 +11449,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>10.1</v>
+        <v>3.3</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11445,7 +11492,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 30961-2022</t>
+          <t>A 20463-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11459,10 +11506,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44768</v>
+        <v>45775</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11476,11 +11523,11 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I130" t="n">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11523,7 +11570,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 3227-2025</t>
+          <t>A 28471-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11537,10 +11584,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45679</v>
+        <v>45103</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11553,7 +11600,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>4.5</v>
+        <v>1.7</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11596,7 +11643,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 42803-2023</t>
+          <t>A 2911-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11606,14 +11653,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45182</v>
+        <v>46038</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11625,13 +11672,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11674,7 +11716,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 23754-2026</t>
+          <t>A 35470-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11688,10 +11730,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46164</v>
+        <v>45531</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11703,13 +11745,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I133" t="n">
-        <v>12.2</v>
+        <v>0.5</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11752,7 +11789,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 4587-2025</t>
+          <t>A 45664-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11766,10 +11803,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45687</v>
+        <v>45923</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11781,8 +11818,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I134" t="n">
-        <v>3.3</v>
+        <v>9</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11825,7 +11867,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 8803-2025</t>
+          <t>A 24666-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11839,10 +11881,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45712</v>
+        <v>46171</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11855,7 +11897,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.5</v>
+        <v>6.1</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11898,7 +11940,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 4587-2025</t>
+          <t>A 47222-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11912,10 +11954,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45687</v>
+        <v>45586</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11927,8 +11969,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I136" t="n">
-        <v>3.3</v>
+        <v>5.3</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11971,7 +12018,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 24666-2026</t>
+          <t>A 16881-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11985,10 +12032,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46171</v>
+        <v>45033</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12000,8 +12047,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I137" t="n">
-        <v>6.1</v>
+        <v>2.3</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -12044,7 +12096,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 25092-2026</t>
+          <t>A 25098-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12054,14 +12106,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D138" s="1" t="n">
         <v>46175</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12079,7 +12131,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -12122,7 +12174,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 25098-2026</t>
+          <t>A 25092-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12132,14 +12184,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D139" s="1" t="n">
         <v>46175</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12157,7 +12209,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12200,7 +12252,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 26608-2026</t>
+          <t>A 61396-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12214,10 +12266,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46184</v>
+        <v>45264</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12229,13 +12281,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I140" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12278,7 +12325,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 27120-2026</t>
+          <t>A 4164-2022</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12292,10 +12339,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46188</v>
+        <v>44588</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12307,8 +12354,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I141" t="n">
-        <v>4.7</v>
+        <v>1.5</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12351,7 +12403,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 26819-2026</t>
+          <t>A 61271-2022</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12365,10 +12417,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46185</v>
+        <v>44909</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12382,11 +12434,11 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I142" t="n">
-        <v>2.4</v>
+        <v>14.1</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12429,7 +12481,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 3239-2026</t>
+          <t>A 57422-2021</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12443,10 +12495,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46041</v>
+        <v>44483</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12459,7 +12511,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12502,7 +12554,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 26820-2026</t>
+          <t>A 26822-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12519,7 +12571,7 @@
         <v>46185</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12537,7 +12589,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>9.9</v>
+        <v>2.2</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12580,7 +12632,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 26821-2026</t>
+          <t>A 26819-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12597,7 +12649,7 @@
         <v>46185</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12615,7 +12667,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>7.9</v>
+        <v>2.4</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12658,7 +12710,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 26822-2026</t>
+          <t>A 3239-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12672,10 +12724,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46185</v>
+        <v>46041</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12687,13 +12739,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I146" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12736,7 +12783,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 26824-2026</t>
+          <t>A 26821-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12753,7 +12800,7 @@
         <v>46185</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12771,7 +12818,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>5</v>
+        <v>7.9</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12814,7 +12861,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 26825-2026</t>
+          <t>A 26820-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12831,7 +12878,7 @@
         <v>46185</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12849,7 +12896,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>0.8</v>
+        <v>9.9</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12892,7 +12939,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 27392-2026</t>
+          <t>A 26608-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12906,10 +12953,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46189</v>
+        <v>46184</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12927,7 +12974,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12970,7 +13017,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 56313-2024</t>
+          <t>A 26824-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12984,10 +13031,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45624</v>
+        <v>46185</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13001,11 +13048,11 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I150" t="n">
-        <v>2.2</v>
+        <v>5</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -13048,7 +13095,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 10743-2023</t>
+          <t>A 26825-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -13062,10 +13109,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44988</v>
+        <v>46185</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13079,11 +13126,11 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I151" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -13126,7 +13173,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 14215-2024</t>
+          <t>A 35060-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13140,10 +13187,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45393</v>
+        <v>45527</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13157,11 +13204,11 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I152" t="n">
-        <v>4.2</v>
+        <v>0.6</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -13204,7 +13251,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 55191-2023</t>
+          <t>A 9917-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13218,10 +13265,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45237</v>
+        <v>46073</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13234,7 +13281,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1.9</v>
+        <v>3.1</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -13277,7 +13324,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 59025-2024</t>
+          <t>A 27392-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13291,10 +13338,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45636</v>
+        <v>46189</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13308,11 +13355,11 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I154" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13355,7 +13402,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 31378-2026</t>
+          <t>A 64060-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13369,10 +13416,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46213</v>
+        <v>45279</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13385,7 +13432,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>3.7</v>
+        <v>1.9</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13428,7 +13475,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 35094-2026</t>
+          <t>A 27120-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13442,10 +13489,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46260</v>
+        <v>46188</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13457,13 +13504,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I156" t="n">
-        <v>1.9</v>
+        <v>4.7</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13506,7 +13548,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 17243-2024</t>
+          <t>A 8990-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13520,10 +13562,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45414</v>
+        <v>44979</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13536,7 +13578,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13579,7 +13621,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 35699-2026</t>
+          <t>A 14215-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13589,14 +13631,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46265</v>
+        <v>45393</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13610,11 +13652,11 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I158" t="n">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13657,7 +13699,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 36374-2026</t>
+          <t>A 50614-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13671,10 +13713,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46268</v>
+        <v>45601</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13686,13 +13728,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I159" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13735,7 +13772,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 35060-2024</t>
+          <t>A 55182-2024</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13749,10 +13786,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45527</v>
+        <v>45618</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13764,13 +13801,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I160" t="n">
-        <v>0.6</v>
+        <v>11.4</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13813,7 +13845,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 37089-2026</t>
+          <t>A 52797-2021</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13827,10 +13859,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46273</v>
+        <v>44467</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13843,7 +13875,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>15.8</v>
+        <v>1.4</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13886,7 +13918,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 52826-2024</t>
+          <t>A 24116-2024</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13900,10 +13932,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45610</v>
+        <v>45456</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13916,7 +13948,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13959,7 +13991,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 52829-2024</t>
+          <t>A 55832-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13973,10 +14005,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45610</v>
+        <v>45239</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13989,7 +14021,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -14032,7 +14064,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 11974-2025</t>
+          <t>A 10515-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -14046,10 +14078,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45728</v>
+        <v>44987</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14062,7 +14094,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -14105,7 +14137,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 61271-2022</t>
+          <t>A 33011-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -14119,10 +14151,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>44909</v>
+        <v>45125</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14134,13 +14166,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I165" t="n">
-        <v>14.1</v>
+        <v>0.8</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -14200,7 +14227,7 @@
         <v>45589</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14256,7 +14283,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 18955-2025</t>
+          <t>A 13454-2022</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -14270,10 +14297,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45764</v>
+        <v>44645</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14286,7 +14313,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>8.1</v>
+        <v>1.7</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14329,7 +14356,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 50614-2024</t>
+          <t>A 10743-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14343,10 +14370,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45601</v>
+        <v>44988</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14358,8 +14385,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I168" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14402,7 +14434,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 55182-2024</t>
+          <t>A 50611-2024</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14416,10 +14448,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45618</v>
+        <v>45601</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14432,7 +14464,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>11.4</v>
+        <v>1</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14475,7 +14507,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 4058-2022</t>
+          <t>A 42802-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14485,14 +14517,14 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>44588</v>
+        <v>45182</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14504,8 +14536,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I170" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14548,7 +14585,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 28100-2024</t>
+          <t>A 52829-2024</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14562,10 +14599,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45476</v>
+        <v>45610</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14578,7 +14615,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14621,7 +14658,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 1106-2024</t>
+          <t>A 56313-2024</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14635,10 +14672,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45302</v>
+        <v>45624</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14650,8 +14687,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I172" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14694,7 +14736,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 39030-2022</t>
+          <t>A 38382-2022</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14708,10 +14750,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>44817</v>
+        <v>44812</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14725,11 +14767,11 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14772,7 +14814,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 38382-2022</t>
+          <t>A 8259-2025</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14786,10 +14828,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>44812</v>
+        <v>45708</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14801,13 +14843,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I174" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14850,7 +14887,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 16881-2023</t>
+          <t>A 24115-2024</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14864,10 +14901,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45033</v>
+        <v>45456</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14879,13 +14916,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I175" t="n">
-        <v>2.3</v>
+        <v>8</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14928,7 +14960,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 57422-2021</t>
+          <t>A 31378-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14942,10 +14974,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>44483</v>
+        <v>46213</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14958,7 +14990,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1.2</v>
+        <v>3.7</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -15001,7 +15033,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 8244-2025</t>
+          <t>A 53620-2024</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -15015,10 +15047,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45708</v>
+        <v>45614</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15031,7 +15063,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -15074,7 +15106,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 38190-2024</t>
+          <t>A 35094-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -15088,10 +15120,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45545</v>
+        <v>46260</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15103,8 +15135,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I178" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -15147,7 +15184,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 20463-2025</t>
+          <t>A 10404-2022</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -15161,10 +15198,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45775</v>
+        <v>44623</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15176,13 +15213,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I179" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -15225,7 +15257,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 35470-2024</t>
+          <t>A 35930-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -15239,10 +15271,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45531</v>
+        <v>45148</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15254,8 +15286,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I180" t="n">
-        <v>0.5</v>
+        <v>5.2</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -15298,7 +15335,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 35445-2024</t>
+          <t>A 47196-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15312,10 +15349,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45531</v>
+        <v>45196</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15328,7 +15365,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>0.5</v>
+        <v>5.9</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15371,7 +15408,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 47094-2023</t>
+          <t>A 53618-2024</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15385,10 +15422,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45196</v>
+        <v>45614</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15401,7 +15438,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.9</v>
+        <v>10.1</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15444,7 +15481,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 38196-2024</t>
+          <t>A 35699-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15454,14 +15491,14 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45545</v>
+        <v>46265</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15473,8 +15510,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I183" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15517,7 +15559,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 50611-2024</t>
+          <t>A 36374-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15531,10 +15573,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45601</v>
+        <v>46268</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15546,8 +15588,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I184" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15590,7 +15637,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 20289-2024</t>
+          <t>A 58388-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15604,10 +15651,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45435</v>
+        <v>45633</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15619,13 +15666,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I185" t="n">
-        <v>0.7</v>
+        <v>5.8</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15668,7 +15710,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 52797-2021</t>
+          <t>A 47201-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15682,10 +15724,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>44467</v>
+        <v>45196</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15698,7 +15740,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15741,7 +15783,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 20086-2024</t>
+          <t>A 37089-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15751,14 +15793,14 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45434</v>
+        <v>46273</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15771,7 +15813,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1.5</v>
+        <v>15.8</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15814,7 +15856,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 13496-2025</t>
+          <t>A 52828-2024</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15828,10 +15870,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45736</v>
+        <v>45610</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15844,7 +15886,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>8.800000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15887,7 +15929,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 56887-2022</t>
+          <t>A 17243-2024</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15901,10 +15943,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>44894</v>
+        <v>45414</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15917,7 +15959,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15960,7 +16002,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 33011-2023</t>
+          <t>A 59938-2023</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15974,10 +16016,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45125</v>
+        <v>45257</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15990,7 +16032,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -16033,7 +16075,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 51344-2023</t>
+          <t>A 38043-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -16047,10 +16089,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45219</v>
+        <v>46280</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16064,11 +16106,11 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I191" t="n">
-        <v>4.5</v>
+        <v>1.1</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -16111,7 +16153,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 10515-2023</t>
+          <t>A 38020-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -16125,10 +16167,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>44987</v>
+        <v>46280</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16140,8 +16182,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I192" t="n">
-        <v>1.9</v>
+        <v>4.1</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -16184,7 +16231,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 39337-2022</t>
+          <t>A 38742-2023</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -16194,14 +16241,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>44817</v>
+        <v>45161</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16213,8 +16260,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I193" t="n">
-        <v>1.5</v>
+        <v>4.2</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -16257,7 +16309,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 53620-2024</t>
+          <t>A 3735-2024</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -16271,10 +16323,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45614</v>
+        <v>45321</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16286,8 +16338,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I194" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -16330,7 +16387,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 13501-2025</t>
+          <t>A 23308-2025</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16344,10 +16401,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45736</v>
+        <v>45791</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16360,7 +16417,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -16403,7 +16460,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 10404-2022</t>
+          <t>A 27498-2025</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16417,10 +16474,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>44623</v>
+        <v>45813</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16433,7 +16490,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16476,7 +16533,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 38742-2023</t>
+          <t>A 54680-2021</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16486,14 +16543,14 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45161</v>
+        <v>44473</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16505,13 +16562,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I197" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16554,7 +16606,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 3735-2024</t>
+          <t>A 30102-2025</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16568,10 +16620,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45321</v>
+        <v>45826</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16583,13 +16635,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I198" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16632,7 +16679,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 23308-2025</t>
+          <t>A 53647-2023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16646,10 +16693,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45791</v>
+        <v>45230</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16662,123 +16709,347 @@
         </is>
       </c>
       <c r="I199" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J199" t="n">
+        <v>0</v>
+      </c>
+      <c r="K199" t="n">
+        <v>0</v>
+      </c>
+      <c r="L199" t="n">
+        <v>0</v>
+      </c>
+      <c r="M199" t="n">
+        <v>0</v>
+      </c>
+      <c r="N199" t="n">
+        <v>0</v>
+      </c>
+      <c r="O199" t="n">
+        <v>0</v>
+      </c>
+      <c r="P199" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q199" t="n">
+        <v>0</v>
+      </c>
+      <c r="R199" t="n">
+        <v>0</v>
+      </c>
+      <c r="S199" t="n">
+        <v>0</v>
+      </c>
+      <c r="T199" t="n">
+        <v>0</v>
+      </c>
+      <c r="U199" t="n">
+        <v>0</v>
+      </c>
+      <c r="V199" s="2" t="inlineStr"/>
+    </row>
+    <row r="200" ht="15" customHeight="1">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>A 23620-2024</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D200" s="1" t="n">
+        <v>45454</v>
+      </c>
+      <c r="E200" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>KARLSKOGA</t>
+        </is>
+      </c>
+      <c r="I200" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J200" t="n">
+        <v>0</v>
+      </c>
+      <c r="K200" t="n">
+        <v>0</v>
+      </c>
+      <c r="L200" t="n">
+        <v>0</v>
+      </c>
+      <c r="M200" t="n">
+        <v>0</v>
+      </c>
+      <c r="N200" t="n">
+        <v>0</v>
+      </c>
+      <c r="O200" t="n">
+        <v>0</v>
+      </c>
+      <c r="P200" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q200" t="n">
+        <v>0</v>
+      </c>
+      <c r="R200" t="n">
+        <v>0</v>
+      </c>
+      <c r="S200" t="n">
+        <v>0</v>
+      </c>
+      <c r="T200" t="n">
+        <v>0</v>
+      </c>
+      <c r="U200" t="n">
+        <v>0</v>
+      </c>
+      <c r="V200" s="2" t="inlineStr"/>
+    </row>
+    <row r="201" ht="15" customHeight="1">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>A 31397-2025</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D201" s="1" t="n">
+        <v>45833</v>
+      </c>
+      <c r="E201" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>KARLSKOGA</t>
+        </is>
+      </c>
+      <c r="I201" t="n">
         <v>1.5</v>
       </c>
-      <c r="J199" t="n">
-        <v>0</v>
-      </c>
-      <c r="K199" t="n">
-        <v>0</v>
-      </c>
-      <c r="L199" t="n">
-        <v>0</v>
-      </c>
-      <c r="M199" t="n">
-        <v>0</v>
-      </c>
-      <c r="N199" t="n">
-        <v>0</v>
-      </c>
-      <c r="O199" t="n">
-        <v>0</v>
-      </c>
-      <c r="P199" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q199" t="n">
-        <v>0</v>
-      </c>
-      <c r="R199" t="n">
-        <v>0</v>
-      </c>
-      <c r="S199" t="n">
-        <v>0</v>
-      </c>
-      <c r="T199" t="n">
-        <v>0</v>
-      </c>
-      <c r="U199" t="n">
-        <v>0</v>
-      </c>
-      <c r="V199" s="2" t="inlineStr"/>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
+      <c r="J201" t="n">
+        <v>0</v>
+      </c>
+      <c r="K201" t="n">
+        <v>0</v>
+      </c>
+      <c r="L201" t="n">
+        <v>0</v>
+      </c>
+      <c r="M201" t="n">
+        <v>0</v>
+      </c>
+      <c r="N201" t="n">
+        <v>0</v>
+      </c>
+      <c r="O201" t="n">
+        <v>0</v>
+      </c>
+      <c r="P201" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q201" t="n">
+        <v>0</v>
+      </c>
+      <c r="R201" t="n">
+        <v>0</v>
+      </c>
+      <c r="S201" t="n">
+        <v>0</v>
+      </c>
+      <c r="T201" t="n">
+        <v>0</v>
+      </c>
+      <c r="U201" t="n">
+        <v>0</v>
+      </c>
+      <c r="V201" s="2" t="inlineStr"/>
+    </row>
+    <row r="202" ht="15" customHeight="1">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>A 32287-2025</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D202" s="1" t="n">
+        <v>45835</v>
+      </c>
+      <c r="E202" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>KARLSKOGA</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I202" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="J202" t="n">
+        <v>0</v>
+      </c>
+      <c r="K202" t="n">
+        <v>0</v>
+      </c>
+      <c r="L202" t="n">
+        <v>0</v>
+      </c>
+      <c r="M202" t="n">
+        <v>0</v>
+      </c>
+      <c r="N202" t="n">
+        <v>0</v>
+      </c>
+      <c r="O202" t="n">
+        <v>0</v>
+      </c>
+      <c r="P202" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q202" t="n">
+        <v>0</v>
+      </c>
+      <c r="R202" t="n">
+        <v>0</v>
+      </c>
+      <c r="S202" t="n">
+        <v>0</v>
+      </c>
+      <c r="T202" t="n">
+        <v>0</v>
+      </c>
+      <c r="U202" t="n">
+        <v>0</v>
+      </c>
+      <c r="V202" s="2" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
         <is>
           <t>S 2960-2025</t>
         </is>
       </c>
-      <c r="B200" t="inlineStr">
+      <c r="B203" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C200" t="inlineStr">
+      <c r="C203" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D200" s="1" t="n">
+      <c r="D203" s="1" t="n">
         <v>45953</v>
       </c>
-      <c r="E200" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F200" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>KARLSKOGA</t>
-        </is>
-      </c>
-      <c r="H200" t="inlineStr">
+      <c r="E203" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>KARLSKOGA</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I200" t="n">
+      <c r="I203" t="n">
         <v>2.4</v>
       </c>
-      <c r="J200" t="n">
-        <v>0</v>
-      </c>
-      <c r="K200" t="n">
-        <v>0</v>
-      </c>
-      <c r="L200" t="n">
-        <v>0</v>
-      </c>
-      <c r="M200" t="n">
-        <v>0</v>
-      </c>
-      <c r="N200" t="n">
-        <v>0</v>
-      </c>
-      <c r="O200" t="n">
-        <v>0</v>
-      </c>
-      <c r="P200" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
-      <c r="R200" t="n">
-        <v>0</v>
-      </c>
-      <c r="S200" t="n">
-        <v>0</v>
-      </c>
-      <c r="T200" t="n">
-        <v>0</v>
-      </c>
-      <c r="U200" t="n">
-        <v>0</v>
-      </c>
-      <c r="V200" s="2" t="inlineStr"/>
+      <c r="J203" t="n">
+        <v>0</v>
+      </c>
+      <c r="K203" t="n">
+        <v>0</v>
+      </c>
+      <c r="L203" t="n">
+        <v>0</v>
+      </c>
+      <c r="M203" t="n">
+        <v>0</v>
+      </c>
+      <c r="N203" t="n">
+        <v>0</v>
+      </c>
+      <c r="O203" t="n">
+        <v>0</v>
+      </c>
+      <c r="P203" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q203" t="n">
+        <v>0</v>
+      </c>
+      <c r="R203" t="n">
+        <v>0</v>
+      </c>
+      <c r="S203" t="n">
+        <v>0</v>
+      </c>
+      <c r="T203" t="n">
+        <v>0</v>
+      </c>
+      <c r="U203" t="n">
+        <v>0</v>
+      </c>
+      <c r="V203" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt KARLSKOGA.xlsx
+++ b/Översikt KARLSKOGA.xlsx
@@ -601,7 +601,7 @@
         <v>45562</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
         <v>45958</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>45989</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>44510</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>46100</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>45989</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>44473</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 63187-2025</t>
+          <t>A 8803-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1490,10 +1490,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46010</v>
+        <v>46066</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1505,19 +1505,14 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I9" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L9" t="n">
         <v>1</v>
@@ -1544,12 +1539,125 @@
         <v>4</v>
       </c>
       <c r="T9" t="n">
+        <v>8</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp
+Platt fjädermossa
+Skogshakmossa
+Trubbfjädermossa</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 8803-2026 artfynd.xlsx", "A 8803-2026")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 8803-2026 karta.png", "A 8803-2026")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 8803-2026 georefererad karta.tif", "A 8803-2026")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 8803-2026 FSC-klagomål.docx", "A 8803-2026")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 8803-2026 FSC-klagomål mail.docx", "A 8803-2026")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 8803-2026 tillsynsbegäran.docx", "A 8803-2026")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 8803-2026 tillsynsbegäran mail.docx", "A 8803-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 63187-2025</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>46010</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>KARLSKOGA</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
         <v>4</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Talltita
 Bronshjon
@@ -1557,111 +1665,111 @@
 Tjäder</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 63187-2025 artfynd.xlsx", "A 63187-2025")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 63187-2025 karta.png", "A 63187-2025")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 63187-2025 georefererad karta.tif", "A 63187-2025")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 63187-2025 FSC-klagomål.docx", "A 63187-2025")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 63187-2025 FSC-klagomål mail.docx", "A 63187-2025")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 63187-2025 tillsynsbegäran.docx", "A 63187-2025")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 63187-2025 tillsynsbegäran mail.docx", "A 63187-2025")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 63187-2025 prioriterade fågelarter.docx", "A 63187-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>A 60085-2021</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
         <v>44495</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>KARLSKOGA</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
+      <c r="E11" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>KARLSKOGA</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>3.6</v>
       </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
         <v>3</v>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
         <v>1</v>
       </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>1</v>
       </c>
-      <c r="R10" t="n">
+      <c r="R11" t="n">
         <v>1</v>
       </c>
-      <c r="S10" t="n">
+      <c r="S11" t="n">
         <v>4</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T11" t="n">
         <v>5</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U11" t="n">
         <v>1</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Citronfingersvamp
 Mörk husmossa
@@ -1669,140 +1777,32 @@
 Västlig hakmossa</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 60085-2021 artfynd.xlsx", "A 60085-2021")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 60085-2021 karta.png", "A 60085-2021")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 60085-2021 georefererad karta.tif", "A 60085-2021")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 60085-2021 FSC-klagomål.docx", "A 60085-2021")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 60085-2021 FSC-klagomål mail.docx", "A 60085-2021")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 60085-2021 tillsynsbegäran.docx", "A 60085-2021")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 60085-2021 tillsynsbegäran mail.docx", "A 60085-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 8803-2026</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>46066</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>KARLSKOGA</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>3</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>4</v>
-      </c>
-      <c r="T11" t="n">
-        <v>8</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Dofttaggsvamp
-Platt fjädermossa
-Skogshakmossa
-Trubbfjädermossa</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 8803-2026 artfynd.xlsx", "A 8803-2026")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 8803-2026 karta.png", "A 8803-2026")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 8803-2026 georefererad karta.tif", "A 8803-2026")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 8803-2026 FSC-klagomål.docx", "A 8803-2026")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 8803-2026 FSC-klagomål mail.docx", "A 8803-2026")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 8803-2026 tillsynsbegäran.docx", "A 8803-2026")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 8803-2026 tillsynsbegäran mail.docx", "A 8803-2026")</f>
         <v/>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
         <v>46136</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 18428-2026</t>
+          <t>A 63185-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1936,14 +1936,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46127</v>
+        <v>46010</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1961,10 +1961,10 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1973,615 +1973,615 @@
         <v>1</v>
       </c>
       <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>1</v>
       </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2</v>
-      </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>3</v>
       </c>
       <c r="T13" t="n">
+        <v>11</v>
+      </c>
+      <c r="U13" t="n">
+        <v>9</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Talltita
+Brudborste
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 63185-2025 artfynd.xlsx", "A 63185-2025")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 63185-2025 karta.png", "A 63185-2025")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 63185-2025 georefererad karta.tif", "A 63185-2025")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 63185-2025 FSC-klagomål.docx", "A 63185-2025")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 63185-2025 FSC-klagomål mail.docx", "A 63185-2025")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 63185-2025 tillsynsbegäran.docx", "A 63185-2025")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 63185-2025 tillsynsbegäran mail.docx", "A 63185-2025")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 63185-2025 prioriterade fågelarter.docx", "A 63185-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 18428-2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>46127</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>KARLSKOGA</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>6</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3</v>
+      </c>
+      <c r="T14" t="n">
         <v>17</v>
       </c>
-      <c r="U13" t="n">
+      <c r="U14" t="n">
         <v>17</v>
       </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Skuggblåslav
 Tjäder</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 18428-2026 artfynd.xlsx", "A 18428-2026")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 18428-2026 karta.png", "A 18428-2026")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 18428-2026 georefererad karta.tif", "A 18428-2026")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 18428-2026 FSC-klagomål.docx", "A 18428-2026")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 18428-2026 FSC-klagomål mail.docx", "A 18428-2026")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 18428-2026 tillsynsbegäran.docx", "A 18428-2026")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 18428-2026 tillsynsbegäran mail.docx", "A 18428-2026")</f>
         <v/>
       </c>
-      <c r="AE13">
+      <c r="AE14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 18428-2026 prioriterade fågelarter.docx", "A 18428-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 63185-2025</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 35696-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
-      <c r="D14" s="1" t="n">
+      <c r="D15" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>KARLSKOGA</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>4</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Grönpyrola
+Mattlummer
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 35696-2026 artfynd.xlsx", "A 35696-2026")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 35696-2026 karta.png", "A 35696-2026")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 35696-2026 georefererad karta.tif", "A 35696-2026")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 35696-2026 FSC-klagomål.docx", "A 35696-2026")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 35696-2026 FSC-klagomål mail.docx", "A 35696-2026")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 35696-2026 tillsynsbegäran.docx", "A 35696-2026")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 35696-2026 tillsynsbegäran mail.docx", "A 35696-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 20108-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>46136</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>KARLSKOGA</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="n">
+        <v>5</v>
+      </c>
+      <c r="U16" t="n">
+        <v>5</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Talltita
+Vedticka</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 20108-2026 artfynd.xlsx", "A 20108-2026")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 20108-2026 karta.png", "A 20108-2026")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 20108-2026 georefererad karta.tif", "A 20108-2026")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 20108-2026 FSC-klagomål.docx", "A 20108-2026")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 20108-2026 FSC-klagomål mail.docx", "A 20108-2026")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 20108-2026 tillsynsbegäran.docx", "A 20108-2026")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 20108-2026 tillsynsbegäran mail.docx", "A 20108-2026")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 20108-2026 prioriterade fågelarter.docx", "A 20108-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 20112-2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>46136</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>KARLSKOGA</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>4</v>
+      </c>
+      <c r="U17" t="n">
+        <v>4</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett
+Spillkråka
+Tofsmes</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 20112-2026 artfynd.xlsx", "A 20112-2026")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 20112-2026 karta.png", "A 20112-2026")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 20112-2026 georefererad karta.tif", "A 20112-2026")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 20112-2026 FSC-klagomål.docx", "A 20112-2026")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 20112-2026 FSC-klagomål mail.docx", "A 20112-2026")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 20112-2026 tillsynsbegäran.docx", "A 20112-2026")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 20112-2026 tillsynsbegäran mail.docx", "A 20112-2026")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 20112-2026 prioriterade fågelarter.docx", "A 20112-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>S 3545-2025</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
         <v>46010</v>
       </c>
-      <c r="E14" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>KARLSKOGA</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
+      <c r="E18" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>KARLSKOGA</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I14" t="n">
+      <c r="I18" t="n">
         <v>8.4</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J18" t="n">
         <v>2</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
         <v>1</v>
       </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
         <v>1</v>
       </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
         <v>3</v>
       </c>
-      <c r="T14" t="n">
+      <c r="T18" t="n">
         <v>11</v>
       </c>
-      <c r="U14" t="n">
+      <c r="U18" t="n">
         <v>9</v>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Talltita
 Brudborste
 Revlummer</t>
         </is>
       </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 63185-2025 artfynd.xlsx", "A 63185-2025")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 63185-2025 karta.png", "A 63185-2025")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 63185-2025 georefererad karta.tif", "A 63185-2025")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 63185-2025 FSC-klagomål.docx", "A 63185-2025")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 63185-2025 FSC-klagomål mail.docx", "A 63185-2025")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 63185-2025 tillsynsbegäran.docx", "A 63185-2025")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 63185-2025 tillsynsbegäran mail.docx", "A 63185-2025")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 63185-2025 prioriterade fågelarter.docx", "A 63185-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 35696-2026</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>KARLSKOGA</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3</v>
-      </c>
-      <c r="T15" t="n">
-        <v>4</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Grönpyrola
-Mattlummer
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 35696-2026 artfynd.xlsx", "A 35696-2026")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 35696-2026 karta.png", "A 35696-2026")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 35696-2026 georefererad karta.tif", "A 35696-2026")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 35696-2026 FSC-klagomål.docx", "A 35696-2026")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 35696-2026 FSC-klagomål mail.docx", "A 35696-2026")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 35696-2026 tillsynsbegäran.docx", "A 35696-2026")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 35696-2026 tillsynsbegäran mail.docx", "A 35696-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 20112-2026</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>46136</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>KARLSKOGA</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J16" t="n">
-        <v>3</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3</v>
-      </c>
-      <c r="T16" t="n">
-        <v>4</v>
-      </c>
-      <c r="U16" t="n">
-        <v>4</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett
-Spillkråka
-Tofsmes</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 20112-2026 artfynd.xlsx", "A 20112-2026")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 20112-2026 karta.png", "A 20112-2026")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 20112-2026 georefererad karta.tif", "A 20112-2026")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 20112-2026 FSC-klagomål.docx", "A 20112-2026")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 20112-2026 FSC-klagomål mail.docx", "A 20112-2026")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 20112-2026 tillsynsbegäran.docx", "A 20112-2026")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 20112-2026 tillsynsbegäran mail.docx", "A 20112-2026")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 20112-2026 prioriterade fågelarter.docx", "A 20112-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 20108-2026</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>46136</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>KARLSKOGA</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>5</v>
-      </c>
-      <c r="U17" t="n">
-        <v>5</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Talltita
-Vedticka</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 20108-2026 artfynd.xlsx", "A 20108-2026")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 20108-2026 karta.png", "A 20108-2026")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 20108-2026 georefererad karta.tif", "A 20108-2026")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 20108-2026 FSC-klagomål.docx", "A 20108-2026")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 20108-2026 FSC-klagomål mail.docx", "A 20108-2026")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 20108-2026 tillsynsbegäran.docx", "A 20108-2026")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 20108-2026 tillsynsbegäran mail.docx", "A 20108-2026")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 20108-2026 prioriterade fågelarter.docx", "A 20108-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>S 3545-2025</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>46010</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>KARLSKOGA</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>11</v>
-      </c>
-      <c r="U18" t="n">
-        <v>9</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Talltita
-Brudborste
-Revlummer</t>
-        </is>
-      </c>
       <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/S 3545-2025 artfynd.xlsx", "S 3545-2025")</f>
         <v/>
@@ -2635,7 +2635,7 @@
         <v>44817</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>45553</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 58091-2022</t>
+          <t>A 52377-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2853,10 +2853,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44900</v>
+        <v>45953</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2907,49 +2907,49 @@
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Hårklomossa</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 58091-2022 artfynd.xlsx", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 52377-2025 artfynd.xlsx", "A 52377-2025")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 58091-2022 karta.png", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 52377-2025 karta.png", "A 52377-2025")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 58091-2022 georefererad karta.tif", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 52377-2025 georefererad karta.tif", "A 52377-2025")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 58091-2022 FSC-klagomål.docx", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 52377-2025 FSC-klagomål.docx", "A 52377-2025")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 58091-2022 FSC-klagomål mail.docx", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 52377-2025 FSC-klagomål mail.docx", "A 52377-2025")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 58091-2022 tillsynsbegäran.docx", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 52377-2025 tillsynsbegäran.docx", "A 52377-2025")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 58091-2022 tillsynsbegäran mail.docx", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 52377-2025 tillsynsbegäran mail.docx", "A 52377-2025")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 28566-2024</t>
+          <t>A 63188-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2963,10 +2963,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45478</v>
+        <v>46010</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2978,8 +2978,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2988,7 +2993,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -3003,7 +3008,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -3012,49 +3017,53 @@
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 28566-2024 artfynd.xlsx", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 63188-2025 artfynd.xlsx", "A 63188-2025")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 28566-2024 karta.png", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 63188-2025 karta.png", "A 63188-2025")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 28566-2024 georefererad karta.tif", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 63188-2025 georefererad karta.tif", "A 63188-2025")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 28566-2024 FSC-klagomål.docx", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 63188-2025 FSC-klagomål.docx", "A 63188-2025")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 28566-2024 FSC-klagomål mail.docx", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 63188-2025 FSC-klagomål mail.docx", "A 63188-2025")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 28566-2024 tillsynsbegäran.docx", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 63188-2025 tillsynsbegäran.docx", "A 63188-2025")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 28566-2024 tillsynsbegäran mail.docx", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 63188-2025 tillsynsbegäran mail.docx", "A 63188-2025")</f>
+        <v/>
+      </c>
+      <c r="AE22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 63188-2025 prioriterade fågelarter.docx", "A 63188-2025")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 63188-2025</t>
+          <t>A 16784-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3068,10 +3077,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46010</v>
+        <v>46113</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3089,7 +3098,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.1</v>
+        <v>4.2</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -3098,7 +3107,7 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -3113,7 +3122,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -3125,50 +3134,46 @@
         <v>2</v>
       </c>
       <c r="U23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Hårklomossa</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 63188-2025 artfynd.xlsx", "A 63188-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 16784-2026 artfynd.xlsx", "A 16784-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 63188-2025 karta.png", "A 63188-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 16784-2026 karta.png", "A 16784-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 63188-2025 georefererad karta.tif", "A 63188-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 16784-2026 georefererad karta.tif", "A 16784-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 63188-2025 FSC-klagomål.docx", "A 63188-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 16784-2026 FSC-klagomål.docx", "A 16784-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 63188-2025 FSC-klagomål mail.docx", "A 63188-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 16784-2026 FSC-klagomål mail.docx", "A 16784-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 63188-2025 tillsynsbegäran.docx", "A 63188-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 16784-2026 tillsynsbegäran.docx", "A 16784-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 63188-2025 tillsynsbegäran mail.docx", "A 63188-2025")</f>
-        <v/>
-      </c>
-      <c r="AE23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 63188-2025 prioriterade fågelarter.docx", "A 63188-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 16784-2026 tillsynsbegäran mail.docx", "A 16784-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 16784-2026</t>
+          <t>A 18427-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3182,10 +3187,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46113</v>
+        <v>46127</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3203,7 +3208,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3236,49 +3241,53 @@
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Hårklomossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 16784-2026 artfynd.xlsx", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 18427-2026 artfynd.xlsx", "A 18427-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 16784-2026 karta.png", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 18427-2026 karta.png", "A 18427-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 16784-2026 georefererad karta.tif", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 18427-2026 georefererad karta.tif", "A 18427-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 16784-2026 FSC-klagomål.docx", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 18427-2026 FSC-klagomål.docx", "A 18427-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 16784-2026 FSC-klagomål mail.docx", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 18427-2026 FSC-klagomål mail.docx", "A 18427-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 16784-2026 tillsynsbegäran.docx", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 18427-2026 tillsynsbegäran.docx", "A 18427-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 16784-2026 tillsynsbegäran mail.docx", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 18427-2026 tillsynsbegäran mail.docx", "A 18427-2026")</f>
+        <v/>
+      </c>
+      <c r="AE24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 18427-2026 prioriterade fågelarter.docx", "A 18427-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 40528-2024</t>
+          <t>A 19233-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3292,10 +3301,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45555</v>
+        <v>46132</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3308,13 +3317,13 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
         <v>1</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -3344,46 +3353,46 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 40528-2024 artfynd.xlsx", "A 40528-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 19233-2026 artfynd.xlsx", "A 19233-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 40528-2024 karta.png", "A 40528-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 19233-2026 karta.png", "A 19233-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 40528-2024 georefererad karta.tif", "A 40528-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 19233-2026 georefererad karta.tif", "A 19233-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 40528-2024 FSC-klagomål.docx", "A 40528-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 19233-2026 FSC-klagomål.docx", "A 19233-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 40528-2024 FSC-klagomål mail.docx", "A 40528-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 19233-2026 FSC-klagomål mail.docx", "A 19233-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 40528-2024 tillsynsbegäran.docx", "A 40528-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 19233-2026 tillsynsbegäran.docx", "A 19233-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 40528-2024 tillsynsbegäran mail.docx", "A 40528-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 19233-2026 tillsynsbegäran mail.docx", "A 19233-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 18427-2026</t>
+          <t>A 28474-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3397,10 +3406,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46127</v>
+        <v>45103</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3412,13 +3421,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>3</v>
+        <v>5.1</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3427,7 +3431,7 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -3442,7 +3446,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3458,46 +3462,46 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåhake</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 18427-2026 artfynd.xlsx", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 28474-2023 artfynd.xlsx", "A 28474-2023")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 18427-2026 karta.png", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 28474-2023 karta.png", "A 28474-2023")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 18427-2026 georefererad karta.tif", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 28474-2023 georefererad karta.tif", "A 28474-2023")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 18427-2026 FSC-klagomål.docx", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 28474-2023 FSC-klagomål.docx", "A 28474-2023")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 18427-2026 FSC-klagomål mail.docx", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 28474-2023 FSC-klagomål mail.docx", "A 28474-2023")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 18427-2026 tillsynsbegäran.docx", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 28474-2023 tillsynsbegäran.docx", "A 28474-2023")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 18427-2026 tillsynsbegäran mail.docx", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 28474-2023 tillsynsbegäran mail.docx", "A 28474-2023")</f>
         <v/>
       </c>
       <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 18427-2026 prioriterade fågelarter.docx", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 28474-2023 prioriterade fågelarter.docx", "A 28474-2023")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 19233-2026</t>
+          <t>A 58091-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3511,10 +3515,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46132</v>
+        <v>44900</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3526,14 +3530,19 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3560,49 +3569,49 @@
         <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Hårklomossa</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 19233-2026 artfynd.xlsx", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 58091-2022 artfynd.xlsx", "A 58091-2022")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 19233-2026 karta.png", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 58091-2022 karta.png", "A 58091-2022")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 19233-2026 georefererad karta.tif", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 58091-2022 georefererad karta.tif", "A 58091-2022")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 19233-2026 FSC-klagomål.docx", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 58091-2022 FSC-klagomål.docx", "A 58091-2022")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 19233-2026 FSC-klagomål mail.docx", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 58091-2022 FSC-klagomål mail.docx", "A 58091-2022")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 19233-2026 tillsynsbegäran.docx", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 58091-2022 tillsynsbegäran.docx", "A 58091-2022")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 19233-2026 tillsynsbegäran mail.docx", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 58091-2022 tillsynsbegäran mail.docx", "A 58091-2022")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 52377-2025</t>
+          <t>A 21019-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3616,10 +3625,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45953</v>
+        <v>46145</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3637,7 +3646,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.6</v>
+        <v>4.7</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
@@ -3673,46 +3682,46 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 52377-2025 artfynd.xlsx", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 21019-2026 artfynd.xlsx", "A 21019-2026")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 52377-2025 karta.png", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 21019-2026 karta.png", "A 21019-2026")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 52377-2025 georefererad karta.tif", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 21019-2026 georefererad karta.tif", "A 21019-2026")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 52377-2025 FSC-klagomål.docx", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 21019-2026 FSC-klagomål.docx", "A 21019-2026")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 52377-2025 FSC-klagomål mail.docx", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 21019-2026 FSC-klagomål mail.docx", "A 21019-2026")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 52377-2025 tillsynsbegäran.docx", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 21019-2026 tillsynsbegäran.docx", "A 21019-2026")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 52377-2025 tillsynsbegäran mail.docx", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 21019-2026 tillsynsbegäran mail.docx", "A 21019-2026")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 21019-2026</t>
+          <t>A 28566-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3726,10 +3735,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46145</v>
+        <v>45478</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3741,13 +3750,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>4.7</v>
+        <v>1</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -3783,39 +3787,39 @@
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 21019-2026 artfynd.xlsx", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 28566-2024 artfynd.xlsx", "A 28566-2024")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 21019-2026 karta.png", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 28566-2024 karta.png", "A 28566-2024")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 21019-2026 georefererad karta.tif", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 28566-2024 georefererad karta.tif", "A 28566-2024")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 21019-2026 FSC-klagomål.docx", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 28566-2024 FSC-klagomål.docx", "A 28566-2024")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 21019-2026 FSC-klagomål mail.docx", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 28566-2024 FSC-klagomål mail.docx", "A 28566-2024")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 21019-2026 tillsynsbegäran.docx", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 28566-2024 tillsynsbegäran.docx", "A 28566-2024")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 21019-2026 tillsynsbegäran mail.docx", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 28566-2024 tillsynsbegäran mail.docx", "A 28566-2024")</f>
         <v/>
       </c>
     </row>
@@ -3839,7 +3843,7 @@
         <v>46175</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3949,7 +3953,7 @@
         <v>46213</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4042,7 +4046,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 28474-2023</t>
+          <t>A 40528-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4056,10 +4060,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45103</v>
+        <v>45555</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4072,7 +4076,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>5.1</v>
+        <v>2.8</v>
       </c>
       <c r="J32" t="n">
         <v>1</v>
@@ -4081,7 +4085,7 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -4096,7 +4100,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -4112,39 +4116,35 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Blåhake</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 28474-2023 artfynd.xlsx", "A 28474-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 40528-2024 artfynd.xlsx", "A 40528-2024")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 28474-2023 karta.png", "A 28474-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 40528-2024 karta.png", "A 40528-2024")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 28474-2023 georefererad karta.tif", "A 28474-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 40528-2024 georefererad karta.tif", "A 40528-2024")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 28474-2023 FSC-klagomål.docx", "A 28474-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 40528-2024 FSC-klagomål.docx", "A 40528-2024")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 28474-2023 FSC-klagomål mail.docx", "A 28474-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 40528-2024 FSC-klagomål mail.docx", "A 40528-2024")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 28474-2023 tillsynsbegäran.docx", "A 28474-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 40528-2024 tillsynsbegäran.docx", "A 40528-2024")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 28474-2023 tillsynsbegäran mail.docx", "A 28474-2023")</f>
-        <v/>
-      </c>
-      <c r="AE32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 28474-2023 prioriterade fågelarter.docx", "A 28474-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 40528-2024 tillsynsbegäran mail.docx", "A 40528-2024")</f>
         <v/>
       </c>
     </row>
@@ -4168,7 +4168,7 @@
         <v>46260</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 20110-2026</t>
+          <t>A 38023-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4275,10 +4275,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46136</v>
+        <v>46280</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4296,7 +4296,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>5.4</v>
+        <v>7.2</v>
       </c>
       <c r="J34" t="n">
         <v>1</v>
@@ -4332,46 +4332,50 @@
         <v>1</v>
       </c>
       <c r="U34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 20110-2026 artfynd.xlsx", "A 20110-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 38023-2026 artfynd.xlsx", "A 38023-2026")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 20110-2026 karta.png", "A 20110-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 38023-2026 karta.png", "A 38023-2026")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 20110-2026 georefererad karta.tif", "A 20110-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 38023-2026 georefererad karta.tif", "A 38023-2026")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 20110-2026 FSC-klagomål.docx", "A 20110-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 38023-2026 FSC-klagomål.docx", "A 38023-2026")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 20110-2026 FSC-klagomål mail.docx", "A 20110-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 38023-2026 FSC-klagomål mail.docx", "A 38023-2026")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 20110-2026 tillsynsbegäran.docx", "A 20110-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 38023-2026 tillsynsbegäran.docx", "A 38023-2026")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 20110-2026 tillsynsbegäran mail.docx", "A 20110-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 38023-2026 tillsynsbegäran mail.docx", "A 38023-2026")</f>
+        <v/>
+      </c>
+      <c r="AE34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 38023-2026 prioriterade fågelarter.docx", "A 38023-2026")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 38023-2026</t>
+          <t>A 20110-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4385,10 +4389,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46280</v>
+        <v>46136</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4406,7 +4410,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>7.2</v>
+        <v>5.4</v>
       </c>
       <c r="J35" t="n">
         <v>1</v>
@@ -4442,43 +4446,39 @@
         <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 38023-2026 artfynd.xlsx", "A 38023-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 20110-2026 artfynd.xlsx", "A 20110-2026")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 38023-2026 karta.png", "A 38023-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 20110-2026 karta.png", "A 20110-2026")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 38023-2026 georefererad karta.tif", "A 38023-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 20110-2026 georefererad karta.tif", "A 20110-2026")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 38023-2026 FSC-klagomål.docx", "A 38023-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 20110-2026 FSC-klagomål.docx", "A 20110-2026")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 38023-2026 FSC-klagomål mail.docx", "A 38023-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 20110-2026 FSC-klagomål mail.docx", "A 20110-2026")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 38023-2026 tillsynsbegäran.docx", "A 38023-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 20110-2026 tillsynsbegäran.docx", "A 20110-2026")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 38023-2026 tillsynsbegäran mail.docx", "A 38023-2026")</f>
-        <v/>
-      </c>
-      <c r="AE35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 38023-2026 prioriterade fågelarter.docx", "A 38023-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 20110-2026 tillsynsbegäran mail.docx", "A 20110-2026")</f>
         <v/>
       </c>
     </row>
@@ -4502,7 +4502,7 @@
         <v>44546</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>44732</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4648,7 +4648,7 @@
         <v>44460</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         <v>44715</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
         <v>44512</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4872,7 +4872,7 @@
         <v>44508</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4950,7 +4950,7 @@
         <v>44480</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5023,7 +5023,7 @@
         <v>44809</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5096,7 +5096,7 @@
         <v>44811</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
         <v>44628</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 35445-2024</t>
+          <t>A 37584-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5244,10 +5244,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45531</v>
+        <v>44809</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.5</v>
+        <v>4.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5303,7 +5303,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 39337-2022</t>
+          <t>A 21612-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44817</v>
+        <v>44706</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5376,7 +5376,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 18955-2025</t>
+          <t>A 21622-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5390,10 +5390,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45764</v>
+        <v>44706</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>8.1</v>
+        <v>0.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5449,7 +5449,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 37584-2022</t>
+          <t>A 39027-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5463,10 +5463,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44809</v>
+        <v>44817</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5478,8 +5478,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>4.9</v>
+        <v>1.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5522,7 +5527,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 21612-2022</t>
+          <t>A 58390-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5536,10 +5541,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44706</v>
+        <v>45633</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5552,7 +5557,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5595,7 +5600,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 21622-2022</t>
+          <t>A 35471-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5609,10 +5614,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44706</v>
+        <v>45531</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5625,7 +5630,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5668,7 +5673,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 39027-2022</t>
+          <t>A 9712-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5682,10 +5687,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44817</v>
+        <v>45362</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5699,11 +5704,11 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5746,7 +5751,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 8803-2025</t>
+          <t>A 42804-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5756,14 +5761,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45712</v>
+        <v>45182</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5775,8 +5780,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5819,7 +5829,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 22867-2022</t>
+          <t>A 9510-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5833,10 +5843,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44715</v>
+        <v>44981</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5849,7 +5859,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5892,7 +5902,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 18978-2025</t>
+          <t>A 1309-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5906,10 +5916,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45764</v>
+        <v>45303</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5922,7 +5932,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.8</v>
+        <v>4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5965,7 +5975,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 4801-2024</t>
+          <t>A 4164-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5979,10 +5989,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45328</v>
+        <v>44588</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5994,8 +6004,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -6038,7 +6053,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 4802-2024</t>
+          <t>A 23263-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6052,10 +6067,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45328</v>
+        <v>44720</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6068,7 +6083,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6111,7 +6126,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 30961-2022</t>
+          <t>A 35444-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6125,10 +6140,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44768</v>
+        <v>45531</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6140,13 +6155,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6189,7 +6199,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 55191-2023</t>
+          <t>A 47201-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6203,10 +6213,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45237</v>
+        <v>45196</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6219,7 +6229,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6262,7 +6272,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 56887-2022</t>
+          <t>A 61396-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6276,10 +6286,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44894</v>
+        <v>45264</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6335,7 +6345,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 38196-2024</t>
+          <t>A 8259-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6349,10 +6359,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45545</v>
+        <v>45708</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6408,7 +6418,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 24255-2024</t>
+          <t>A 24116-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6422,10 +6432,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45457</v>
+        <v>45456</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6438,7 +6448,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6481,7 +6491,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 13496-2025</t>
+          <t>A 1788-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6495,10 +6505,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45736</v>
+        <v>46034</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6511,7 +6521,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>8.800000000000001</v>
+        <v>3.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6554,7 +6564,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 17815-2025</t>
+          <t>A 27498-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6568,10 +6578,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45758</v>
+        <v>45813</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6583,13 +6593,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6632,7 +6637,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 11974-2025</t>
+          <t>A 17815-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6646,10 +6651,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45728</v>
+        <v>45758</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6661,8 +6666,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6705,7 +6715,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 20289-2024</t>
+          <t>A 35930-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6719,10 +6729,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45435</v>
+        <v>45148</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6740,7 +6750,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.7</v>
+        <v>5.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6783,7 +6793,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 13473-2026</t>
+          <t>A 23620-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6797,10 +6807,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46094</v>
+        <v>45454</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6813,7 +6823,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6856,7 +6866,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 38190-2024</t>
+          <t>A 53647-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6870,10 +6880,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45545</v>
+        <v>45230</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6886,7 +6896,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6929,7 +6939,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 63863-2023</t>
+          <t>A 30102-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6943,10 +6953,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45278</v>
+        <v>45826</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6959,7 +6969,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7002,7 +7012,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 14580-2026</t>
+          <t>A 63863-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7016,10 +7026,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46101</v>
+        <v>45278</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7031,13 +7041,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7080,7 +7085,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 9712-2024</t>
+          <t>A 54680-2021</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7094,10 +7099,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45362</v>
+        <v>44473</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7109,13 +7114,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7158,7 +7158,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 12897-2026</t>
+          <t>A 31397-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7172,10 +7172,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46092</v>
+        <v>45833</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7231,7 +7231,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 4058-2022</t>
+          <t>A 32287-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7245,10 +7245,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44588</v>
+        <v>45835</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7260,8 +7260,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>1.7</v>
+        <v>10.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7304,7 +7309,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 15256-2025</t>
+          <t>A 44946-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7318,10 +7323,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45744</v>
+        <v>45918</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7333,13 +7338,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>5.5</v>
+        <v>2.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7382,7 +7382,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 1309-2024</t>
+          <t>A 44949-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7396,10 +7396,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45303</v>
+        <v>45918</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7412,7 +7412,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>4</v>
+        <v>0.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7455,7 +7455,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 16782-2026</t>
+          <t>A 59938-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7469,10 +7469,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46113</v>
+        <v>45257</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7484,13 +7484,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7533,7 +7528,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 16783-2026</t>
+          <t>A 52828-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7547,10 +7542,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46113</v>
+        <v>45610</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7562,13 +7557,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>1.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7611,7 +7601,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 16787-2026</t>
+          <t>A 45664-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7625,10 +7615,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46113</v>
+        <v>45923</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7646,7 +7636,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.8</v>
+        <v>9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7689,7 +7679,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 44946-2025</t>
+          <t>A 2911-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7703,10 +7693,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45918</v>
+        <v>46038</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7719,7 +7709,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7762,7 +7752,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 44949-2025</t>
+          <t>A 15256-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7776,10 +7766,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45918</v>
+        <v>45744</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7791,8 +7781,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>0.8</v>
+        <v>5.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7835,7 +7830,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 43075-2023</t>
+          <t>A 47222-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7849,10 +7844,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45182</v>
+        <v>45586</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7864,8 +7859,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>3.1</v>
+        <v>5.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7908,7 +7908,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 23263-2022</t>
+          <t>A 24115-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7922,10 +7922,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44720</v>
+        <v>45456</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7938,7 +7938,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.2</v>
+        <v>8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7981,7 +7981,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 15060-2026</t>
+          <t>A 50958-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7995,10 +7995,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46104</v>
+        <v>45946</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>11.5</v>
+        <v>0.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8054,7 +8054,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 15058-2026</t>
+          <t>A 24255-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8068,10 +8068,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46104</v>
+        <v>45457</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8084,7 +8084,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>4.3</v>
+        <v>2.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8127,7 +8127,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 17734-2026</t>
+          <t>A 18768-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8141,10 +8141,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46122</v>
+        <v>45764</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8205,7 +8205,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 35444-2024</t>
+          <t>A 55025-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8219,10 +8219,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45531</v>
+        <v>45967</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8235,7 +8235,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8278,7 +8278,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 35471-2024</t>
+          <t>A 4801-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8292,10 +8292,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45531</v>
+        <v>45328</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8308,7 +8308,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8351,7 +8351,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 58390-2024</t>
+          <t>A 4802-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8365,10 +8365,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45633</v>
+        <v>45328</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8381,7 +8381,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3</v>
+        <v>0.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8424,7 +8424,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 19011-2026</t>
+          <t>A 8990-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8438,10 +8438,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46130</v>
+        <v>44979</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8453,13 +8453,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8502,7 +8497,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 19010-2026</t>
+          <t>A 42802-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8512,14 +8507,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46130</v>
+        <v>45182</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8537,7 +8532,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8580,7 +8575,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 52826-2024</t>
+          <t>A 9917-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8594,10 +8589,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45610</v>
+        <v>46073</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8610,7 +8605,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8653,7 +8648,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 19009-2026</t>
+          <t>A 28471-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8667,10 +8662,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46130</v>
+        <v>45103</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8682,13 +8677,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>6.3</v>
+        <v>1.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8731,7 +8721,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 19008-2026</t>
+          <t>A 22867-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8745,10 +8735,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46130</v>
+        <v>44715</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8760,13 +8750,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I93" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8809,7 +8794,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 19663-2026</t>
+          <t>A 59522-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8819,14 +8804,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46134</v>
+        <v>45989</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8844,7 +8829,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8887,7 +8872,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 50958-2025</t>
+          <t>A 64060-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8901,10 +8886,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45946</v>
+        <v>45279</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8917,7 +8902,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8960,7 +8945,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 18768-2025</t>
+          <t>A 48707-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8974,10 +8959,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45764</v>
+        <v>45593</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8989,13 +8974,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I96" t="n">
-        <v>0.7</v>
+        <v>6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9038,7 +9018,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 42803-2023</t>
+          <t>A 60506-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9048,14 +9028,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45182</v>
+        <v>45995</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9067,13 +9047,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I97" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9116,7 +9091,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 6835-2025</t>
+          <t>A 60508-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9130,10 +9105,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45700</v>
+        <v>45995</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9146,7 +9121,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9189,7 +9164,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 21210-2025</t>
+          <t>A 60503-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9203,10 +9178,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45779</v>
+        <v>45995</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9218,13 +9193,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I99" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9267,7 +9237,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 20086-2024</t>
+          <t>A 55832-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9277,14 +9247,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45434</v>
+        <v>45239</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9297,7 +9267,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9340,7 +9310,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 23717-2025</t>
+          <t>A 58388-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9354,10 +9324,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45793</v>
+        <v>45633</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9370,7 +9340,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.1</v>
+        <v>5.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9413,7 +9383,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 9510-2023</t>
+          <t>A 61788-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9427,10 +9397,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44981</v>
+        <v>46002</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9442,8 +9412,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9486,7 +9461,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 55025-2025</t>
+          <t>A 18978-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9500,10 +9475,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45967</v>
+        <v>45764</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9516,7 +9491,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9559,7 +9534,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 917-2026</t>
+          <t>A 64066-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9569,14 +9544,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46030</v>
+        <v>46013</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9589,7 +9564,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>3.7</v>
+        <v>1.9</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9632,7 +9607,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 1106-2024</t>
+          <t>A 13473-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9646,10 +9621,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45302</v>
+        <v>46094</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9662,7 +9637,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9705,7 +9680,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 48707-2024</t>
+          <t>A 63628-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9719,10 +9694,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45593</v>
+        <v>46014</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9735,7 +9710,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>6</v>
+        <v>3.8</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9778,7 +9753,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 59025-2024</t>
+          <t>A 31921-2022</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9792,10 +9767,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45636</v>
+        <v>44777</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9807,13 +9782,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9856,7 +9826,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 59522-2025</t>
+          <t>A 43075-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9866,14 +9836,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45989</v>
+        <v>45182</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9885,13 +9855,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I108" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9934,7 +9899,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 60503-2025</t>
+          <t>A 47196-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9948,10 +9913,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45995</v>
+        <v>45196</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9964,7 +9929,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2.2</v>
+        <v>5.9</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10007,7 +9972,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 13501-2025</t>
+          <t>A 13454-2022</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10021,10 +9986,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45736</v>
+        <v>44645</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10037,7 +10002,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>3.2</v>
+        <v>1.7</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10080,7 +10045,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 47094-2023</t>
+          <t>A 12897-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10094,10 +10059,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45196</v>
+        <v>46092</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10110,7 +10075,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10153,7 +10118,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 60508-2025</t>
+          <t>A 14580-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10167,10 +10132,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45995</v>
+        <v>46101</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10182,8 +10147,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I112" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10226,7 +10196,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 21253-2026</t>
+          <t>A 53618-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10240,10 +10210,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46147</v>
+        <v>45614</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10256,7 +10226,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>3.4</v>
+        <v>10.1</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10299,7 +10269,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 60506-2025</t>
+          <t>A 30961-2022</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10313,10 +10283,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45995</v>
+        <v>44768</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10328,8 +10298,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I114" t="n">
-        <v>0.8</v>
+        <v>3.3</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10372,7 +10347,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 21257-2026</t>
+          <t>A 16783-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10386,10 +10361,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46147</v>
+        <v>46113</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10401,8 +10376,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I115" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10445,7 +10425,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 31921-2022</t>
+          <t>A 16787-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10459,10 +10439,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44777</v>
+        <v>46113</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10474,8 +10454,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I116" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10518,7 +10503,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 42804-2023</t>
+          <t>A 16782-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10528,14 +10513,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45182</v>
+        <v>46113</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10553,7 +10538,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10596,7 +10581,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 39030-2022</t>
+          <t>A 42803-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10606,14 +10591,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44817</v>
+        <v>45182</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10631,7 +10616,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10674,7 +10659,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 61788-2025</t>
+          <t>A 15058-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10688,10 +10673,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46002</v>
+        <v>46104</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10703,13 +10688,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I119" t="n">
-        <v>0.9</v>
+        <v>4.3</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10752,7 +10732,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 8244-2025</t>
+          <t>A 15060-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10766,10 +10746,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45708</v>
+        <v>46104</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10782,7 +10762,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.1</v>
+        <v>11.5</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10825,7 +10805,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 28100-2024</t>
+          <t>A 17734-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10839,10 +10819,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45476</v>
+        <v>46122</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10854,8 +10834,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I121" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10898,7 +10883,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 3227-2025</t>
+          <t>A 8803-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10912,10 +10897,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45679</v>
+        <v>45712</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10928,7 +10913,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10971,7 +10956,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 51344-2023</t>
+          <t>A 19009-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10985,10 +10970,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45219</v>
+        <v>46130</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11002,11 +10987,11 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I123" t="n">
-        <v>4.5</v>
+        <v>6.3</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -11049,7 +11034,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 64066-2025</t>
+          <t>A 19011-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11059,14 +11044,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46013</v>
+        <v>46130</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11078,8 +11063,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I124" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -11122,7 +11112,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 63628-2025</t>
+          <t>A 19010-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11136,10 +11126,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46014</v>
+        <v>46130</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11151,8 +11141,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I125" t="n">
-        <v>3.8</v>
+        <v>1.9</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11195,7 +11190,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 23754-2026</t>
+          <t>A 19008-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11209,10 +11204,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46164</v>
+        <v>46130</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11230,7 +11225,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>12.2</v>
+        <v>1.9</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11273,7 +11268,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 1788-2026</t>
+          <t>A 56313-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11287,10 +11282,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46034</v>
+        <v>45624</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11302,8 +11297,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I127" t="n">
-        <v>3.5</v>
+        <v>2.2</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11346,7 +11346,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 4587-2025</t>
+          <t>A 10743-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11360,10 +11360,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45687</v>
+        <v>44988</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11375,8 +11375,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I128" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11419,7 +11424,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 4587-2025</t>
+          <t>A 14215-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11433,10 +11438,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45687</v>
+        <v>45393</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11448,8 +11453,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I129" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11492,7 +11502,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 20463-2025</t>
+          <t>A 19663-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11506,10 +11516,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45775</v>
+        <v>46134</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11527,7 +11537,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11570,7 +11580,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 28471-2023</t>
+          <t>A 55191-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11584,10 +11594,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45103</v>
+        <v>45237</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11600,7 +11610,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11643,7 +11653,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 2911-2026</t>
+          <t>A 59025-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11657,10 +11667,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46038</v>
+        <v>45636</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11672,8 +11682,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I132" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11716,7 +11731,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 35470-2024</t>
+          <t>A 17243-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11730,10 +11745,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45531</v>
+        <v>45414</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11746,7 +11761,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>0.5</v>
+        <v>3.2</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11789,7 +11804,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 45664-2025</t>
+          <t>A 6835-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11803,10 +11818,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45923</v>
+        <v>45700</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11818,13 +11833,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I134" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11867,7 +11877,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 24666-2026</t>
+          <t>A 21210-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11881,10 +11891,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46171</v>
+        <v>45779</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11896,8 +11906,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I135" t="n">
-        <v>6.1</v>
+        <v>1.1</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11940,7 +11955,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 47222-2024</t>
+          <t>A 23717-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11954,10 +11969,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45586</v>
+        <v>45793</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11969,13 +11984,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>5.3</v>
+        <v>2.1</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -12018,7 +12028,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 16881-2023</t>
+          <t>A 35060-2024</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12032,10 +12042,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45033</v>
+        <v>45527</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12053,7 +12063,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -12096,7 +12106,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 25098-2026</t>
+          <t>A 52826-2024</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12106,14 +12116,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46175</v>
+        <v>45610</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12125,13 +12135,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I138" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -12174,7 +12179,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 25092-2026</t>
+          <t>A 52829-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12188,10 +12193,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46175</v>
+        <v>45610</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12203,13 +12208,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I139" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12252,7 +12252,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 61396-2023</t>
+          <t>A 917-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12266,10 +12266,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45264</v>
+        <v>46030</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12282,7 +12282,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.8</v>
+        <v>3.7</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12325,7 +12325,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 4164-2022</t>
+          <t>A 11974-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12339,10 +12339,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44588</v>
+        <v>45728</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12354,13 +12354,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I141" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12420,7 +12415,7 @@
         <v>44909</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12481,7 +12476,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 57422-2021</t>
+          <t>A 48168-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12495,10 +12490,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>44483</v>
+        <v>45589</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12511,7 +12506,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.2</v>
+        <v>5.5</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12554,7 +12549,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 26822-2026</t>
+          <t>A 21253-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12568,10 +12563,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46185</v>
+        <v>46147</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12583,13 +12578,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I144" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12632,7 +12622,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 26819-2026</t>
+          <t>A 21257-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12646,10 +12636,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46185</v>
+        <v>46147</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12661,13 +12651,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I145" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12710,7 +12695,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 3239-2026</t>
+          <t>A 18955-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12724,10 +12709,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46041</v>
+        <v>45764</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12740,7 +12725,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.6</v>
+        <v>8.1</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12783,7 +12768,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 26821-2026</t>
+          <t>A 50614-2024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12797,10 +12782,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46185</v>
+        <v>45601</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12812,13 +12797,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I147" t="n">
-        <v>7.9</v>
+        <v>0.7</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12861,7 +12841,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 26820-2026</t>
+          <t>A 55182-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12875,10 +12855,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46185</v>
+        <v>45618</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12890,13 +12870,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I148" t="n">
-        <v>9.9</v>
+        <v>11.4</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12939,7 +12914,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 26608-2026</t>
+          <t>A 3227-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12953,10 +12928,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46184</v>
+        <v>45679</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12968,13 +12943,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I149" t="n">
-        <v>1.6</v>
+        <v>4.5</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -13017,7 +12987,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 26824-2026</t>
+          <t>A 4058-2022</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -13031,10 +13001,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46185</v>
+        <v>44588</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13046,13 +13016,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I150" t="n">
-        <v>5</v>
+        <v>1.7</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -13095,7 +13060,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 26825-2026</t>
+          <t>A 23754-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -13109,10 +13074,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46185</v>
+        <v>46164</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13130,7 +13095,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0.8</v>
+        <v>12.2</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -13173,7 +13138,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 35060-2024</t>
+          <t>A 4587-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13187,10 +13152,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45527</v>
+        <v>45687</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13202,13 +13167,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I152" t="n">
-        <v>0.6</v>
+        <v>3.3</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -13251,7 +13211,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 9917-2026</t>
+          <t>A 28100-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13265,10 +13225,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46073</v>
+        <v>45476</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13281,7 +13241,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -13324,7 +13284,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 27392-2026</t>
+          <t>A 4587-2025</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13338,10 +13298,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46189</v>
+        <v>45687</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13353,13 +13313,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I154" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13402,7 +13357,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 64060-2023</t>
+          <t>A 1106-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13416,10 +13371,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45279</v>
+        <v>45302</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13475,7 +13430,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 27120-2026</t>
+          <t>A 24666-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13489,10 +13444,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46188</v>
+        <v>46171</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13505,7 +13460,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>4.7</v>
+        <v>6.1</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13548,7 +13503,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 8990-2023</t>
+          <t>A 39030-2022</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13562,10 +13517,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>44979</v>
+        <v>44817</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13577,8 +13532,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I157" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13621,7 +13581,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 14215-2024</t>
+          <t>A 38382-2022</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13635,10 +13595,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45393</v>
+        <v>44812</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13652,11 +13612,11 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I158" t="n">
-        <v>4.2</v>
+        <v>2.2</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13699,7 +13659,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 50614-2024</t>
+          <t>A 25092-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13713,10 +13673,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45601</v>
+        <v>46175</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13728,8 +13688,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I159" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13772,7 +13737,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 55182-2024</t>
+          <t>A 25098-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13782,14 +13747,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45618</v>
+        <v>46175</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13801,8 +13766,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I160" t="n">
-        <v>11.4</v>
+        <v>1.4</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13845,7 +13815,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 52797-2021</t>
+          <t>A 16881-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13859,10 +13829,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>44467</v>
+        <v>45033</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13874,8 +13844,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I161" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13918,7 +13893,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 24116-2024</t>
+          <t>A 57422-2021</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13932,10 +13907,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45456</v>
+        <v>44483</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13948,7 +13923,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13991,7 +13966,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 55832-2023</t>
+          <t>A 26608-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -14005,10 +13980,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45239</v>
+        <v>46184</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14020,8 +13995,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I163" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -14064,7 +14044,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 10515-2023</t>
+          <t>A 8244-2025</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -14078,10 +14058,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>44987</v>
+        <v>45708</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14094,7 +14074,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -14137,7 +14117,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 33011-2023</t>
+          <t>A 27120-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -14151,10 +14131,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45125</v>
+        <v>46188</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14167,7 +14147,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>0.8</v>
+        <v>4.7</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -14210,7 +14190,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 48168-2024</t>
+          <t>A 26819-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -14224,10 +14204,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45589</v>
+        <v>46185</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14239,8 +14219,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I166" t="n">
-        <v>5.5</v>
+        <v>2.4</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -14283,7 +14268,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 13454-2022</t>
+          <t>A 38190-2024</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -14297,10 +14282,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>44645</v>
+        <v>45545</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14313,7 +14298,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14356,7 +14341,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 10743-2023</t>
+          <t>A 3239-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14370,10 +14355,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>44988</v>
+        <v>46041</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14385,13 +14370,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I168" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14434,7 +14414,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 50611-2024</t>
+          <t>A 26820-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14448,10 +14428,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45601</v>
+        <v>46185</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14463,8 +14443,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I169" t="n">
-        <v>1</v>
+        <v>9.9</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14507,7 +14492,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 42802-2023</t>
+          <t>A 26821-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14517,14 +14502,14 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45182</v>
+        <v>46185</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14542,7 +14527,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0.6</v>
+        <v>7.9</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14585,7 +14570,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 52829-2024</t>
+          <t>A 26822-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14599,10 +14584,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45610</v>
+        <v>46185</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14614,8 +14599,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I171" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14658,7 +14648,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 56313-2024</t>
+          <t>A 26824-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14672,10 +14662,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45624</v>
+        <v>46185</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14689,11 +14679,11 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I172" t="n">
-        <v>2.2</v>
+        <v>5</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14736,7 +14726,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 38382-2022</t>
+          <t>A 26825-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14750,10 +14740,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>44812</v>
+        <v>46185</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14767,11 +14757,11 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I173" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14814,7 +14804,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 8259-2025</t>
+          <t>A 20463-2025</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14828,10 +14818,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45708</v>
+        <v>45775</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14843,8 +14833,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I174" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14887,7 +14882,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 24115-2024</t>
+          <t>A 27392-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14901,10 +14896,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45456</v>
+        <v>46189</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14916,8 +14911,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I175" t="n">
-        <v>8</v>
+        <v>2.8</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14960,7 +14960,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 31378-2026</t>
+          <t>A 35470-2024</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14974,10 +14974,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46213</v>
+        <v>45531</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14990,7 +14990,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>3.7</v>
+        <v>0.5</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -15033,7 +15033,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 53620-2024</t>
+          <t>A 35445-2024</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -15047,10 +15047,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45614</v>
+        <v>45531</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15063,7 +15063,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -15106,7 +15106,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 35094-2026</t>
+          <t>A 47094-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -15120,10 +15120,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46260</v>
+        <v>45196</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15133,11 +15133,6 @@
       <c r="G178" t="inlineStr">
         <is>
           <t>KARLSKOGA</t>
-        </is>
-      </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I178" t="n">
@@ -15184,7 +15179,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 10404-2022</t>
+          <t>A 38196-2024</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -15198,10 +15193,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>44623</v>
+        <v>45545</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15214,7 +15209,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -15257,7 +15252,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 35930-2023</t>
+          <t>A 50611-2024</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -15271,10 +15266,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45148</v>
+        <v>45601</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15286,13 +15281,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I180" t="n">
-        <v>5.2</v>
+        <v>1</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -15335,7 +15325,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 47196-2023</t>
+          <t>A 20289-2024</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15349,10 +15339,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45196</v>
+        <v>45435</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15364,8 +15354,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I181" t="n">
-        <v>5.9</v>
+        <v>0.7</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15408,7 +15403,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 53618-2024</t>
+          <t>A 52797-2021</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15422,10 +15417,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45614</v>
+        <v>44467</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15438,7 +15433,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>10.1</v>
+        <v>1.4</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15481,7 +15476,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 35699-2026</t>
+          <t>A 20086-2024</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15491,14 +15486,14 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46265</v>
+        <v>45434</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15510,13 +15505,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I183" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15559,7 +15549,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 36374-2026</t>
+          <t>A 13496-2025</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15573,10 +15563,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46268</v>
+        <v>45736</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15588,13 +15578,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I184" t="n">
-        <v>1.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15637,7 +15622,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 58388-2024</t>
+          <t>A 56887-2022</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15651,10 +15636,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45633</v>
+        <v>44894</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15667,7 +15652,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>5.8</v>
+        <v>1.8</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15710,7 +15695,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 47201-2023</t>
+          <t>A 31378-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15724,10 +15709,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45196</v>
+        <v>46213</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15740,7 +15725,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15783,7 +15768,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 37089-2026</t>
+          <t>A 35094-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15797,10 +15782,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46273</v>
+        <v>46260</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15812,8 +15797,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I187" t="n">
-        <v>15.8</v>
+        <v>1.9</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15856,7 +15846,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 52828-2024</t>
+          <t>A 33011-2023</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15870,10 +15860,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45610</v>
+        <v>45125</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15886,7 +15876,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>8.300000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15929,7 +15919,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 17243-2024</t>
+          <t>A 35699-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15939,14 +15929,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45414</v>
+        <v>46265</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15958,8 +15948,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I189" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -16002,7 +15997,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 59938-2023</t>
+          <t>A 51344-2023</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -16016,10 +16011,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45257</v>
+        <v>45219</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16031,8 +16026,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I190" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -16075,7 +16075,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 38043-2026</t>
+          <t>A 10515-2023</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -16089,10 +16089,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46280</v>
+        <v>44987</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16104,13 +16104,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I191" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -16153,7 +16148,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 38020-2026</t>
+          <t>A 36374-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -16167,10 +16162,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46280</v>
+        <v>46268</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16184,11 +16179,11 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I192" t="n">
-        <v>4.1</v>
+        <v>1.6</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -16231,7 +16226,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 38742-2023</t>
+          <t>A 39337-2022</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -16241,14 +16236,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45161</v>
+        <v>44817</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16260,13 +16255,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I193" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -16309,7 +16299,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 3735-2024</t>
+          <t>A 53620-2024</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -16323,10 +16313,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45321</v>
+        <v>45614</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16338,13 +16328,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I194" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -16387,7 +16372,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 23308-2025</t>
+          <t>A 37089-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16401,10 +16386,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45791</v>
+        <v>46273</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16417,7 +16402,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1.5</v>
+        <v>15.8</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -16460,7 +16445,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 27498-2025</t>
+          <t>A 13501-2025</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16474,10 +16459,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45813</v>
+        <v>45736</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16490,7 +16475,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>1.2</v>
+        <v>3.2</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16533,7 +16518,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 54680-2021</t>
+          <t>A 10404-2022</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16547,10 +16532,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>44473</v>
+        <v>44623</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16563,7 +16548,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16606,7 +16591,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 30102-2025</t>
+          <t>A 38043-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16620,10 +16605,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45826</v>
+        <v>46280</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16635,8 +16620,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I198" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16679,7 +16669,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 53647-2023</t>
+          <t>A 38020-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16693,10 +16683,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45230</v>
+        <v>46280</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16708,8 +16698,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I199" t="n">
-        <v>0.6</v>
+        <v>4.1</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16752,7 +16747,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 23620-2024</t>
+          <t>A 38742-2023</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16762,14 +16757,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45454</v>
+        <v>45161</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16781,8 +16776,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I200" t="n">
-        <v>2.2</v>
+        <v>4.2</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16825,7 +16825,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 31397-2025</t>
+          <t>A 3735-2024</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16839,10 +16839,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45833</v>
+        <v>45321</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16854,8 +16854,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I201" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16898,7 +16903,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 32287-2025</t>
+          <t>A 23308-2025</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16912,10 +16917,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45835</v>
+        <v>45791</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16927,13 +16932,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I202" t="n">
-        <v>10.9</v>
+        <v>1.5</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16993,7 +16993,7 @@
         <v>45953</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>

--- a/Översikt KARLSKOGA.xlsx
+++ b/Översikt KARLSKOGA.xlsx
@@ -601,7 +601,7 @@
         <v>45562</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
         <v>3</v>
       </c>
       <c r="L2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M2" t="n">
         <v>3</v>
@@ -643,19 +643,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R2" t="n">
         <v>3</v>
       </c>
       <c r="S2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="T2" t="n">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="U2" t="n">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
@@ -667,6 +667,7 @@
 Dvärgbägarlav
 Kattfotslav
 Kolflarnlav
+Motaggsvamp
 Mörk kolflarnlav
 Skuggblåslav
 Strandlummer
@@ -743,7 +744,7 @@
         <v>45958</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -873,7 +874,7 @@
         <v>45989</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1003,7 +1004,7 @@
         <v>44510</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1123,7 +1124,7 @@
         <v>46100</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1251,7 +1252,7 @@
         <v>45989</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1374,7 +1375,7 @@
         <v>44473</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1493,7 +1494,7 @@
         <v>46066</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1601,7 +1602,7 @@
         <v>46010</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1718,7 +1719,7 @@
         <v>44495</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1826,7 +1827,7 @@
         <v>46136</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1926,7 +1927,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 63185-2025</t>
+          <t>A 18428-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1936,14 +1937,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46010</v>
+        <v>46127</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1961,10 +1962,10 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>8.4</v>
+        <v>6</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1973,7 +1974,7 @@
         <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1985,292 +1986,292 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
+        <v>2</v>
+      </c>
+      <c r="R13" t="n">
         <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>3</v>
       </c>
       <c r="T13" t="n">
+        <v>17</v>
+      </c>
+      <c r="U13" t="n">
+        <v>17</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Skuggblåslav
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 18428-2026 artfynd.xlsx", "A 18428-2026")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 18428-2026 karta.png", "A 18428-2026")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 18428-2026 georefererad karta.tif", "A 18428-2026")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 18428-2026 FSC-klagomål.docx", "A 18428-2026")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 18428-2026 FSC-klagomål mail.docx", "A 18428-2026")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 18428-2026 tillsynsbegäran.docx", "A 18428-2026")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 18428-2026 tillsynsbegäran mail.docx", "A 18428-2026")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 18428-2026 prioriterade fågelarter.docx", "A 18428-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 35696-2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>KARLSKOGA</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3</v>
+      </c>
+      <c r="T14" t="n">
+        <v>4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Grönpyrola
+Mattlummer
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 35696-2026 artfynd.xlsx", "A 35696-2026")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 35696-2026 karta.png", "A 35696-2026")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 35696-2026 georefererad karta.tif", "A 35696-2026")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 35696-2026 FSC-klagomål.docx", "A 35696-2026")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 35696-2026 FSC-klagomål mail.docx", "A 35696-2026")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 35696-2026 tillsynsbegäran.docx", "A 35696-2026")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 35696-2026 tillsynsbegäran mail.docx", "A 35696-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 63185-2025</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>46010</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>KARLSKOGA</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>13</v>
+      </c>
+      <c r="U15" t="n">
         <v>11</v>
       </c>
-      <c r="U13" t="n">
-        <v>9</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Talltita
 Brudborste
 Revlummer</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 63185-2025 artfynd.xlsx", "A 63185-2025")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 63185-2025 karta.png", "A 63185-2025")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 63185-2025 georefererad karta.tif", "A 63185-2025")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 63185-2025 FSC-klagomål.docx", "A 63185-2025")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 63185-2025 FSC-klagomål mail.docx", "A 63185-2025")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 63185-2025 tillsynsbegäran.docx", "A 63185-2025")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 63185-2025 tillsynsbegäran mail.docx", "A 63185-2025")</f>
         <v/>
       </c>
-      <c r="AE13">
+      <c r="AE15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 63185-2025 prioriterade fågelarter.docx", "A 63185-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 18428-2026</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>46127</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>KARLSKOGA</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>6</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3</v>
-      </c>
-      <c r="T14" t="n">
-        <v>17</v>
-      </c>
-      <c r="U14" t="n">
-        <v>17</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Skuggblåslav
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 18428-2026 artfynd.xlsx", "A 18428-2026")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 18428-2026 karta.png", "A 18428-2026")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 18428-2026 georefererad karta.tif", "A 18428-2026")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 18428-2026 FSC-klagomål.docx", "A 18428-2026")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 18428-2026 FSC-klagomål mail.docx", "A 18428-2026")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 18428-2026 tillsynsbegäran.docx", "A 18428-2026")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 18428-2026 tillsynsbegäran mail.docx", "A 18428-2026")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 18428-2026 prioriterade fågelarter.docx", "A 18428-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 35696-2026</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>KARLSKOGA</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3</v>
-      </c>
-      <c r="T15" t="n">
-        <v>4</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Grönpyrola
-Mattlummer
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 35696-2026 artfynd.xlsx", "A 35696-2026")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 35696-2026 karta.png", "A 35696-2026")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 35696-2026 georefererad karta.tif", "A 35696-2026")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 35696-2026 FSC-klagomål.docx", "A 35696-2026")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 35696-2026 FSC-klagomål mail.docx", "A 35696-2026")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 35696-2026 tillsynsbegäran.docx", "A 35696-2026")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 35696-2026 tillsynsbegäran mail.docx", "A 35696-2026")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 20108-2026</t>
+          <t>A 20112-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2287,7 +2288,7 @@
         <v>46136</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2305,197 +2306,197 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>1</v>
       </c>
       <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
         <v>1</v>
       </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2</v>
-      </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
       </c>
       <c r="T16" t="n">
+        <v>4</v>
+      </c>
+      <c r="U16" t="n">
+        <v>4</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett
+Spillkråka
+Tofsmes</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 20112-2026 artfynd.xlsx", "A 20112-2026")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 20112-2026 karta.png", "A 20112-2026")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 20112-2026 georefererad karta.tif", "A 20112-2026")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 20112-2026 FSC-klagomål.docx", "A 20112-2026")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 20112-2026 FSC-klagomål mail.docx", "A 20112-2026")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 20112-2026 tillsynsbegäran.docx", "A 20112-2026")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 20112-2026 tillsynsbegäran mail.docx", "A 20112-2026")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 20112-2026 prioriterade fågelarter.docx", "A 20112-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 20108-2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>46136</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>KARLSKOGA</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3</v>
+      </c>
+      <c r="T17" t="n">
         <v>5</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U17" t="n">
         <v>5</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Talltita
 Vedticka</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 20108-2026 artfynd.xlsx", "A 20108-2026")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 20108-2026 karta.png", "A 20108-2026")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 20108-2026 georefererad karta.tif", "A 20108-2026")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 20108-2026 FSC-klagomål.docx", "A 20108-2026")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 20108-2026 FSC-klagomål mail.docx", "A 20108-2026")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 20108-2026 tillsynsbegäran.docx", "A 20108-2026")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 20108-2026 tillsynsbegäran mail.docx", "A 20108-2026")</f>
         <v/>
       </c>
-      <c r="AE16">
+      <c r="AE17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 20108-2026 prioriterade fågelarter.docx", "A 20108-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 20112-2026</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>46136</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>KARLSKOGA</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J17" t="n">
-        <v>3</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>4</v>
-      </c>
-      <c r="U17" t="n">
-        <v>4</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett
-Spillkråka
-Tofsmes</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 20112-2026 artfynd.xlsx", "A 20112-2026")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 20112-2026 karta.png", "A 20112-2026")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 20112-2026 georefererad karta.tif", "A 20112-2026")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 20112-2026 FSC-klagomål.docx", "A 20112-2026")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 20112-2026 FSC-klagomål mail.docx", "A 20112-2026")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 20112-2026 tillsynsbegäran.docx", "A 20112-2026")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 20112-2026 tillsynsbegäran mail.docx", "A 20112-2026")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 20112-2026 prioriterade fågelarter.docx", "A 20112-2026")</f>
         <v/>
       </c>
     </row>
@@ -2519,7 +2520,7 @@
         <v>46010</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2570,10 +2571,10 @@
         <v>3</v>
       </c>
       <c r="T18" t="n">
+        <v>13</v>
+      </c>
+      <c r="U18" t="n">
         <v>11</v>
-      </c>
-      <c r="U18" t="n">
-        <v>9</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
@@ -2618,7 +2619,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 39025-2022</t>
+          <t>A 39936-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2632,10 +2633,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44817</v>
+        <v>45553</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2647,16 +2648,11 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>3.2</v>
+        <v>6.4</v>
       </c>
       <c r="J19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -2686,160 +2682,165 @@
         <v>2</v>
       </c>
       <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Storgröe
+Utter</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 39936-2024 artfynd.xlsx", "A 39936-2024")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 39936-2024 karta.png", "A 39936-2024")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 39936-2024 georefererad karta.tif", "A 39936-2024")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 39936-2024 FSC-klagomål.docx", "A 39936-2024")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 39936-2024 FSC-klagomål mail.docx", "A 39936-2024")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 39936-2024 tillsynsbegäran.docx", "A 39936-2024")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 39936-2024 tillsynsbegäran mail.docx", "A 39936-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 39025-2022</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>44817</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>KARLSKOGA</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J20" t="n">
         <v>2</v>
       </c>
-      <c r="U19" t="n">
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
         <v>2</v>
       </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Talltita
 Tjäder</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 39025-2022 artfynd.xlsx", "A 39025-2022")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 39025-2022 karta.png", "A 39025-2022")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 39025-2022 georefererad karta.tif", "A 39025-2022")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 39025-2022 FSC-klagomål.docx", "A 39025-2022")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 39025-2022 FSC-klagomål mail.docx", "A 39025-2022")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 39025-2022 tillsynsbegäran.docx", "A 39025-2022")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 39025-2022 tillsynsbegäran mail.docx", "A 39025-2022")</f>
         <v/>
       </c>
-      <c r="AE19">
+      <c r="AE20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 39025-2022 prioriterade fågelarter.docx", "A 39025-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 39936-2024</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>45553</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>KARLSKOGA</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Storgröe
-Utter</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 39936-2024 artfynd.xlsx", "A 39936-2024")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 39936-2024 karta.png", "A 39936-2024")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 39936-2024 georefererad karta.tif", "A 39936-2024")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 39936-2024 FSC-klagomål.docx", "A 39936-2024")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 39936-2024 FSC-klagomål mail.docx", "A 39936-2024")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 39936-2024 tillsynsbegäran.docx", "A 39936-2024")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 39936-2024 tillsynsbegäran mail.docx", "A 39936-2024")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 52377-2025</t>
+          <t>A 58091-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2853,10 +2854,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45953</v>
+        <v>44900</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2874,7 +2875,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2907,49 +2908,49 @@
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Hårklomossa</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 52377-2025 artfynd.xlsx", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 58091-2022 artfynd.xlsx", "A 58091-2022")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 52377-2025 karta.png", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 58091-2022 karta.png", "A 58091-2022")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 52377-2025 georefererad karta.tif", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 58091-2022 georefererad karta.tif", "A 58091-2022")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 52377-2025 FSC-klagomål.docx", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 58091-2022 FSC-klagomål.docx", "A 58091-2022")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 52377-2025 FSC-klagomål mail.docx", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 58091-2022 FSC-klagomål mail.docx", "A 58091-2022")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 52377-2025 tillsynsbegäran.docx", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 58091-2022 tillsynsbegäran.docx", "A 58091-2022")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 52377-2025 tillsynsbegäran mail.docx", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 58091-2022 tillsynsbegäran mail.docx", "A 58091-2022")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 63188-2025</t>
+          <t>A 28566-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2963,10 +2964,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46010</v>
+        <v>45478</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2978,13 +2979,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2993,7 +2989,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -3008,7 +3004,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -3017,53 +3013,49 @@
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 63188-2025 artfynd.xlsx", "A 63188-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 28566-2024 artfynd.xlsx", "A 28566-2024")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 63188-2025 karta.png", "A 63188-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 28566-2024 karta.png", "A 28566-2024")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 63188-2025 georefererad karta.tif", "A 63188-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 28566-2024 georefererad karta.tif", "A 28566-2024")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 63188-2025 FSC-klagomål.docx", "A 63188-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 28566-2024 FSC-klagomål.docx", "A 28566-2024")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 63188-2025 FSC-klagomål mail.docx", "A 63188-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 28566-2024 FSC-klagomål mail.docx", "A 28566-2024")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 63188-2025 tillsynsbegäran.docx", "A 63188-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 28566-2024 tillsynsbegäran.docx", "A 28566-2024")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 63188-2025 tillsynsbegäran mail.docx", "A 63188-2025")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 63188-2025 prioriterade fågelarter.docx", "A 63188-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 28566-2024 tillsynsbegäran mail.docx", "A 28566-2024")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 16784-2026</t>
+          <t>A 63188-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3077,10 +3069,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46113</v>
+        <v>46010</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3098,7 +3090,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>4.2</v>
+        <v>1.1</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -3107,7 +3099,7 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -3122,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -3134,46 +3126,50 @@
         <v>2</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Hårklomossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 16784-2026 artfynd.xlsx", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 63188-2025 artfynd.xlsx", "A 63188-2025")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 16784-2026 karta.png", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 63188-2025 karta.png", "A 63188-2025")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 16784-2026 georefererad karta.tif", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 63188-2025 georefererad karta.tif", "A 63188-2025")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 16784-2026 FSC-klagomål.docx", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 63188-2025 FSC-klagomål.docx", "A 63188-2025")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 16784-2026 FSC-klagomål mail.docx", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 63188-2025 FSC-klagomål mail.docx", "A 63188-2025")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 16784-2026 tillsynsbegäran.docx", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 63188-2025 tillsynsbegäran.docx", "A 63188-2025")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 16784-2026 tillsynsbegäran mail.docx", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 63188-2025 tillsynsbegäran mail.docx", "A 63188-2025")</f>
+        <v/>
+      </c>
+      <c r="AE23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 63188-2025 prioriterade fågelarter.docx", "A 63188-2025")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 18427-2026</t>
+          <t>A 16784-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3187,10 +3183,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46127</v>
+        <v>46113</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3208,7 +3204,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3241,53 +3237,49 @@
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Hårklomossa</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 18427-2026 artfynd.xlsx", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 16784-2026 artfynd.xlsx", "A 16784-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 18427-2026 karta.png", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 16784-2026 karta.png", "A 16784-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 18427-2026 georefererad karta.tif", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 16784-2026 georefererad karta.tif", "A 16784-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 18427-2026 FSC-klagomål.docx", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 16784-2026 FSC-klagomål.docx", "A 16784-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 18427-2026 FSC-klagomål mail.docx", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 16784-2026 FSC-klagomål mail.docx", "A 16784-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 18427-2026 tillsynsbegäran.docx", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 16784-2026 tillsynsbegäran.docx", "A 16784-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 18427-2026 tillsynsbegäran mail.docx", "A 18427-2026")</f>
-        <v/>
-      </c>
-      <c r="AE24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 18427-2026 prioriterade fågelarter.docx", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 16784-2026 tillsynsbegäran mail.docx", "A 16784-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 19233-2026</t>
+          <t>A 18427-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3301,10 +3293,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46132</v>
+        <v>46127</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3316,14 +3308,19 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -3353,46 +3350,50 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 19233-2026 artfynd.xlsx", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 18427-2026 artfynd.xlsx", "A 18427-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 19233-2026 karta.png", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 18427-2026 karta.png", "A 18427-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 19233-2026 georefererad karta.tif", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 18427-2026 georefererad karta.tif", "A 18427-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 19233-2026 FSC-klagomål.docx", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 18427-2026 FSC-klagomål.docx", "A 18427-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 19233-2026 FSC-klagomål mail.docx", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 18427-2026 FSC-klagomål mail.docx", "A 18427-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 19233-2026 tillsynsbegäran.docx", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 18427-2026 tillsynsbegäran.docx", "A 18427-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 19233-2026 tillsynsbegäran mail.docx", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 18427-2026 tillsynsbegäran mail.docx", "A 18427-2026")</f>
+        <v/>
+      </c>
+      <c r="AE25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 18427-2026 prioriterade fågelarter.docx", "A 18427-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 28474-2023</t>
+          <t>A 19233-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3406,10 +3407,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45103</v>
+        <v>46132</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3422,16 +3423,16 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>5.1</v>
+        <v>1.6</v>
       </c>
       <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
         <v>1</v>
       </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -3446,7 +3447,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3458,50 +3459,46 @@
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Blåhake</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 28474-2023 artfynd.xlsx", "A 28474-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 19233-2026 artfynd.xlsx", "A 19233-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 28474-2023 karta.png", "A 28474-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 19233-2026 karta.png", "A 19233-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 28474-2023 georefererad karta.tif", "A 28474-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 19233-2026 georefererad karta.tif", "A 19233-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 28474-2023 FSC-klagomål.docx", "A 28474-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 19233-2026 FSC-klagomål.docx", "A 19233-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 28474-2023 FSC-klagomål mail.docx", "A 28474-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 19233-2026 FSC-klagomål mail.docx", "A 19233-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 28474-2023 tillsynsbegäran.docx", "A 28474-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 19233-2026 tillsynsbegäran.docx", "A 19233-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 28474-2023 tillsynsbegäran mail.docx", "A 28474-2023")</f>
-        <v/>
-      </c>
-      <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 28474-2023 prioriterade fågelarter.docx", "A 28474-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 19233-2026 tillsynsbegäran mail.docx", "A 19233-2026")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 58091-2022</t>
+          <t>A 21019-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3515,10 +3512,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44900</v>
+        <v>46145</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3536,7 +3533,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.1</v>
+        <v>4.7</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
@@ -3569,49 +3566,49 @@
         <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Hårklomossa</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 58091-2022 artfynd.xlsx", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 21019-2026 artfynd.xlsx", "A 21019-2026")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 58091-2022 karta.png", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 21019-2026 karta.png", "A 21019-2026")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 58091-2022 georefererad karta.tif", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 21019-2026 georefererad karta.tif", "A 21019-2026")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 58091-2022 FSC-klagomål.docx", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 21019-2026 FSC-klagomål.docx", "A 21019-2026")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 58091-2022 FSC-klagomål mail.docx", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 21019-2026 FSC-klagomål mail.docx", "A 21019-2026")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 58091-2022 tillsynsbegäran.docx", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 21019-2026 tillsynsbegäran.docx", "A 21019-2026")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 58091-2022 tillsynsbegäran mail.docx", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 21019-2026 tillsynsbegäran mail.docx", "A 21019-2026")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 21019-2026</t>
+          <t>A 25093-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3625,10 +3622,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46145</v>
+        <v>46175</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3646,13 +3643,13 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
         <v>1</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -3682,46 +3679,46 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 21019-2026 artfynd.xlsx", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 25093-2026 artfynd.xlsx", "A 25093-2026")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 21019-2026 karta.png", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 25093-2026 karta.png", "A 25093-2026")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 21019-2026 georefererad karta.tif", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 25093-2026 georefererad karta.tif", "A 25093-2026")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 21019-2026 FSC-klagomål.docx", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 25093-2026 FSC-klagomål.docx", "A 25093-2026")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 21019-2026 FSC-klagomål mail.docx", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 25093-2026 FSC-klagomål mail.docx", "A 25093-2026")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 21019-2026 tillsynsbegäran.docx", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 25093-2026 tillsynsbegäran.docx", "A 25093-2026")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 21019-2026 tillsynsbegäran mail.docx", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 25093-2026 tillsynsbegäran mail.docx", "A 25093-2026")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 28566-2024</t>
+          <t>A 52377-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3735,10 +3732,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45478</v>
+        <v>45953</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3750,8 +3747,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -3791,42 +3793,42 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 28566-2024 artfynd.xlsx", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 52377-2025 artfynd.xlsx", "A 52377-2025")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 28566-2024 karta.png", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 52377-2025 karta.png", "A 52377-2025")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 28566-2024 georefererad karta.tif", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 52377-2025 georefererad karta.tif", "A 52377-2025")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 28566-2024 FSC-klagomål.docx", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 52377-2025 FSC-klagomål.docx", "A 52377-2025")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 28566-2024 FSC-klagomål mail.docx", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 52377-2025 FSC-klagomål mail.docx", "A 52377-2025")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 28566-2024 tillsynsbegäran.docx", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 52377-2025 tillsynsbegäran.docx", "A 52377-2025")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 28566-2024 tillsynsbegäran mail.docx", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 52377-2025 tillsynsbegäran mail.docx", "A 52377-2025")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 25093-2026</t>
+          <t>A 28474-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3840,10 +3842,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46175</v>
+        <v>45103</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3855,23 +3857,18 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
         <v>1</v>
       </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
@@ -3885,7 +3882,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -3901,35 +3898,39 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåhake</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 25093-2026 artfynd.xlsx", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 28474-2023 artfynd.xlsx", "A 28474-2023")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 25093-2026 karta.png", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 28474-2023 karta.png", "A 28474-2023")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 25093-2026 georefererad karta.tif", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 28474-2023 georefererad karta.tif", "A 28474-2023")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 25093-2026 FSC-klagomål.docx", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 28474-2023 FSC-klagomål.docx", "A 28474-2023")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 25093-2026 FSC-klagomål mail.docx", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 28474-2023 FSC-klagomål mail.docx", "A 28474-2023")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 25093-2026 tillsynsbegäran.docx", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 28474-2023 tillsynsbegäran.docx", "A 28474-2023")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 25093-2026 tillsynsbegäran mail.docx", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 28474-2023 tillsynsbegäran mail.docx", "A 28474-2023")</f>
+        <v/>
+      </c>
+      <c r="AE30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 28474-2023 prioriterade fågelarter.docx", "A 28474-2023")</f>
         <v/>
       </c>
     </row>
@@ -3953,7 +3954,7 @@
         <v>46213</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4046,7 +4047,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 40528-2024</t>
+          <t>A 35199-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4060,10 +4061,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45555</v>
+        <v>46260</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4075,8 +4076,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>2.8</v>
+        <v>5.6</v>
       </c>
       <c r="J32" t="n">
         <v>1</v>
@@ -4085,7 +4091,7 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -4100,7 +4106,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -4112,46 +4118,46 @@
         <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 40528-2024 artfynd.xlsx", "A 40528-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 35199-2026 artfynd.xlsx", "A 35199-2026")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 40528-2024 karta.png", "A 40528-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 35199-2026 karta.png", "A 35199-2026")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 40528-2024 georefererad karta.tif", "A 40528-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 35199-2026 georefererad karta.tif", "A 35199-2026")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 40528-2024 FSC-klagomål.docx", "A 40528-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 35199-2026 FSC-klagomål.docx", "A 35199-2026")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 40528-2024 FSC-klagomål mail.docx", "A 40528-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 35199-2026 FSC-klagomål mail.docx", "A 35199-2026")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 40528-2024 tillsynsbegäran.docx", "A 40528-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 35199-2026 tillsynsbegäran.docx", "A 35199-2026")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 40528-2024 tillsynsbegäran mail.docx", "A 40528-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 35199-2026 tillsynsbegäran mail.docx", "A 35199-2026")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 35199-2026</t>
+          <t>A 40528-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4165,10 +4171,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46260</v>
+        <v>45555</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4180,13 +4186,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>5.6</v>
+        <v>2.8</v>
       </c>
       <c r="J33" t="n">
         <v>1</v>
@@ -4195,7 +4196,7 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -4210,7 +4211,7 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -4222,39 +4223,39 @@
         <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 35199-2026 artfynd.xlsx", "A 35199-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 40528-2024 artfynd.xlsx", "A 40528-2024")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 35199-2026 karta.png", "A 35199-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 40528-2024 karta.png", "A 40528-2024")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 35199-2026 georefererad karta.tif", "A 35199-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 40528-2024 georefererad karta.tif", "A 40528-2024")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 35199-2026 FSC-klagomål.docx", "A 35199-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 40528-2024 FSC-klagomål.docx", "A 40528-2024")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 35199-2026 FSC-klagomål mail.docx", "A 35199-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 40528-2024 FSC-klagomål mail.docx", "A 40528-2024")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 35199-2026 tillsynsbegäran.docx", "A 35199-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 40528-2024 tillsynsbegäran.docx", "A 40528-2024")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 35199-2026 tillsynsbegäran mail.docx", "A 35199-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 40528-2024 tillsynsbegäran mail.docx", "A 40528-2024")</f>
         <v/>
       </c>
     </row>
@@ -4278,7 +4279,7 @@
         <v>46280</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4392,7 +4393,7 @@
         <v>46136</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4502,7 +4503,7 @@
         <v>44546</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4575,7 +4576,7 @@
         <v>44732</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4648,7 +4649,7 @@
         <v>44460</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4704,7 +4705,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 22861-2022</t>
+          <t>A 64869-2021</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4718,10 +4719,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44715</v>
+        <v>44512</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4733,8 +4734,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>0.6</v>
+        <v>3.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4777,7 +4783,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 64869-2021</t>
+          <t>A 22861-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4791,10 +4797,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44512</v>
+        <v>44715</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4806,13 +4812,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>3.6</v>
+        <v>0.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4872,7 +4873,7 @@
         <v>44508</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4950,7 +4951,7 @@
         <v>44480</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5023,7 +5024,7 @@
         <v>44809</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5096,7 +5097,7 @@
         <v>44811</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5169,7 +5170,7 @@
         <v>44628</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5247,7 +5248,7 @@
         <v>44809</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5320,7 +5321,7 @@
         <v>44706</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5393,7 +5394,7 @@
         <v>44706</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5466,7 +5467,7 @@
         <v>44817</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5527,7 +5528,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 58390-2024</t>
+          <t>A 8803-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5541,10 +5542,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45633</v>
+        <v>45712</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5557,7 +5558,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5600,7 +5601,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 35471-2024</t>
+          <t>A 35445-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5617,7 +5618,7 @@
         <v>45531</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5673,7 +5674,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 9712-2024</t>
+          <t>A 39337-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5687,10 +5688,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45362</v>
+        <v>44817</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5702,13 +5703,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5751,7 +5747,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 42804-2023</t>
+          <t>A 56887-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5761,14 +5757,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45182</v>
+        <v>44894</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5780,13 +5776,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5829,7 +5820,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 9510-2023</t>
+          <t>A 20289-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5843,10 +5834,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44981</v>
+        <v>45435</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5858,8 +5849,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5902,7 +5898,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 1309-2024</t>
+          <t>A 38190-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5916,10 +5912,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45303</v>
+        <v>45545</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5932,7 +5928,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5975,7 +5971,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 4164-2022</t>
+          <t>A 38196-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5989,10 +5985,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44588</v>
+        <v>45545</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6004,13 +6000,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -6053,7 +6044,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 23263-2022</t>
+          <t>A 9712-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6067,10 +6058,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44720</v>
+        <v>45362</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6082,8 +6073,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6126,7 +6122,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 35444-2024</t>
+          <t>A 15256-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6140,10 +6136,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45531</v>
+        <v>45744</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6155,8 +6151,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>0.5</v>
+        <v>5.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6199,7 +6200,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 47201-2023</t>
+          <t>A 43075-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6213,10 +6214,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45196</v>
+        <v>45182</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6229,7 +6230,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6272,7 +6273,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 61396-2023</t>
+          <t>A 23263-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6286,10 +6287,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45264</v>
+        <v>44720</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6302,7 +6303,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6345,7 +6346,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 8259-2025</t>
+          <t>A 4058-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6359,10 +6360,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45708</v>
+        <v>44588</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6375,7 +6376,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6418,7 +6419,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 24116-2024</t>
+          <t>A 35444-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6432,10 +6433,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45456</v>
+        <v>45531</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6448,7 +6449,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6491,7 +6492,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 1788-2026</t>
+          <t>A 35471-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6505,10 +6506,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46034</v>
+        <v>45531</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6521,7 +6522,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6564,7 +6565,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 27498-2025</t>
+          <t>A 54680-2021</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6578,10 +6579,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45813</v>
+        <v>44473</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6594,7 +6595,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6637,7 +6638,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 17815-2025</t>
+          <t>A 30102-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6651,10 +6652,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45758</v>
+        <v>45826</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6664,11 +6665,6 @@
       <c r="G65" t="inlineStr">
         <is>
           <t>KARLSKOGA</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I65" t="n">
@@ -6715,7 +6711,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 35930-2023</t>
+          <t>A 53647-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6729,10 +6725,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45148</v>
+        <v>45230</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6744,13 +6740,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>5.2</v>
+        <v>0.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6810,7 +6801,7 @@
         <v>45454</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6866,7 +6857,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 53647-2023</t>
+          <t>A 58390-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6880,10 +6871,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45230</v>
+        <v>45633</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6896,7 +6887,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6939,7 +6930,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 30102-2025</t>
+          <t>A 9917-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6953,10 +6944,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45826</v>
+        <v>46073</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6969,7 +6960,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7012,7 +7003,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 63863-2023</t>
+          <t>A 31397-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7026,10 +7017,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45278</v>
+        <v>45833</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7042,7 +7033,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7085,7 +7076,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 54680-2021</t>
+          <t>A 32287-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7099,10 +7090,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44473</v>
+        <v>45835</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7114,8 +7105,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>2.9</v>
+        <v>10.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7158,7 +7154,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 31397-2025</t>
+          <t>A 18768-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7172,10 +7168,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45833</v>
+        <v>45764</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7187,8 +7183,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7231,7 +7232,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 32287-2025</t>
+          <t>A 42803-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7241,14 +7242,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45835</v>
+        <v>45182</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7262,11 +7263,11 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>10.9</v>
+        <v>0.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7309,7 +7310,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 44946-2025</t>
+          <t>A 24255-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7323,10 +7324,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45918</v>
+        <v>45457</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7382,7 +7383,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 44949-2025</t>
+          <t>A 13473-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7396,10 +7397,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45918</v>
+        <v>46094</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7412,7 +7413,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7455,7 +7456,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 59938-2023</t>
+          <t>A 14580-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7469,10 +7470,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45257</v>
+        <v>46101</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7484,8 +7485,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7528,7 +7534,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 52828-2024</t>
+          <t>A 20086-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7538,14 +7544,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45610</v>
+        <v>45434</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7558,7 +7564,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>8.300000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7601,7 +7607,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 45664-2025</t>
+          <t>A 12897-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7615,10 +7621,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45923</v>
+        <v>46092</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7630,13 +7636,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>9</v>
+        <v>1.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7679,7 +7680,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 2911-2026</t>
+          <t>A 9510-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7693,10 +7694,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46038</v>
+        <v>44981</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7709,7 +7710,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7752,7 +7753,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 15256-2025</t>
+          <t>A 16782-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7766,10 +7767,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45744</v>
+        <v>46113</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7787,7 +7788,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>5.5</v>
+        <v>2.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7830,7 +7831,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 47222-2024</t>
+          <t>A 16783-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7844,10 +7845,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45586</v>
+        <v>46113</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7865,7 +7866,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>5.3</v>
+        <v>1.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7908,7 +7909,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 24115-2024</t>
+          <t>A 16787-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7922,10 +7923,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45456</v>
+        <v>46113</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7937,8 +7938,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>8</v>
+        <v>2.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7981,7 +7987,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 50958-2025</t>
+          <t>A 17815-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7995,10 +8001,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45946</v>
+        <v>45758</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8010,8 +8016,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8054,7 +8065,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 24255-2024</t>
+          <t>A 15060-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8068,10 +8079,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45457</v>
+        <v>46104</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8084,7 +8095,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.4</v>
+        <v>11.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8127,7 +8138,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 18768-2025</t>
+          <t>A 15058-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8141,10 +8152,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45764</v>
+        <v>46104</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8156,13 +8167,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>0.7</v>
+        <v>4.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8205,7 +8211,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 55025-2025</t>
+          <t>A 17734-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8219,10 +8225,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45967</v>
+        <v>46122</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8234,8 +8240,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8278,7 +8289,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 4801-2024</t>
+          <t>A 19011-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8292,10 +8303,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45328</v>
+        <v>46130</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8305,6 +8316,11 @@
       <c r="G87" t="inlineStr">
         <is>
           <t>KARLSKOGA</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I87" t="n">
@@ -8351,7 +8367,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 4802-2024</t>
+          <t>A 59025-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8365,10 +8381,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45328</v>
+        <v>45636</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8380,8 +8396,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8424,7 +8445,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 8990-2023</t>
+          <t>A 19010-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8438,10 +8459,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44979</v>
+        <v>46130</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8453,8 +8474,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8497,7 +8523,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 42802-2023</t>
+          <t>A 19009-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8507,14 +8533,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45182</v>
+        <v>46130</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8532,7 +8558,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.6</v>
+        <v>6.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8575,7 +8601,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 9917-2026</t>
+          <t>A 19008-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8589,10 +8615,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46073</v>
+        <v>46130</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8604,8 +8630,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8648,7 +8679,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 28471-2023</t>
+          <t>A 19663-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8662,10 +8693,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45103</v>
+        <v>46134</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8677,8 +8708,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8721,7 +8757,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 22867-2022</t>
+          <t>A 13501-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8735,10 +8771,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44715</v>
+        <v>45736</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8751,7 +8787,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.8</v>
+        <v>3.2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8794,7 +8830,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 59522-2025</t>
+          <t>A 47094-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8804,14 +8840,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45989</v>
+        <v>45196</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8823,13 +8859,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8872,7 +8903,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 64060-2023</t>
+          <t>A 31921-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8886,10 +8917,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45279</v>
+        <v>44777</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8902,7 +8933,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8945,7 +8976,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 48707-2024</t>
+          <t>A 42804-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8955,14 +8986,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45593</v>
+        <v>45182</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8974,8 +9005,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I96" t="n">
-        <v>6</v>
+        <v>0.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9018,7 +9054,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 60506-2025</t>
+          <t>A 39030-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9032,10 +9068,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45995</v>
+        <v>44817</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9047,8 +9083,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I97" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9091,7 +9132,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 60508-2025</t>
+          <t>A 6835-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9105,10 +9146,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45995</v>
+        <v>45700</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9121,7 +9162,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9164,7 +9205,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 60503-2025</t>
+          <t>A 8244-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9178,10 +9219,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45995</v>
+        <v>45708</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9194,7 +9235,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9237,7 +9278,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 55832-2023</t>
+          <t>A 44946-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9251,10 +9292,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45239</v>
+        <v>45918</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9267,7 +9308,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9310,7 +9351,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 58388-2024</t>
+          <t>A 44949-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9324,10 +9365,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45633</v>
+        <v>45918</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9340,7 +9381,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>5.8</v>
+        <v>0.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9383,7 +9424,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 61788-2025</t>
+          <t>A 28100-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9397,10 +9438,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46002</v>
+        <v>45476</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9412,13 +9453,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9461,7 +9497,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 18978-2025</t>
+          <t>A 51344-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9475,10 +9511,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45764</v>
+        <v>45219</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9490,8 +9526,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>0.8</v>
+        <v>4.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9534,7 +9575,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 64066-2025</t>
+          <t>A 21210-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9544,14 +9585,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46013</v>
+        <v>45779</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9563,8 +9604,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I104" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9607,7 +9653,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 13473-2026</t>
+          <t>A 23717-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9621,10 +9667,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46094</v>
+        <v>45793</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9637,7 +9683,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9680,7 +9726,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 63628-2025</t>
+          <t>A 917-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9694,10 +9740,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46014</v>
+        <v>46030</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9710,7 +9756,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9753,7 +9799,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 31921-2022</t>
+          <t>A 20463-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9767,10 +9813,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44777</v>
+        <v>45775</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9782,8 +9828,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9826,7 +9877,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 43075-2023</t>
+          <t>A 28471-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9840,10 +9891,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45182</v>
+        <v>45103</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9856,7 +9907,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9899,7 +9950,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 47196-2023</t>
+          <t>A 16881-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9913,10 +9964,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45196</v>
+        <v>45033</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9928,8 +9979,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I109" t="n">
-        <v>5.9</v>
+        <v>2.3</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9972,7 +10028,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 13454-2022</t>
+          <t>A 61396-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9986,10 +10042,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44645</v>
+        <v>45264</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10002,7 +10058,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10045,7 +10101,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 12897-2026</t>
+          <t>A 21253-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10059,10 +10115,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46092</v>
+        <v>46147</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10075,7 +10131,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.3</v>
+        <v>3.4</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10118,7 +10174,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 14580-2026</t>
+          <t>A 21257-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10132,10 +10188,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46101</v>
+        <v>46147</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10147,13 +10203,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I112" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10196,7 +10247,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 53618-2024</t>
+          <t>A 4164-2022</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10210,10 +10261,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45614</v>
+        <v>44588</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10225,8 +10276,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I113" t="n">
-        <v>10.1</v>
+        <v>1.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10269,7 +10325,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 30961-2022</t>
+          <t>A 61271-2022</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10283,10 +10339,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44768</v>
+        <v>44909</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10300,11 +10356,11 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I114" t="n">
-        <v>3.3</v>
+        <v>14.1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10347,7 +10403,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 16783-2026</t>
+          <t>A 3227-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10361,10 +10417,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46113</v>
+        <v>45679</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10376,13 +10432,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I115" t="n">
-        <v>1.7</v>
+        <v>4.5</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10425,7 +10476,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 16787-2026</t>
+          <t>A 57422-2021</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10439,10 +10490,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46113</v>
+        <v>44483</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10454,13 +10505,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10503,7 +10549,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 16782-2026</t>
+          <t>A 35060-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10517,10 +10563,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46113</v>
+        <v>45527</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10534,11 +10580,11 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10581,7 +10627,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 42803-2023</t>
+          <t>A 23754-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10591,14 +10637,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45182</v>
+        <v>46164</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10616,7 +10662,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.7</v>
+        <v>12.2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10659,7 +10705,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 15058-2026</t>
+          <t>A 64060-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10673,10 +10719,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46104</v>
+        <v>45279</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10689,7 +10735,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>4.3</v>
+        <v>1.9</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10732,7 +10778,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 15060-2026</t>
+          <t>A 4587-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10746,10 +10792,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46104</v>
+        <v>45687</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10762,7 +10808,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>11.5</v>
+        <v>3.3</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10805,7 +10851,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 17734-2026</t>
+          <t>A 4587-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10819,10 +10865,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46122</v>
+        <v>45687</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10834,13 +10880,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I121" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10883,7 +10924,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 8803-2025</t>
+          <t>A 14215-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10897,10 +10938,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45712</v>
+        <v>45393</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10912,8 +10953,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I122" t="n">
-        <v>1.5</v>
+        <v>4.2</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10956,7 +11002,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 19009-2026</t>
+          <t>A 24666-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10970,10 +11016,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46130</v>
+        <v>46171</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10985,13 +11031,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I123" t="n">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -11034,7 +11075,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 19011-2026</t>
+          <t>A 25098-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11044,14 +11085,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46130</v>
+        <v>46175</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11069,7 +11110,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -11112,7 +11153,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 19010-2026</t>
+          <t>A 24116-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11126,10 +11167,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46130</v>
+        <v>45456</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11141,13 +11182,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I125" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11190,7 +11226,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 19008-2026</t>
+          <t>A 25092-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11204,10 +11240,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46130</v>
+        <v>46175</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11268,7 +11304,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 56313-2024</t>
+          <t>A 55832-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11282,10 +11318,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45624</v>
+        <v>45239</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11297,13 +11333,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I127" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11346,7 +11377,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 10743-2023</t>
+          <t>A 10515-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11360,10 +11391,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44988</v>
+        <v>44987</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11375,13 +11406,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I128" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11424,7 +11450,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 14215-2024</t>
+          <t>A 50958-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11438,10 +11464,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45393</v>
+        <v>45946</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11453,13 +11479,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I129" t="n">
-        <v>4.2</v>
+        <v>0.4</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11502,7 +11523,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 19663-2026</t>
+          <t>A 33011-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11516,10 +11537,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46134</v>
+        <v>45125</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11531,13 +11552,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I130" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11580,7 +11596,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 55191-2023</t>
+          <t>A 26822-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11594,10 +11610,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45237</v>
+        <v>46185</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11609,8 +11625,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I131" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11653,7 +11674,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 59025-2024</t>
+          <t>A 26819-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11667,10 +11688,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45636</v>
+        <v>46185</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11684,11 +11705,11 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I132" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11731,7 +11752,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 17243-2024</t>
+          <t>A 3239-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11745,10 +11766,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45414</v>
+        <v>46041</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11761,7 +11782,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11804,7 +11825,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 6835-2025</t>
+          <t>A 26821-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11818,10 +11839,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45700</v>
+        <v>46185</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11833,8 +11854,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I134" t="n">
-        <v>3</v>
+        <v>7.9</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11877,7 +11903,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 21210-2025</t>
+          <t>A 26820-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11891,10 +11917,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45779</v>
+        <v>46185</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11912,7 +11938,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.1</v>
+        <v>9.9</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11955,7 +11981,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 23717-2025</t>
+          <t>A 26608-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11969,10 +11995,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45793</v>
+        <v>46184</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11984,8 +12010,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I136" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -12028,7 +12059,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 35060-2024</t>
+          <t>A 26824-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12042,10 +12073,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45527</v>
+        <v>46185</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12059,11 +12090,11 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I137" t="n">
-        <v>0.6</v>
+        <v>5</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -12106,7 +12137,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 52826-2024</t>
+          <t>A 26825-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12120,10 +12151,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45610</v>
+        <v>46185</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12135,8 +12166,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I138" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -12179,7 +12215,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 52829-2024</t>
+          <t>A 48168-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12193,10 +12229,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45610</v>
+        <v>45589</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12209,7 +12245,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>2</v>
+        <v>5.5</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12252,7 +12288,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 917-2026</t>
+          <t>A 27392-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12266,10 +12302,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46030</v>
+        <v>46189</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12281,8 +12317,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I140" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12325,7 +12366,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 11974-2025</t>
+          <t>A 27120-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12339,10 +12380,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45728</v>
+        <v>46188</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12355,7 +12396,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.4</v>
+        <v>4.7</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12398,7 +12439,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 61271-2022</t>
+          <t>A 13454-2022</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12412,10 +12453,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44909</v>
+        <v>44645</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12427,13 +12468,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I142" t="n">
-        <v>14.1</v>
+        <v>1.7</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12476,7 +12512,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 48168-2024</t>
+          <t>A 10743-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12490,10 +12526,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45589</v>
+        <v>44988</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12505,8 +12541,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I143" t="n">
-        <v>5.5</v>
+        <v>2.4</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12549,7 +12590,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 21253-2026</t>
+          <t>A 50611-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12563,10 +12604,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46147</v>
+        <v>45601</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12579,7 +12620,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12622,7 +12663,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 21257-2026</t>
+          <t>A 42802-2023</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12632,14 +12673,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46147</v>
+        <v>45182</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12651,8 +12692,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I145" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12695,7 +12741,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 18955-2025</t>
+          <t>A 52829-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12709,10 +12755,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45764</v>
+        <v>45610</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12725,7 +12771,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>8.1</v>
+        <v>2</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12768,7 +12814,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 50614-2024</t>
+          <t>A 55025-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12782,10 +12828,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45601</v>
+        <v>45967</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12798,7 +12844,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12841,7 +12887,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 55182-2024</t>
+          <t>A 56313-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12855,10 +12901,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45618</v>
+        <v>45624</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12870,8 +12916,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I148" t="n">
-        <v>11.4</v>
+        <v>2.2</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12914,7 +12965,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 3227-2025</t>
+          <t>A 38382-2022</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12928,10 +12979,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45679</v>
+        <v>44812</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12943,8 +12994,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I149" t="n">
-        <v>4.5</v>
+        <v>2.2</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12987,7 +13043,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 4058-2022</t>
+          <t>A 24115-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -13001,10 +13057,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>44588</v>
+        <v>45456</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13017,7 +13073,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.7</v>
+        <v>8</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -13060,7 +13116,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 23754-2026</t>
+          <t>A 10404-2022</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -13074,10 +13130,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46164</v>
+        <v>44623</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13089,13 +13145,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I151" t="n">
-        <v>12.2</v>
+        <v>1</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -13138,7 +13189,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 4587-2025</t>
+          <t>A 18955-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13152,10 +13203,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45687</v>
+        <v>45764</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13168,7 +13219,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>3.3</v>
+        <v>8.1</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -13211,7 +13262,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 28100-2024</t>
+          <t>A 59522-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13221,14 +13272,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45476</v>
+        <v>45989</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13240,8 +13291,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I153" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -13284,7 +13340,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 4587-2025</t>
+          <t>A 22867-2022</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13298,10 +13354,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45687</v>
+        <v>44715</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13314,7 +13370,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>3.3</v>
+        <v>0.8</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13357,7 +13413,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 1106-2024</t>
+          <t>A 18978-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13371,10 +13427,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45302</v>
+        <v>45764</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13387,7 +13443,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13430,7 +13486,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 24666-2026</t>
+          <t>A 31378-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13444,10 +13500,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46171</v>
+        <v>46213</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13460,7 +13516,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>6.1</v>
+        <v>3.7</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13503,7 +13559,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 39030-2022</t>
+          <t>A 4801-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13517,10 +13573,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>44817</v>
+        <v>45328</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13532,13 +13588,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I157" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13581,7 +13632,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 38382-2022</t>
+          <t>A 4802-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13595,10 +13646,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>44812</v>
+        <v>45328</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13610,13 +13661,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I158" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13659,7 +13705,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 25092-2026</t>
+          <t>A 30961-2022</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13673,10 +13719,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46175</v>
+        <v>44768</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13690,11 +13736,11 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.9</v>
+        <v>3.3</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13737,7 +13783,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 25098-2026</t>
+          <t>A 60503-2025</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13747,14 +13793,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46175</v>
+        <v>45995</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13766,13 +13812,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I160" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13815,7 +13856,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 16881-2023</t>
+          <t>A 35094-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13829,10 +13870,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45033</v>
+        <v>46260</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13850,7 +13891,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13893,7 +13934,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 57422-2021</t>
+          <t>A 55191-2023</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13907,10 +13948,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>44483</v>
+        <v>45237</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13923,7 +13964,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13966,7 +14007,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 26608-2026</t>
+          <t>A 60508-2025</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13980,10 +14021,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46184</v>
+        <v>45995</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13995,13 +14036,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I163" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -14044,7 +14080,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 8244-2025</t>
+          <t>A 60506-2025</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -14058,10 +14094,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45708</v>
+        <v>45995</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14074,7 +14110,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -14117,7 +14153,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 27120-2026</t>
+          <t>A 61788-2025</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -14131,10 +14167,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46188</v>
+        <v>46002</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14146,8 +14182,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I165" t="n">
-        <v>4.7</v>
+        <v>0.9</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -14190,7 +14231,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 26819-2026</t>
+          <t>A 35699-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -14200,14 +14241,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46185</v>
+        <v>46265</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14225,7 +14266,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -14268,7 +14309,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 38190-2024</t>
+          <t>A 13496-2025</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -14282,10 +14323,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45545</v>
+        <v>45736</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14298,7 +14339,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>2.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14341,7 +14382,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 3239-2026</t>
+          <t>A 11974-2025</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14355,10 +14396,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46041</v>
+        <v>45728</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14371,7 +14412,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14414,7 +14455,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 26820-2026</t>
+          <t>A 36374-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14428,10 +14469,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46185</v>
+        <v>46268</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14445,11 +14486,11 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I169" t="n">
-        <v>9.9</v>
+        <v>1.6</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14492,7 +14533,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 26821-2026</t>
+          <t>A 63863-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14506,10 +14547,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46185</v>
+        <v>45278</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14521,13 +14562,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I170" t="n">
-        <v>7.9</v>
+        <v>1.1</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14570,7 +14606,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 26822-2026</t>
+          <t>A 1309-2024</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14584,10 +14620,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46185</v>
+        <v>45303</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14599,13 +14635,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I171" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14648,7 +14679,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 26824-2026</t>
+          <t>A 37089-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14662,10 +14693,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46185</v>
+        <v>46273</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14677,13 +14708,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I172" t="n">
-        <v>5</v>
+        <v>15.8</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14726,7 +14752,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 26825-2026</t>
+          <t>A 64066-2025</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14736,14 +14762,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46185</v>
+        <v>46013</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14755,13 +14781,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I173" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14804,7 +14825,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 20463-2025</t>
+          <t>A 63628-2025</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14818,10 +14839,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45775</v>
+        <v>46014</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14833,13 +14854,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I174" t="n">
-        <v>0.9</v>
+        <v>3.8</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14882,7 +14898,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 27392-2026</t>
+          <t>A 52826-2024</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14896,10 +14912,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46189</v>
+        <v>45610</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14911,13 +14927,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I175" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14960,7 +14971,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 35470-2024</t>
+          <t>A 38043-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14974,10 +14985,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45531</v>
+        <v>46280</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14989,8 +15000,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I176" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -15033,7 +15049,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 35445-2024</t>
+          <t>A 38020-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -15047,10 +15063,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45531</v>
+        <v>46280</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15062,8 +15078,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I177" t="n">
-        <v>0.5</v>
+        <v>4.1</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -15106,7 +15127,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 47094-2023</t>
+          <t>A 1106-2024</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -15120,10 +15141,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45196</v>
+        <v>45302</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15179,7 +15200,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 38196-2024</t>
+          <t>A 48707-2024</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -15193,10 +15214,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45545</v>
+        <v>45593</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15209,7 +15230,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>0.7</v>
+        <v>6</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -15252,7 +15273,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 50611-2024</t>
+          <t>A 1788-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -15266,10 +15287,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45601</v>
+        <v>46034</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15282,7 +15303,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -15325,7 +15346,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 20289-2024</t>
+          <t>A 2911-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15339,10 +15360,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45435</v>
+        <v>46038</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15354,13 +15375,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I181" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15403,7 +15419,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 52797-2021</t>
+          <t>A 35470-2024</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15417,10 +15433,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>44467</v>
+        <v>45531</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15433,7 +15449,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15476,7 +15492,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 20086-2024</t>
+          <t>A 45664-2025</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15486,14 +15502,14 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45434</v>
+        <v>45923</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15505,8 +15521,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I183" t="n">
-        <v>1.5</v>
+        <v>9</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15549,7 +15570,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 13496-2025</t>
+          <t>A 47222-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15563,10 +15584,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45736</v>
+        <v>45586</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15578,8 +15599,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I184" t="n">
-        <v>8.800000000000001</v>
+        <v>5.3</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15622,7 +15648,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 56887-2022</t>
+          <t>A 8990-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15636,10 +15662,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>44894</v>
+        <v>44979</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15652,7 +15678,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15695,7 +15721,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 31378-2026</t>
+          <t>A 50614-2024</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15709,10 +15735,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46213</v>
+        <v>45601</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15725,7 +15751,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>3.7</v>
+        <v>0.7</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15768,7 +15794,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 35094-2026</t>
+          <t>A 55182-2024</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15782,10 +15808,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46260</v>
+        <v>45618</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15797,13 +15823,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I187" t="n">
-        <v>1.9</v>
+        <v>11.4</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15846,7 +15867,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 33011-2023</t>
+          <t>A 52797-2021</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15860,10 +15881,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45125</v>
+        <v>44467</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15876,7 +15897,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15919,7 +15940,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 35699-2026</t>
+          <t>A 8259-2025</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15929,14 +15950,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46265</v>
+        <v>45708</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15948,13 +15969,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I189" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15997,7 +16013,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 51344-2023</t>
+          <t>A 53620-2024</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -16011,10 +16027,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45219</v>
+        <v>45614</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16026,13 +16042,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I190" t="n">
-        <v>4.5</v>
+        <v>0.7</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -16075,7 +16086,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 10515-2023</t>
+          <t>A 35930-2023</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -16089,10 +16100,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>44987</v>
+        <v>45148</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16104,8 +16115,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I191" t="n">
-        <v>1.9</v>
+        <v>5.2</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -16148,7 +16164,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 36374-2026</t>
+          <t>A 47196-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -16162,10 +16178,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46268</v>
+        <v>45196</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16177,13 +16193,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I192" t="n">
-        <v>1.6</v>
+        <v>5.9</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -16226,7 +16237,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 39337-2022</t>
+          <t>A 53618-2024</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -16240,10 +16251,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>44817</v>
+        <v>45614</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16256,7 +16267,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1.5</v>
+        <v>10.1</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -16299,7 +16310,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 53620-2024</t>
+          <t>A 58388-2024</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -16313,10 +16324,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45614</v>
+        <v>45633</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16329,7 +16340,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>0.7</v>
+        <v>5.8</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -16372,7 +16383,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 37089-2026</t>
+          <t>A 47201-2023</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16386,10 +16397,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46273</v>
+        <v>45196</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16402,7 +16413,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>15.8</v>
+        <v>2.7</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -16445,7 +16456,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 13501-2025</t>
+          <t>A 52828-2024</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16459,10 +16470,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45736</v>
+        <v>45610</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16475,7 +16486,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>3.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16518,7 +16529,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 10404-2022</t>
+          <t>A 17243-2024</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16532,10 +16543,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>44623</v>
+        <v>45414</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16548,7 +16559,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>1</v>
+        <v>3.2</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16591,7 +16602,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 38043-2026</t>
+          <t>A 59938-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16605,10 +16616,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46280</v>
+        <v>45257</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16620,13 +16631,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I198" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16669,7 +16675,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 38020-2026</t>
+          <t>A 38742-2023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16679,14 +16685,14 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46280</v>
+        <v>45161</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16700,11 +16706,11 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I199" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16747,7 +16753,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 38742-2023</t>
+          <t>A 3735-2024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16757,14 +16763,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45161</v>
+        <v>45321</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16782,7 +16788,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>4.2</v>
+        <v>1.6</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16825,7 +16831,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 3735-2024</t>
+          <t>A 23308-2025</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16839,10 +16845,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45321</v>
+        <v>45791</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16854,13 +16860,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I201" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16903,7 +16904,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 23308-2025</t>
+          <t>A 27498-2025</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16917,10 +16918,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45791</v>
+        <v>45813</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16933,7 +16934,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16993,7 +16994,7 @@
         <v>45953</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>

--- a/Översikt KARLSKOGA.xlsx
+++ b/Översikt KARLSKOGA.xlsx
@@ -601,7 +601,7 @@
         <v>45562</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>45958</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         <v>45989</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>44510</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>46100</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>45989</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1303,10 +1303,10 @@
         <v>10</v>
       </c>
       <c r="T7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="U7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>44473</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1477,75 +1477,425 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
+          <t>A 63185-2025</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>46010</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>KARLSKOGA</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="J9" t="n">
+        <v>7</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>4</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>4</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>8</v>
+      </c>
+      <c r="T9" t="n">
+        <v>28</v>
+      </c>
+      <c r="U9" t="n">
+        <v>26</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Duvhök
+Järnsparv
+Mindre hackspett
+Talltita
+Brudborste
+Järpe
+Spillkråka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 63185-2025 artfynd.xlsx", "A 63185-2025")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 63185-2025 karta.png", "A 63185-2025")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 63185-2025 georefererad karta.tif", "A 63185-2025")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 63185-2025 FSC-klagomål.docx", "A 63185-2025")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 63185-2025 FSC-klagomål mail.docx", "A 63185-2025")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 63185-2025 tillsynsbegäran.docx", "A 63185-2025")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 63185-2025 tillsynsbegäran mail.docx", "A 63185-2025")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 63185-2025 prioriterade fågelarter.docx", "A 63185-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>S 3545-2025</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>46010</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>KARLSKOGA</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="J10" t="n">
+        <v>7</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>4</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>8</v>
+      </c>
+      <c r="T10" t="n">
+        <v>28</v>
+      </c>
+      <c r="U10" t="n">
+        <v>26</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Duvhök
+Järnsparv
+Mindre hackspett
+Talltita
+Brudborste
+Järpe
+Spillkråka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/S 3545-2025 artfynd.xlsx", "S 3545-2025")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/S 3545-2025 karta.png", "S 3545-2025")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/S 3545-2025 georefererad karta.tif", "S 3545-2025")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/S 3545-2025 FSC-klagomål.docx", "S 3545-2025")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/S 3545-2025 FSC-klagomål mail.docx", "S 3545-2025")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/S 3545-2025 tillsynsbegäran.docx", "S 3545-2025")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/S 3545-2025 tillsynsbegäran mail.docx", "S 3545-2025")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/S 3545-2025 prioriterade fågelarter.docx", "S 3545-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 60085-2021</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>44495</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>KARLSKOGA</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4</v>
+      </c>
+      <c r="T11" t="n">
+        <v>5</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Citronfingersvamp
+Mörk husmossa
+Svart trolldruva
+Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 60085-2021 artfynd.xlsx", "A 60085-2021")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 60085-2021 karta.png", "A 60085-2021")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 60085-2021 georefererad karta.tif", "A 60085-2021")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 60085-2021 FSC-klagomål.docx", "A 60085-2021")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 60085-2021 FSC-klagomål mail.docx", "A 60085-2021")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 60085-2021 tillsynsbegäran.docx", "A 60085-2021")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 60085-2021 tillsynsbegäran mail.docx", "A 60085-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>A 8803-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
         <v>46066</v>
       </c>
-      <c r="E9" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>KARLSKOGA</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
+      <c r="E12" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>KARLSKOGA</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
         <v>2.7</v>
       </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
         <v>3</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L12" t="n">
         <v>1</v>
       </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
         <v>1</v>
       </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
         <v>4</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T12" t="n">
         <v>8</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Dofttaggsvamp
 Platt fjädermossa
@@ -1553,112 +1903,112 @@
 Trubbfjädermossa</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 8803-2026 artfynd.xlsx", "A 8803-2026")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 8803-2026 karta.png", "A 8803-2026")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 8803-2026 georefererad karta.tif", "A 8803-2026")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 8803-2026 FSC-klagomål.docx", "A 8803-2026")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 8803-2026 FSC-klagomål mail.docx", "A 8803-2026")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 8803-2026 tillsynsbegäran.docx", "A 8803-2026")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 8803-2026 tillsynsbegäran mail.docx", "A 8803-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>A 63187-2025</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
         <v>46010</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>KARLSKOGA</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
+      <c r="E13" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>KARLSKOGA</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I10" t="n">
+      <c r="I13" t="n">
         <v>1.3</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J13" t="n">
         <v>2</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K13" t="n">
         <v>2</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L13" t="n">
         <v>1</v>
       </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>1</v>
       </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
         <v>4</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T13" t="n">
         <v>4</v>
       </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Talltita
 Bronshjon
@@ -1666,224 +2016,116 @@
 Tjäder</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 63187-2025 artfynd.xlsx", "A 63187-2025")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 63187-2025 karta.png", "A 63187-2025")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 63187-2025 georefererad karta.tif", "A 63187-2025")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 63187-2025 FSC-klagomål.docx", "A 63187-2025")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 63187-2025 FSC-klagomål mail.docx", "A 63187-2025")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 63187-2025 tillsynsbegäran.docx", "A 63187-2025")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 63187-2025 tillsynsbegäran mail.docx", "A 63187-2025")</f>
         <v/>
       </c>
-      <c r="AE10">
+      <c r="AE13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 63187-2025 prioriterade fågelarter.docx", "A 63187-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 60085-2021</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>44495</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>KARLSKOGA</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>3</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 20111-2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>46136</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>KARLSKOGA</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="J14" t="n">
         <v>4</v>
       </c>
-      <c r="T11" t="n">
-        <v>5</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Citronfingersvamp
-Mörk husmossa
-Svart trolldruva
-Västlig hakmossa</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 60085-2021 artfynd.xlsx", "A 60085-2021")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 60085-2021 karta.png", "A 60085-2021")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 60085-2021 georefererad karta.tif", "A 60085-2021")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 60085-2021 FSC-klagomål.docx", "A 60085-2021")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 60085-2021 FSC-klagomål mail.docx", "A 60085-2021")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 60085-2021 tillsynsbegäran.docx", "A 60085-2021")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 60085-2021 tillsynsbegäran mail.docx", "A 60085-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 20111-2026</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>46136</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>KARLSKOGA</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="J12" t="n">
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
         <v>4</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>4</v>
-      </c>
-      <c r="T12" t="n">
+      <c r="T14" t="n">
         <v>7</v>
       </c>
-      <c r="U12" t="n">
+      <c r="U14" t="n">
         <v>7</v>
       </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Tjäder
@@ -1891,735 +2133,503 @@
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 20111-2026 artfynd.xlsx", "A 20111-2026")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 20111-2026 karta.png", "A 20111-2026")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 20111-2026 georefererad karta.tif", "A 20111-2026")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 20111-2026 FSC-klagomål.docx", "A 20111-2026")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 20111-2026 FSC-klagomål mail.docx", "A 20111-2026")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 20111-2026 tillsynsbegäran.docx", "A 20111-2026")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 20111-2026 tillsynsbegäran mail.docx", "A 20111-2026")</f>
         <v/>
       </c>
-      <c r="AE12">
+      <c r="AE14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 20111-2026 prioriterade fågelarter.docx", "A 20111-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>A 18428-2026</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
         <v>46127</v>
       </c>
-      <c r="E13" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>KARLSKOGA</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
+      <c r="E15" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>KARLSKOGA</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I13" t="n">
+      <c r="I15" t="n">
         <v>6</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J15" t="n">
         <v>1</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>1</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M15" t="n">
         <v>1</v>
       </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
         <v>2</v>
       </c>
-      <c r="R13" t="n">
+      <c r="R15" t="n">
         <v>1</v>
       </c>
-      <c r="S13" t="n">
+      <c r="S15" t="n">
         <v>3</v>
       </c>
-      <c r="T13" t="n">
+      <c r="T15" t="n">
         <v>17</v>
       </c>
-      <c r="U13" t="n">
+      <c r="U15" t="n">
         <v>17</v>
       </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Skuggblåslav
 Tjäder</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 18428-2026 artfynd.xlsx", "A 18428-2026")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 18428-2026 karta.png", "A 18428-2026")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 18428-2026 georefererad karta.tif", "A 18428-2026")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 18428-2026 FSC-klagomål.docx", "A 18428-2026")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 18428-2026 FSC-klagomål mail.docx", "A 18428-2026")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 18428-2026 tillsynsbegäran.docx", "A 18428-2026")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 18428-2026 tillsynsbegäran mail.docx", "A 18428-2026")</f>
         <v/>
       </c>
-      <c r="AE13">
+      <c r="AE15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 18428-2026 prioriterade fågelarter.docx", "A 18428-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>A 35696-2026</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
         <is>
           <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
-      <c r="D14" s="1" t="n">
+      <c r="D16" s="1" t="n">
         <v>46265</v>
       </c>
-      <c r="E14" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>KARLSKOGA</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
+      <c r="E16" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>KARLSKOGA</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I14" t="n">
+      <c r="I16" t="n">
         <v>4.6</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J16" t="n">
         <v>2</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K16" t="n">
         <v>1</v>
       </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
         <v>3</v>
       </c>
-      <c r="T14" t="n">
+      <c r="T16" t="n">
         <v>4</v>
       </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Grönpyrola
 Mattlummer
 Revlummer</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 35696-2026 artfynd.xlsx", "A 35696-2026")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 35696-2026 karta.png", "A 35696-2026")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 35696-2026 georefererad karta.tif", "A 35696-2026")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 35696-2026 FSC-klagomål.docx", "A 35696-2026")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 35696-2026 FSC-klagomål mail.docx", "A 35696-2026")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 35696-2026 tillsynsbegäran.docx", "A 35696-2026")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 35696-2026 tillsynsbegäran mail.docx", "A 35696-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 63185-2025</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>46010</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>KARLSKOGA</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 20108-2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>46136</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>KARLSKOGA</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I15" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="J15" t="n">
+      <c r="I17" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
         <v>2</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
+      <c r="R17" t="n">
         <v>1</v>
       </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
+      <c r="S17" t="n">
+        <v>3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>5</v>
+      </c>
+      <c r="U17" t="n">
+        <v>5</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Talltita
+Vedticka</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 20108-2026 artfynd.xlsx", "A 20108-2026")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 20108-2026 karta.png", "A 20108-2026")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 20108-2026 georefererad karta.tif", "A 20108-2026")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 20108-2026 FSC-klagomål.docx", "A 20108-2026")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 20108-2026 FSC-klagomål mail.docx", "A 20108-2026")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 20108-2026 tillsynsbegäran.docx", "A 20108-2026")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 20108-2026 tillsynsbegäran mail.docx", "A 20108-2026")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 20108-2026 prioriterade fågelarter.docx", "A 20108-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 20112-2026</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>46136</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>KARLSKOGA</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
         <v>1</v>
       </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
         <v>3</v>
       </c>
-      <c r="T15" t="n">
-        <v>13</v>
-      </c>
-      <c r="U15" t="n">
-        <v>11</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Talltita
-Brudborste
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 63185-2025 artfynd.xlsx", "A 63185-2025")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 63185-2025 karta.png", "A 63185-2025")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 63185-2025 georefererad karta.tif", "A 63185-2025")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 63185-2025 FSC-klagomål.docx", "A 63185-2025")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 63185-2025 FSC-klagomål mail.docx", "A 63185-2025")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 63185-2025 tillsynsbegäran.docx", "A 63185-2025")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 63185-2025 tillsynsbegäran mail.docx", "A 63185-2025")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 63185-2025 prioriterade fågelarter.docx", "A 63185-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 20112-2026</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>46136</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>KARLSKOGA</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J16" t="n">
-        <v>3</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3</v>
-      </c>
-      <c r="T16" t="n">
+      <c r="T18" t="n">
         <v>4</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U18" t="n">
         <v>4</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Tretåig hackspett
 Spillkråka
 Tofsmes</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 20112-2026 artfynd.xlsx", "A 20112-2026")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 20112-2026 karta.png", "A 20112-2026")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 20112-2026 georefererad karta.tif", "A 20112-2026")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 20112-2026 FSC-klagomål.docx", "A 20112-2026")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 20112-2026 FSC-klagomål mail.docx", "A 20112-2026")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 20112-2026 tillsynsbegäran.docx", "A 20112-2026")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 20112-2026 tillsynsbegäran mail.docx", "A 20112-2026")</f>
         <v/>
       </c>
-      <c r="AE16">
+      <c r="AE18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 20112-2026 prioriterade fågelarter.docx", "A 20112-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 20108-2026</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>46136</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>KARLSKOGA</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>5</v>
-      </c>
-      <c r="U17" t="n">
-        <v>5</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Talltita
-Vedticka</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 20108-2026 artfynd.xlsx", "A 20108-2026")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 20108-2026 karta.png", "A 20108-2026")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 20108-2026 georefererad karta.tif", "A 20108-2026")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 20108-2026 FSC-klagomål.docx", "A 20108-2026")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 20108-2026 FSC-klagomål mail.docx", "A 20108-2026")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 20108-2026 tillsynsbegäran.docx", "A 20108-2026")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 20108-2026 tillsynsbegäran mail.docx", "A 20108-2026")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 20108-2026 prioriterade fågelarter.docx", "A 20108-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>S 3545-2025</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>46010</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>KARLSKOGA</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>13</v>
-      </c>
-      <c r="U18" t="n">
-        <v>11</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Talltita
-Brudborste
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/S 3545-2025 artfynd.xlsx", "S 3545-2025")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/S 3545-2025 karta.png", "S 3545-2025")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/S 3545-2025 georefererad karta.tif", "S 3545-2025")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/S 3545-2025 FSC-klagomål.docx", "S 3545-2025")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/S 3545-2025 FSC-klagomål mail.docx", "S 3545-2025")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/S 3545-2025 tillsynsbegäran.docx", "S 3545-2025")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/S 3545-2025 tillsynsbegäran mail.docx", "S 3545-2025")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/S 3545-2025 prioriterade fågelarter.docx", "S 3545-2025")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 39936-2024</t>
+          <t>A 39025-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2633,10 +2643,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45553</v>
+        <v>44817</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2648,11 +2658,16 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>6.4</v>
+        <v>3.2</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -2682,165 +2697,160 @@
         <v>2</v>
       </c>
       <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Talltita
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 39025-2022 artfynd.xlsx", "A 39025-2022")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 39025-2022 karta.png", "A 39025-2022")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 39025-2022 georefererad karta.tif", "A 39025-2022")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 39025-2022 FSC-klagomål.docx", "A 39025-2022")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 39025-2022 FSC-klagomål mail.docx", "A 39025-2022")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 39025-2022 tillsynsbegäran.docx", "A 39025-2022")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 39025-2022 tillsynsbegäran mail.docx", "A 39025-2022")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 39025-2022 prioriterade fågelarter.docx", "A 39025-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 39936-2024</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>45553</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>KARLSKOGA</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2</v>
+      </c>
+      <c r="T20" t="n">
         <v>3</v>
       </c>
-      <c r="U19" t="n">
+      <c r="U20" t="n">
         <v>1</v>
       </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Storgröe
 Utter</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 39936-2024 artfynd.xlsx", "A 39936-2024")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 39936-2024 karta.png", "A 39936-2024")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 39936-2024 georefererad karta.tif", "A 39936-2024")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 39936-2024 FSC-klagomål.docx", "A 39936-2024")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 39936-2024 FSC-klagomål mail.docx", "A 39936-2024")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 39936-2024 tillsynsbegäran.docx", "A 39936-2024")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 39936-2024 tillsynsbegäran mail.docx", "A 39936-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 39025-2022</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>44817</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>KARLSKOGA</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Talltita
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 39025-2022 artfynd.xlsx", "A 39025-2022")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 39025-2022 karta.png", "A 39025-2022")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 39025-2022 georefererad karta.tif", "A 39025-2022")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 39025-2022 FSC-klagomål.docx", "A 39025-2022")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 39025-2022 FSC-klagomål mail.docx", "A 39025-2022")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 39025-2022 tillsynsbegäran.docx", "A 39025-2022")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 39025-2022 tillsynsbegäran mail.docx", "A 39025-2022")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 39025-2022 prioriterade fågelarter.docx", "A 39025-2022")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 58091-2022</t>
+          <t>A 21019-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2854,10 +2864,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44900</v>
+        <v>46145</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2875,7 +2885,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.1</v>
+        <v>4.7</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2908,49 +2918,49 @@
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Hårklomossa</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 58091-2022 artfynd.xlsx", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 21019-2026 artfynd.xlsx", "A 21019-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 58091-2022 karta.png", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 21019-2026 karta.png", "A 21019-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 58091-2022 georefererad karta.tif", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 21019-2026 georefererad karta.tif", "A 21019-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 58091-2022 FSC-klagomål.docx", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 21019-2026 FSC-klagomål.docx", "A 21019-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 58091-2022 FSC-klagomål mail.docx", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 21019-2026 FSC-klagomål mail.docx", "A 21019-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 58091-2022 tillsynsbegäran.docx", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 21019-2026 tillsynsbegäran.docx", "A 21019-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 58091-2022 tillsynsbegäran mail.docx", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 21019-2026 tillsynsbegäran mail.docx", "A 21019-2026")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 28566-2024</t>
+          <t>A 52377-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2964,10 +2974,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45478</v>
+        <v>45953</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2979,8 +2989,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -3020,42 +3035,42 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 28566-2024 artfynd.xlsx", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 52377-2025 artfynd.xlsx", "A 52377-2025")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 28566-2024 karta.png", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 52377-2025 karta.png", "A 52377-2025")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 28566-2024 georefererad karta.tif", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 52377-2025 georefererad karta.tif", "A 52377-2025")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 28566-2024 FSC-klagomål.docx", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 52377-2025 FSC-klagomål.docx", "A 52377-2025")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 28566-2024 FSC-klagomål mail.docx", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 52377-2025 FSC-klagomål mail.docx", "A 52377-2025")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 28566-2024 tillsynsbegäran.docx", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 52377-2025 tillsynsbegäran.docx", "A 52377-2025")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 28566-2024 tillsynsbegäran mail.docx", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 52377-2025 tillsynsbegäran mail.docx", "A 52377-2025")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 63188-2025</t>
+          <t>A 28474-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3069,10 +3084,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46010</v>
+        <v>45103</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3084,13 +3099,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>1.1</v>
+        <v>5.1</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -3123,53 +3133,53 @@
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåhake</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 63188-2025 artfynd.xlsx", "A 63188-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 28474-2023 artfynd.xlsx", "A 28474-2023")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 63188-2025 karta.png", "A 63188-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 28474-2023 karta.png", "A 28474-2023")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 63188-2025 georefererad karta.tif", "A 63188-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 28474-2023 georefererad karta.tif", "A 28474-2023")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 63188-2025 FSC-klagomål.docx", "A 63188-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 28474-2023 FSC-klagomål.docx", "A 28474-2023")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 63188-2025 FSC-klagomål mail.docx", "A 63188-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 28474-2023 FSC-klagomål mail.docx", "A 28474-2023")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 63188-2025 tillsynsbegäran.docx", "A 63188-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 28474-2023 tillsynsbegäran.docx", "A 28474-2023")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 63188-2025 tillsynsbegäran mail.docx", "A 63188-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 28474-2023 tillsynsbegäran mail.docx", "A 28474-2023")</f>
         <v/>
       </c>
       <c r="AE23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 63188-2025 prioriterade fågelarter.docx", "A 63188-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 28474-2023 prioriterade fågelarter.docx", "A 28474-2023")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 16784-2026</t>
+          <t>A 58091-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3183,10 +3193,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46113</v>
+        <v>44900</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3204,7 +3214,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3248,38 +3258,38 @@
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 16784-2026 artfynd.xlsx", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 58091-2022 artfynd.xlsx", "A 58091-2022")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 16784-2026 karta.png", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 58091-2022 karta.png", "A 58091-2022")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 16784-2026 georefererad karta.tif", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 58091-2022 georefererad karta.tif", "A 58091-2022")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 16784-2026 FSC-klagomål.docx", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 58091-2022 FSC-klagomål.docx", "A 58091-2022")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 16784-2026 FSC-klagomål mail.docx", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 58091-2022 FSC-klagomål mail.docx", "A 58091-2022")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 16784-2026 tillsynsbegäran.docx", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 58091-2022 tillsynsbegäran.docx", "A 58091-2022")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 16784-2026 tillsynsbegäran mail.docx", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 58091-2022 tillsynsbegäran mail.docx", "A 58091-2022")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 18427-2026</t>
+          <t>A 25093-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3293,10 +3303,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46127</v>
+        <v>46175</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3314,13 +3324,13 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
         <v>1</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -3354,46 +3364,42 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 18427-2026 artfynd.xlsx", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 25093-2026 artfynd.xlsx", "A 25093-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 18427-2026 karta.png", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 25093-2026 karta.png", "A 25093-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 18427-2026 georefererad karta.tif", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 25093-2026 georefererad karta.tif", "A 25093-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 18427-2026 FSC-klagomål.docx", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 25093-2026 FSC-klagomål.docx", "A 25093-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 18427-2026 FSC-klagomål mail.docx", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 25093-2026 FSC-klagomål mail.docx", "A 25093-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 18427-2026 tillsynsbegäran.docx", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 25093-2026 tillsynsbegäran.docx", "A 25093-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 18427-2026 tillsynsbegäran mail.docx", "A 18427-2026")</f>
-        <v/>
-      </c>
-      <c r="AE25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 18427-2026 prioriterade fågelarter.docx", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 25093-2026 tillsynsbegäran mail.docx", "A 25093-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 19233-2026</t>
+          <t>A 28566-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3407,10 +3413,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46132</v>
+        <v>45478</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3423,13 +3429,13 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -3459,46 +3465,46 @@
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 19233-2026 artfynd.xlsx", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 28566-2024 artfynd.xlsx", "A 28566-2024")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 19233-2026 karta.png", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 28566-2024 karta.png", "A 28566-2024")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 19233-2026 georefererad karta.tif", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 28566-2024 georefererad karta.tif", "A 28566-2024")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 19233-2026 FSC-klagomål.docx", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 28566-2024 FSC-klagomål.docx", "A 28566-2024")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 19233-2026 FSC-klagomål mail.docx", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 28566-2024 FSC-klagomål mail.docx", "A 28566-2024")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 19233-2026 tillsynsbegäran.docx", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 28566-2024 tillsynsbegäran.docx", "A 28566-2024")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 19233-2026 tillsynsbegäran mail.docx", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 28566-2024 tillsynsbegäran mail.docx", "A 28566-2024")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 21019-2026</t>
+          <t>A 63188-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3512,10 +3518,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46145</v>
+        <v>46010</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3533,7 +3539,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>4.7</v>
+        <v>1.1</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
@@ -3542,7 +3548,7 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -3557,7 +3563,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -3566,49 +3572,53 @@
         <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 21019-2026 artfynd.xlsx", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 63188-2025 artfynd.xlsx", "A 63188-2025")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 21019-2026 karta.png", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 63188-2025 karta.png", "A 63188-2025")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 21019-2026 georefererad karta.tif", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 63188-2025 georefererad karta.tif", "A 63188-2025")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 21019-2026 FSC-klagomål.docx", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 63188-2025 FSC-klagomål.docx", "A 63188-2025")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 21019-2026 FSC-klagomål mail.docx", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 63188-2025 FSC-klagomål mail.docx", "A 63188-2025")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 21019-2026 tillsynsbegäran.docx", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 63188-2025 tillsynsbegäran.docx", "A 63188-2025")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 21019-2026 tillsynsbegäran mail.docx", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 63188-2025 tillsynsbegäran mail.docx", "A 63188-2025")</f>
+        <v/>
+      </c>
+      <c r="AE27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 63188-2025 prioriterade fågelarter.docx", "A 63188-2025")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 25093-2026</t>
+          <t>A 16784-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3622,10 +3632,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46175</v>
+        <v>46113</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3643,13 +3653,13 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -3676,49 +3686,49 @@
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Hårklomossa</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 25093-2026 artfynd.xlsx", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 16784-2026 artfynd.xlsx", "A 16784-2026")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 25093-2026 karta.png", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 16784-2026 karta.png", "A 16784-2026")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 25093-2026 georefererad karta.tif", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 16784-2026 georefererad karta.tif", "A 16784-2026")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 25093-2026 FSC-klagomål.docx", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 16784-2026 FSC-klagomål.docx", "A 16784-2026")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 25093-2026 FSC-klagomål mail.docx", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 16784-2026 FSC-klagomål mail.docx", "A 16784-2026")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 25093-2026 tillsynsbegäran.docx", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 16784-2026 tillsynsbegäran.docx", "A 16784-2026")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 25093-2026 tillsynsbegäran mail.docx", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 16784-2026 tillsynsbegäran mail.docx", "A 16784-2026")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 52377-2025</t>
+          <t>A 18427-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3732,10 +3742,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45953</v>
+        <v>46127</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3753,7 +3763,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -3793,42 +3803,46 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 52377-2025 artfynd.xlsx", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 18427-2026 artfynd.xlsx", "A 18427-2026")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 52377-2025 karta.png", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 18427-2026 karta.png", "A 18427-2026")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 52377-2025 georefererad karta.tif", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 18427-2026 georefererad karta.tif", "A 18427-2026")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 52377-2025 FSC-klagomål.docx", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 18427-2026 FSC-klagomål.docx", "A 18427-2026")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 52377-2025 FSC-klagomål mail.docx", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 18427-2026 FSC-klagomål mail.docx", "A 18427-2026")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 52377-2025 tillsynsbegäran.docx", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 18427-2026 tillsynsbegäran.docx", "A 18427-2026")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 52377-2025 tillsynsbegäran mail.docx", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 18427-2026 tillsynsbegäran mail.docx", "A 18427-2026")</f>
+        <v/>
+      </c>
+      <c r="AE29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 18427-2026 prioriterade fågelarter.docx", "A 18427-2026")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 28474-2023</t>
+          <t>A 19233-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3842,10 +3856,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45103</v>
+        <v>46132</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3858,16 +3872,16 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>5.1</v>
+        <v>1.6</v>
       </c>
       <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
         <v>1</v>
       </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
       <c r="L30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -3882,7 +3896,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -3894,50 +3908,46 @@
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Blåhake</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 28474-2023 artfynd.xlsx", "A 28474-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 19233-2026 artfynd.xlsx", "A 19233-2026")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 28474-2023 karta.png", "A 28474-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 19233-2026 karta.png", "A 19233-2026")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 28474-2023 georefererad karta.tif", "A 28474-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 19233-2026 georefererad karta.tif", "A 19233-2026")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 28474-2023 FSC-klagomål.docx", "A 28474-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 19233-2026 FSC-klagomål.docx", "A 19233-2026")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 28474-2023 FSC-klagomål mail.docx", "A 28474-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 19233-2026 FSC-klagomål mail.docx", "A 19233-2026")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 28474-2023 tillsynsbegäran.docx", "A 28474-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 19233-2026 tillsynsbegäran.docx", "A 19233-2026")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 28474-2023 tillsynsbegäran mail.docx", "A 28474-2023")</f>
-        <v/>
-      </c>
-      <c r="AE30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 28474-2023 prioriterade fågelarter.docx", "A 28474-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 19233-2026 tillsynsbegäran mail.docx", "A 19233-2026")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 30915-2026</t>
+          <t>A 40528-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3951,10 +3961,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46213</v>
+        <v>45555</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3966,13 +3976,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>8.9</v>
+        <v>2.8</v>
       </c>
       <c r="J31" t="n">
         <v>1</v>
@@ -4008,46 +4013,46 @@
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 30915-2026 artfynd.xlsx", "A 30915-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 40528-2024 artfynd.xlsx", "A 40528-2024")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 30915-2026 karta.png", "A 30915-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 40528-2024 karta.png", "A 40528-2024")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 30915-2026 georefererad karta.tif", "A 30915-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 40528-2024 georefererad karta.tif", "A 40528-2024")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 30915-2026 FSC-klagomål.docx", "A 30915-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 40528-2024 FSC-klagomål.docx", "A 40528-2024")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 30915-2026 FSC-klagomål mail.docx", "A 30915-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 40528-2024 FSC-klagomål mail.docx", "A 40528-2024")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 30915-2026 tillsynsbegäran.docx", "A 30915-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 40528-2024 tillsynsbegäran.docx", "A 40528-2024")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 30915-2026 tillsynsbegäran mail.docx", "A 30915-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 40528-2024 tillsynsbegäran mail.docx", "A 40528-2024")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 35199-2026</t>
+          <t>A 30915-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4061,10 +4066,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46260</v>
+        <v>46213</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4082,7 +4087,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>5.6</v>
+        <v>8.9</v>
       </c>
       <c r="J32" t="n">
         <v>1</v>
@@ -4091,7 +4096,7 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -4106,7 +4111,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -4122,42 +4127,42 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 35199-2026 artfynd.xlsx", "A 35199-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 30915-2026 artfynd.xlsx", "A 30915-2026")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 35199-2026 karta.png", "A 35199-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 30915-2026 karta.png", "A 30915-2026")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 35199-2026 georefererad karta.tif", "A 35199-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 30915-2026 georefererad karta.tif", "A 30915-2026")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 35199-2026 FSC-klagomål.docx", "A 35199-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 30915-2026 FSC-klagomål.docx", "A 30915-2026")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 35199-2026 FSC-klagomål mail.docx", "A 35199-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 30915-2026 FSC-klagomål mail.docx", "A 30915-2026")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 35199-2026 tillsynsbegäran.docx", "A 35199-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 30915-2026 tillsynsbegäran.docx", "A 30915-2026")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 35199-2026 tillsynsbegäran mail.docx", "A 35199-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 30915-2026 tillsynsbegäran mail.docx", "A 30915-2026")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 40528-2024</t>
+          <t>A 35199-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4171,10 +4176,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45555</v>
+        <v>46260</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4186,8 +4191,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>2.8</v>
+        <v>5.6</v>
       </c>
       <c r="J33" t="n">
         <v>1</v>
@@ -4196,7 +4206,7 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -4211,7 +4221,7 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -4223,39 +4233,39 @@
         <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 40528-2024 artfynd.xlsx", "A 40528-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 35199-2026 artfynd.xlsx", "A 35199-2026")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 40528-2024 karta.png", "A 40528-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 35199-2026 karta.png", "A 35199-2026")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 40528-2024 georefererad karta.tif", "A 40528-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 35199-2026 georefererad karta.tif", "A 35199-2026")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 40528-2024 FSC-klagomål.docx", "A 40528-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 35199-2026 FSC-klagomål.docx", "A 35199-2026")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 40528-2024 FSC-klagomål mail.docx", "A 40528-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 35199-2026 FSC-klagomål mail.docx", "A 35199-2026")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 40528-2024 tillsynsbegäran.docx", "A 40528-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 35199-2026 tillsynsbegäran.docx", "A 35199-2026")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 40528-2024 tillsynsbegäran mail.docx", "A 40528-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 35199-2026 tillsynsbegäran mail.docx", "A 35199-2026")</f>
         <v/>
       </c>
     </row>
@@ -4279,7 +4289,7 @@
         <v>46280</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4393,7 +4403,7 @@
         <v>46136</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4503,7 +4513,7 @@
         <v>44546</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4576,7 +4586,7 @@
         <v>44732</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4649,7 +4659,7 @@
         <v>44460</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4722,7 +4732,7 @@
         <v>44512</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4800,7 +4810,7 @@
         <v>44715</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4873,7 +4883,7 @@
         <v>44508</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4951,7 +4961,7 @@
         <v>44480</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5024,7 +5034,7 @@
         <v>44809</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5097,7 +5107,7 @@
         <v>44811</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5170,7 +5180,7 @@
         <v>44628</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5248,7 +5258,7 @@
         <v>44809</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5321,7 +5331,7 @@
         <v>44706</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5394,7 +5404,7 @@
         <v>44706</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5467,7 +5477,7 @@
         <v>44817</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5528,7 +5538,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 8803-2025</t>
+          <t>A 58390-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5542,10 +5552,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45712</v>
+        <v>45633</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5558,7 +5568,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5601,7 +5611,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 35445-2024</t>
+          <t>A 4164-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5615,10 +5625,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45531</v>
+        <v>44588</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5630,8 +5640,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5674,7 +5689,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 39337-2022</t>
+          <t>A 9712-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5688,10 +5703,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44817</v>
+        <v>45362</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5703,8 +5718,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5747,7 +5767,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 56887-2022</t>
+          <t>A 42804-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5757,14 +5777,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44894</v>
+        <v>45182</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5776,8 +5796,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5820,7 +5845,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 20289-2024</t>
+          <t>A 9510-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5834,10 +5859,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45435</v>
+        <v>44981</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5849,13 +5874,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5898,7 +5918,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 38190-2024</t>
+          <t>A 1309-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5912,10 +5932,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45545</v>
+        <v>45303</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5928,7 +5948,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5971,7 +5991,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 38196-2024</t>
+          <t>A 35471-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5985,10 +6005,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45545</v>
+        <v>45531</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6001,7 +6021,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -6044,7 +6064,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 9712-2024</t>
+          <t>A 35444-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6058,10 +6078,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45362</v>
+        <v>45531</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6073,13 +6093,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6122,7 +6137,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 15256-2025</t>
+          <t>A 23263-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6136,10 +6151,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45744</v>
+        <v>44720</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6151,13 +6166,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>5.5</v>
+        <v>2.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6200,7 +6210,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 43075-2023</t>
+          <t>A 47201-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6214,10 +6224,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45182</v>
+        <v>45196</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6230,7 +6240,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6273,7 +6283,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 23263-2022</t>
+          <t>A 61396-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6287,10 +6297,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44720</v>
+        <v>45264</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6303,7 +6313,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6346,7 +6356,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 4058-2022</t>
+          <t>A 8259-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6360,10 +6370,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44588</v>
+        <v>45708</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6376,7 +6386,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6419,7 +6429,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 35444-2024</t>
+          <t>A 24116-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6433,10 +6443,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45531</v>
+        <v>45456</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6449,7 +6459,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6492,7 +6502,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 35471-2024</t>
+          <t>A 35930-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6506,10 +6516,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45531</v>
+        <v>45148</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6521,8 +6531,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>0.5</v>
+        <v>5.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6565,7 +6580,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 54680-2021</t>
+          <t>A 63863-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6579,10 +6594,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44473</v>
+        <v>45278</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6595,7 +6610,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6638,7 +6653,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 30102-2025</t>
+          <t>A 59938-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6652,10 +6667,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45826</v>
+        <v>45257</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6668,7 +6683,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6711,7 +6726,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 53647-2023</t>
+          <t>A 52828-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6725,10 +6740,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45230</v>
+        <v>45610</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6741,7 +6756,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6784,7 +6799,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 23620-2024</t>
+          <t>A 15256-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6798,10 +6813,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45454</v>
+        <v>45744</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6813,8 +6828,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>2.2</v>
+        <v>5.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6857,7 +6877,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 58390-2024</t>
+          <t>A 24115-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6871,10 +6891,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45633</v>
+        <v>45456</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6887,7 +6907,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6930,7 +6950,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 9917-2026</t>
+          <t>A 18768-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6944,10 +6964,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46073</v>
+        <v>45764</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6959,8 +6979,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>3.1</v>
+        <v>0.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7003,7 +7028,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 31397-2025</t>
+          <t>A 4801-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7017,10 +7042,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45833</v>
+        <v>45328</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7033,7 +7058,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7076,7 +7101,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 32287-2025</t>
+          <t>A 4802-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7090,10 +7115,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45835</v>
+        <v>45328</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7105,13 +7130,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>10.9</v>
+        <v>0.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7154,7 +7174,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 18768-2025</t>
+          <t>A 8990-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7168,10 +7188,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45764</v>
+        <v>44979</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7183,13 +7203,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7232,7 +7247,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 42803-2023</t>
+          <t>A 42802-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7249,7 +7264,7 @@
         <v>45182</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7267,7 +7282,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7310,7 +7325,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 24255-2024</t>
+          <t>A 6835-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7324,10 +7339,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45457</v>
+        <v>45700</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7340,7 +7355,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7383,7 +7398,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 13473-2026</t>
+          <t>A 28471-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7397,10 +7412,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46094</v>
+        <v>45103</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7413,7 +7428,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7456,7 +7471,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 14580-2026</t>
+          <t>A 22867-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7470,10 +7485,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46101</v>
+        <v>44715</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7485,13 +7500,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7534,7 +7544,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 20086-2024</t>
+          <t>A 64060-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7544,14 +7554,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45434</v>
+        <v>45279</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7564,7 +7574,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7607,7 +7617,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 12897-2026</t>
+          <t>A 24255-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7621,10 +7631,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46092</v>
+        <v>45457</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7637,7 +7647,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7680,7 +7690,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 9510-2023</t>
+          <t>A 48707-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7694,10 +7704,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44981</v>
+        <v>45593</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7710,7 +7720,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.9</v>
+        <v>6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7753,7 +7763,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 16782-2026</t>
+          <t>A 17815-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7767,10 +7777,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46113</v>
+        <v>45758</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7788,7 +7798,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7831,7 +7841,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 16783-2026</t>
+          <t>A 21210-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7845,10 +7855,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46113</v>
+        <v>45779</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7866,7 +7876,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7909,7 +7919,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 16787-2026</t>
+          <t>A 23717-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7923,10 +7933,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46113</v>
+        <v>45793</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7938,13 +7948,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7987,7 +7992,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 17815-2025</t>
+          <t>A 55832-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8001,10 +8006,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45758</v>
+        <v>45239</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8016,13 +8021,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8065,7 +8065,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 15060-2026</t>
+          <t>A 58388-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8079,10 +8079,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46104</v>
+        <v>45633</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8095,7 +8095,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>11.5</v>
+        <v>5.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8138,7 +8138,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 15058-2026</t>
+          <t>A 18978-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8152,10 +8152,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46104</v>
+        <v>45764</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8168,7 +8168,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>4.3</v>
+        <v>0.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8211,7 +8211,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 17734-2026</t>
+          <t>A 917-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8225,10 +8225,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46122</v>
+        <v>46030</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8240,13 +8240,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8289,7 +8284,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 19011-2026</t>
+          <t>A 44946-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8303,10 +8298,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46130</v>
+        <v>45918</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8318,13 +8313,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8367,7 +8357,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 59025-2024</t>
+          <t>A 44949-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8381,10 +8371,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45636</v>
+        <v>45918</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8396,13 +8386,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8445,7 +8430,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 19010-2026</t>
+          <t>A 31921-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8459,10 +8444,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46130</v>
+        <v>44777</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8474,13 +8459,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8523,7 +8503,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 19009-2026</t>
+          <t>A 43075-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8537,10 +8517,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46130</v>
+        <v>45182</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8552,13 +8532,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>6.3</v>
+        <v>3.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8601,7 +8576,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 19008-2026</t>
+          <t>A 47196-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8615,10 +8590,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46130</v>
+        <v>45196</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8630,13 +8605,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>1.9</v>
+        <v>5.9</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8679,7 +8649,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 19663-2026</t>
+          <t>A 13454-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8693,10 +8663,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46134</v>
+        <v>44645</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8708,13 +8678,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8757,7 +8722,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 13501-2025</t>
+          <t>A 53618-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8771,10 +8736,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45736</v>
+        <v>45614</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8787,7 +8752,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>3.2</v>
+        <v>10.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8830,7 +8795,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 47094-2023</t>
+          <t>A 21253-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8844,10 +8809,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45196</v>
+        <v>46147</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8860,7 +8825,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.9</v>
+        <v>3.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8903,7 +8868,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 31921-2022</t>
+          <t>A 30961-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8917,10 +8882,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44777</v>
+        <v>44768</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8932,8 +8897,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I95" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8976,7 +8946,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 42804-2023</t>
+          <t>A 21257-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8986,14 +8956,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45182</v>
+        <v>46147</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9005,13 +8975,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I96" t="n">
-        <v>0.6</v>
+        <v>2.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9054,7 +9019,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 39030-2022</t>
+          <t>A 42803-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9064,14 +9029,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44817</v>
+        <v>45182</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9089,7 +9054,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9132,7 +9097,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 6835-2025</t>
+          <t>A 8803-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9146,10 +9111,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45700</v>
+        <v>45712</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9162,7 +9127,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9205,7 +9170,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 8244-2025</t>
+          <t>A 50958-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9219,10 +9184,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45708</v>
+        <v>45946</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9235,7 +9200,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9278,7 +9243,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 44946-2025</t>
+          <t>A 56313-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9292,10 +9257,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45918</v>
+        <v>45624</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9307,8 +9272,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I100" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9351,7 +9321,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 44949-2025</t>
+          <t>A 10743-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9365,10 +9335,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45918</v>
+        <v>44988</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9380,8 +9350,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9424,7 +9399,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 28100-2024</t>
+          <t>A 14215-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9438,10 +9413,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45476</v>
+        <v>45393</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9453,8 +9428,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>1.8</v>
+        <v>4.2</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9497,7 +9477,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 51344-2023</t>
+          <t>A 55191-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9511,10 +9491,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45219</v>
+        <v>45237</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9526,13 +9506,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I103" t="n">
-        <v>4.5</v>
+        <v>1.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9575,7 +9550,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 21210-2025</t>
+          <t>A 59025-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9589,10 +9564,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45779</v>
+        <v>45636</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9606,11 +9581,11 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9653,7 +9628,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 23717-2025</t>
+          <t>A 55025-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9667,10 +9642,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45793</v>
+        <v>45967</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9683,7 +9658,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9726,7 +9701,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 917-2026</t>
+          <t>A 3227-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9740,10 +9715,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46030</v>
+        <v>45679</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9756,7 +9731,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9799,7 +9774,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 20463-2025</t>
+          <t>A 17243-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9813,10 +9788,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45775</v>
+        <v>45414</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9828,13 +9803,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>0.9</v>
+        <v>3.2</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9877,7 +9847,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 28471-2023</t>
+          <t>A 35060-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9891,10 +9861,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45103</v>
+        <v>45527</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9906,8 +9876,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I108" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9950,7 +9925,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 16881-2023</t>
+          <t>A 59522-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9960,14 +9935,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45033</v>
+        <v>45989</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9981,11 +9956,11 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10028,7 +10003,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 61396-2023</t>
+          <t>A 52826-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10042,10 +10017,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45264</v>
+        <v>45610</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10058,7 +10033,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10101,7 +10076,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 21253-2026</t>
+          <t>A 52829-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10115,10 +10090,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46147</v>
+        <v>45610</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10131,7 +10106,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10174,7 +10149,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 21257-2026</t>
+          <t>A 11974-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10188,10 +10163,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46147</v>
+        <v>45728</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10204,7 +10179,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10247,7 +10222,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 4164-2022</t>
+          <t>A 60506-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10261,10 +10236,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44588</v>
+        <v>45995</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10276,13 +10251,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10325,7 +10295,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 61271-2022</t>
+          <t>A 60508-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10339,10 +10309,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44909</v>
+        <v>45995</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10354,13 +10324,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I114" t="n">
-        <v>14.1</v>
+        <v>2.1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10403,7 +10368,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 3227-2025</t>
+          <t>A 60503-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10417,10 +10382,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45679</v>
+        <v>45995</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10433,7 +10398,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>4.5</v>
+        <v>2.2</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10476,7 +10441,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 57422-2021</t>
+          <t>A 61271-2022</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10490,10 +10455,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44483</v>
+        <v>44909</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10505,8 +10470,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I116" t="n">
-        <v>1.2</v>
+        <v>14.1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10549,7 +10519,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 35060-2024</t>
+          <t>A 23754-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10563,10 +10533,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45527</v>
+        <v>46164</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10580,11 +10550,11 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.6</v>
+        <v>12.2</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10627,7 +10597,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 23754-2026</t>
+          <t>A 48168-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10641,10 +10611,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46164</v>
+        <v>45589</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10656,13 +10626,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I118" t="n">
-        <v>12.2</v>
+        <v>5.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10705,7 +10670,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 64060-2023</t>
+          <t>A 61788-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10719,10 +10684,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45279</v>
+        <v>46002</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10734,8 +10699,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I119" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10795,7 +10765,7 @@
         <v>45687</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10851,7 +10821,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 4587-2025</t>
+          <t>A 18955-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10865,10 +10835,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45687</v>
+        <v>45764</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10881,7 +10851,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>3.3</v>
+        <v>8.1</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10924,7 +10894,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 14215-2024</t>
+          <t>A 64066-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10934,14 +10904,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45393</v>
+        <v>46013</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10953,13 +10923,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I122" t="n">
-        <v>4.2</v>
+        <v>1.9</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -11002,7 +10967,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 24666-2026</t>
+          <t>A 50614-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11016,10 +10981,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46171</v>
+        <v>45601</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11032,7 +10997,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>6.1</v>
+        <v>0.7</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -11075,7 +11040,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 25098-2026</t>
+          <t>A 63628-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11085,14 +11050,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46175</v>
+        <v>46014</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11104,13 +11069,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I124" t="n">
-        <v>1.4</v>
+        <v>3.8</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -11153,7 +11113,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 24116-2024</t>
+          <t>A 4587-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11167,10 +11127,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45456</v>
+        <v>45687</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11183,7 +11143,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11226,7 +11186,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 25092-2026</t>
+          <t>A 55182-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11240,10 +11200,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46175</v>
+        <v>45618</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11255,13 +11215,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I126" t="n">
-        <v>1.9</v>
+        <v>11.4</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11304,7 +11259,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 55832-2023</t>
+          <t>A 4058-2022</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11318,10 +11273,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45239</v>
+        <v>44588</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11334,7 +11289,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11377,7 +11332,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 10515-2023</t>
+          <t>A 1788-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11391,10 +11346,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44987</v>
+        <v>46034</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11407,7 +11362,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.9</v>
+        <v>3.5</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11450,7 +11405,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 50958-2025</t>
+          <t>A 24666-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11464,10 +11419,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45946</v>
+        <v>46171</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11480,7 +11435,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.4</v>
+        <v>6.1</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11523,7 +11478,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 33011-2023</t>
+          <t>A 45664-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11537,10 +11492,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45125</v>
+        <v>45923</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11552,8 +11507,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I130" t="n">
-        <v>0.8</v>
+        <v>9</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11596,7 +11556,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 26822-2026</t>
+          <t>A 2911-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11610,10 +11570,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46185</v>
+        <v>46038</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11625,13 +11585,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I131" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11674,7 +11629,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 26819-2026</t>
+          <t>A 47222-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11688,10 +11643,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46185</v>
+        <v>45586</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11709,7 +11664,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>2.4</v>
+        <v>5.3</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11752,7 +11707,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 3239-2026</t>
+          <t>A 25092-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11766,10 +11721,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46041</v>
+        <v>46175</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11781,8 +11736,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I133" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11825,7 +11785,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 26821-2026</t>
+          <t>A 28100-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11839,10 +11799,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46185</v>
+        <v>45476</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11854,13 +11814,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I134" t="n">
-        <v>7.9</v>
+        <v>1.8</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11903,7 +11858,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 26820-2026</t>
+          <t>A 25098-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11913,14 +11868,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46185</v>
+        <v>46175</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11938,7 +11893,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>9.9</v>
+        <v>1.4</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11981,7 +11936,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 26608-2026</t>
+          <t>A 1106-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11995,10 +11950,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46184</v>
+        <v>45302</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12010,13 +11965,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -12059,7 +12009,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 26824-2026</t>
+          <t>A 39030-2022</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12073,10 +12023,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46185</v>
+        <v>44817</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12094,7 +12044,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -12137,7 +12087,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 26825-2026</t>
+          <t>A 38382-2022</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12151,10 +12101,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46185</v>
+        <v>44812</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12168,11 +12118,11 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I138" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -12215,7 +12165,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 48168-2024</t>
+          <t>A 16881-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12229,10 +12179,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45589</v>
+        <v>45033</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12244,8 +12194,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I139" t="n">
-        <v>5.5</v>
+        <v>2.3</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12288,7 +12243,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 27392-2026</t>
+          <t>A 9917-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12302,10 +12257,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46189</v>
+        <v>46073</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12317,13 +12272,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I140" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12366,7 +12316,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 27120-2026</t>
+          <t>A 26608-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12380,10 +12330,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46188</v>
+        <v>46184</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12395,8 +12345,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I141" t="n">
-        <v>4.7</v>
+        <v>1.6</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12439,7 +12394,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 13454-2022</t>
+          <t>A 57422-2021</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12453,10 +12408,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44645</v>
+        <v>44483</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12469,7 +12424,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12512,7 +12467,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 10743-2023</t>
+          <t>A 27120-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12526,10 +12481,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>44988</v>
+        <v>46188</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12541,13 +12496,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I143" t="n">
-        <v>2.4</v>
+        <v>4.7</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12590,7 +12540,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 50611-2024</t>
+          <t>A 26819-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12604,10 +12554,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45601</v>
+        <v>46185</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12619,8 +12569,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I144" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12663,7 +12618,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 42802-2023</t>
+          <t>A 3239-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12673,14 +12628,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45182</v>
+        <v>46041</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12692,13 +12647,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I145" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12741,7 +12691,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 52829-2024</t>
+          <t>A 8244-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12755,10 +12705,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45610</v>
+        <v>45708</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12771,7 +12721,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12814,7 +12764,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 55025-2025</t>
+          <t>A 26820-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12828,10 +12778,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45967</v>
+        <v>46185</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12843,8 +12793,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I147" t="n">
-        <v>2.4</v>
+        <v>9.9</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12887,7 +12842,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 56313-2024</t>
+          <t>A 26821-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12901,10 +12856,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45624</v>
+        <v>46185</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12918,11 +12873,11 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I148" t="n">
-        <v>2.2</v>
+        <v>7.9</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12965,7 +12920,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 38382-2022</t>
+          <t>A 26822-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12979,10 +12934,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>44812</v>
+        <v>46185</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12996,7 +12951,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I149" t="n">
@@ -13043,7 +12998,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 24115-2024</t>
+          <t>A 26824-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -13057,10 +13012,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45456</v>
+        <v>46185</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13072,8 +13027,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I150" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -13116,7 +13076,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 10404-2022</t>
+          <t>A 26825-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -13130,10 +13090,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44623</v>
+        <v>46185</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13145,8 +13105,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I151" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -13189,7 +13154,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 18955-2025</t>
+          <t>A 38190-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13203,10 +13168,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45764</v>
+        <v>45545</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13219,7 +13184,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>8.1</v>
+        <v>2.1</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -13262,7 +13227,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 59522-2025</t>
+          <t>A 13473-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13272,14 +13237,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45989</v>
+        <v>46094</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13291,13 +13256,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I153" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -13340,7 +13300,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 22867-2022</t>
+          <t>A 20463-2025</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13354,10 +13314,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>44715</v>
+        <v>45775</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13369,8 +13329,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I154" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13413,7 +13378,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 18978-2025</t>
+          <t>A 27392-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13427,10 +13392,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45764</v>
+        <v>46189</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13442,8 +13407,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I155" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13486,7 +13456,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 31378-2026</t>
+          <t>A 12897-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13500,10 +13470,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46213</v>
+        <v>46092</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13516,7 +13486,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>3.7</v>
+        <v>1.3</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13559,7 +13529,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 4801-2024</t>
+          <t>A 14580-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13573,10 +13543,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45328</v>
+        <v>46101</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13588,8 +13558,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I157" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13632,7 +13607,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 4802-2024</t>
+          <t>A 35470-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13646,10 +13621,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45328</v>
+        <v>45531</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13662,7 +13637,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13705,7 +13680,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 30961-2022</t>
+          <t>A 35445-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13719,10 +13694,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>44768</v>
+        <v>45531</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13734,13 +13709,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I159" t="n">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13783,7 +13753,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 60503-2025</t>
+          <t>A 47094-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13797,10 +13767,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45995</v>
+        <v>45196</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13813,7 +13783,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13856,7 +13826,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 35094-2026</t>
+          <t>A 38196-2024</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13870,10 +13840,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46260</v>
+        <v>45545</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13885,13 +13855,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I161" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13934,7 +13899,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 55191-2023</t>
+          <t>A 16783-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13948,10 +13913,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45237</v>
+        <v>46113</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13963,8 +13928,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I162" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -14007,7 +13977,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 60508-2025</t>
+          <t>A 16787-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -14021,10 +13991,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45995</v>
+        <v>46113</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14036,8 +14006,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I163" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -14080,7 +14055,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 60506-2025</t>
+          <t>A 16782-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -14094,10 +14069,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45995</v>
+        <v>46113</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14109,8 +14084,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I164" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -14153,7 +14133,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 61788-2025</t>
+          <t>A 15058-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -14167,10 +14147,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46002</v>
+        <v>46104</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14182,13 +14162,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I165" t="n">
-        <v>0.9</v>
+        <v>4.3</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -14231,7 +14206,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 35699-2026</t>
+          <t>A 15060-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -14241,14 +14216,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46265</v>
+        <v>46104</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14260,13 +14235,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I166" t="n">
-        <v>2.8</v>
+        <v>11.5</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -14309,7 +14279,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 13496-2025</t>
+          <t>A 50611-2024</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -14323,10 +14293,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45736</v>
+        <v>45601</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14339,7 +14309,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>8.800000000000001</v>
+        <v>1</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14382,7 +14352,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 11974-2025</t>
+          <t>A 17734-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14396,10 +14366,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45728</v>
+        <v>46122</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14411,8 +14381,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I168" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14455,7 +14430,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 36374-2026</t>
+          <t>A 20289-2024</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14469,10 +14444,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46268</v>
+        <v>45435</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14486,11 +14461,11 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14533,7 +14508,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 63863-2023</t>
+          <t>A 52797-2021</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14547,10 +14522,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45278</v>
+        <v>44467</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14563,7 +14538,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14606,7 +14581,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 1309-2024</t>
+          <t>A 19009-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14620,10 +14595,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45303</v>
+        <v>46130</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14635,8 +14610,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I171" t="n">
-        <v>4</v>
+        <v>6.3</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14679,7 +14659,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 37089-2026</t>
+          <t>A 19011-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14693,10 +14673,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46273</v>
+        <v>46130</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14708,8 +14688,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I172" t="n">
-        <v>15.8</v>
+        <v>0.9</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14752,7 +14737,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 64066-2025</t>
+          <t>A 19010-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14762,14 +14747,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46013</v>
+        <v>46130</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14779,6 +14764,11 @@
       <c r="G173" t="inlineStr">
         <is>
           <t>KARLSKOGA</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I173" t="n">
@@ -14825,7 +14815,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 63628-2025</t>
+          <t>A 19008-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14839,10 +14829,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46014</v>
+        <v>46130</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14854,8 +14844,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I174" t="n">
-        <v>3.8</v>
+        <v>1.9</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14898,7 +14893,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 52826-2024</t>
+          <t>A 20086-2024</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14908,14 +14903,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45610</v>
+        <v>45434</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14928,7 +14923,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14971,7 +14966,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 38043-2026</t>
+          <t>A 19663-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14985,10 +14980,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46280</v>
+        <v>46134</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15002,11 +14997,11 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -15049,7 +15044,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 38020-2026</t>
+          <t>A 13496-2025</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -15063,10 +15058,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46280</v>
+        <v>45736</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15078,13 +15073,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I177" t="n">
-        <v>4.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -15127,7 +15117,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 1106-2024</t>
+          <t>A 56887-2022</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -15141,10 +15131,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45302</v>
+        <v>44894</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15157,7 +15147,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -15200,7 +15190,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 48707-2024</t>
+          <t>A 33011-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -15214,10 +15204,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45593</v>
+        <v>45125</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15230,7 +15220,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>6</v>
+        <v>0.8</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -15273,7 +15263,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 1788-2026</t>
+          <t>A 51344-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -15287,10 +15277,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46034</v>
+        <v>45219</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15302,8 +15292,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I180" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -15346,7 +15341,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 2911-2026</t>
+          <t>A 31378-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15360,10 +15355,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46038</v>
+        <v>46213</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15376,7 +15371,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.1</v>
+        <v>3.7</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15419,7 +15414,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 35470-2024</t>
+          <t>A 10515-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15433,10 +15428,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45531</v>
+        <v>44987</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15449,7 +15444,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15492,7 +15487,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 45664-2025</t>
+          <t>A 39337-2022</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15506,10 +15501,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45923</v>
+        <v>44817</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15521,13 +15516,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I183" t="n">
-        <v>9</v>
+        <v>1.5</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15570,7 +15560,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 47222-2024</t>
+          <t>A 35094-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15584,10 +15574,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45586</v>
+        <v>46260</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15601,11 +15591,11 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I184" t="n">
-        <v>5.3</v>
+        <v>1.9</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15648,7 +15638,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 8990-2023</t>
+          <t>A 53620-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15662,10 +15652,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>44979</v>
+        <v>45614</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15678,7 +15668,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15721,7 +15711,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 50614-2024</t>
+          <t>A 35699-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15731,14 +15721,14 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45601</v>
+        <v>46265</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15750,8 +15740,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I186" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15794,7 +15789,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 55182-2024</t>
+          <t>A 13501-2025</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15808,10 +15803,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45618</v>
+        <v>45736</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15824,7 +15819,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>11.4</v>
+        <v>3.2</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15867,7 +15862,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 52797-2021</t>
+          <t>A 10404-2022</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15881,10 +15876,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>44467</v>
+        <v>44623</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15897,7 +15892,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15940,7 +15935,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 8259-2025</t>
+          <t>A 36374-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15954,10 +15949,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45708</v>
+        <v>46268</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15969,8 +15964,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I189" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -16013,7 +16013,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 53620-2024</t>
+          <t>A 37089-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45614</v>
+        <v>46273</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16043,7 +16043,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>0.7</v>
+        <v>15.8</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -16086,7 +16086,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 35930-2023</t>
+          <t>A 38742-2023</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -16096,14 +16096,14 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45148</v>
+        <v>45161</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16117,11 +16117,11 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I191" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -16164,7 +16164,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 47196-2023</t>
+          <t>A 3735-2024</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -16178,10 +16178,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45196</v>
+        <v>45321</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16193,8 +16193,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I192" t="n">
-        <v>5.9</v>
+        <v>1.6</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -16237,7 +16242,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 53618-2024</t>
+          <t>A 38043-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -16251,10 +16256,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45614</v>
+        <v>46280</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16266,8 +16271,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I193" t="n">
-        <v>10.1</v>
+        <v>1.1</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -16310,7 +16320,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 58388-2024</t>
+          <t>A 23308-2025</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -16324,10 +16334,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45633</v>
+        <v>45791</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16340,7 +16350,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>5.8</v>
+        <v>1.5</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -16383,7 +16393,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 47201-2023</t>
+          <t>A 38020-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16397,10 +16407,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45196</v>
+        <v>46280</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16412,8 +16422,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I195" t="n">
-        <v>2.7</v>
+        <v>4.1</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -16456,7 +16471,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 52828-2024</t>
+          <t>A 27498-2025</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16470,10 +16485,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45610</v>
+        <v>45813</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16486,7 +16501,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>8.300000000000001</v>
+        <v>1.2</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16529,7 +16544,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 17243-2024</t>
+          <t>A 23620-2024</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16543,10 +16558,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45414</v>
+        <v>45454</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16559,7 +16574,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16602,7 +16617,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 59938-2023</t>
+          <t>A 53647-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16616,10 +16631,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45257</v>
+        <v>45230</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16632,7 +16647,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16675,7 +16690,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 38742-2023</t>
+          <t>A 30102-2025</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16685,14 +16700,14 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45161</v>
+        <v>45826</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16704,13 +16719,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I199" t="n">
-        <v>4.2</v>
+        <v>1</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16753,7 +16763,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 3735-2024</t>
+          <t>A 54680-2021</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16767,10 +16777,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45321</v>
+        <v>44473</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16782,13 +16792,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I200" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16831,7 +16836,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 23308-2025</t>
+          <t>A 31397-2025</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16845,10 +16850,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45791</v>
+        <v>45833</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16904,7 +16909,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 27498-2025</t>
+          <t>A 32287-2025</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16918,10 +16923,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45813</v>
+        <v>45835</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16933,8 +16938,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I202" t="n">
-        <v>1.2</v>
+        <v>10.9</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16994,7 +17004,7 @@
         <v>45953</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>

--- a/Översikt KARLSKOGA.xlsx
+++ b/Översikt KARLSKOGA.xlsx
@@ -601,7 +601,7 @@
         <v>45562</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>45958</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         <v>45989</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>44510</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>46100</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>45989</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>44473</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>46010</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1545,10 +1545,10 @@
         <v>8</v>
       </c>
       <c r="T9" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="U9" t="n">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>46010</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1666,10 +1666,10 @@
         <v>8</v>
       </c>
       <c r="T10" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="U10" t="n">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>44495</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>46066</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>46010</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>46136</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>46127</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2302,7 +2302,7 @@
         <v>46265</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         <v>46136</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>46136</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>44817</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 39936-2024</t>
+          <t>A 38023-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2758,10 +2758,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45553</v>
+        <v>46280</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2773,17 +2773,22 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2798,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2807,160 +2812,160 @@
         <v>2</v>
       </c>
       <c r="T20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
         <v>1</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
+          <t>Tjäder
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 38023-2026 artfynd.xlsx", "A 38023-2026")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 38023-2026 karta.png", "A 38023-2026")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 38023-2026 georefererad karta.tif", "A 38023-2026")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 38023-2026 FSC-klagomål.docx", "A 38023-2026")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 38023-2026 FSC-klagomål mail.docx", "A 38023-2026")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 38023-2026 tillsynsbegäran.docx", "A 38023-2026")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 38023-2026 tillsynsbegäran mail.docx", "A 38023-2026")</f>
+        <v/>
+      </c>
+      <c r="AE20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 38023-2026 prioriterade fågelarter.docx", "A 38023-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 39936-2024</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>45553</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>KARLSKOGA</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
           <t>Storgröe
 Utter</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 39936-2024 artfynd.xlsx", "A 39936-2024")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 39936-2024 karta.png", "A 39936-2024")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 39936-2024 georefererad karta.tif", "A 39936-2024")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 39936-2024 FSC-klagomål.docx", "A 39936-2024")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 39936-2024 FSC-klagomål mail.docx", "A 39936-2024")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 39936-2024 tillsynsbegäran.docx", "A 39936-2024")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 39936-2024 tillsynsbegäran mail.docx", "A 39936-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 21019-2026</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>46145</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46284</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>KARLSKOGA</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>1</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Åkergroda</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 21019-2026 artfynd.xlsx", "A 21019-2026")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 21019-2026 karta.png", "A 21019-2026")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 21019-2026 georefererad karta.tif", "A 21019-2026")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 21019-2026 FSC-klagomål.docx", "A 21019-2026")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 21019-2026 FSC-klagomål mail.docx", "A 21019-2026")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 21019-2026 tillsynsbegäran.docx", "A 21019-2026")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 21019-2026 tillsynsbegäran mail.docx", "A 21019-2026")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 52377-2025</t>
+          <t>A 21019-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2974,10 +2979,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45953</v>
+        <v>46145</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2995,7 +3000,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.6</v>
+        <v>4.7</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -3031,46 +3036,46 @@
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 52377-2025 artfynd.xlsx", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 21019-2026 artfynd.xlsx", "A 21019-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 52377-2025 karta.png", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 21019-2026 karta.png", "A 21019-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 52377-2025 georefererad karta.tif", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 21019-2026 georefererad karta.tif", "A 21019-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 52377-2025 FSC-klagomål.docx", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 21019-2026 FSC-klagomål.docx", "A 21019-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 52377-2025 FSC-klagomål mail.docx", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 21019-2026 FSC-klagomål mail.docx", "A 21019-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 52377-2025 tillsynsbegäran.docx", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 21019-2026 tillsynsbegäran.docx", "A 21019-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 52377-2025 tillsynsbegäran mail.docx", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 21019-2026 tillsynsbegäran mail.docx", "A 21019-2026")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 28474-2023</t>
+          <t>A 52377-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3084,10 +3089,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45103</v>
+        <v>45953</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3099,8 +3104,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>5.1</v>
+        <v>2.6</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -3109,7 +3119,7 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -3124,7 +3134,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -3140,46 +3150,42 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Blåhake</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 28474-2023 artfynd.xlsx", "A 28474-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 52377-2025 artfynd.xlsx", "A 52377-2025")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 28474-2023 karta.png", "A 28474-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 52377-2025 karta.png", "A 52377-2025")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 28474-2023 georefererad karta.tif", "A 28474-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 52377-2025 georefererad karta.tif", "A 52377-2025")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 28474-2023 FSC-klagomål.docx", "A 28474-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 52377-2025 FSC-klagomål.docx", "A 52377-2025")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 28474-2023 FSC-klagomål mail.docx", "A 28474-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 52377-2025 FSC-klagomål mail.docx", "A 52377-2025")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 28474-2023 tillsynsbegäran.docx", "A 28474-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 52377-2025 tillsynsbegäran.docx", "A 52377-2025")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 28474-2023 tillsynsbegäran mail.docx", "A 28474-2023")</f>
-        <v/>
-      </c>
-      <c r="AE23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 28474-2023 prioriterade fågelarter.docx", "A 28474-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 52377-2025 tillsynsbegäran mail.docx", "A 52377-2025")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 58091-2022</t>
+          <t>A 28474-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3193,10 +3199,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44900</v>
+        <v>45103</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3208,13 +3214,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>2.1</v>
+        <v>5.1</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3223,7 +3224,7 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -3238,7 +3239,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3247,49 +3248,53 @@
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Hårklomossa</t>
+          <t>Blåhake</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 58091-2022 artfynd.xlsx", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 28474-2023 artfynd.xlsx", "A 28474-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 58091-2022 karta.png", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 28474-2023 karta.png", "A 28474-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 58091-2022 georefererad karta.tif", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 28474-2023 georefererad karta.tif", "A 28474-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 58091-2022 FSC-klagomål.docx", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 28474-2023 FSC-klagomål.docx", "A 28474-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 58091-2022 FSC-klagomål mail.docx", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 28474-2023 FSC-klagomål mail.docx", "A 28474-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 58091-2022 tillsynsbegäran.docx", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 28474-2023 tillsynsbegäran.docx", "A 28474-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 58091-2022 tillsynsbegäran mail.docx", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 28474-2023 tillsynsbegäran mail.docx", "A 28474-2023")</f>
+        <v/>
+      </c>
+      <c r="AE24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 28474-2023 prioriterade fågelarter.docx", "A 28474-2023")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 25093-2026</t>
+          <t>A 58091-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3303,10 +3308,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46175</v>
+        <v>44900</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3324,13 +3329,13 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -3357,49 +3362,49 @@
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Hårklomossa</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 25093-2026 artfynd.xlsx", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 58091-2022 artfynd.xlsx", "A 58091-2022")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 25093-2026 karta.png", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 58091-2022 karta.png", "A 58091-2022")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 25093-2026 georefererad karta.tif", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 58091-2022 georefererad karta.tif", "A 58091-2022")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 25093-2026 FSC-klagomål.docx", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 58091-2022 FSC-klagomål.docx", "A 58091-2022")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 25093-2026 FSC-klagomål mail.docx", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 58091-2022 FSC-klagomål mail.docx", "A 58091-2022")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 25093-2026 tillsynsbegäran.docx", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 58091-2022 tillsynsbegäran.docx", "A 58091-2022")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 25093-2026 tillsynsbegäran mail.docx", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 58091-2022 tillsynsbegäran mail.docx", "A 58091-2022")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 28566-2024</t>
+          <t>A 25093-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3413,10 +3418,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45478</v>
+        <v>46175</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3428,14 +3433,19 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I26" t="n">
+        <v>4</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
         <v>1</v>
-      </c>
-      <c r="J26" t="n">
-        <v>1</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -3469,42 +3479,42 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 28566-2024 artfynd.xlsx", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 25093-2026 artfynd.xlsx", "A 25093-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 28566-2024 karta.png", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 25093-2026 karta.png", "A 25093-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 28566-2024 georefererad karta.tif", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 25093-2026 georefererad karta.tif", "A 25093-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 28566-2024 FSC-klagomål.docx", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 25093-2026 FSC-klagomål.docx", "A 25093-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 28566-2024 FSC-klagomål mail.docx", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 25093-2026 FSC-klagomål mail.docx", "A 25093-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 28566-2024 tillsynsbegäran.docx", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 25093-2026 tillsynsbegäran.docx", "A 25093-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 28566-2024 tillsynsbegäran mail.docx", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 25093-2026 tillsynsbegäran mail.docx", "A 25093-2026")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 63188-2025</t>
+          <t>A 28566-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3518,10 +3528,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46010</v>
+        <v>45478</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3533,13 +3543,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
@@ -3548,7 +3553,7 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -3563,7 +3568,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -3572,53 +3577,49 @@
         <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 63188-2025 artfynd.xlsx", "A 63188-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 28566-2024 artfynd.xlsx", "A 28566-2024")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 63188-2025 karta.png", "A 63188-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 28566-2024 karta.png", "A 28566-2024")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 63188-2025 georefererad karta.tif", "A 63188-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 28566-2024 georefererad karta.tif", "A 28566-2024")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 63188-2025 FSC-klagomål.docx", "A 63188-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 28566-2024 FSC-klagomål.docx", "A 28566-2024")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 63188-2025 FSC-klagomål mail.docx", "A 63188-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 28566-2024 FSC-klagomål mail.docx", "A 28566-2024")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 63188-2025 tillsynsbegäran.docx", "A 63188-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 28566-2024 tillsynsbegäran.docx", "A 28566-2024")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 63188-2025 tillsynsbegäran mail.docx", "A 63188-2025")</f>
-        <v/>
-      </c>
-      <c r="AE27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 63188-2025 prioriterade fågelarter.docx", "A 63188-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 28566-2024 tillsynsbegäran mail.docx", "A 28566-2024")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 16784-2026</t>
+          <t>A 63188-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3632,10 +3633,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46113</v>
+        <v>46010</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3653,7 +3654,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>4.2</v>
+        <v>1.1</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
@@ -3662,7 +3663,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -3677,7 +3678,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -3689,46 +3690,50 @@
         <v>2</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Hårklomossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 16784-2026 artfynd.xlsx", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 63188-2025 artfynd.xlsx", "A 63188-2025")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 16784-2026 karta.png", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 63188-2025 karta.png", "A 63188-2025")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 16784-2026 georefererad karta.tif", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 63188-2025 georefererad karta.tif", "A 63188-2025")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 16784-2026 FSC-klagomål.docx", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 63188-2025 FSC-klagomål.docx", "A 63188-2025")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 16784-2026 FSC-klagomål mail.docx", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 63188-2025 FSC-klagomål mail.docx", "A 63188-2025")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 16784-2026 tillsynsbegäran.docx", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 63188-2025 tillsynsbegäran.docx", "A 63188-2025")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 16784-2026 tillsynsbegäran mail.docx", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 63188-2025 tillsynsbegäran mail.docx", "A 63188-2025")</f>
+        <v/>
+      </c>
+      <c r="AE28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 63188-2025 prioriterade fågelarter.docx", "A 63188-2025")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 18427-2026</t>
+          <t>A 16784-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3742,10 +3747,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46127</v>
+        <v>46113</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3763,7 +3768,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -3796,53 +3801,49 @@
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Hårklomossa</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 18427-2026 artfynd.xlsx", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 16784-2026 artfynd.xlsx", "A 16784-2026")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 18427-2026 karta.png", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 16784-2026 karta.png", "A 16784-2026")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 18427-2026 georefererad karta.tif", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 16784-2026 georefererad karta.tif", "A 16784-2026")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 18427-2026 FSC-klagomål.docx", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 16784-2026 FSC-klagomål.docx", "A 16784-2026")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 18427-2026 FSC-klagomål mail.docx", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 16784-2026 FSC-klagomål mail.docx", "A 16784-2026")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 18427-2026 tillsynsbegäran.docx", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 16784-2026 tillsynsbegäran.docx", "A 16784-2026")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 18427-2026 tillsynsbegäran mail.docx", "A 18427-2026")</f>
-        <v/>
-      </c>
-      <c r="AE29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 18427-2026 prioriterade fågelarter.docx", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 16784-2026 tillsynsbegäran mail.docx", "A 16784-2026")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 19233-2026</t>
+          <t>A 18427-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3856,10 +3857,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46132</v>
+        <v>46127</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3871,14 +3872,19 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -3908,46 +3914,50 @@
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 19233-2026 artfynd.xlsx", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 18427-2026 artfynd.xlsx", "A 18427-2026")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 19233-2026 karta.png", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 18427-2026 karta.png", "A 18427-2026")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 19233-2026 georefererad karta.tif", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 18427-2026 georefererad karta.tif", "A 18427-2026")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 19233-2026 FSC-klagomål.docx", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 18427-2026 FSC-klagomål.docx", "A 18427-2026")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 19233-2026 FSC-klagomål mail.docx", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 18427-2026 FSC-klagomål mail.docx", "A 18427-2026")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 19233-2026 tillsynsbegäran.docx", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 18427-2026 tillsynsbegäran.docx", "A 18427-2026")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 19233-2026 tillsynsbegäran mail.docx", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 18427-2026 tillsynsbegäran mail.docx", "A 18427-2026")</f>
+        <v/>
+      </c>
+      <c r="AE30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 18427-2026 prioriterade fågelarter.docx", "A 18427-2026")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 40528-2024</t>
+          <t>A 19233-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3961,10 +3971,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45555</v>
+        <v>46132</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3977,13 +3987,13 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
         <v>1</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -4013,46 +4023,46 @@
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 40528-2024 artfynd.xlsx", "A 40528-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 19233-2026 artfynd.xlsx", "A 19233-2026")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 40528-2024 karta.png", "A 40528-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 19233-2026 karta.png", "A 19233-2026")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 40528-2024 georefererad karta.tif", "A 40528-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 19233-2026 georefererad karta.tif", "A 19233-2026")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 40528-2024 FSC-klagomål.docx", "A 40528-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 19233-2026 FSC-klagomål.docx", "A 19233-2026")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 40528-2024 FSC-klagomål mail.docx", "A 40528-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 19233-2026 FSC-klagomål mail.docx", "A 19233-2026")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 40528-2024 tillsynsbegäran.docx", "A 40528-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 19233-2026 tillsynsbegäran.docx", "A 19233-2026")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 40528-2024 tillsynsbegäran mail.docx", "A 40528-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 19233-2026 tillsynsbegäran mail.docx", "A 19233-2026")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 30915-2026</t>
+          <t>A 40528-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4066,10 +4076,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46213</v>
+        <v>45555</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4081,13 +4091,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>8.9</v>
+        <v>2.8</v>
       </c>
       <c r="J32" t="n">
         <v>1</v>
@@ -4123,46 +4128,46 @@
         <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 30915-2026 artfynd.xlsx", "A 30915-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 40528-2024 artfynd.xlsx", "A 40528-2024")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 30915-2026 karta.png", "A 30915-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 40528-2024 karta.png", "A 40528-2024")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 30915-2026 georefererad karta.tif", "A 30915-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 40528-2024 georefererad karta.tif", "A 40528-2024")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 30915-2026 FSC-klagomål.docx", "A 30915-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 40528-2024 FSC-klagomål.docx", "A 40528-2024")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 30915-2026 FSC-klagomål mail.docx", "A 30915-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 40528-2024 FSC-klagomål mail.docx", "A 40528-2024")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 30915-2026 tillsynsbegäran.docx", "A 30915-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 40528-2024 tillsynsbegäran.docx", "A 40528-2024")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 30915-2026 tillsynsbegäran mail.docx", "A 30915-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 40528-2024 tillsynsbegäran mail.docx", "A 40528-2024")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 35199-2026</t>
+          <t>A 30915-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4176,10 +4181,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46260</v>
+        <v>46213</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4197,7 +4202,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>5.6</v>
+        <v>8.9</v>
       </c>
       <c r="J33" t="n">
         <v>1</v>
@@ -4206,7 +4211,7 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -4221,7 +4226,7 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -4237,42 +4242,42 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 35199-2026 artfynd.xlsx", "A 35199-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 30915-2026 artfynd.xlsx", "A 30915-2026")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 35199-2026 karta.png", "A 35199-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 30915-2026 karta.png", "A 30915-2026")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 35199-2026 georefererad karta.tif", "A 35199-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 30915-2026 georefererad karta.tif", "A 30915-2026")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 35199-2026 FSC-klagomål.docx", "A 35199-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 30915-2026 FSC-klagomål.docx", "A 30915-2026")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 35199-2026 FSC-klagomål mail.docx", "A 35199-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 30915-2026 FSC-klagomål mail.docx", "A 30915-2026")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 35199-2026 tillsynsbegäran.docx", "A 35199-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 30915-2026 tillsynsbegäran.docx", "A 30915-2026")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 35199-2026 tillsynsbegäran mail.docx", "A 35199-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 30915-2026 tillsynsbegäran mail.docx", "A 30915-2026")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 38023-2026</t>
+          <t>A 35199-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4286,10 +4291,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46280</v>
+        <v>46260</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4303,11 +4308,11 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>7.2</v>
+        <v>5.6</v>
       </c>
       <c r="J34" t="n">
         <v>1</v>
@@ -4316,7 +4321,7 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -4331,7 +4336,7 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -4347,39 +4352,35 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 38023-2026 artfynd.xlsx", "A 38023-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 35199-2026 artfynd.xlsx", "A 35199-2026")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 38023-2026 karta.png", "A 38023-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 35199-2026 karta.png", "A 35199-2026")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 38023-2026 georefererad karta.tif", "A 38023-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 35199-2026 georefererad karta.tif", "A 35199-2026")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 38023-2026 FSC-klagomål.docx", "A 38023-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 35199-2026 FSC-klagomål.docx", "A 35199-2026")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 38023-2026 FSC-klagomål mail.docx", "A 38023-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 35199-2026 FSC-klagomål mail.docx", "A 35199-2026")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 38023-2026 tillsynsbegäran.docx", "A 38023-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 35199-2026 tillsynsbegäran.docx", "A 35199-2026")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 38023-2026 tillsynsbegäran mail.docx", "A 38023-2026")</f>
-        <v/>
-      </c>
-      <c r="AE34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 38023-2026 prioriterade fågelarter.docx", "A 38023-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 35199-2026 tillsynsbegäran mail.docx", "A 35199-2026")</f>
         <v/>
       </c>
     </row>
@@ -4403,7 +4404,7 @@
         <v>46136</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4513,7 +4514,7 @@
         <v>44546</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4586,7 +4587,7 @@
         <v>44732</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4659,7 +4660,7 @@
         <v>44460</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4732,7 +4733,7 @@
         <v>44512</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4810,7 +4811,7 @@
         <v>44715</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4883,7 +4884,7 @@
         <v>44508</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4961,7 +4962,7 @@
         <v>44480</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5034,7 +5035,7 @@
         <v>44809</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5107,7 +5108,7 @@
         <v>44811</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5180,7 +5181,7 @@
         <v>44628</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5258,7 +5259,7 @@
         <v>44809</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5331,7 +5332,7 @@
         <v>44706</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5404,7 +5405,7 @@
         <v>44706</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5477,7 +5478,7 @@
         <v>44817</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5555,7 +5556,7 @@
         <v>45633</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5628,7 +5629,7 @@
         <v>44588</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5706,7 +5707,7 @@
         <v>45362</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5784,7 +5785,7 @@
         <v>45182</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5862,7 +5863,7 @@
         <v>44981</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5935,7 +5936,7 @@
         <v>45303</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6008,7 +6009,7 @@
         <v>45531</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6081,7 +6082,7 @@
         <v>45531</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6154,7 +6155,7 @@
         <v>44720</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6227,7 +6228,7 @@
         <v>45196</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6300,7 +6301,7 @@
         <v>45264</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6373,7 +6374,7 @@
         <v>45708</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6446,7 +6447,7 @@
         <v>45456</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6519,7 +6520,7 @@
         <v>45148</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6597,7 +6598,7 @@
         <v>45278</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6670,7 +6671,7 @@
         <v>45257</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6743,7 +6744,7 @@
         <v>45610</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6816,7 +6817,7 @@
         <v>45744</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6894,7 +6895,7 @@
         <v>45456</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6967,7 +6968,7 @@
         <v>45764</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7045,7 +7046,7 @@
         <v>45328</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7118,7 +7119,7 @@
         <v>45328</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7191,7 +7192,7 @@
         <v>44979</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7264,7 +7265,7 @@
         <v>45182</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7342,7 +7343,7 @@
         <v>45700</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7415,7 +7416,7 @@
         <v>45103</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7488,7 +7489,7 @@
         <v>44715</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7561,7 +7562,7 @@
         <v>45279</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7634,7 +7635,7 @@
         <v>45457</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7707,7 +7708,7 @@
         <v>45593</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7780,7 +7781,7 @@
         <v>45758</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7858,7 +7859,7 @@
         <v>45779</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7936,7 +7937,7 @@
         <v>45793</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8009,7 +8010,7 @@
         <v>45239</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8082,7 +8083,7 @@
         <v>45633</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8155,7 +8156,7 @@
         <v>45764</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8228,7 +8229,7 @@
         <v>46030</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8301,7 +8302,7 @@
         <v>45918</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8374,7 +8375,7 @@
         <v>45918</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8447,7 +8448,7 @@
         <v>44777</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8520,7 +8521,7 @@
         <v>45182</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8593,7 +8594,7 @@
         <v>45196</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8666,7 +8667,7 @@
         <v>44645</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8739,7 +8740,7 @@
         <v>45614</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8812,7 +8813,7 @@
         <v>46147</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8885,7 +8886,7 @@
         <v>44768</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8963,7 +8964,7 @@
         <v>46147</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9036,7 +9037,7 @@
         <v>45182</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9114,7 +9115,7 @@
         <v>45712</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9187,7 +9188,7 @@
         <v>45946</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9260,7 +9261,7 @@
         <v>45624</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9338,7 +9339,7 @@
         <v>44988</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9416,7 +9417,7 @@
         <v>45393</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9494,7 +9495,7 @@
         <v>45237</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9567,7 +9568,7 @@
         <v>45636</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9645,7 +9646,7 @@
         <v>45967</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9718,7 +9719,7 @@
         <v>45679</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9791,7 +9792,7 @@
         <v>45414</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9864,7 +9865,7 @@
         <v>45527</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9942,7 +9943,7 @@
         <v>45989</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10020,7 +10021,7 @@
         <v>45610</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10093,7 +10094,7 @@
         <v>45610</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10166,7 +10167,7 @@
         <v>45728</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10239,7 +10240,7 @@
         <v>45995</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10312,7 +10313,7 @@
         <v>45995</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10385,7 +10386,7 @@
         <v>45995</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10458,7 +10459,7 @@
         <v>44909</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10536,7 +10537,7 @@
         <v>46164</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10614,7 +10615,7 @@
         <v>45589</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10687,7 +10688,7 @@
         <v>46002</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10765,7 +10766,7 @@
         <v>45687</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10838,7 +10839,7 @@
         <v>45764</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10911,7 +10912,7 @@
         <v>46013</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10984,7 +10985,7 @@
         <v>45601</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11057,7 +11058,7 @@
         <v>46014</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11130,7 +11131,7 @@
         <v>45687</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11203,7 +11204,7 @@
         <v>45618</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11276,7 +11277,7 @@
         <v>44588</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11349,7 +11350,7 @@
         <v>46034</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11422,7 +11423,7 @@
         <v>46171</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11495,7 +11496,7 @@
         <v>45923</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11573,7 +11574,7 @@
         <v>46038</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11646,7 +11647,7 @@
         <v>45586</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11724,7 +11725,7 @@
         <v>46175</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11802,7 +11803,7 @@
         <v>45476</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11875,7 +11876,7 @@
         <v>46175</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11953,7 +11954,7 @@
         <v>45302</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12026,7 +12027,7 @@
         <v>44817</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12104,7 +12105,7 @@
         <v>44812</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12182,7 +12183,7 @@
         <v>45033</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12260,7 +12261,7 @@
         <v>46073</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12333,7 +12334,7 @@
         <v>46184</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12411,7 +12412,7 @@
         <v>44483</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12484,7 +12485,7 @@
         <v>46188</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12557,7 +12558,7 @@
         <v>46185</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12635,7 +12636,7 @@
         <v>46041</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12708,7 +12709,7 @@
         <v>45708</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12781,7 +12782,7 @@
         <v>46185</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12859,7 +12860,7 @@
         <v>46185</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12937,7 +12938,7 @@
         <v>46185</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13015,7 +13016,7 @@
         <v>46185</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13093,7 +13094,7 @@
         <v>46185</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13171,7 +13172,7 @@
         <v>45545</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13244,7 +13245,7 @@
         <v>46094</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13317,7 +13318,7 @@
         <v>45775</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13395,7 +13396,7 @@
         <v>46189</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13473,7 +13474,7 @@
         <v>46092</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13546,7 +13547,7 @@
         <v>46101</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13624,7 +13625,7 @@
         <v>45531</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13697,7 +13698,7 @@
         <v>45531</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13770,7 +13771,7 @@
         <v>45196</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13843,7 +13844,7 @@
         <v>45545</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13916,7 +13917,7 @@
         <v>46113</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13994,7 +13995,7 @@
         <v>46113</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14072,7 +14073,7 @@
         <v>46113</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14150,7 +14151,7 @@
         <v>46104</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14223,7 +14224,7 @@
         <v>46104</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14296,7 +14297,7 @@
         <v>45601</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14369,7 +14370,7 @@
         <v>46122</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14447,7 +14448,7 @@
         <v>45435</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14525,7 +14526,7 @@
         <v>44467</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14598,7 +14599,7 @@
         <v>46130</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14676,7 +14677,7 @@
         <v>46130</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14754,7 +14755,7 @@
         <v>46130</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14832,7 +14833,7 @@
         <v>46130</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14910,7 +14911,7 @@
         <v>45434</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14983,7 +14984,7 @@
         <v>46134</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15061,7 +15062,7 @@
         <v>45736</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15134,7 +15135,7 @@
         <v>44894</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15207,7 +15208,7 @@
         <v>45125</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15280,7 +15281,7 @@
         <v>45219</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15358,7 +15359,7 @@
         <v>46213</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15431,7 +15432,7 @@
         <v>44987</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15504,7 +15505,7 @@
         <v>44817</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15577,7 +15578,7 @@
         <v>46260</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15655,7 +15656,7 @@
         <v>45614</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15728,7 +15729,7 @@
         <v>46265</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15806,7 +15807,7 @@
         <v>45736</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15879,7 +15880,7 @@
         <v>44623</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15952,7 +15953,7 @@
         <v>46268</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16030,7 +16031,7 @@
         <v>46273</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16103,7 +16104,7 @@
         <v>45161</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16181,7 +16182,7 @@
         <v>45321</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16259,7 +16260,7 @@
         <v>46280</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16337,7 +16338,7 @@
         <v>45791</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16410,7 +16411,7 @@
         <v>46280</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16488,7 +16489,7 @@
         <v>45813</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16561,7 +16562,7 @@
         <v>45454</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16634,7 +16635,7 @@
         <v>45230</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16707,7 +16708,7 @@
         <v>45826</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16780,7 +16781,7 @@
         <v>44473</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16853,7 +16854,7 @@
         <v>45833</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16926,7 +16927,7 @@
         <v>45835</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17004,7 +17005,7 @@
         <v>45953</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>

--- a/Översikt KARLSKOGA.xlsx
+++ b/Översikt KARLSKOGA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE203"/>
+  <dimension ref="A1:AE197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45562</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -652,10 +652,10 @@
         <v>30</v>
       </c>
       <c r="T2" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="U2" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>45958</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         <v>45989</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>44510</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>46100</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>45989</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>44473</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>46010</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1545,10 +1545,10 @@
         <v>8</v>
       </c>
       <c r="T9" t="n">
+        <v>58</v>
+      </c>
+      <c r="U9" t="n">
         <v>56</v>
-      </c>
-      <c r="U9" t="n">
-        <v>54</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>46010</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1666,10 +1666,10 @@
         <v>8</v>
       </c>
       <c r="T10" t="n">
+        <v>58</v>
+      </c>
+      <c r="U10" t="n">
         <v>56</v>
-      </c>
-      <c r="U10" t="n">
-        <v>54</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>44495</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>46066</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>46010</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 20111-2026</t>
+          <t>A 18428-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2066,10 +2066,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46136</v>
+        <v>46127</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2087,19 +2087,19 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>8.699999999999999</v>
+        <v>6</v>
       </c>
       <c r="J14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2111,293 +2111,291 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T14" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="U14" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Tjäder
-Grönsiska
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 20111-2026 artfynd.xlsx", "A 20111-2026")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 20111-2026 karta.png", "A 20111-2026")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 20111-2026 georefererad karta.tif", "A 20111-2026")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 20111-2026 FSC-klagomål.docx", "A 20111-2026")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 20111-2026 FSC-klagomål mail.docx", "A 20111-2026")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 20111-2026 tillsynsbegäran.docx", "A 20111-2026")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 20111-2026 tillsynsbegäran mail.docx", "A 20111-2026")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 20111-2026 prioriterade fågelarter.docx", "A 20111-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 18428-2026</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>46127</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>KARLSKOGA</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>6</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3</v>
-      </c>
-      <c r="T15" t="n">
-        <v>17</v>
-      </c>
-      <c r="U15" t="n">
-        <v>17</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Skuggblåslav
 Tjäder</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 18428-2026 artfynd.xlsx", "A 18428-2026")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 18428-2026 karta.png", "A 18428-2026")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 18428-2026 georefererad karta.tif", "A 18428-2026")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 18428-2026 FSC-klagomål.docx", "A 18428-2026")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 18428-2026 FSC-klagomål mail.docx", "A 18428-2026")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 18428-2026 tillsynsbegäran.docx", "A 18428-2026")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 18428-2026 tillsynsbegäran mail.docx", "A 18428-2026")</f>
         <v/>
       </c>
-      <c r="AE15">
+      <c r="AE14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 18428-2026 prioriterade fågelarter.docx", "A 18428-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>A 35696-2026</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
-      <c r="D16" s="1" t="n">
+      <c r="D15" s="1" t="n">
         <v>46265</v>
       </c>
-      <c r="E16" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>KARLSKOGA</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
+      <c r="E15" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>KARLSKOGA</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I16" t="n">
+      <c r="I15" t="n">
         <v>4.6</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J15" t="n">
         <v>2</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K15" t="n">
         <v>1</v>
       </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
         <v>3</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T15" t="n">
         <v>4</v>
       </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Grönpyrola
 Mattlummer
 Revlummer</t>
         </is>
       </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 35696-2026 artfynd.xlsx", "A 35696-2026")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 35696-2026 karta.png", "A 35696-2026")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 35696-2026 georefererad karta.tif", "A 35696-2026")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 35696-2026 FSC-klagomål.docx", "A 35696-2026")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 35696-2026 FSC-klagomål mail.docx", "A 35696-2026")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 35696-2026 tillsynsbegäran.docx", "A 35696-2026")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 35696-2026 tillsynsbegäran mail.docx", "A 35696-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 39025-2022</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>44817</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>KARLSKOGA</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Talltita
+Tjäder</t>
+        </is>
+      </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 35696-2026 artfynd.xlsx", "A 35696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 39025-2022 artfynd.xlsx", "A 39025-2022")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 35696-2026 karta.png", "A 35696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 39025-2022 karta.png", "A 39025-2022")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 35696-2026 georefererad karta.tif", "A 35696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 39025-2022 georefererad karta.tif", "A 39025-2022")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 35696-2026 FSC-klagomål.docx", "A 35696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 39025-2022 FSC-klagomål.docx", "A 39025-2022")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 35696-2026 FSC-klagomål mail.docx", "A 35696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 39025-2022 FSC-klagomål mail.docx", "A 39025-2022")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 35696-2026 tillsynsbegäran.docx", "A 35696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 39025-2022 tillsynsbegäran.docx", "A 39025-2022")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 35696-2026 tillsynsbegäran mail.docx", "A 35696-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 39025-2022 tillsynsbegäran mail.docx", "A 39025-2022")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 39025-2022 prioriterade fågelarter.docx", "A 39025-2022")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 20108-2026</t>
+          <t>A 38023-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2411,10 +2409,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46136</v>
+        <v>46280</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2432,88 +2430,87 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.8</v>
+        <v>7.2</v>
       </c>
       <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>5</v>
-      </c>
-      <c r="U17" t="n">
-        <v>5</v>
-      </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Garnlav
-Talltita
-Vedticka</t>
+          <t>Tjäder
+Revlummer</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 20108-2026 artfynd.xlsx", "A 20108-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 38023-2026 artfynd.xlsx", "A 38023-2026")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 20108-2026 karta.png", "A 20108-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 38023-2026 karta.png", "A 38023-2026")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 20108-2026 georefererad karta.tif", "A 20108-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 38023-2026 georefererad karta.tif", "A 38023-2026")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 20108-2026 FSC-klagomål.docx", "A 20108-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 38023-2026 FSC-klagomål.docx", "A 38023-2026")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 20108-2026 FSC-klagomål mail.docx", "A 20108-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 38023-2026 FSC-klagomål mail.docx", "A 38023-2026")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 20108-2026 tillsynsbegäran.docx", "A 20108-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 38023-2026 tillsynsbegäran.docx", "A 38023-2026")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 20108-2026 tillsynsbegäran mail.docx", "A 20108-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 38023-2026 tillsynsbegäran mail.docx", "A 38023-2026")</f>
         <v/>
       </c>
       <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 20108-2026 prioriterade fågelarter.docx", "A 20108-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 38023-2026 prioriterade fågelarter.docx", "A 38023-2026")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 20112-2026</t>
+          <t>A 39936-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2527,10 +2524,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46136</v>
+        <v>45553</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2542,16 +2539,11 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>2.9</v>
+        <v>6.4</v>
       </c>
       <c r="J18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -2578,58 +2570,53 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="n">
         <v>3</v>
       </c>
-      <c r="T18" t="n">
-        <v>4</v>
-      </c>
       <c r="U18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett
-Spillkråka
-Tofsmes</t>
+          <t>Storgröe
+Utter</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 20112-2026 artfynd.xlsx", "A 20112-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 39936-2024 artfynd.xlsx", "A 39936-2024")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 20112-2026 karta.png", "A 20112-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 39936-2024 karta.png", "A 39936-2024")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 20112-2026 georefererad karta.tif", "A 20112-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 39936-2024 georefererad karta.tif", "A 39936-2024")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 20112-2026 FSC-klagomål.docx", "A 20112-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 39936-2024 FSC-klagomål.docx", "A 39936-2024")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 20112-2026 FSC-klagomål mail.docx", "A 20112-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 39936-2024 FSC-klagomål mail.docx", "A 39936-2024")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 20112-2026 tillsynsbegäran.docx", "A 20112-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 39936-2024 tillsynsbegäran.docx", "A 39936-2024")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 20112-2026 tillsynsbegäran mail.docx", "A 20112-2026")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 20112-2026 prioriterade fågelarter.docx", "A 20112-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 39936-2024 tillsynsbegäran mail.docx", "A 39936-2024")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 39025-2022</t>
+          <t>A 21019-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2643,10 +2630,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44817</v>
+        <v>46145</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2664,87 +2651,82 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.2</v>
+        <v>4.7</v>
       </c>
       <c r="J19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>1</v>
       </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
+      <c r="T19" t="n">
         <v>1</v>
       </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2</v>
-      </c>
       <c r="U19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Talltita
-Tjäder</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 39025-2022 artfynd.xlsx", "A 39025-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 21019-2026 artfynd.xlsx", "A 21019-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 39025-2022 karta.png", "A 39025-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 21019-2026 karta.png", "A 21019-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 39025-2022 georefererad karta.tif", "A 39025-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 21019-2026 georefererad karta.tif", "A 21019-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 39025-2022 FSC-klagomål.docx", "A 39025-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 21019-2026 FSC-klagomål.docx", "A 21019-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 39025-2022 FSC-klagomål mail.docx", "A 39025-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 21019-2026 FSC-klagomål mail.docx", "A 21019-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 39025-2022 tillsynsbegäran.docx", "A 39025-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 21019-2026 tillsynsbegäran.docx", "A 21019-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 39025-2022 tillsynsbegäran mail.docx", "A 39025-2022")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 39025-2022 prioriterade fågelarter.docx", "A 39025-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 21019-2026 tillsynsbegäran mail.docx", "A 21019-2026")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 38023-2026</t>
+          <t>A 52377-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2758,10 +2740,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46280</v>
+        <v>45953</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2779,10 +2761,10 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>7.2</v>
+        <v>2.6</v>
       </c>
       <c r="J20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -2809,57 +2791,52 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U20" t="n">
         <v>1</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Tjäder
-Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 38023-2026 artfynd.xlsx", "A 38023-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 52377-2025 artfynd.xlsx", "A 52377-2025")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 38023-2026 karta.png", "A 38023-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 52377-2025 karta.png", "A 52377-2025")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 38023-2026 georefererad karta.tif", "A 38023-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 52377-2025 georefererad karta.tif", "A 52377-2025")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 38023-2026 FSC-klagomål.docx", "A 38023-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 52377-2025 FSC-klagomål.docx", "A 52377-2025")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 38023-2026 FSC-klagomål mail.docx", "A 38023-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 52377-2025 FSC-klagomål mail.docx", "A 52377-2025")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 38023-2026 tillsynsbegäran.docx", "A 38023-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 52377-2025 tillsynsbegäran.docx", "A 52377-2025")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 38023-2026 tillsynsbegäran mail.docx", "A 38023-2026")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 38023-2026 prioriterade fågelarter.docx", "A 38023-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 52377-2025 tillsynsbegäran mail.docx", "A 52377-2025")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 39936-2024</t>
+          <t>A 25093-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2873,10 +2850,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45553</v>
+        <v>46175</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2888,84 +2865,88 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>6.4</v>
+        <v>4</v>
       </c>
       <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
         <v>1</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
       <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
         <v>1</v>
       </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
+      <c r="T21" t="n">
         <v>1</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3</v>
       </c>
       <c r="U21" t="n">
         <v>1</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Storgröe
-Utter</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 39936-2024 artfynd.xlsx", "A 39936-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 25093-2026 artfynd.xlsx", "A 25093-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 39936-2024 karta.png", "A 39936-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 25093-2026 karta.png", "A 25093-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 39936-2024 georefererad karta.tif", "A 39936-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 25093-2026 georefererad karta.tif", "A 25093-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 39936-2024 FSC-klagomål.docx", "A 39936-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 25093-2026 FSC-klagomål.docx", "A 25093-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 39936-2024 FSC-klagomål mail.docx", "A 39936-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 25093-2026 FSC-klagomål mail.docx", "A 25093-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 39936-2024 tillsynsbegäran.docx", "A 39936-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 25093-2026 tillsynsbegäran.docx", "A 25093-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 39936-2024 tillsynsbegäran mail.docx", "A 39936-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 25093-2026 tillsynsbegäran mail.docx", "A 25093-2026")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 21019-2026</t>
+          <t>A 28474-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2979,10 +2960,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46145</v>
+        <v>45103</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2994,13 +2975,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -3009,7 +2985,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -3024,7 +3000,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -3036,46 +3012,50 @@
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Blåhake</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 21019-2026 artfynd.xlsx", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 28474-2023 artfynd.xlsx", "A 28474-2023")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 21019-2026 karta.png", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 28474-2023 karta.png", "A 28474-2023")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 21019-2026 georefererad karta.tif", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 28474-2023 georefererad karta.tif", "A 28474-2023")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 21019-2026 FSC-klagomål.docx", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 28474-2023 FSC-klagomål.docx", "A 28474-2023")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 21019-2026 FSC-klagomål mail.docx", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 28474-2023 FSC-klagomål mail.docx", "A 28474-2023")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 21019-2026 tillsynsbegäran.docx", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 28474-2023 tillsynsbegäran.docx", "A 28474-2023")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 21019-2026 tillsynsbegäran mail.docx", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 28474-2023 tillsynsbegäran mail.docx", "A 28474-2023")</f>
+        <v/>
+      </c>
+      <c r="AE22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 28474-2023 prioriterade fågelarter.docx", "A 28474-2023")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 52377-2025</t>
+          <t>A 58091-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3089,10 +3069,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45953</v>
+        <v>44900</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3110,7 +3090,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -3143,49 +3123,49 @@
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Hårklomossa</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 52377-2025 artfynd.xlsx", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 58091-2022 artfynd.xlsx", "A 58091-2022")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 52377-2025 karta.png", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 58091-2022 karta.png", "A 58091-2022")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 52377-2025 georefererad karta.tif", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 58091-2022 georefererad karta.tif", "A 58091-2022")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 52377-2025 FSC-klagomål.docx", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 58091-2022 FSC-klagomål.docx", "A 58091-2022")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 52377-2025 FSC-klagomål mail.docx", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 58091-2022 FSC-klagomål mail.docx", "A 58091-2022")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 52377-2025 tillsynsbegäran.docx", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 58091-2022 tillsynsbegäran.docx", "A 58091-2022")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 52377-2025 tillsynsbegäran mail.docx", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 58091-2022 tillsynsbegäran mail.docx", "A 58091-2022")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 28474-2023</t>
+          <t>A 63188-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3199,10 +3179,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45103</v>
+        <v>46010</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3214,8 +3194,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>5.1</v>
+        <v>1.1</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3248,53 +3233,53 @@
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Blåhake</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 28474-2023 artfynd.xlsx", "A 28474-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 63188-2025 artfynd.xlsx", "A 63188-2025")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 28474-2023 karta.png", "A 28474-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 63188-2025 karta.png", "A 63188-2025")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 28474-2023 georefererad karta.tif", "A 28474-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 63188-2025 georefererad karta.tif", "A 63188-2025")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 28474-2023 FSC-klagomål.docx", "A 28474-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 63188-2025 FSC-klagomål.docx", "A 63188-2025")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 28474-2023 FSC-klagomål mail.docx", "A 28474-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 63188-2025 FSC-klagomål mail.docx", "A 63188-2025")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 28474-2023 tillsynsbegäran.docx", "A 28474-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 63188-2025 tillsynsbegäran.docx", "A 63188-2025")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 28474-2023 tillsynsbegäran mail.docx", "A 28474-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 63188-2025 tillsynsbegäran mail.docx", "A 63188-2025")</f>
         <v/>
       </c>
       <c r="AE24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 28474-2023 prioriterade fågelarter.docx", "A 28474-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 63188-2025 prioriterade fågelarter.docx", "A 63188-2025")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 58091-2022</t>
+          <t>A 16784-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3308,10 +3293,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44900</v>
+        <v>46113</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3329,7 +3314,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3373,38 +3358,38 @@
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 58091-2022 artfynd.xlsx", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 16784-2026 artfynd.xlsx", "A 16784-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 58091-2022 karta.png", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 16784-2026 karta.png", "A 16784-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 58091-2022 georefererad karta.tif", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 16784-2026 georefererad karta.tif", "A 16784-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 58091-2022 FSC-klagomål.docx", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 16784-2026 FSC-klagomål.docx", "A 16784-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 58091-2022 FSC-klagomål mail.docx", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 16784-2026 FSC-klagomål mail.docx", "A 16784-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 58091-2022 tillsynsbegäran.docx", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 16784-2026 tillsynsbegäran.docx", "A 16784-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 58091-2022 tillsynsbegäran mail.docx", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 16784-2026 tillsynsbegäran mail.docx", "A 16784-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 25093-2026</t>
+          <t>A 28566-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3418,10 +3403,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46175</v>
+        <v>45478</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3433,19 +3418,14 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -3479,42 +3459,42 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 25093-2026 artfynd.xlsx", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 28566-2024 artfynd.xlsx", "A 28566-2024")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 25093-2026 karta.png", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 28566-2024 karta.png", "A 28566-2024")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 25093-2026 georefererad karta.tif", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 28566-2024 georefererad karta.tif", "A 28566-2024")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 25093-2026 FSC-klagomål.docx", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 28566-2024 FSC-klagomål.docx", "A 28566-2024")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 25093-2026 FSC-klagomål mail.docx", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 28566-2024 FSC-klagomål mail.docx", "A 28566-2024")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 25093-2026 tillsynsbegäran.docx", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 28566-2024 tillsynsbegäran.docx", "A 28566-2024")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 25093-2026 tillsynsbegäran mail.docx", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 28566-2024 tillsynsbegäran mail.docx", "A 28566-2024")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 28566-2024</t>
+          <t>A 18427-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3528,10 +3508,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45478</v>
+        <v>46127</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3543,8 +3523,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
@@ -3584,42 +3569,46 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 28566-2024 artfynd.xlsx", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 18427-2026 artfynd.xlsx", "A 18427-2026")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 28566-2024 karta.png", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 18427-2026 karta.png", "A 18427-2026")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 28566-2024 georefererad karta.tif", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 18427-2026 georefererad karta.tif", "A 18427-2026")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 28566-2024 FSC-klagomål.docx", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 18427-2026 FSC-klagomål.docx", "A 18427-2026")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 28566-2024 FSC-klagomål mail.docx", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 18427-2026 FSC-klagomål mail.docx", "A 18427-2026")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 28566-2024 tillsynsbegäran.docx", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 18427-2026 tillsynsbegäran.docx", "A 18427-2026")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 28566-2024 tillsynsbegäran mail.docx", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 18427-2026 tillsynsbegäran mail.docx", "A 18427-2026")</f>
+        <v/>
+      </c>
+      <c r="AE27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 18427-2026 prioriterade fågelarter.docx", "A 18427-2026")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 63188-2025</t>
+          <t>A 19233-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3633,10 +3622,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46010</v>
+        <v>46132</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3648,22 +3637,17 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
         <v>1</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
       <c r="L28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -3678,7 +3662,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -3687,53 +3671,49 @@
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 63188-2025 artfynd.xlsx", "A 63188-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 19233-2026 artfynd.xlsx", "A 19233-2026")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 63188-2025 karta.png", "A 63188-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 19233-2026 karta.png", "A 19233-2026")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 63188-2025 georefererad karta.tif", "A 63188-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 19233-2026 georefererad karta.tif", "A 19233-2026")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 63188-2025 FSC-klagomål.docx", "A 63188-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 19233-2026 FSC-klagomål.docx", "A 19233-2026")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 63188-2025 FSC-klagomål mail.docx", "A 63188-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 19233-2026 FSC-klagomål mail.docx", "A 19233-2026")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 63188-2025 tillsynsbegäran.docx", "A 63188-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 19233-2026 tillsynsbegäran.docx", "A 19233-2026")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 63188-2025 tillsynsbegäran mail.docx", "A 63188-2025")</f>
-        <v/>
-      </c>
-      <c r="AE28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 63188-2025 prioriterade fågelarter.docx", "A 63188-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 19233-2026 tillsynsbegäran mail.docx", "A 19233-2026")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 16784-2026</t>
+          <t>A 30915-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3747,10 +3727,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46113</v>
+        <v>46213</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3764,11 +3744,11 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>4.2</v>
+        <v>8.9</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -3801,49 +3781,49 @@
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Hårklomossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 16784-2026 artfynd.xlsx", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 30915-2026 artfynd.xlsx", "A 30915-2026")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 16784-2026 karta.png", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 30915-2026 karta.png", "A 30915-2026")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 16784-2026 georefererad karta.tif", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 30915-2026 georefererad karta.tif", "A 30915-2026")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 16784-2026 FSC-klagomål.docx", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 30915-2026 FSC-klagomål.docx", "A 30915-2026")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 16784-2026 FSC-klagomål mail.docx", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 30915-2026 FSC-klagomål mail.docx", "A 30915-2026")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 16784-2026 tillsynsbegäran.docx", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 30915-2026 tillsynsbegäran.docx", "A 30915-2026")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 16784-2026 tillsynsbegäran mail.docx", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 30915-2026 tillsynsbegäran mail.docx", "A 30915-2026")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 18427-2026</t>
+          <t>A 35199-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3857,10 +3837,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46127</v>
+        <v>46260</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3874,11 +3854,11 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3</v>
+        <v>5.6</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
@@ -3887,7 +3867,7 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -3902,7 +3882,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -3914,50 +3894,46 @@
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 18427-2026 artfynd.xlsx", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 35199-2026 artfynd.xlsx", "A 35199-2026")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 18427-2026 karta.png", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 35199-2026 karta.png", "A 35199-2026")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 18427-2026 georefererad karta.tif", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 35199-2026 georefererad karta.tif", "A 35199-2026")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 18427-2026 FSC-klagomål.docx", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 35199-2026 FSC-klagomål.docx", "A 35199-2026")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 18427-2026 FSC-klagomål mail.docx", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 35199-2026 FSC-klagomål mail.docx", "A 35199-2026")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 18427-2026 tillsynsbegäran.docx", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 35199-2026 tillsynsbegäran.docx", "A 35199-2026")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 18427-2026 tillsynsbegäran mail.docx", "A 18427-2026")</f>
-        <v/>
-      </c>
-      <c r="AE30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 18427-2026 prioriterade fågelarter.docx", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 35199-2026 tillsynsbegäran mail.docx", "A 35199-2026")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 19233-2026</t>
+          <t>A 40528-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3971,10 +3947,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46132</v>
+        <v>45555</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3987,13 +3963,13 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -4023,46 +3999,46 @@
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 19233-2026 artfynd.xlsx", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 40528-2024 artfynd.xlsx", "A 40528-2024")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 19233-2026 karta.png", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 40528-2024 karta.png", "A 40528-2024")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 19233-2026 georefererad karta.tif", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 40528-2024 georefererad karta.tif", "A 40528-2024")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 19233-2026 FSC-klagomål.docx", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 40528-2024 FSC-klagomål.docx", "A 40528-2024")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 19233-2026 FSC-klagomål mail.docx", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 40528-2024 FSC-klagomål mail.docx", "A 40528-2024")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 19233-2026 tillsynsbegäran.docx", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 40528-2024 tillsynsbegäran.docx", "A 40528-2024")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 19233-2026 tillsynsbegäran mail.docx", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 40528-2024 tillsynsbegäran mail.docx", "A 40528-2024")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 40528-2024</t>
+          <t>A 72803-2021</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4076,10 +4052,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45555</v>
+        <v>44546</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4092,10 +4068,10 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -4122,52 +4098,20 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>1</v>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>Mattlummer</t>
-        </is>
-      </c>
-      <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 40528-2024 artfynd.xlsx", "A 40528-2024")</f>
-        <v/>
-      </c>
-      <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 40528-2024 karta.png", "A 40528-2024")</f>
-        <v/>
-      </c>
-      <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 40528-2024 georefererad karta.tif", "A 40528-2024")</f>
-        <v/>
-      </c>
-      <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 40528-2024 FSC-klagomål.docx", "A 40528-2024")</f>
-        <v/>
-      </c>
-      <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 40528-2024 FSC-klagomål mail.docx", "A 40528-2024")</f>
-        <v/>
-      </c>
-      <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 40528-2024 tillsynsbegäran.docx", "A 40528-2024")</f>
-        <v/>
-      </c>
-      <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 40528-2024 tillsynsbegäran mail.docx", "A 40528-2024")</f>
-        <v/>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V32" s="2" t="inlineStr"/>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 30915-2026</t>
+          <t>A 25548-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4181,10 +4125,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46213</v>
+        <v>44732</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4196,16 +4140,11 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>8.9</v>
+        <v>2.3</v>
       </c>
       <c r="J33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -4232,52 +4171,20 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
         <v>0</v>
       </c>
-      <c r="V33" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 30915-2026 artfynd.xlsx", "A 30915-2026")</f>
-        <v/>
-      </c>
-      <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 30915-2026 karta.png", "A 30915-2026")</f>
-        <v/>
-      </c>
-      <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 30915-2026 georefererad karta.tif", "A 30915-2026")</f>
-        <v/>
-      </c>
-      <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 30915-2026 FSC-klagomål.docx", "A 30915-2026")</f>
-        <v/>
-      </c>
-      <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 30915-2026 FSC-klagomål mail.docx", "A 30915-2026")</f>
-        <v/>
-      </c>
-      <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 30915-2026 tillsynsbegäran.docx", "A 30915-2026")</f>
-        <v/>
-      </c>
-      <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 30915-2026 tillsynsbegäran mail.docx", "A 30915-2026")</f>
-        <v/>
-      </c>
+      <c r="V33" s="2" t="inlineStr"/>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 35199-2026</t>
+          <t>A 64869-2021</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4291,10 +4198,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46260</v>
+        <v>44512</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4308,20 +4215,20 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>5.6</v>
+        <v>3.6</v>
       </c>
       <c r="J34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -4336,58 +4243,26 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
         <v>0</v>
       </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>Nordfladdermus</t>
-        </is>
-      </c>
-      <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 35199-2026 artfynd.xlsx", "A 35199-2026")</f>
-        <v/>
-      </c>
-      <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 35199-2026 karta.png", "A 35199-2026")</f>
-        <v/>
-      </c>
-      <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 35199-2026 georefererad karta.tif", "A 35199-2026")</f>
-        <v/>
-      </c>
-      <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 35199-2026 FSC-klagomål.docx", "A 35199-2026")</f>
-        <v/>
-      </c>
-      <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 35199-2026 FSC-klagomål mail.docx", "A 35199-2026")</f>
-        <v/>
-      </c>
-      <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 35199-2026 tillsynsbegäran.docx", "A 35199-2026")</f>
-        <v/>
-      </c>
-      <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 35199-2026 tillsynsbegäran mail.docx", "A 35199-2026")</f>
-        <v/>
-      </c>
+      <c r="V34" s="2" t="inlineStr"/>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 20110-2026</t>
+          <t>A 22861-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4401,10 +4276,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46136</v>
+        <v>44715</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4416,16 +4291,11 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>5.4</v>
+        <v>0.6</v>
       </c>
       <c r="J35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -4452,52 +4322,20 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>1</v>
-      </c>
-      <c r="V35" s="2" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 20110-2026 artfynd.xlsx", "A 20110-2026")</f>
-        <v/>
-      </c>
-      <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 20110-2026 karta.png", "A 20110-2026")</f>
-        <v/>
-      </c>
-      <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 20110-2026 georefererad karta.tif", "A 20110-2026")</f>
-        <v/>
-      </c>
-      <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 20110-2026 FSC-klagomål.docx", "A 20110-2026")</f>
-        <v/>
-      </c>
-      <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 20110-2026 FSC-klagomål mail.docx", "A 20110-2026")</f>
-        <v/>
-      </c>
-      <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 20110-2026 tillsynsbegäran.docx", "A 20110-2026")</f>
-        <v/>
-      </c>
-      <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 20110-2026 tillsynsbegäran mail.docx", "A 20110-2026")</f>
-        <v/>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V35" s="2" t="inlineStr"/>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 72803-2021</t>
+          <t>A 63671-2021</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4511,10 +4349,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44546</v>
+        <v>44508</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4524,6 +4362,11 @@
       <c r="G36" t="inlineStr">
         <is>
           <t>KARLSKOGA</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I36" t="n">
@@ -4570,7 +4413,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 25548-2022</t>
+          <t>A 56435-2021</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4584,10 +4427,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44732</v>
+        <v>44480</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4600,7 +4443,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4643,7 +4486,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 50991-2021</t>
+          <t>A 37582-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4657,10 +4500,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44460</v>
+        <v>44809</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4716,7 +4559,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 64869-2021</t>
+          <t>A 38012-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4730,10 +4573,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44512</v>
+        <v>44811</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4745,13 +4588,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4794,7 +4632,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 22861-2022</t>
+          <t>A 11081-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4804,14 +4642,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44715</v>
+        <v>44628</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4823,8 +4661,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4867,7 +4710,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 63671-2021</t>
+          <t>A 37584-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4881,10 +4724,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44508</v>
+        <v>44809</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4896,13 +4739,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>4.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4945,7 +4783,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 56435-2021</t>
+          <t>A 21612-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4959,10 +4797,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44480</v>
+        <v>44706</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4975,7 +4813,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -5018,7 +4856,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 37582-2022</t>
+          <t>A 21622-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5032,10 +4870,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44809</v>
+        <v>44706</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5091,7 +4929,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 38012-2022</t>
+          <t>A 39027-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5105,10 +4943,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44811</v>
+        <v>44817</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5120,8 +4958,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>3.7</v>
+        <v>1.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5164,7 +5007,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 11081-2022</t>
+          <t>A 35471-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5174,14 +5017,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44628</v>
+        <v>45531</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5193,13 +5036,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5242,7 +5080,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 37584-2022</t>
+          <t>A 58390-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5256,10 +5094,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44809</v>
+        <v>45633</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5272,7 +5110,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>4.9</v>
+        <v>3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5315,7 +5153,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 21612-2022</t>
+          <t>A 9712-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5329,10 +5167,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44706</v>
+        <v>45362</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5344,8 +5182,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5388,7 +5231,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 21622-2022</t>
+          <t>A 42804-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5398,14 +5241,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44706</v>
+        <v>45182</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5417,8 +5260,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5461,7 +5309,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 39027-2022</t>
+          <t>A 9510-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5475,10 +5323,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44817</v>
+        <v>44981</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5490,13 +5338,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5539,7 +5382,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 58390-2024</t>
+          <t>A 1309-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5553,10 +5396,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45633</v>
+        <v>45303</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5569,7 +5412,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5629,7 +5472,7 @@
         <v>44588</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5690,7 +5533,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 9712-2024</t>
+          <t>A 23263-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5704,10 +5547,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45362</v>
+        <v>44720</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5719,13 +5562,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5768,7 +5606,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 42804-2023</t>
+          <t>A 35444-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5778,14 +5616,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45182</v>
+        <v>45531</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5797,13 +5635,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5846,7 +5679,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 9510-2023</t>
+          <t>A 61396-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5860,10 +5693,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44981</v>
+        <v>45264</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5876,7 +5709,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5919,7 +5752,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 1309-2024</t>
+          <t>A 8259-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5933,10 +5766,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45303</v>
+        <v>45708</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5949,7 +5782,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>4</v>
+        <v>0.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5992,7 +5825,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 35471-2024</t>
+          <t>A 24116-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6006,10 +5839,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45531</v>
+        <v>45456</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6022,7 +5855,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -6065,7 +5898,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 35444-2024</t>
+          <t>A 47201-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6079,10 +5912,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45531</v>
+        <v>45196</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6095,7 +5928,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6138,7 +5971,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 23263-2022</t>
+          <t>A 35930-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6152,10 +5985,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44720</v>
+        <v>45148</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6167,8 +6000,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>2.2</v>
+        <v>5.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6211,7 +6049,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 47201-2023</t>
+          <t>A 63863-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6225,10 +6063,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45196</v>
+        <v>45278</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6241,7 +6079,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6284,7 +6122,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 61396-2023</t>
+          <t>A 59938-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6298,10 +6136,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45264</v>
+        <v>45257</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6314,7 +6152,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6357,7 +6195,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 8259-2025</t>
+          <t>A 52828-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6371,10 +6209,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45708</v>
+        <v>45610</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6387,7 +6225,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6430,7 +6268,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 24116-2024</t>
+          <t>A 15256-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6444,10 +6282,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45456</v>
+        <v>45744</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6459,8 +6297,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>1.8</v>
+        <v>5.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6503,7 +6346,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 35930-2023</t>
+          <t>A 24115-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6517,10 +6360,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45148</v>
+        <v>45456</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6532,13 +6375,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>5.2</v>
+        <v>8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6581,7 +6419,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 63863-2023</t>
+          <t>A 19663-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6595,10 +6433,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45278</v>
+        <v>46134</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6610,8 +6448,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6654,7 +6497,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 59938-2023</t>
+          <t>A 17815-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6668,10 +6511,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45257</v>
+        <v>45758</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6683,8 +6526,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6727,7 +6575,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 52828-2024</t>
+          <t>A 18768-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6741,10 +6589,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45610</v>
+        <v>45764</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6756,8 +6604,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>8.300000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6800,7 +6653,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 15256-2025</t>
+          <t>A 4801-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6814,10 +6667,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45744</v>
+        <v>45328</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6829,13 +6682,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>5.5</v>
+        <v>0.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6878,7 +6726,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 24115-2024</t>
+          <t>A 4802-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6892,10 +6740,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45456</v>
+        <v>45328</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6908,7 +6756,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>8</v>
+        <v>0.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6951,7 +6799,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 18768-2025</t>
+          <t>A 6835-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6965,10 +6813,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45764</v>
+        <v>45700</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6980,13 +6828,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7029,7 +6872,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 4801-2024</t>
+          <t>A 8990-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7043,10 +6886,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45328</v>
+        <v>44979</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7059,7 +6902,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7102,7 +6945,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 4802-2024</t>
+          <t>A 24255-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7116,10 +6959,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45328</v>
+        <v>45457</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7132,7 +6975,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7175,7 +7018,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 8990-2023</t>
+          <t>A 21210-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7189,10 +7032,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44979</v>
+        <v>45779</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7204,8 +7047,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7248,7 +7096,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 42802-2023</t>
+          <t>A 23717-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7258,14 +7106,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45182</v>
+        <v>45793</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7277,13 +7125,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7326,7 +7169,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 6835-2025</t>
+          <t>A 42802-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7336,14 +7179,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45700</v>
+        <v>45182</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7355,8 +7198,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7399,7 +7247,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 28471-2023</t>
+          <t>A 44946-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7413,10 +7261,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45103</v>
+        <v>45918</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7429,7 +7277,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7472,7 +7320,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 22867-2022</t>
+          <t>A 44949-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7486,10 +7334,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44715</v>
+        <v>45918</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7545,7 +7393,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 64060-2023</t>
+          <t>A 28471-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7559,10 +7407,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45279</v>
+        <v>45103</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7575,7 +7423,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7618,7 +7466,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 24255-2024</t>
+          <t>A 22867-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7632,10 +7480,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45457</v>
+        <v>44715</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7648,7 +7496,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7691,7 +7539,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 48707-2024</t>
+          <t>A 64060-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7705,10 +7553,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45593</v>
+        <v>45279</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7721,7 +7569,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>6</v>
+        <v>1.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7764,7 +7612,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 17815-2025</t>
+          <t>A 48707-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7778,10 +7626,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45758</v>
+        <v>45593</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7793,13 +7641,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7842,7 +7685,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 21210-2025</t>
+          <t>A 55832-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7856,10 +7699,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45779</v>
+        <v>45239</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7871,13 +7714,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7920,7 +7758,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 23717-2025</t>
+          <t>A 917-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7934,10 +7772,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45793</v>
+        <v>46030</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7950,7 +7788,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.1</v>
+        <v>3.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7993,7 +7831,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 55832-2023</t>
+          <t>A 21253-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8007,10 +7845,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45239</v>
+        <v>46147</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8023,7 +7861,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8083,7 +7921,7 @@
         <v>45633</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8139,7 +7977,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 18978-2025</t>
+          <t>A 21257-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8153,10 +7991,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45764</v>
+        <v>46147</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8169,7 +8007,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8212,7 +8050,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 917-2026</t>
+          <t>A 3227-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8226,10 +8064,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46030</v>
+        <v>45679</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8242,7 +8080,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8285,7 +8123,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 44946-2025</t>
+          <t>A 18978-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8299,10 +8137,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45918</v>
+        <v>45764</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8315,7 +8153,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8358,7 +8196,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 44949-2025</t>
+          <t>A 50958-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8372,10 +8210,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45918</v>
+        <v>45946</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8388,7 +8226,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8448,7 +8286,7 @@
         <v>44777</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8521,7 +8359,7 @@
         <v>45182</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8594,7 +8432,7 @@
         <v>45196</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8667,7 +8505,7 @@
         <v>44645</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8723,7 +8561,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 53618-2024</t>
+          <t>A 55025-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8737,10 +8575,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45614</v>
+        <v>45967</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8753,7 +8591,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>10.1</v>
+        <v>2.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8796,7 +8634,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 21253-2026</t>
+          <t>A 53618-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8810,10 +8648,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46147</v>
+        <v>45614</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8826,7 +8664,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3.4</v>
+        <v>10.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8886,7 +8724,7 @@
         <v>44768</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8947,7 +8785,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 21257-2026</t>
+          <t>A 23754-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8961,10 +8799,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46147</v>
+        <v>46164</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8976,8 +8814,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I96" t="n">
-        <v>2.7</v>
+        <v>12.2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9020,7 +8863,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 42803-2023</t>
+          <t>A 4587-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9030,14 +8873,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45182</v>
+        <v>45687</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9049,13 +8892,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I97" t="n">
-        <v>0.7</v>
+        <v>3.3</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9098,7 +8936,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 8803-2025</t>
+          <t>A 42803-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9108,14 +8946,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45712</v>
+        <v>45182</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9127,8 +8965,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I98" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9171,7 +9014,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 50958-2025</t>
+          <t>A 8803-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9185,10 +9028,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45946</v>
+        <v>45712</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9201,7 +9044,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9244,7 +9087,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 56313-2024</t>
+          <t>A 4587-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9258,10 +9101,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45624</v>
+        <v>45687</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9273,13 +9116,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9322,7 +9160,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 10743-2023</t>
+          <t>A 59522-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9332,14 +9170,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44988</v>
+        <v>45989</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9353,11 +9191,11 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9400,7 +9238,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 14215-2024</t>
+          <t>A 24666-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9414,10 +9252,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45393</v>
+        <v>46171</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9429,13 +9267,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>4.2</v>
+        <v>6.1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9478,7 +9311,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 55191-2023</t>
+          <t>A 60506-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9492,10 +9325,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45237</v>
+        <v>45995</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9508,7 +9341,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9551,7 +9384,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 59025-2024</t>
+          <t>A 60508-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9565,10 +9398,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45636</v>
+        <v>45995</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9580,13 +9413,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I104" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9629,7 +9457,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 55025-2025</t>
+          <t>A 60503-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9643,10 +9471,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45967</v>
+        <v>45995</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9659,7 +9487,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9702,7 +9530,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 3227-2025</t>
+          <t>A 56313-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9716,10 +9544,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45679</v>
+        <v>45624</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9731,8 +9559,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I106" t="n">
-        <v>4.5</v>
+        <v>2.2</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9775,7 +9608,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 17243-2024</t>
+          <t>A 10743-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9789,10 +9622,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45414</v>
+        <v>44988</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9804,8 +9637,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9848,7 +9686,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 35060-2024</t>
+          <t>A 25092-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9862,10 +9700,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45527</v>
+        <v>46175</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9879,11 +9717,11 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9926,7 +9764,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 59522-2025</t>
+          <t>A 14215-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9936,14 +9774,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45989</v>
+        <v>45393</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9957,11 +9795,11 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2.6</v>
+        <v>4.2</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10004,7 +9842,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 52826-2024</t>
+          <t>A 55191-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10018,10 +9856,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45610</v>
+        <v>45237</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10034,7 +9872,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10077,7 +9915,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 52829-2024</t>
+          <t>A 25098-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10087,14 +9925,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45610</v>
+        <v>46175</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10106,8 +9944,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I111" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10150,7 +9993,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 11974-2025</t>
+          <t>A 61788-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10164,10 +10007,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45728</v>
+        <v>46002</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10179,8 +10022,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I112" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10223,7 +10071,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 60506-2025</t>
+          <t>A 59025-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10237,10 +10085,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45995</v>
+        <v>45636</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10252,8 +10100,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I113" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10296,7 +10149,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 60508-2025</t>
+          <t>A 64066-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10306,14 +10159,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45995</v>
+        <v>46013</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10326,7 +10179,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10369,7 +10222,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 60503-2025</t>
+          <t>A 63628-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10383,10 +10236,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45995</v>
+        <v>46014</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10399,7 +10252,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>2.2</v>
+        <v>3.8</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10442,7 +10295,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 61271-2022</t>
+          <t>A 17243-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10456,10 +10309,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44909</v>
+        <v>45414</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10471,13 +10324,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>14.1</v>
+        <v>3.2</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10520,7 +10368,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 23754-2026</t>
+          <t>A 1788-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10534,10 +10382,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46164</v>
+        <v>46034</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10549,13 +10397,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I117" t="n">
-        <v>12.2</v>
+        <v>3.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10598,7 +10441,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 48168-2024</t>
+          <t>A 26608-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10612,10 +10455,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45589</v>
+        <v>46184</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10627,8 +10470,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I118" t="n">
-        <v>5.5</v>
+        <v>1.6</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10671,7 +10519,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 61788-2025</t>
+          <t>A 35060-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10685,10 +10533,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46002</v>
+        <v>45527</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10706,7 +10554,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10749,7 +10597,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 4587-2025</t>
+          <t>A 27120-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10763,10 +10611,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45687</v>
+        <v>46188</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10779,7 +10627,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>3.3</v>
+        <v>4.7</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10822,7 +10670,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 18955-2025</t>
+          <t>A 26819-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10836,10 +10684,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45764</v>
+        <v>46185</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10851,8 +10699,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I121" t="n">
-        <v>8.1</v>
+        <v>2.4</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10895,7 +10748,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 64066-2025</t>
+          <t>A 3239-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10905,14 +10758,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46013</v>
+        <v>46041</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10925,7 +10778,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10968,7 +10821,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 50614-2024</t>
+          <t>A 45664-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10982,10 +10835,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45601</v>
+        <v>45923</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10997,8 +10850,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I123" t="n">
-        <v>0.7</v>
+        <v>9</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -11041,7 +10899,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 63628-2025</t>
+          <t>A 2911-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11055,10 +10913,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46014</v>
+        <v>46038</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11071,7 +10929,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>3.8</v>
+        <v>1.1</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -11114,7 +10972,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 4587-2025</t>
+          <t>A 26820-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11128,10 +10986,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45687</v>
+        <v>46185</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11143,8 +11001,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I125" t="n">
-        <v>3.3</v>
+        <v>9.9</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11187,7 +11050,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 55182-2024</t>
+          <t>A 26821-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11201,10 +11064,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45618</v>
+        <v>46185</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11216,8 +11079,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I126" t="n">
-        <v>11.4</v>
+        <v>7.9</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11260,7 +11128,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 4058-2022</t>
+          <t>A 26822-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11274,10 +11142,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44588</v>
+        <v>46185</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11289,8 +11157,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I127" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11333,7 +11206,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 1788-2026</t>
+          <t>A 26824-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11347,10 +11220,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46034</v>
+        <v>46185</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11362,8 +11235,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I128" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11406,7 +11284,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 24666-2026</t>
+          <t>A 26825-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11420,10 +11298,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46171</v>
+        <v>46185</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11435,8 +11313,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I129" t="n">
-        <v>6.1</v>
+        <v>0.8</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11479,7 +11362,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 45664-2025</t>
+          <t>A 47222-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11493,10 +11376,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45923</v>
+        <v>45586</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11514,7 +11397,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>9</v>
+        <v>5.3</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11557,7 +11440,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 2911-2026</t>
+          <t>A 27392-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11571,10 +11454,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46038</v>
+        <v>46189</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11586,8 +11469,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I131" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11630,7 +11518,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 47222-2024</t>
+          <t>A 52826-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11644,10 +11532,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45586</v>
+        <v>45610</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11659,13 +11547,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>5.3</v>
+        <v>2.2</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11708,7 +11591,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 25092-2026</t>
+          <t>A 52829-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11722,10 +11605,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46175</v>
+        <v>45610</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11737,13 +11620,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I133" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11786,7 +11664,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 28100-2024</t>
+          <t>A 11974-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11800,10 +11678,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45476</v>
+        <v>45728</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11816,7 +11694,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11859,7 +11737,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 25098-2026</t>
+          <t>A 61271-2022</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11869,14 +11747,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46175</v>
+        <v>44909</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11890,11 +11768,11 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.4</v>
+        <v>14.1</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11937,7 +11815,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 1106-2024</t>
+          <t>A 48168-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11951,10 +11829,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45302</v>
+        <v>45589</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11967,7 +11845,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.9</v>
+        <v>5.5</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -12010,7 +11888,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 39030-2022</t>
+          <t>A 18955-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12024,10 +11902,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44817</v>
+        <v>45764</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12039,13 +11917,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I137" t="n">
-        <v>1</v>
+        <v>8.1</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -12088,7 +11961,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 38382-2022</t>
+          <t>A 9917-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12102,10 +11975,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44812</v>
+        <v>46073</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12117,13 +11990,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I138" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -12166,7 +12034,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 16881-2023</t>
+          <t>A 50614-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12180,10 +12048,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45033</v>
+        <v>45601</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12195,13 +12063,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I139" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12244,7 +12107,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 9917-2026</t>
+          <t>A 55182-2024</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12258,10 +12121,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46073</v>
+        <v>45618</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12274,7 +12137,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>3.1</v>
+        <v>11.4</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12317,7 +12180,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 26608-2026</t>
+          <t>A 4058-2022</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12331,10 +12194,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46184</v>
+        <v>44588</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12346,13 +12209,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I141" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12395,7 +12253,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 57422-2021</t>
+          <t>A 13473-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12409,10 +12267,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44483</v>
+        <v>46094</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12425,7 +12283,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12468,7 +12326,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 27120-2026</t>
+          <t>A 12897-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12482,10 +12340,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46188</v>
+        <v>46092</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12498,7 +12356,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>4.7</v>
+        <v>1.3</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12541,7 +12399,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 26819-2026</t>
+          <t>A 14580-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12555,10 +12413,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46185</v>
+        <v>46101</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12576,7 +12434,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12619,7 +12477,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 3239-2026</t>
+          <t>A 28100-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12633,10 +12491,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46041</v>
+        <v>45476</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12649,7 +12507,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12692,7 +12550,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 8244-2025</t>
+          <t>A 16783-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12706,10 +12564,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45708</v>
+        <v>46113</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12721,8 +12579,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I146" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12765,7 +12628,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 26820-2026</t>
+          <t>A 16787-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12779,10 +12642,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46185</v>
+        <v>46113</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12800,7 +12663,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>9.9</v>
+        <v>2.8</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12843,7 +12706,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 26821-2026</t>
+          <t>A 16782-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12857,10 +12720,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46185</v>
+        <v>46113</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12878,7 +12741,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>7.9</v>
+        <v>2.6</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12921,7 +12784,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 26822-2026</t>
+          <t>A 15058-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12935,10 +12798,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46185</v>
+        <v>46104</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12950,13 +12813,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I149" t="n">
-        <v>2.2</v>
+        <v>4.3</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12999,7 +12857,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 26824-2026</t>
+          <t>A 1106-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -13013,10 +12871,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46185</v>
+        <v>45302</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13028,13 +12886,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I150" t="n">
-        <v>5</v>
+        <v>1.9</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -13077,7 +12930,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 26825-2026</t>
+          <t>A 39030-2022</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -13091,10 +12944,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46185</v>
+        <v>44817</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13112,7 +12965,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -13155,7 +13008,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 38190-2024</t>
+          <t>A 17734-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13169,10 +13022,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45545</v>
+        <v>46122</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13184,8 +13037,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I152" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -13228,7 +13086,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 13473-2026</t>
+          <t>A 38382-2022</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13242,10 +13100,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46094</v>
+        <v>44812</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13257,8 +13115,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I153" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -13301,7 +13164,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 20463-2025</t>
+          <t>A 19009-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13315,10 +13178,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45775</v>
+        <v>46130</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13336,7 +13199,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>0.9</v>
+        <v>6.3</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13379,7 +13242,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 27392-2026</t>
+          <t>A 19011-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13393,10 +13256,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46189</v>
+        <v>46130</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13414,7 +13277,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13457,7 +13320,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 12897-2026</t>
+          <t>A 19010-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13471,10 +13334,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46092</v>
+        <v>46130</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13486,8 +13349,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I156" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13530,7 +13398,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 14580-2026</t>
+          <t>A 19008-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13544,10 +13412,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46101</v>
+        <v>46130</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13565,7 +13433,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13608,7 +13476,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 35470-2024</t>
+          <t>A 16881-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13622,10 +13490,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45531</v>
+        <v>45033</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13637,8 +13505,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I158" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13681,7 +13554,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 35445-2024</t>
+          <t>A 57422-2021</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13695,10 +13568,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45531</v>
+        <v>44483</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13711,7 +13584,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13754,7 +13627,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 47094-2023</t>
+          <t>A 8244-2025</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13768,10 +13641,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45196</v>
+        <v>45708</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13784,7 +13657,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13827,7 +13700,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 38196-2024</t>
+          <t>A 38190-2024</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13844,7 +13717,7 @@
         <v>45545</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13857,7 +13730,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13900,7 +13773,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 16783-2026</t>
+          <t>A 31378-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13914,10 +13787,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46113</v>
+        <v>46213</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13929,13 +13802,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I162" t="n">
-        <v>1.7</v>
+        <v>3.7</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13978,7 +13846,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 16787-2026</t>
+          <t>A 20463-2025</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13992,10 +13860,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46113</v>
+        <v>45775</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14013,7 +13881,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -14056,7 +13924,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 16782-2026</t>
+          <t>A 35470-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -14070,10 +13938,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46113</v>
+        <v>45531</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14085,13 +13953,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I164" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -14134,7 +13997,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 15058-2026</t>
+          <t>A 35094-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -14148,10 +14011,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46104</v>
+        <v>46260</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14163,8 +14026,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I165" t="n">
-        <v>4.3</v>
+        <v>1.9</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -14207,7 +14075,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 15060-2026</t>
+          <t>A 35445-2024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -14221,10 +14089,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46104</v>
+        <v>45531</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14237,7 +14105,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>11.5</v>
+        <v>0.5</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -14280,7 +14148,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 50611-2024</t>
+          <t>A 47094-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -14294,10 +14162,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45601</v>
+        <v>45196</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14310,7 +14178,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14353,7 +14221,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 17734-2026</t>
+          <t>A 38196-2024</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14367,10 +14235,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46122</v>
+        <v>45545</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14382,13 +14250,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I168" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14431,7 +14294,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 20289-2024</t>
+          <t>A 50611-2024</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14445,10 +14308,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45435</v>
+        <v>45601</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14460,13 +14323,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I169" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14509,7 +14367,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 52797-2021</t>
+          <t>A 35699-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14519,14 +14377,14 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>44467</v>
+        <v>46265</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14538,8 +14396,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I170" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14582,7 +14445,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 19009-2026</t>
+          <t>A 20289-2024</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14596,10 +14459,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46130</v>
+        <v>45435</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14617,7 +14480,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>6.3</v>
+        <v>0.7</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14660,7 +14523,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 19011-2026</t>
+          <t>A 52797-2021</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14674,10 +14537,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46130</v>
+        <v>44467</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14689,13 +14552,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I172" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14738,7 +14596,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 19010-2026</t>
+          <t>A 20086-2024</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14748,14 +14606,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46130</v>
+        <v>45434</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14767,13 +14625,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I173" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14816,7 +14669,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 19008-2026</t>
+          <t>A 36374-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14830,10 +14683,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46130</v>
+        <v>46268</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14847,11 +14700,11 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14894,7 +14747,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 20086-2024</t>
+          <t>A 13496-2025</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14904,14 +14757,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45434</v>
+        <v>45736</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14924,7 +14777,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14967,7 +14820,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 19663-2026</t>
+          <t>A 56887-2022</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14981,10 +14834,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46134</v>
+        <v>44894</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14996,13 +14849,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I176" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -15045,7 +14893,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 13496-2025</t>
+          <t>A 37089-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -15059,10 +14907,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45736</v>
+        <v>46273</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15075,7 +14923,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>8.800000000000001</v>
+        <v>15.8</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -15118,7 +14966,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 56887-2022</t>
+          <t>A 33011-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -15132,10 +14980,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>44894</v>
+        <v>45125</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15148,7 +14996,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -15191,7 +15039,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 33011-2023</t>
+          <t>A 51344-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -15205,10 +15053,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45125</v>
+        <v>45219</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15220,8 +15068,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I179" t="n">
-        <v>0.8</v>
+        <v>4.5</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -15264,7 +15117,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 51344-2023</t>
+          <t>A 38043-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -15278,10 +15131,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45219</v>
+        <v>46280</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15295,11 +15148,11 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I180" t="n">
-        <v>4.5</v>
+        <v>1.1</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -15342,7 +15195,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 31378-2026</t>
+          <t>A 38020-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15356,10 +15209,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46213</v>
+        <v>46280</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15371,8 +15224,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I181" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15432,7 +15290,7 @@
         <v>44987</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15505,7 +15363,7 @@
         <v>44817</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15561,7 +15419,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 35094-2026</t>
+          <t>A 53620-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15575,10 +15433,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46260</v>
+        <v>45614</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15590,13 +15448,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I184" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15639,7 +15492,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 53620-2024</t>
+          <t>A 13501-2025</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15653,10 +15506,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45614</v>
+        <v>45736</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15669,7 +15522,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>0.7</v>
+        <v>3.2</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15712,7 +15565,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 35699-2026</t>
+          <t>A 10404-2022</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15722,14 +15575,14 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46265</v>
+        <v>44623</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15741,13 +15594,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I186" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15790,7 +15638,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 13501-2025</t>
+          <t>A 38742-2023</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15800,14 +15648,14 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45736</v>
+        <v>45161</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15819,8 +15667,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I187" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15863,7 +15716,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 10404-2022</t>
+          <t>A 3735-2024</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15877,10 +15730,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>44623</v>
+        <v>45321</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15892,8 +15745,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I188" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15936,7 +15794,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 36374-2026</t>
+          <t>A 23308-2025</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15950,10 +15808,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46268</v>
+        <v>45791</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15965,13 +15823,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I189" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -16014,7 +15867,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 37089-2026</t>
+          <t>A 27498-2025</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -16028,10 +15881,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46273</v>
+        <v>45813</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16044,7 +15897,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>15.8</v>
+        <v>1.2</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -16087,7 +15940,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 38742-2023</t>
+          <t>A 23620-2024</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -16097,14 +15950,14 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45161</v>
+        <v>45454</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16116,13 +15969,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I191" t="n">
-        <v>4.2</v>
+        <v>2.2</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -16165,7 +16013,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 3735-2024</t>
+          <t>A 53647-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -16179,10 +16027,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45321</v>
+        <v>45230</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16194,13 +16042,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I192" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -16243,7 +16086,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 38043-2026</t>
+          <t>A 30102-2025</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -16257,10 +16100,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46280</v>
+        <v>45826</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16272,13 +16115,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I193" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -16321,7 +16159,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 23308-2025</t>
+          <t>A 54680-2021</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -16335,10 +16173,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45791</v>
+        <v>44473</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16351,7 +16189,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -16394,7 +16232,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 38020-2026</t>
+          <t>A 31397-2025</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16408,10 +16246,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46280</v>
+        <v>45833</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16423,13 +16261,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I195" t="n">
-        <v>4.1</v>
+        <v>1.5</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -16472,7 +16305,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 27498-2025</t>
+          <t>A 32287-2025</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16486,10 +16319,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45813</v>
+        <v>45835</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16501,8 +16334,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I196" t="n">
-        <v>1.2</v>
+        <v>10.9</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16542,27 +16380,27 @@
       </c>
       <c r="V196" s="2" t="inlineStr"/>
     </row>
-    <row r="197" ht="15" customHeight="1">
+    <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 23620-2024</t>
+          <t>S 2960-2025</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45454</v>
+        <v>45953</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16574,8 +16412,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I197" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16614,454 +16457,6 @@
         <v>0</v>
       </c>
       <c r="V197" s="2" t="inlineStr"/>
-    </row>
-    <row r="198" ht="15" customHeight="1">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>A 53647-2023</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D198" s="1" t="n">
-        <v>45230</v>
-      </c>
-      <c r="E198" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>KARLSKOGA</t>
-        </is>
-      </c>
-      <c r="I198" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J198" t="n">
-        <v>0</v>
-      </c>
-      <c r="K198" t="n">
-        <v>0</v>
-      </c>
-      <c r="L198" t="n">
-        <v>0</v>
-      </c>
-      <c r="M198" t="n">
-        <v>0</v>
-      </c>
-      <c r="N198" t="n">
-        <v>0</v>
-      </c>
-      <c r="O198" t="n">
-        <v>0</v>
-      </c>
-      <c r="P198" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
-      <c r="R198" t="n">
-        <v>0</v>
-      </c>
-      <c r="S198" t="n">
-        <v>0</v>
-      </c>
-      <c r="T198" t="n">
-        <v>0</v>
-      </c>
-      <c r="U198" t="n">
-        <v>0</v>
-      </c>
-      <c r="V198" s="2" t="inlineStr"/>
-    </row>
-    <row r="199" ht="15" customHeight="1">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>A 30102-2025</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D199" s="1" t="n">
-        <v>45826</v>
-      </c>
-      <c r="E199" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F199" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>KARLSKOGA</t>
-        </is>
-      </c>
-      <c r="I199" t="n">
-        <v>1</v>
-      </c>
-      <c r="J199" t="n">
-        <v>0</v>
-      </c>
-      <c r="K199" t="n">
-        <v>0</v>
-      </c>
-      <c r="L199" t="n">
-        <v>0</v>
-      </c>
-      <c r="M199" t="n">
-        <v>0</v>
-      </c>
-      <c r="N199" t="n">
-        <v>0</v>
-      </c>
-      <c r="O199" t="n">
-        <v>0</v>
-      </c>
-      <c r="P199" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q199" t="n">
-        <v>0</v>
-      </c>
-      <c r="R199" t="n">
-        <v>0</v>
-      </c>
-      <c r="S199" t="n">
-        <v>0</v>
-      </c>
-      <c r="T199" t="n">
-        <v>0</v>
-      </c>
-      <c r="U199" t="n">
-        <v>0</v>
-      </c>
-      <c r="V199" s="2" t="inlineStr"/>
-    </row>
-    <row r="200" ht="15" customHeight="1">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>A 54680-2021</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D200" s="1" t="n">
-        <v>44473</v>
-      </c>
-      <c r="E200" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F200" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>KARLSKOGA</t>
-        </is>
-      </c>
-      <c r="I200" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J200" t="n">
-        <v>0</v>
-      </c>
-      <c r="K200" t="n">
-        <v>0</v>
-      </c>
-      <c r="L200" t="n">
-        <v>0</v>
-      </c>
-      <c r="M200" t="n">
-        <v>0</v>
-      </c>
-      <c r="N200" t="n">
-        <v>0</v>
-      </c>
-      <c r="O200" t="n">
-        <v>0</v>
-      </c>
-      <c r="P200" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
-      <c r="R200" t="n">
-        <v>0</v>
-      </c>
-      <c r="S200" t="n">
-        <v>0</v>
-      </c>
-      <c r="T200" t="n">
-        <v>0</v>
-      </c>
-      <c r="U200" t="n">
-        <v>0</v>
-      </c>
-      <c r="V200" s="2" t="inlineStr"/>
-    </row>
-    <row r="201" ht="15" customHeight="1">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>A 31397-2025</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D201" s="1" t="n">
-        <v>45833</v>
-      </c>
-      <c r="E201" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F201" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>KARLSKOGA</t>
-        </is>
-      </c>
-      <c r="I201" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J201" t="n">
-        <v>0</v>
-      </c>
-      <c r="K201" t="n">
-        <v>0</v>
-      </c>
-      <c r="L201" t="n">
-        <v>0</v>
-      </c>
-      <c r="M201" t="n">
-        <v>0</v>
-      </c>
-      <c r="N201" t="n">
-        <v>0</v>
-      </c>
-      <c r="O201" t="n">
-        <v>0</v>
-      </c>
-      <c r="P201" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q201" t="n">
-        <v>0</v>
-      </c>
-      <c r="R201" t="n">
-        <v>0</v>
-      </c>
-      <c r="S201" t="n">
-        <v>0</v>
-      </c>
-      <c r="T201" t="n">
-        <v>0</v>
-      </c>
-      <c r="U201" t="n">
-        <v>0</v>
-      </c>
-      <c r="V201" s="2" t="inlineStr"/>
-    </row>
-    <row r="202" ht="15" customHeight="1">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>A 32287-2025</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D202" s="1" t="n">
-        <v>45835</v>
-      </c>
-      <c r="E202" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F202" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>KARLSKOGA</t>
-        </is>
-      </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
-      <c r="I202" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="J202" t="n">
-        <v>0</v>
-      </c>
-      <c r="K202" t="n">
-        <v>0</v>
-      </c>
-      <c r="L202" t="n">
-        <v>0</v>
-      </c>
-      <c r="M202" t="n">
-        <v>0</v>
-      </c>
-      <c r="N202" t="n">
-        <v>0</v>
-      </c>
-      <c r="O202" t="n">
-        <v>0</v>
-      </c>
-      <c r="P202" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q202" t="n">
-        <v>0</v>
-      </c>
-      <c r="R202" t="n">
-        <v>0</v>
-      </c>
-      <c r="S202" t="n">
-        <v>0</v>
-      </c>
-      <c r="T202" t="n">
-        <v>0</v>
-      </c>
-      <c r="U202" t="n">
-        <v>0</v>
-      </c>
-      <c r="V202" s="2" t="inlineStr"/>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>S 2960-2025</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D203" s="1" t="n">
-        <v>45953</v>
-      </c>
-      <c r="E203" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F203" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G203" t="inlineStr">
-        <is>
-          <t>KARLSKOGA</t>
-        </is>
-      </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I203" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J203" t="n">
-        <v>0</v>
-      </c>
-      <c r="K203" t="n">
-        <v>0</v>
-      </c>
-      <c r="L203" t="n">
-        <v>0</v>
-      </c>
-      <c r="M203" t="n">
-        <v>0</v>
-      </c>
-      <c r="N203" t="n">
-        <v>0</v>
-      </c>
-      <c r="O203" t="n">
-        <v>0</v>
-      </c>
-      <c r="P203" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q203" t="n">
-        <v>0</v>
-      </c>
-      <c r="R203" t="n">
-        <v>0</v>
-      </c>
-      <c r="S203" t="n">
-        <v>0</v>
-      </c>
-      <c r="T203" t="n">
-        <v>0</v>
-      </c>
-      <c r="U203" t="n">
-        <v>0</v>
-      </c>
-      <c r="V203" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt KARLSKOGA.xlsx
+++ b/Översikt KARLSKOGA.xlsx
@@ -601,7 +601,7 @@
         <v>45562</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>45958</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         <v>45989</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>44510</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>46100</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>45989</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>44473</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>46010</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>46010</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>44495</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>46066</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>46010</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>46127</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>46265</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 39025-2022</t>
+          <t>A 39936-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44817</v>
+        <v>45553</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2309,16 +2309,11 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>3.2</v>
+        <v>6.4</v>
       </c>
       <c r="J16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -2348,275 +2343,280 @@
         <v>2</v>
       </c>
       <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Storgröe
+Utter</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 39936-2024 artfynd.xlsx", "A 39936-2024")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 39936-2024 karta.png", "A 39936-2024")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 39936-2024 georefererad karta.tif", "A 39936-2024")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 39936-2024 FSC-klagomål.docx", "A 39936-2024")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 39936-2024 FSC-klagomål mail.docx", "A 39936-2024")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 39936-2024 tillsynsbegäran.docx", "A 39936-2024")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 39936-2024 tillsynsbegäran mail.docx", "A 39936-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 39025-2022</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>44817</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>KARLSKOGA</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J17" t="n">
         <v>2</v>
       </c>
-      <c r="U16" t="n">
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
         <v>2</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Talltita
 Tjäder</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 39025-2022 artfynd.xlsx", "A 39025-2022")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 39025-2022 karta.png", "A 39025-2022")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 39025-2022 georefererad karta.tif", "A 39025-2022")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 39025-2022 FSC-klagomål.docx", "A 39025-2022")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 39025-2022 FSC-klagomål mail.docx", "A 39025-2022")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 39025-2022 tillsynsbegäran.docx", "A 39025-2022")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 39025-2022 tillsynsbegäran mail.docx", "A 39025-2022")</f>
         <v/>
       </c>
-      <c r="AE16">
+      <c r="AE17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 39025-2022 prioriterade fågelarter.docx", "A 39025-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>A 38023-2026</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
         <v>46280</v>
       </c>
-      <c r="E17" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>KARLSKOGA</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
+      <c r="E18" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>KARLSKOGA</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I17" t="n">
+      <c r="I18" t="n">
         <v>7.2</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J18" t="n">
         <v>2</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
         <v>2</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T18" t="n">
         <v>2</v>
       </c>
-      <c r="U17" t="n">
+      <c r="U18" t="n">
         <v>1</v>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Tjäder
 Revlummer</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 38023-2026 artfynd.xlsx", "A 38023-2026")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 38023-2026 karta.png", "A 38023-2026")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 38023-2026 georefererad karta.tif", "A 38023-2026")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 38023-2026 FSC-klagomål.docx", "A 38023-2026")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 38023-2026 FSC-klagomål mail.docx", "A 38023-2026")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 38023-2026 tillsynsbegäran.docx", "A 38023-2026")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 38023-2026 tillsynsbegäran mail.docx", "A 38023-2026")</f>
         <v/>
       </c>
-      <c r="AE17">
+      <c r="AE18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 38023-2026 prioriterade fågelarter.docx", "A 38023-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 39936-2024</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45553</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>KARLSKOGA</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Storgröe
-Utter</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 39936-2024 artfynd.xlsx", "A 39936-2024")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 39936-2024 karta.png", "A 39936-2024")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 39936-2024 georefererad karta.tif", "A 39936-2024")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 39936-2024 FSC-klagomål.docx", "A 39936-2024")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 39936-2024 FSC-klagomål mail.docx", "A 39936-2024")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 39936-2024 tillsynsbegäran.docx", "A 39936-2024")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 39936-2024 tillsynsbegäran mail.docx", "A 39936-2024")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 21019-2026</t>
+          <t>A 58091-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2630,10 +2630,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46145</v>
+        <v>44900</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>4.7</v>
+        <v>2.1</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2684,49 +2684,49 @@
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Hårklomossa</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 21019-2026 artfynd.xlsx", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 58091-2022 artfynd.xlsx", "A 58091-2022")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 21019-2026 karta.png", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 58091-2022 karta.png", "A 58091-2022")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 21019-2026 georefererad karta.tif", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 58091-2022 georefererad karta.tif", "A 58091-2022")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 21019-2026 FSC-klagomål.docx", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 58091-2022 FSC-klagomål.docx", "A 58091-2022")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 21019-2026 FSC-klagomål mail.docx", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 58091-2022 FSC-klagomål mail.docx", "A 58091-2022")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 21019-2026 tillsynsbegäran.docx", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 58091-2022 tillsynsbegäran.docx", "A 58091-2022")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 21019-2026 tillsynsbegäran mail.docx", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 58091-2022 tillsynsbegäran mail.docx", "A 58091-2022")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 52377-2025</t>
+          <t>A 28566-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2740,10 +2740,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45953</v>
+        <v>45478</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2755,13 +2755,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2801,42 +2796,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 52377-2025 artfynd.xlsx", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 28566-2024 artfynd.xlsx", "A 28566-2024")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 52377-2025 karta.png", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 28566-2024 karta.png", "A 28566-2024")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 52377-2025 georefererad karta.tif", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 28566-2024 georefererad karta.tif", "A 28566-2024")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 52377-2025 FSC-klagomål.docx", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 28566-2024 FSC-klagomål.docx", "A 28566-2024")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 52377-2025 FSC-klagomål mail.docx", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 28566-2024 FSC-klagomål mail.docx", "A 28566-2024")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 52377-2025 tillsynsbegäran.docx", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 28566-2024 tillsynsbegäran.docx", "A 28566-2024")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 52377-2025 tillsynsbegäran mail.docx", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 28566-2024 tillsynsbegäran mail.docx", "A 28566-2024")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 25093-2026</t>
+          <t>A 52377-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2850,10 +2845,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46175</v>
+        <v>45953</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2871,13 +2866,13 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2911,35 +2906,35 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 25093-2026 artfynd.xlsx", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 52377-2025 artfynd.xlsx", "A 52377-2025")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 25093-2026 karta.png", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 52377-2025 karta.png", "A 52377-2025")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 25093-2026 georefererad karta.tif", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 52377-2025 georefererad karta.tif", "A 52377-2025")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 25093-2026 FSC-klagomål.docx", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 52377-2025 FSC-klagomål.docx", "A 52377-2025")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 25093-2026 FSC-klagomål mail.docx", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 52377-2025 FSC-klagomål mail.docx", "A 52377-2025")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 25093-2026 tillsynsbegäran.docx", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 52377-2025 tillsynsbegäran.docx", "A 52377-2025")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 25093-2026 tillsynsbegäran mail.docx", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 52377-2025 tillsynsbegäran mail.docx", "A 52377-2025")</f>
         <v/>
       </c>
     </row>
@@ -2963,7 +2958,7 @@
         <v>45103</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3055,7 +3050,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 58091-2022</t>
+          <t>A 40528-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3069,10 +3064,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44900</v>
+        <v>45555</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3084,13 +3079,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -3123,42 +3113,42 @@
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Hårklomossa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 58091-2022 artfynd.xlsx", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 40528-2024 artfynd.xlsx", "A 40528-2024")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 58091-2022 karta.png", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 40528-2024 karta.png", "A 40528-2024")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 58091-2022 georefererad karta.tif", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 40528-2024 georefererad karta.tif", "A 40528-2024")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 58091-2022 FSC-klagomål.docx", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 40528-2024 FSC-klagomål.docx", "A 40528-2024")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 58091-2022 FSC-klagomål mail.docx", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 40528-2024 FSC-klagomål mail.docx", "A 40528-2024")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 58091-2022 tillsynsbegäran.docx", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 40528-2024 tillsynsbegäran.docx", "A 40528-2024")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 58091-2022 tillsynsbegäran mail.docx", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 40528-2024 tillsynsbegäran mail.docx", "A 40528-2024")</f>
         <v/>
       </c>
     </row>
@@ -3182,7 +3172,7 @@
         <v>46010</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3296,7 +3286,7 @@
         <v>46113</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3389,7 +3379,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 28566-2024</t>
+          <t>A 18427-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3403,10 +3393,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45478</v>
+        <v>46127</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3418,8 +3408,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3459,42 +3454,46 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 28566-2024 artfynd.xlsx", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 18427-2026 artfynd.xlsx", "A 18427-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 28566-2024 karta.png", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 18427-2026 karta.png", "A 18427-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 28566-2024 georefererad karta.tif", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 18427-2026 georefererad karta.tif", "A 18427-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 28566-2024 FSC-klagomål.docx", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 18427-2026 FSC-klagomål.docx", "A 18427-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 28566-2024 FSC-klagomål mail.docx", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 18427-2026 FSC-klagomål mail.docx", "A 18427-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 28566-2024 tillsynsbegäran.docx", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 18427-2026 tillsynsbegäran.docx", "A 18427-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 28566-2024 tillsynsbegäran mail.docx", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 18427-2026 tillsynsbegäran mail.docx", "A 18427-2026")</f>
+        <v/>
+      </c>
+      <c r="AE26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 18427-2026 prioriterade fågelarter.docx", "A 18427-2026")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 18427-2026</t>
+          <t>A 19233-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3508,10 +3507,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46127</v>
+        <v>46132</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3523,19 +3522,14 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
         <v>1</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3565,50 +3559,46 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 18427-2026 artfynd.xlsx", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 19233-2026 artfynd.xlsx", "A 19233-2026")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 18427-2026 karta.png", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 19233-2026 karta.png", "A 19233-2026")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 18427-2026 georefererad karta.tif", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 19233-2026 georefererad karta.tif", "A 19233-2026")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 18427-2026 FSC-klagomål.docx", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 19233-2026 FSC-klagomål.docx", "A 19233-2026")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 18427-2026 FSC-klagomål mail.docx", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 19233-2026 FSC-klagomål mail.docx", "A 19233-2026")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 18427-2026 tillsynsbegäran.docx", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 19233-2026 tillsynsbegäran.docx", "A 19233-2026")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 18427-2026 tillsynsbegäran mail.docx", "A 18427-2026")</f>
-        <v/>
-      </c>
-      <c r="AE27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 18427-2026 prioriterade fågelarter.docx", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 19233-2026 tillsynsbegäran mail.docx", "A 19233-2026")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 19233-2026</t>
+          <t>A 21019-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3622,10 +3612,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46132</v>
+        <v>46145</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3637,14 +3627,19 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>1.6</v>
+        <v>4.7</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -3678,42 +3673,42 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 19233-2026 artfynd.xlsx", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 21019-2026 artfynd.xlsx", "A 21019-2026")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 19233-2026 karta.png", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 21019-2026 karta.png", "A 21019-2026")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 19233-2026 georefererad karta.tif", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 21019-2026 georefererad karta.tif", "A 21019-2026")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 19233-2026 FSC-klagomål.docx", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 21019-2026 FSC-klagomål.docx", "A 21019-2026")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 19233-2026 FSC-klagomål mail.docx", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 21019-2026 FSC-klagomål mail.docx", "A 21019-2026")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 19233-2026 tillsynsbegäran.docx", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 21019-2026 tillsynsbegäran.docx", "A 21019-2026")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 19233-2026 tillsynsbegäran mail.docx", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 21019-2026 tillsynsbegäran mail.docx", "A 21019-2026")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 30915-2026</t>
+          <t>A 25093-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3727,10 +3722,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46213</v>
+        <v>46175</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3744,17 +3739,17 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>8.9</v>
+        <v>4</v>
       </c>
       <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
         <v>1</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -3784,46 +3779,46 @@
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 30915-2026 artfynd.xlsx", "A 30915-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 25093-2026 artfynd.xlsx", "A 25093-2026")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 30915-2026 karta.png", "A 30915-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 25093-2026 karta.png", "A 25093-2026")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 30915-2026 georefererad karta.tif", "A 30915-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 25093-2026 georefererad karta.tif", "A 25093-2026")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 30915-2026 FSC-klagomål.docx", "A 30915-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 25093-2026 FSC-klagomål.docx", "A 25093-2026")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 30915-2026 FSC-klagomål mail.docx", "A 30915-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 25093-2026 FSC-klagomål mail.docx", "A 25093-2026")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 30915-2026 tillsynsbegäran.docx", "A 30915-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 25093-2026 tillsynsbegäran.docx", "A 25093-2026")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 30915-2026 tillsynsbegäran mail.docx", "A 30915-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 25093-2026 tillsynsbegäran mail.docx", "A 25093-2026")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 35199-2026</t>
+          <t>A 30915-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3837,10 +3832,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46260</v>
+        <v>46213</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3858,7 +3853,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>5.6</v>
+        <v>8.9</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
@@ -3867,7 +3862,7 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -3882,7 +3877,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -3898,42 +3893,42 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 35199-2026 artfynd.xlsx", "A 35199-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 30915-2026 artfynd.xlsx", "A 30915-2026")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 35199-2026 karta.png", "A 35199-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 30915-2026 karta.png", "A 30915-2026")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 35199-2026 georefererad karta.tif", "A 35199-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 30915-2026 georefererad karta.tif", "A 30915-2026")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 35199-2026 FSC-klagomål.docx", "A 35199-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 30915-2026 FSC-klagomål.docx", "A 30915-2026")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 35199-2026 FSC-klagomål mail.docx", "A 35199-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 30915-2026 FSC-klagomål mail.docx", "A 30915-2026")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 35199-2026 tillsynsbegäran.docx", "A 35199-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 30915-2026 tillsynsbegäran.docx", "A 30915-2026")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 35199-2026 tillsynsbegäran mail.docx", "A 35199-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 30915-2026 tillsynsbegäran mail.docx", "A 30915-2026")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 40528-2024</t>
+          <t>A 35199-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3947,10 +3942,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45555</v>
+        <v>46260</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3962,8 +3957,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>2.8</v>
+        <v>5.6</v>
       </c>
       <c r="J31" t="n">
         <v>1</v>
@@ -3972,7 +3972,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -3999,39 +3999,39 @@
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 40528-2024 artfynd.xlsx", "A 40528-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 35199-2026 artfynd.xlsx", "A 35199-2026")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 40528-2024 karta.png", "A 40528-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 35199-2026 karta.png", "A 35199-2026")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 40528-2024 georefererad karta.tif", "A 40528-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 35199-2026 georefererad karta.tif", "A 35199-2026")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 40528-2024 FSC-klagomål.docx", "A 40528-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 35199-2026 FSC-klagomål.docx", "A 35199-2026")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 40528-2024 FSC-klagomål mail.docx", "A 40528-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 35199-2026 FSC-klagomål mail.docx", "A 35199-2026")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 40528-2024 tillsynsbegäran.docx", "A 40528-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 35199-2026 tillsynsbegäran.docx", "A 35199-2026")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 40528-2024 tillsynsbegäran mail.docx", "A 40528-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 35199-2026 tillsynsbegäran mail.docx", "A 35199-2026")</f>
         <v/>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
         <v>44546</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>44732</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4184,7 +4184,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 64869-2021</t>
+          <t>A 22861-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4198,10 +4198,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44512</v>
+        <v>44715</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4213,13 +4213,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>3.6</v>
+        <v>0.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4262,7 +4257,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 22861-2022</t>
+          <t>A 64869-2021</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4276,10 +4271,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44715</v>
+        <v>44512</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4291,8 +4286,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>0.6</v>
+        <v>3.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4352,7 +4352,7 @@
         <v>44508</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         <v>44480</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>44809</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
         <v>44811</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4649,7 +4649,7 @@
         <v>44628</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
         <v>44809</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         <v>44706</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4873,7 +4873,7 @@
         <v>44706</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 39027-2022</t>
+          <t>A 13501-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44817</v>
+        <v>45736</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4958,13 +4958,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5007,7 +5002,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 35471-2024</t>
+          <t>A 47094-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5021,10 +5016,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45531</v>
+        <v>45196</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5037,7 +5032,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5080,7 +5075,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 58390-2024</t>
+          <t>A 31921-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5094,10 +5089,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45633</v>
+        <v>44777</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5110,7 +5105,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5153,7 +5148,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 9712-2024</t>
+          <t>A 42804-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5163,14 +5158,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45362</v>
+        <v>45182</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5184,11 +5179,11 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5231,7 +5226,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 42804-2023</t>
+          <t>A 39030-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5241,14 +5236,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45182</v>
+        <v>44817</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5266,7 +5261,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5309,7 +5304,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 9510-2023</t>
+          <t>A 39027-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5323,10 +5318,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44981</v>
+        <v>44817</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5338,8 +5333,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5382,7 +5382,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 1309-2024</t>
+          <t>A 8244-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5396,10 +5396,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45303</v>
+        <v>45708</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5412,7 +5412,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>4</v>
+        <v>1.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5455,7 +5455,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 4164-2022</t>
+          <t>A 28100-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5469,10 +5469,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44588</v>
+        <v>45476</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5484,13 +5484,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5533,7 +5528,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 23263-2022</t>
+          <t>A 51344-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5547,10 +5542,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44720</v>
+        <v>45219</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5562,8 +5557,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>2.2</v>
+        <v>4.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5606,7 +5606,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 35444-2024</t>
+          <t>A 8803-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5620,10 +5620,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45531</v>
+        <v>45712</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5679,7 +5679,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 61396-2023</t>
+          <t>A 3735-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5693,10 +5693,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45264</v>
+        <v>45321</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5708,8 +5708,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5752,7 +5757,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 8259-2025</t>
+          <t>A 35445-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5766,10 +5771,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45708</v>
+        <v>45531</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5782,7 +5787,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5825,7 +5830,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 24116-2024</t>
+          <t>A 39337-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5839,10 +5844,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45456</v>
+        <v>44817</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5855,7 +5860,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5898,7 +5903,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 47201-2023</t>
+          <t>A 23308-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5912,10 +5917,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45196</v>
+        <v>45791</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5928,7 +5933,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5971,7 +5976,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 35930-2023</t>
+          <t>A 20463-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5985,10 +5990,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45148</v>
+        <v>45775</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6006,7 +6011,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>5.2</v>
+        <v>0.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6049,7 +6054,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 63863-2023</t>
+          <t>A 28471-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6063,10 +6068,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45278</v>
+        <v>45103</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6079,7 +6084,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6122,7 +6127,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 59938-2023</t>
+          <t>A 16881-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6136,10 +6141,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45257</v>
+        <v>45033</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6151,8 +6156,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6195,7 +6205,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 52828-2024</t>
+          <t>A 61396-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6209,10 +6219,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45610</v>
+        <v>45264</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6225,7 +6235,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>8.300000000000001</v>
+        <v>1.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6268,7 +6278,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 15256-2025</t>
+          <t>A 4164-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6282,10 +6292,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45744</v>
+        <v>44588</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6299,11 +6309,11 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>5.5</v>
+        <v>1.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6346,7 +6356,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 24115-2024</t>
+          <t>A 24255-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6360,10 +6370,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45456</v>
+        <v>45457</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6376,7 +6386,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>8</v>
+        <v>2.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6419,7 +6429,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 19663-2026</t>
+          <t>A 61271-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6433,10 +6443,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46134</v>
+        <v>44909</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6450,11 +6460,11 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.6</v>
+        <v>14.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6514,7 +6524,7 @@
         <v>45758</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6575,7 +6585,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 18768-2025</t>
+          <t>A 57422-2021</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6589,10 +6599,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45764</v>
+        <v>44483</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6604,13 +6614,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6653,7 +6658,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 4801-2024</t>
+          <t>A 56887-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6667,10 +6672,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45328</v>
+        <v>44894</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6683,7 +6688,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6726,7 +6731,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 4802-2024</t>
+          <t>A 38196-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6740,10 +6745,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45328</v>
+        <v>45545</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6756,7 +6761,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6799,7 +6804,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 6835-2025</t>
+          <t>A 35060-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6813,10 +6818,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45700</v>
+        <v>45527</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6828,8 +6833,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6872,7 +6882,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 8990-2023</t>
+          <t>A 64060-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6886,10 +6896,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44979</v>
+        <v>45279</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6902,7 +6912,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6945,7 +6955,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 24255-2024</t>
+          <t>A 14215-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6959,10 +6969,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45457</v>
+        <v>45393</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6974,8 +6984,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>2.4</v>
+        <v>4.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7018,7 +7033,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 21210-2025</t>
+          <t>A 20289-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7032,10 +7047,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45779</v>
+        <v>45435</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7053,7 +7068,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7096,7 +7111,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 23717-2025</t>
+          <t>A 38190-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7110,10 +7125,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45793</v>
+        <v>45545</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7169,7 +7184,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 42802-2023</t>
+          <t>A 44946-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7179,14 +7194,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45182</v>
+        <v>45918</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7198,13 +7213,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7247,7 +7257,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 44946-2025</t>
+          <t>A 44949-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7264,7 +7274,7 @@
         <v>45918</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7277,7 +7287,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7320,7 +7330,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 44949-2025</t>
+          <t>A 9712-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7334,10 +7344,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45918</v>
+        <v>45362</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7347,6 +7357,11 @@
       <c r="G76" t="inlineStr">
         <is>
           <t>KARLSKOGA</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I76" t="n">
@@ -7393,7 +7408,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 28471-2023</t>
+          <t>A 24116-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7407,10 +7422,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45103</v>
+        <v>45456</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7423,7 +7438,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7466,7 +7481,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 22867-2022</t>
+          <t>A 55832-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7480,10 +7495,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44715</v>
+        <v>45239</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7496,7 +7511,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7539,7 +7554,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 64060-2023</t>
+          <t>A 10515-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7553,10 +7568,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45279</v>
+        <v>44987</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7612,7 +7627,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 48707-2024</t>
+          <t>A 4058-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7626,10 +7641,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45593</v>
+        <v>44588</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7642,7 +7657,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>6</v>
+        <v>1.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7685,7 +7700,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 55832-2023</t>
+          <t>A 15256-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7699,10 +7714,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45239</v>
+        <v>45744</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7714,8 +7729,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>0.5</v>
+        <v>5.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7758,7 +7778,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 917-2026</t>
+          <t>A 27498-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7772,10 +7792,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46030</v>
+        <v>45813</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7788,7 +7808,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3.7</v>
+        <v>1.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7831,7 +7851,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 21253-2026</t>
+          <t>A 33011-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7845,10 +7865,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46147</v>
+        <v>45125</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7861,7 +7881,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.4</v>
+        <v>0.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7904,7 +7924,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 58388-2024</t>
+          <t>A 43075-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7918,10 +7938,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45633</v>
+        <v>45182</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7934,7 +7954,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>5.8</v>
+        <v>3.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7977,7 +7997,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 21257-2026</t>
+          <t>A 23263-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7991,10 +8011,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46147</v>
+        <v>44720</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8007,7 +8027,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8050,7 +8070,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 3227-2025</t>
+          <t>A 48168-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8064,10 +8084,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45679</v>
+        <v>45589</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8080,7 +8100,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8123,7 +8143,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 18978-2025</t>
+          <t>A 35444-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8137,10 +8157,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45764</v>
+        <v>45531</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8153,7 +8173,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8196,7 +8216,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 50958-2025</t>
+          <t>A 35471-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8210,10 +8230,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45946</v>
+        <v>45531</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8226,7 +8246,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8269,7 +8289,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 31921-2022</t>
+          <t>A 58390-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8283,10 +8303,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44777</v>
+        <v>45633</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8299,7 +8319,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8342,7 +8362,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 43075-2023</t>
+          <t>A 50958-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8356,10 +8376,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45182</v>
+        <v>45946</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8372,7 +8392,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3.1</v>
+        <v>0.4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8415,7 +8435,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 47196-2023</t>
+          <t>A 13454-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8429,10 +8449,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45196</v>
+        <v>44645</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8445,7 +8465,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>5.9</v>
+        <v>1.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8488,7 +8508,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 13454-2022</t>
+          <t>A 10743-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8502,10 +8522,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44645</v>
+        <v>44988</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8517,8 +8537,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8561,7 +8586,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 55025-2025</t>
+          <t>A 50611-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8575,10 +8600,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45967</v>
+        <v>45601</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8591,7 +8616,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8634,7 +8659,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 53618-2024</t>
+          <t>A 42802-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8644,14 +8669,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45614</v>
+        <v>45182</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8663,8 +8688,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>10.1</v>
+        <v>0.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8707,7 +8737,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 30961-2022</t>
+          <t>A 52829-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8721,10 +8751,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44768</v>
+        <v>45610</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8736,13 +8766,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8785,7 +8810,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 23754-2026</t>
+          <t>A 18768-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8799,10 +8824,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46164</v>
+        <v>45764</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8820,7 +8845,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>12.2</v>
+        <v>0.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8863,7 +8888,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 4587-2025</t>
+          <t>A 56313-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8877,10 +8902,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45687</v>
+        <v>45624</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8892,8 +8917,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I97" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8953,7 +8983,7 @@
         <v>45182</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9014,7 +9044,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 8803-2025</t>
+          <t>A 38382-2022</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9028,10 +9058,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45712</v>
+        <v>44812</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9043,8 +9073,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9087,7 +9122,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 4587-2025</t>
+          <t>A 24115-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9101,10 +9136,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45687</v>
+        <v>45456</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9117,7 +9152,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>3.3</v>
+        <v>8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9160,7 +9195,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 59522-2025</t>
+          <t>A 55025-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9170,14 +9205,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45989</v>
+        <v>45967</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9189,13 +9224,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9238,7 +9268,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 24666-2026</t>
+          <t>A 20086-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9248,14 +9278,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46171</v>
+        <v>45434</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9268,7 +9298,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>6.1</v>
+        <v>1.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9311,7 +9341,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 60506-2025</t>
+          <t>A 9510-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9325,10 +9355,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45995</v>
+        <v>44981</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9341,7 +9371,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9384,7 +9414,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 60508-2025</t>
+          <t>A 10404-2022</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9398,10 +9428,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45995</v>
+        <v>44623</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9414,7 +9444,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9457,7 +9487,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 60503-2025</t>
+          <t>A 54680-2021</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9471,10 +9501,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45995</v>
+        <v>44473</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9487,7 +9517,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9530,7 +9560,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 56313-2024</t>
+          <t>A 30102-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9544,10 +9574,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45624</v>
+        <v>45826</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9559,13 +9589,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I106" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9608,7 +9633,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 10743-2023</t>
+          <t>A 18955-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9622,10 +9647,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44988</v>
+        <v>45764</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9637,13 +9662,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>2.4</v>
+        <v>8.1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9686,7 +9706,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 25092-2026</t>
+          <t>A 59522-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9696,14 +9716,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46175</v>
+        <v>45989</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9721,7 +9741,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9764,7 +9784,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 14215-2024</t>
+          <t>A 53647-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9778,10 +9798,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45393</v>
+        <v>45230</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9793,13 +9813,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I109" t="n">
-        <v>4.2</v>
+        <v>0.6</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9842,7 +9857,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 55191-2023</t>
+          <t>A 23620-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9856,10 +9871,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45237</v>
+        <v>45454</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9872,7 +9887,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9915,7 +9930,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 25098-2026</t>
+          <t>A 59025-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9925,14 +9940,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46175</v>
+        <v>45636</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9946,11 +9961,11 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9993,7 +10008,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 61788-2025</t>
+          <t>A 60503-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10007,10 +10022,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46002</v>
+        <v>45995</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10022,13 +10037,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I112" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10071,7 +10081,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 59025-2024</t>
+          <t>A 22867-2022</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10085,10 +10095,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45636</v>
+        <v>44715</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10100,13 +10110,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10149,7 +10154,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 64066-2025</t>
+          <t>A 60508-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10159,14 +10164,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46013</v>
+        <v>45995</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10179,7 +10184,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10222,7 +10227,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 63628-2025</t>
+          <t>A 60506-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10236,10 +10241,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46014</v>
+        <v>45995</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10252,7 +10257,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>3.8</v>
+        <v>0.8</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10295,7 +10300,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 17243-2024</t>
+          <t>A 31397-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10309,10 +10314,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45414</v>
+        <v>45833</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10325,7 +10330,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10368,7 +10373,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 1788-2026</t>
+          <t>A 61788-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10382,10 +10387,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46034</v>
+        <v>46002</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10397,8 +10402,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I117" t="n">
-        <v>3.5</v>
+        <v>0.9</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10441,7 +10451,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 26608-2026</t>
+          <t>A 18978-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10455,10 +10465,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46184</v>
+        <v>45764</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10470,13 +10480,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I118" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10519,7 +10524,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 35060-2024</t>
+          <t>A 4801-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10533,10 +10538,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45527</v>
+        <v>45328</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10548,13 +10553,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I119" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10597,7 +10597,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 27120-2026</t>
+          <t>A 4802-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10611,10 +10611,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46188</v>
+        <v>45328</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>4.7</v>
+        <v>0.9</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10670,7 +10670,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 26819-2026</t>
+          <t>A 1788-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10684,10 +10684,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46185</v>
+        <v>46034</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10699,13 +10699,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I121" t="n">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10748,7 +10743,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 3239-2026</t>
+          <t>A 30961-2022</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10762,10 +10757,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46041</v>
+        <v>44768</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10777,8 +10772,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I122" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10821,7 +10821,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 45664-2025</t>
+          <t>A 55191-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10835,10 +10835,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45923</v>
+        <v>45237</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10850,13 +10850,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I123" t="n">
-        <v>9</v>
+        <v>1.9</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10899,7 +10894,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 2911-2026</t>
+          <t>A 32287-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10913,10 +10908,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46038</v>
+        <v>45835</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10928,8 +10923,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I124" t="n">
-        <v>1.1</v>
+        <v>10.9</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10972,7 +10972,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 26820-2026</t>
+          <t>A 2911-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10986,10 +10986,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46185</v>
+        <v>46038</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11001,13 +11001,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I125" t="n">
-        <v>9.9</v>
+        <v>1.1</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11050,7 +11045,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 26821-2026</t>
+          <t>A 45664-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11064,10 +11059,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46185</v>
+        <v>45923</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11085,7 +11080,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>7.9</v>
+        <v>9</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11128,7 +11123,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 26822-2026</t>
+          <t>A 47222-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11142,10 +11137,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46185</v>
+        <v>45586</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11163,7 +11158,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>2.2</v>
+        <v>5.3</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11206,7 +11201,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 26824-2026</t>
+          <t>A 64066-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11216,14 +11211,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46185</v>
+        <v>46013</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11235,13 +11230,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I128" t="n">
-        <v>5</v>
+        <v>1.9</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11284,7 +11274,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 26825-2026</t>
+          <t>A 63628-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11298,10 +11288,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46185</v>
+        <v>46014</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11313,13 +11303,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I129" t="n">
-        <v>0.8</v>
+        <v>3.8</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11362,7 +11347,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 47222-2024</t>
+          <t>A 13496-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11376,10 +11361,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45586</v>
+        <v>45736</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11391,13 +11376,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I130" t="n">
-        <v>5.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11440,7 +11420,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 27392-2026</t>
+          <t>A 11974-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11454,10 +11434,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46189</v>
+        <v>45728</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11469,13 +11449,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I131" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11518,7 +11493,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 52826-2024</t>
+          <t>A 63863-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11532,10 +11507,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45610</v>
+        <v>45278</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11548,7 +11523,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11591,7 +11566,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 52829-2024</t>
+          <t>A 1309-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11605,10 +11580,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45610</v>
+        <v>45303</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11621,7 +11596,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11664,7 +11639,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 11974-2025</t>
+          <t>A 52826-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11678,10 +11653,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45728</v>
+        <v>45610</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11694,7 +11669,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11737,7 +11712,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 61271-2022</t>
+          <t>A 9917-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11751,10 +11726,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44909</v>
+        <v>46073</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11766,13 +11741,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I135" t="n">
-        <v>14.1</v>
+        <v>3.1</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11815,7 +11785,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 48168-2024</t>
+          <t>A 1106-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11829,10 +11799,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45589</v>
+        <v>45302</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11845,7 +11815,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>5.5</v>
+        <v>1.9</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11888,7 +11858,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 18955-2025</t>
+          <t>A 48707-2024</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11902,10 +11872,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45764</v>
+        <v>45593</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11918,7 +11888,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>8.1</v>
+        <v>6</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11961,7 +11931,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 9917-2026</t>
+          <t>A 13473-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11975,10 +11945,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46073</v>
+        <v>46094</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11991,7 +11961,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>3.1</v>
+        <v>1</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -12034,7 +12004,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 50614-2024</t>
+          <t>A 14580-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12048,10 +12018,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45601</v>
+        <v>46101</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12063,8 +12033,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I139" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12107,7 +12082,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 55182-2024</t>
+          <t>A 12897-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12121,10 +12096,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45618</v>
+        <v>46092</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12137,7 +12112,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>11.4</v>
+        <v>1.3</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12180,7 +12155,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 4058-2022</t>
+          <t>A 35470-2024</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12194,10 +12169,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44588</v>
+        <v>45531</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12210,7 +12185,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12253,7 +12228,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 13473-2026</t>
+          <t>A 16782-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12267,10 +12242,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46094</v>
+        <v>46113</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12282,8 +12257,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I142" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12326,7 +12306,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 12897-2026</t>
+          <t>A 16783-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12340,10 +12320,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46092</v>
+        <v>46113</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12355,8 +12335,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I143" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12399,7 +12384,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 14580-2026</t>
+          <t>A 16787-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12413,10 +12398,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46101</v>
+        <v>46113</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12434,7 +12419,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12477,7 +12462,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 28100-2024</t>
+          <t>A 15058-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12491,10 +12476,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45476</v>
+        <v>46104</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12507,7 +12492,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.8</v>
+        <v>4.3</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12550,7 +12535,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 16783-2026</t>
+          <t>A 8990-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12564,10 +12549,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46113</v>
+        <v>44979</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12579,13 +12564,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I146" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12628,7 +12608,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 16787-2026</t>
+          <t>A 17734-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12642,10 +12622,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46113</v>
+        <v>46122</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12663,7 +12643,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12706,7 +12686,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 16782-2026</t>
+          <t>A 50614-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12720,10 +12700,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46113</v>
+        <v>45601</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12735,13 +12715,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I148" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12784,7 +12759,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 15058-2026</t>
+          <t>A 19011-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12798,10 +12773,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46104</v>
+        <v>46130</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12813,8 +12788,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I149" t="n">
-        <v>4.3</v>
+        <v>0.9</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12857,7 +12837,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 1106-2024</t>
+          <t>A 55182-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12871,10 +12851,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45302</v>
+        <v>45618</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12887,7 +12867,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.9</v>
+        <v>11.4</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12930,7 +12910,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 39030-2022</t>
+          <t>A 19010-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12944,10 +12924,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44817</v>
+        <v>46130</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12965,7 +12945,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -13008,7 +12988,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 17734-2026</t>
+          <t>A 19009-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13022,10 +13002,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46122</v>
+        <v>46130</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13043,7 +13023,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>3</v>
+        <v>6.3</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -13086,7 +13066,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 38382-2022</t>
+          <t>A 19008-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13100,10 +13080,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>44812</v>
+        <v>46130</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13117,11 +13097,11 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I153" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -13164,7 +13144,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 19009-2026</t>
+          <t>A 52797-2021</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13178,10 +13158,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46130</v>
+        <v>44467</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13193,13 +13173,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I154" t="n">
-        <v>6.3</v>
+        <v>1.4</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13242,7 +13217,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 19011-2026</t>
+          <t>A 19663-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13256,10 +13231,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46130</v>
+        <v>46134</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13277,7 +13252,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13320,7 +13295,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 19010-2026</t>
+          <t>A 6835-2025</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13334,10 +13309,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46130</v>
+        <v>45700</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13349,13 +13324,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I156" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13398,7 +13368,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 19008-2026</t>
+          <t>A 8259-2025</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13412,10 +13382,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46130</v>
+        <v>45708</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13427,13 +13397,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I157" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13476,7 +13441,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 16881-2023</t>
+          <t>A 53620-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13490,10 +13455,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45033</v>
+        <v>45614</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13505,13 +13470,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I158" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13554,7 +13514,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 57422-2021</t>
+          <t>A 21210-2025</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13568,10 +13528,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>44483</v>
+        <v>45779</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13583,8 +13543,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I159" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13627,7 +13592,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 8244-2025</t>
+          <t>A 35930-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13641,10 +13606,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45708</v>
+        <v>45148</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13656,8 +13621,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I160" t="n">
-        <v>1.1</v>
+        <v>5.2</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13700,7 +13670,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 38190-2024</t>
+          <t>A 23717-2025</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13714,10 +13684,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45545</v>
+        <v>45793</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13773,7 +13743,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 31378-2026</t>
+          <t>A 47196-2023</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13787,10 +13757,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46213</v>
+        <v>45196</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13803,7 +13773,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>3.7</v>
+        <v>5.9</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13846,7 +13816,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 20463-2025</t>
+          <t>A 53618-2024</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13860,10 +13830,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45775</v>
+        <v>45614</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13875,13 +13845,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I163" t="n">
-        <v>0.9</v>
+        <v>10.1</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13924,7 +13889,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 35470-2024</t>
+          <t>A 917-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13938,10 +13903,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45531</v>
+        <v>46030</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13954,7 +13919,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>0.5</v>
+        <v>3.7</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13997,7 +13962,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 35094-2026</t>
+          <t>A 58388-2024</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -14011,10 +13976,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46260</v>
+        <v>45633</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14026,13 +13991,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I165" t="n">
-        <v>1.9</v>
+        <v>5.8</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -14075,7 +14035,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 35445-2024</t>
+          <t>A 47201-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -14089,10 +14049,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45531</v>
+        <v>45196</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14105,7 +14065,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -14148,7 +14108,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 47094-2023</t>
+          <t>A 52828-2024</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -14162,10 +14122,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45196</v>
+        <v>45610</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14178,7 +14138,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14221,7 +14181,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 38196-2024</t>
+          <t>A 17243-2024</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14235,10 +14195,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45545</v>
+        <v>45414</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14251,7 +14211,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>0.7</v>
+        <v>3.2</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14294,7 +14254,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 50611-2024</t>
+          <t>A 59938-2023</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14308,10 +14268,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45601</v>
+        <v>45257</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14324,7 +14284,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14367,7 +14327,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 35699-2026</t>
+          <t>A 21253-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14377,14 +14337,14 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46265</v>
+        <v>46147</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14396,13 +14356,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I170" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14445,7 +14400,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 20289-2024</t>
+          <t>A 21257-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14459,10 +14414,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45435</v>
+        <v>46147</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14474,13 +14429,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I171" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14523,7 +14473,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 52797-2021</t>
+          <t>A 3227-2025</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14537,10 +14487,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>44467</v>
+        <v>45679</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14553,7 +14503,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1.4</v>
+        <v>4.5</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14596,7 +14546,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 20086-2024</t>
+          <t>A 38742-2023</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14610,10 +14560,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45434</v>
+        <v>45161</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14625,8 +14575,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I173" t="n">
-        <v>1.5</v>
+        <v>4.2</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14669,7 +14624,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 36374-2026</t>
+          <t>A 23754-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14683,10 +14638,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46268</v>
+        <v>46164</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14700,11 +14655,11 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1.6</v>
+        <v>12.2</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14747,7 +14702,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 13496-2025</t>
+          <t>A 4587-2025</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14761,10 +14716,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45736</v>
+        <v>45687</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14777,7 +14732,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>8.800000000000001</v>
+        <v>3.3</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14820,7 +14775,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 56887-2022</t>
+          <t>A 4587-2025</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14834,10 +14789,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>44894</v>
+        <v>45687</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14850,7 +14805,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14893,7 +14848,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 37089-2026</t>
+          <t>A 24666-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14907,10 +14862,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46273</v>
+        <v>46171</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14923,7 +14878,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>15.8</v>
+        <v>6.1</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14966,7 +14921,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 33011-2023</t>
+          <t>A 25098-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14976,14 +14931,14 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45125</v>
+        <v>46175</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14995,8 +14950,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I178" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -15039,7 +14999,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 51344-2023</t>
+          <t>A 25092-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -15053,10 +15013,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45219</v>
+        <v>46175</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15070,11 +15030,11 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I179" t="n">
-        <v>4.5</v>
+        <v>1.9</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -15117,7 +15077,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 38043-2026</t>
+          <t>A 26822-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -15131,10 +15091,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46280</v>
+        <v>46185</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15148,11 +15108,11 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -15195,7 +15155,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 38020-2026</t>
+          <t>A 26819-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15209,10 +15169,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46280</v>
+        <v>46185</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15230,7 +15190,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>4.1</v>
+        <v>2.4</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15273,7 +15233,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 10515-2023</t>
+          <t>A 3239-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15287,10 +15247,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>44987</v>
+        <v>46041</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15303,7 +15263,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15346,7 +15306,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 39337-2022</t>
+          <t>A 26821-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15360,10 +15320,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>44817</v>
+        <v>46185</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15375,8 +15335,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I183" t="n">
-        <v>1.5</v>
+        <v>7.9</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15419,7 +15384,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 53620-2024</t>
+          <t>A 26820-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15433,10 +15398,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45614</v>
+        <v>46185</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15448,8 +15413,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I184" t="n">
-        <v>0.7</v>
+        <v>9.9</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15492,7 +15462,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 13501-2025</t>
+          <t>A 26608-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15506,10 +15476,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45736</v>
+        <v>46184</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15521,8 +15491,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I185" t="n">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15565,7 +15540,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 10404-2022</t>
+          <t>A 26824-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15579,10 +15554,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>44623</v>
+        <v>46185</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15594,8 +15569,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I186" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15638,7 +15618,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 38742-2023</t>
+          <t>A 26825-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15648,14 +15628,14 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45161</v>
+        <v>46185</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15669,11 +15649,11 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I187" t="n">
-        <v>4.2</v>
+        <v>0.8</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15716,7 +15696,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 3735-2024</t>
+          <t>A 27392-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15730,10 +15710,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45321</v>
+        <v>46189</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15747,11 +15727,11 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15794,7 +15774,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 23308-2025</t>
+          <t>A 27120-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15808,10 +15788,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45791</v>
+        <v>46188</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15824,7 +15804,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>1.5</v>
+        <v>4.7</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15867,7 +15847,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 27498-2025</t>
+          <t>A 31378-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15881,10 +15861,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45813</v>
+        <v>46213</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15897,7 +15877,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>1.2</v>
+        <v>3.7</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15940,7 +15920,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 23620-2024</t>
+          <t>A 35094-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15954,10 +15934,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45454</v>
+        <v>46260</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15969,8 +15949,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I191" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -16013,7 +15998,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 53647-2023</t>
+          <t>A 35699-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -16023,14 +16008,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45230</v>
+        <v>46265</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16042,8 +16027,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I192" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -16086,7 +16076,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 30102-2025</t>
+          <t>A 36374-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -16100,10 +16090,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45826</v>
+        <v>46268</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16115,8 +16105,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I193" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -16159,7 +16154,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 54680-2021</t>
+          <t>A 37089-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -16173,10 +16168,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>44473</v>
+        <v>46273</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16189,7 +16184,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>2.9</v>
+        <v>15.8</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -16232,7 +16227,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 31397-2025</t>
+          <t>A 38043-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16246,10 +16241,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45833</v>
+        <v>46280</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16261,8 +16256,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I195" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -16305,7 +16305,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 32287-2025</t>
+          <t>A 38020-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16319,10 +16319,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45835</v>
+        <v>46280</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16336,11 +16336,11 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I196" t="n">
-        <v>10.9</v>
+        <v>4.1</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16400,7 +16400,7 @@
         <v>45953</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>

--- a/Översikt KARLSKOGA.xlsx
+++ b/Översikt KARLSKOGA.xlsx
@@ -601,7 +601,7 @@
         <v>45562</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>45958</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         <v>45989</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>44510</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>46100</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>45989</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>44473</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>46010</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>46010</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>44495</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>46066</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>46010</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>46127</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>46265</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 39936-2024</t>
+          <t>A 39025-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45553</v>
+        <v>44817</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2309,11 +2309,16 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>6.4</v>
+        <v>3.2</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -2343,280 +2348,275 @@
         <v>2</v>
       </c>
       <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Talltita
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 39025-2022 artfynd.xlsx", "A 39025-2022")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 39025-2022 karta.png", "A 39025-2022")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 39025-2022 georefererad karta.tif", "A 39025-2022")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 39025-2022 FSC-klagomål.docx", "A 39025-2022")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 39025-2022 FSC-klagomål mail.docx", "A 39025-2022")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 39025-2022 tillsynsbegäran.docx", "A 39025-2022")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 39025-2022 tillsynsbegäran mail.docx", "A 39025-2022")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 39025-2022 prioriterade fågelarter.docx", "A 39025-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 38023-2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>KARLSKOGA</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Tjäder
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 38023-2026 artfynd.xlsx", "A 38023-2026")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 38023-2026 karta.png", "A 38023-2026")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 38023-2026 georefererad karta.tif", "A 38023-2026")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 38023-2026 FSC-klagomål.docx", "A 38023-2026")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 38023-2026 FSC-klagomål mail.docx", "A 38023-2026")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 38023-2026 tillsynsbegäran.docx", "A 38023-2026")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 38023-2026 tillsynsbegäran mail.docx", "A 38023-2026")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 38023-2026 prioriterade fågelarter.docx", "A 38023-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 39936-2024</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45553</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>KARLSKOGA</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="n">
         <v>3</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U18" t="n">
         <v>1</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Storgröe
 Utter</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 39936-2024 artfynd.xlsx", "A 39936-2024")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 39936-2024 karta.png", "A 39936-2024")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 39936-2024 georefererad karta.tif", "A 39936-2024")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 39936-2024 FSC-klagomål.docx", "A 39936-2024")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 39936-2024 FSC-klagomål mail.docx", "A 39936-2024")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 39936-2024 tillsynsbegäran.docx", "A 39936-2024")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 39936-2024 tillsynsbegäran mail.docx", "A 39936-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 39025-2022</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>44817</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>KARLSKOGA</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Talltita
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 39025-2022 artfynd.xlsx", "A 39025-2022")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 39025-2022 karta.png", "A 39025-2022")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 39025-2022 georefererad karta.tif", "A 39025-2022")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 39025-2022 FSC-klagomål.docx", "A 39025-2022")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 39025-2022 FSC-klagomål mail.docx", "A 39025-2022")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 39025-2022 tillsynsbegäran.docx", "A 39025-2022")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 39025-2022 tillsynsbegäran mail.docx", "A 39025-2022")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 39025-2022 prioriterade fågelarter.docx", "A 39025-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 38023-2026</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>KARLSKOGA</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Tjäder
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 38023-2026 artfynd.xlsx", "A 38023-2026")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 38023-2026 karta.png", "A 38023-2026")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 38023-2026 georefererad karta.tif", "A 38023-2026")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 38023-2026 FSC-klagomål.docx", "A 38023-2026")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 38023-2026 FSC-klagomål mail.docx", "A 38023-2026")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 38023-2026 tillsynsbegäran.docx", "A 38023-2026")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 38023-2026 tillsynsbegäran mail.docx", "A 38023-2026")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 38023-2026 prioriterade fågelarter.docx", "A 38023-2026")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 58091-2022</t>
+          <t>A 52377-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2630,10 +2630,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44900</v>
+        <v>45953</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2684,49 +2684,49 @@
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Hårklomossa</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 58091-2022 artfynd.xlsx", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 52377-2025 artfynd.xlsx", "A 52377-2025")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 58091-2022 karta.png", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 52377-2025 karta.png", "A 52377-2025")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 58091-2022 georefererad karta.tif", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 52377-2025 georefererad karta.tif", "A 52377-2025")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 58091-2022 FSC-klagomål.docx", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 52377-2025 FSC-klagomål.docx", "A 52377-2025")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 58091-2022 FSC-klagomål mail.docx", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 52377-2025 FSC-klagomål mail.docx", "A 52377-2025")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 58091-2022 tillsynsbegäran.docx", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 52377-2025 tillsynsbegäran.docx", "A 52377-2025")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 58091-2022 tillsynsbegäran mail.docx", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 52377-2025 tillsynsbegäran mail.docx", "A 52377-2025")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 28566-2024</t>
+          <t>A 21019-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2740,10 +2740,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45478</v>
+        <v>46145</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2755,8 +2755,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>4.7</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2792,46 +2797,46 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 28566-2024 artfynd.xlsx", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 21019-2026 artfynd.xlsx", "A 21019-2026")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 28566-2024 karta.png", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 21019-2026 karta.png", "A 21019-2026")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 28566-2024 georefererad karta.tif", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 21019-2026 georefererad karta.tif", "A 21019-2026")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 28566-2024 FSC-klagomål.docx", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 21019-2026 FSC-klagomål.docx", "A 21019-2026")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 28566-2024 FSC-klagomål mail.docx", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 21019-2026 FSC-klagomål mail.docx", "A 21019-2026")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 28566-2024 tillsynsbegäran.docx", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 21019-2026 tillsynsbegäran.docx", "A 21019-2026")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 28566-2024 tillsynsbegäran mail.docx", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 21019-2026 tillsynsbegäran mail.docx", "A 21019-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 52377-2025</t>
+          <t>A 28474-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2845,10 +2850,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45953</v>
+        <v>45103</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2860,13 +2865,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>2.6</v>
+        <v>5.1</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2875,7 +2875,7 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2890,7 +2890,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2906,42 +2906,46 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Blåhake</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 52377-2025 artfynd.xlsx", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 28474-2023 artfynd.xlsx", "A 28474-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 52377-2025 karta.png", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 28474-2023 karta.png", "A 28474-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 52377-2025 georefererad karta.tif", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 28474-2023 georefererad karta.tif", "A 28474-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 52377-2025 FSC-klagomål.docx", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 28474-2023 FSC-klagomål.docx", "A 28474-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 52377-2025 FSC-klagomål mail.docx", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 28474-2023 FSC-klagomål mail.docx", "A 28474-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 52377-2025 tillsynsbegäran.docx", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 28474-2023 tillsynsbegäran.docx", "A 28474-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 52377-2025 tillsynsbegäran mail.docx", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 28474-2023 tillsynsbegäran mail.docx", "A 28474-2023")</f>
+        <v/>
+      </c>
+      <c r="AE21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 28474-2023 prioriterade fågelarter.docx", "A 28474-2023")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 28474-2023</t>
+          <t>A 58091-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2955,10 +2959,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45103</v>
+        <v>44900</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2970,8 +2974,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>5.1</v>
+        <v>2.1</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2980,7 +2989,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2995,7 +3004,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -3004,53 +3013,49 @@
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Blåhake</t>
+          <t>Hårklomossa</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 28474-2023 artfynd.xlsx", "A 28474-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 58091-2022 artfynd.xlsx", "A 58091-2022")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 28474-2023 karta.png", "A 28474-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 58091-2022 karta.png", "A 58091-2022")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 28474-2023 georefererad karta.tif", "A 28474-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 58091-2022 georefererad karta.tif", "A 58091-2022")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 28474-2023 FSC-klagomål.docx", "A 28474-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 58091-2022 FSC-klagomål.docx", "A 58091-2022")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 28474-2023 FSC-klagomål mail.docx", "A 28474-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 58091-2022 FSC-klagomål mail.docx", "A 58091-2022")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 28474-2023 tillsynsbegäran.docx", "A 28474-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 58091-2022 tillsynsbegäran.docx", "A 58091-2022")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 28474-2023 tillsynsbegäran mail.docx", "A 28474-2023")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 28474-2023 prioriterade fågelarter.docx", "A 28474-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 58091-2022 tillsynsbegäran mail.docx", "A 58091-2022")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 40528-2024</t>
+          <t>A 25093-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3064,10 +3069,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45555</v>
+        <v>46175</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3079,14 +3084,19 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
         <v>1</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -3120,35 +3130,35 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 40528-2024 artfynd.xlsx", "A 40528-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 25093-2026 artfynd.xlsx", "A 25093-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 40528-2024 karta.png", "A 40528-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 25093-2026 karta.png", "A 25093-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 40528-2024 georefererad karta.tif", "A 40528-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 25093-2026 georefererad karta.tif", "A 25093-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 40528-2024 FSC-klagomål.docx", "A 40528-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 25093-2026 FSC-klagomål.docx", "A 25093-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 40528-2024 FSC-klagomål mail.docx", "A 40528-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 25093-2026 FSC-klagomål mail.docx", "A 25093-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 40528-2024 tillsynsbegäran.docx", "A 40528-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 25093-2026 tillsynsbegäran.docx", "A 25093-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 40528-2024 tillsynsbegäran mail.docx", "A 40528-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 25093-2026 tillsynsbegäran mail.docx", "A 25093-2026")</f>
         <v/>
       </c>
     </row>
@@ -3172,7 +3182,7 @@
         <v>46010</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3269,7 +3279,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 16784-2026</t>
+          <t>A 28566-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3283,10 +3293,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46113</v>
+        <v>45478</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3298,13 +3308,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>4.2</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3337,49 +3342,49 @@
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Hårklomossa</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 16784-2026 artfynd.xlsx", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 28566-2024 artfynd.xlsx", "A 28566-2024")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 16784-2026 karta.png", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 28566-2024 karta.png", "A 28566-2024")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 16784-2026 georefererad karta.tif", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 28566-2024 georefererad karta.tif", "A 28566-2024")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 16784-2026 FSC-klagomål.docx", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 28566-2024 FSC-klagomål.docx", "A 28566-2024")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 16784-2026 FSC-klagomål mail.docx", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 28566-2024 FSC-klagomål mail.docx", "A 28566-2024")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 16784-2026 tillsynsbegäran.docx", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 28566-2024 tillsynsbegäran.docx", "A 28566-2024")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 16784-2026 tillsynsbegäran mail.docx", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 28566-2024 tillsynsbegäran mail.docx", "A 28566-2024")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 18427-2026</t>
+          <t>A 16784-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3393,10 +3398,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46127</v>
+        <v>46113</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3414,7 +3419,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3447,53 +3452,49 @@
         <v>1</v>
       </c>
       <c r="T26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Hårklomossa</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 18427-2026 artfynd.xlsx", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 16784-2026 artfynd.xlsx", "A 16784-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 18427-2026 karta.png", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 16784-2026 karta.png", "A 16784-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 18427-2026 georefererad karta.tif", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 16784-2026 georefererad karta.tif", "A 16784-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 18427-2026 FSC-klagomål.docx", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 16784-2026 FSC-klagomål.docx", "A 16784-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 18427-2026 FSC-klagomål mail.docx", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 16784-2026 FSC-klagomål mail.docx", "A 16784-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 18427-2026 tillsynsbegäran.docx", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 16784-2026 tillsynsbegäran.docx", "A 16784-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 18427-2026 tillsynsbegäran mail.docx", "A 18427-2026")</f>
-        <v/>
-      </c>
-      <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 18427-2026 prioriterade fågelarter.docx", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 16784-2026 tillsynsbegäran mail.docx", "A 16784-2026")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 19233-2026</t>
+          <t>A 18427-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3507,10 +3508,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46132</v>
+        <v>46127</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3522,14 +3523,19 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3559,46 +3565,50 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 19233-2026 artfynd.xlsx", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 18427-2026 artfynd.xlsx", "A 18427-2026")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 19233-2026 karta.png", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 18427-2026 karta.png", "A 18427-2026")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 19233-2026 georefererad karta.tif", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 18427-2026 georefererad karta.tif", "A 18427-2026")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 19233-2026 FSC-klagomål.docx", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 18427-2026 FSC-klagomål.docx", "A 18427-2026")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 19233-2026 FSC-klagomål mail.docx", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 18427-2026 FSC-klagomål mail.docx", "A 18427-2026")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 19233-2026 tillsynsbegäran.docx", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 18427-2026 tillsynsbegäran.docx", "A 18427-2026")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 19233-2026 tillsynsbegäran mail.docx", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 18427-2026 tillsynsbegäran mail.docx", "A 18427-2026")</f>
+        <v/>
+      </c>
+      <c r="AE27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 18427-2026 prioriterade fågelarter.docx", "A 18427-2026")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 21019-2026</t>
+          <t>A 19233-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3612,10 +3622,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46145</v>
+        <v>46132</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3627,19 +3637,14 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>4.7</v>
+        <v>1.6</v>
       </c>
       <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
         <v>1</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -3673,42 +3678,42 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 21019-2026 artfynd.xlsx", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 19233-2026 artfynd.xlsx", "A 19233-2026")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 21019-2026 karta.png", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 19233-2026 karta.png", "A 19233-2026")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 21019-2026 georefererad karta.tif", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 19233-2026 georefererad karta.tif", "A 19233-2026")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 21019-2026 FSC-klagomål.docx", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 19233-2026 FSC-klagomål.docx", "A 19233-2026")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 21019-2026 FSC-klagomål mail.docx", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 19233-2026 FSC-klagomål mail.docx", "A 19233-2026")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 21019-2026 tillsynsbegäran.docx", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 19233-2026 tillsynsbegäran.docx", "A 19233-2026")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 21019-2026 tillsynsbegäran mail.docx", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 19233-2026 tillsynsbegäran mail.docx", "A 19233-2026")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 25093-2026</t>
+          <t>A 30915-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3722,10 +3727,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46175</v>
+        <v>46213</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3739,17 +3744,17 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>4</v>
+        <v>8.9</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -3779,46 +3784,46 @@
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 25093-2026 artfynd.xlsx", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 30915-2026 artfynd.xlsx", "A 30915-2026")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 25093-2026 karta.png", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 30915-2026 karta.png", "A 30915-2026")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 25093-2026 georefererad karta.tif", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 30915-2026 georefererad karta.tif", "A 30915-2026")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 25093-2026 FSC-klagomål.docx", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 30915-2026 FSC-klagomål.docx", "A 30915-2026")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 25093-2026 FSC-klagomål mail.docx", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 30915-2026 FSC-klagomål mail.docx", "A 30915-2026")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 25093-2026 tillsynsbegäran.docx", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 30915-2026 tillsynsbegäran.docx", "A 30915-2026")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 25093-2026 tillsynsbegäran mail.docx", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 30915-2026 tillsynsbegäran mail.docx", "A 30915-2026")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 30915-2026</t>
+          <t>A 35199-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3832,10 +3837,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46213</v>
+        <v>46260</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3853,7 +3858,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>8.9</v>
+        <v>5.6</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
@@ -3862,7 +3867,7 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -3877,7 +3882,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -3893,42 +3898,42 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 30915-2026 artfynd.xlsx", "A 30915-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 35199-2026 artfynd.xlsx", "A 35199-2026")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 30915-2026 karta.png", "A 30915-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 35199-2026 karta.png", "A 35199-2026")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 30915-2026 georefererad karta.tif", "A 30915-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 35199-2026 georefererad karta.tif", "A 35199-2026")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 30915-2026 FSC-klagomål.docx", "A 30915-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 35199-2026 FSC-klagomål.docx", "A 35199-2026")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 30915-2026 FSC-klagomål mail.docx", "A 30915-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 35199-2026 FSC-klagomål mail.docx", "A 35199-2026")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 30915-2026 tillsynsbegäran.docx", "A 30915-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 35199-2026 tillsynsbegäran.docx", "A 35199-2026")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 30915-2026 tillsynsbegäran mail.docx", "A 30915-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 35199-2026 tillsynsbegäran mail.docx", "A 35199-2026")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 35199-2026</t>
+          <t>A 40528-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3942,10 +3947,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46260</v>
+        <v>45555</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3957,13 +3962,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>5.6</v>
+        <v>2.8</v>
       </c>
       <c r="J31" t="n">
         <v>1</v>
@@ -3972,7 +3972,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -3999,39 +3999,39 @@
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 35199-2026 artfynd.xlsx", "A 35199-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 40528-2024 artfynd.xlsx", "A 40528-2024")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 35199-2026 karta.png", "A 35199-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 40528-2024 karta.png", "A 40528-2024")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 35199-2026 georefererad karta.tif", "A 35199-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 40528-2024 georefererad karta.tif", "A 40528-2024")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 35199-2026 FSC-klagomål.docx", "A 35199-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 40528-2024 FSC-klagomål.docx", "A 40528-2024")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 35199-2026 FSC-klagomål mail.docx", "A 35199-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 40528-2024 FSC-klagomål mail.docx", "A 40528-2024")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 35199-2026 tillsynsbegäran.docx", "A 35199-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 40528-2024 tillsynsbegäran.docx", "A 40528-2024")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 35199-2026 tillsynsbegäran mail.docx", "A 35199-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 40528-2024 tillsynsbegäran mail.docx", "A 40528-2024")</f>
         <v/>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
         <v>44546</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>44732</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4184,7 +4184,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 22861-2022</t>
+          <t>A 64869-2021</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4198,10 +4198,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44715</v>
+        <v>44512</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4213,8 +4213,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>0.6</v>
+        <v>3.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4257,7 +4262,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 64869-2021</t>
+          <t>A 22861-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4271,10 +4276,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44512</v>
+        <v>44715</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4286,13 +4291,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>3.6</v>
+        <v>0.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4352,7 +4352,7 @@
         <v>44508</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         <v>44480</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>44809</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
         <v>44811</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4649,7 +4649,7 @@
         <v>44628</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
         <v>44809</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         <v>44706</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4873,7 +4873,7 @@
         <v>44706</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 13501-2025</t>
+          <t>A 39027-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45736</v>
+        <v>44817</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4958,8 +4958,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5002,7 +5007,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 47094-2023</t>
+          <t>A 35471-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5016,10 +5021,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45196</v>
+        <v>45531</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5032,7 +5037,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5075,7 +5080,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 31921-2022</t>
+          <t>A 4164-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5089,10 +5094,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44777</v>
+        <v>44588</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5104,8 +5109,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5148,7 +5158,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 42804-2023</t>
+          <t>A 9712-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5158,14 +5168,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45182</v>
+        <v>45362</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5179,11 +5189,11 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5226,7 +5236,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 39030-2022</t>
+          <t>A 58390-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5240,10 +5250,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44817</v>
+        <v>45633</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5255,13 +5265,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5304,7 +5309,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 39027-2022</t>
+          <t>A 42804-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5314,14 +5319,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44817</v>
+        <v>45182</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5339,7 +5344,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5382,7 +5387,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 8244-2025</t>
+          <t>A 9510-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5396,10 +5401,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45708</v>
+        <v>44981</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5412,7 +5417,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5455,7 +5460,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 28100-2024</t>
+          <t>A 1309-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5469,10 +5474,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45476</v>
+        <v>45303</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5485,7 +5490,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5528,7 +5533,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 51344-2023</t>
+          <t>A 35444-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5542,10 +5547,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45219</v>
+        <v>45531</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5557,13 +5562,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5606,7 +5606,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 8803-2025</t>
+          <t>A 23263-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5620,10 +5620,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45712</v>
+        <v>44720</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5679,7 +5679,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 3735-2024</t>
+          <t>A 47201-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5693,10 +5693,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45321</v>
+        <v>45196</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5708,13 +5708,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5757,7 +5752,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 35445-2024</t>
+          <t>A 61396-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5771,10 +5766,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45531</v>
+        <v>45264</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5787,7 +5782,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5830,7 +5825,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 39337-2022</t>
+          <t>A 8259-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5844,10 +5839,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44817</v>
+        <v>45708</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5860,7 +5855,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5903,7 +5898,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 23308-2025</t>
+          <t>A 24116-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5917,10 +5912,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45791</v>
+        <v>45456</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5933,7 +5928,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5976,7 +5971,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 20463-2025</t>
+          <t>A 35930-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5990,10 +5985,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45775</v>
+        <v>45148</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6011,7 +6006,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.9</v>
+        <v>5.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6054,7 +6049,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 28471-2023</t>
+          <t>A 63863-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6068,10 +6063,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45103</v>
+        <v>45278</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6084,7 +6079,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6127,7 +6122,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 16881-2023</t>
+          <t>A 59938-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6141,10 +6136,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45033</v>
+        <v>45257</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6156,13 +6151,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6205,7 +6195,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 61396-2023</t>
+          <t>A 52828-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6219,10 +6209,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45264</v>
+        <v>45610</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6235,7 +6225,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6278,7 +6268,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 4164-2022</t>
+          <t>A 15256-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6292,10 +6282,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44588</v>
+        <v>45744</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6309,11 +6299,11 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.5</v>
+        <v>5.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6356,7 +6346,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 24255-2024</t>
+          <t>A 24115-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6370,10 +6360,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45457</v>
+        <v>45456</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6386,7 +6376,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.4</v>
+        <v>8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6429,7 +6419,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 61271-2022</t>
+          <t>A 19663-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6443,10 +6433,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44909</v>
+        <v>46134</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6460,11 +6450,11 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>14.1</v>
+        <v>1.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6524,7 +6514,7 @@
         <v>45758</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6585,7 +6575,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 57422-2021</t>
+          <t>A 18768-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6599,10 +6589,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44483</v>
+        <v>45764</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6614,8 +6604,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6658,7 +6653,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 56887-2022</t>
+          <t>A 4801-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6672,10 +6667,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44894</v>
+        <v>45328</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6688,7 +6683,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6731,7 +6726,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 38196-2024</t>
+          <t>A 4802-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6745,10 +6740,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45545</v>
+        <v>45328</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6761,7 +6756,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6804,7 +6799,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 35060-2024</t>
+          <t>A 8990-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6818,10 +6813,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45527</v>
+        <v>44979</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6833,13 +6828,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6882,7 +6872,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 64060-2023</t>
+          <t>A 24255-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6896,10 +6886,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45279</v>
+        <v>45457</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6912,7 +6902,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6955,7 +6945,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 14215-2024</t>
+          <t>A 42802-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6965,14 +6955,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45393</v>
+        <v>45182</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6986,11 +6976,11 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>4.2</v>
+        <v>0.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7033,7 +7023,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 20289-2024</t>
+          <t>A 28471-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7047,10 +7037,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45435</v>
+        <v>45103</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7062,13 +7052,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7111,7 +7096,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 38190-2024</t>
+          <t>A 44946-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7125,10 +7110,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45545</v>
+        <v>45918</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7141,7 +7126,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7184,7 +7169,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 44946-2025</t>
+          <t>A 22867-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7198,10 +7183,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45918</v>
+        <v>44715</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7214,7 +7199,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7274,7 +7259,7 @@
         <v>45918</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7330,7 +7315,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 9712-2024</t>
+          <t>A 6835-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7344,10 +7329,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45362</v>
+        <v>45700</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7359,13 +7344,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7408,7 +7388,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 24116-2024</t>
+          <t>A 64060-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7422,10 +7402,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45456</v>
+        <v>45279</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7438,7 +7418,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7481,7 +7461,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 55832-2023</t>
+          <t>A 48707-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7495,10 +7475,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45239</v>
+        <v>45593</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7511,7 +7491,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.5</v>
+        <v>6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7554,7 +7534,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 10515-2023</t>
+          <t>A 55832-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7568,10 +7548,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44987</v>
+        <v>45239</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7584,7 +7564,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7627,7 +7607,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 4058-2022</t>
+          <t>A 58388-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7641,10 +7621,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44588</v>
+        <v>45633</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7657,7 +7637,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.7</v>
+        <v>5.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7700,7 +7680,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 15256-2025</t>
+          <t>A 21210-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7714,10 +7694,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45744</v>
+        <v>45779</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7735,7 +7715,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>5.5</v>
+        <v>1.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7778,7 +7758,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 27498-2025</t>
+          <t>A 18978-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7792,10 +7772,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45813</v>
+        <v>45764</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7808,7 +7788,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7851,7 +7831,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 33011-2023</t>
+          <t>A 23717-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7865,10 +7845,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45125</v>
+        <v>45793</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7881,7 +7861,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7924,7 +7904,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 43075-2023</t>
+          <t>A 50958-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7938,10 +7918,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45182</v>
+        <v>45946</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7954,7 +7934,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3.1</v>
+        <v>0.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7997,7 +7977,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 23263-2022</t>
+          <t>A 31921-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8011,10 +7991,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44720</v>
+        <v>44777</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8027,7 +8007,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8070,7 +8050,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 48168-2024</t>
+          <t>A 43075-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8084,10 +8064,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45589</v>
+        <v>45182</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8100,7 +8080,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>5.5</v>
+        <v>3.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8143,7 +8123,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 35444-2024</t>
+          <t>A 47196-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8157,10 +8137,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45531</v>
+        <v>45196</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8173,7 +8153,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.5</v>
+        <v>5.9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8216,7 +8196,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 35471-2024</t>
+          <t>A 13454-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8230,10 +8210,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45531</v>
+        <v>44645</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8246,7 +8226,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8289,7 +8269,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 58390-2024</t>
+          <t>A 53618-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8303,10 +8283,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45633</v>
+        <v>45614</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8319,7 +8299,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3</v>
+        <v>10.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8362,7 +8342,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 50958-2025</t>
+          <t>A 30961-2022</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8376,10 +8356,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45946</v>
+        <v>44768</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8391,8 +8371,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>0.4</v>
+        <v>3.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8435,7 +8420,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 13454-2022</t>
+          <t>A 55025-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8449,10 +8434,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44645</v>
+        <v>45967</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8465,7 +8450,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8508,7 +8493,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 10743-2023</t>
+          <t>A 42803-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8518,14 +8503,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44988</v>
+        <v>45182</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8539,11 +8524,11 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8586,7 +8571,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 50611-2024</t>
+          <t>A 8803-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8600,10 +8585,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45601</v>
+        <v>45712</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8616,7 +8601,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8659,7 +8644,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 42802-2023</t>
+          <t>A 917-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8669,14 +8654,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45182</v>
+        <v>46030</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8688,13 +8673,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>0.6</v>
+        <v>3.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8737,7 +8717,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 52829-2024</t>
+          <t>A 56313-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8751,10 +8731,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45610</v>
+        <v>45624</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8766,8 +8746,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I95" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8810,7 +8795,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 18768-2025</t>
+          <t>A 59522-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8820,14 +8805,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45764</v>
+        <v>45989</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8845,7 +8830,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8888,7 +8873,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 56313-2024</t>
+          <t>A 21253-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8902,10 +8887,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45624</v>
+        <v>46147</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8917,13 +8902,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I97" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8966,7 +8946,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 42803-2023</t>
+          <t>A 21257-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8976,14 +8956,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45182</v>
+        <v>46147</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8995,13 +8975,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I98" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9044,7 +9019,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 38382-2022</t>
+          <t>A 10743-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9058,10 +9033,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44812</v>
+        <v>44988</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9079,7 +9054,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9122,7 +9097,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 24115-2024</t>
+          <t>A 14215-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9136,10 +9111,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45456</v>
+        <v>45393</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9151,8 +9126,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I100" t="n">
-        <v>8</v>
+        <v>4.2</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9195,7 +9175,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 55025-2025</t>
+          <t>A 55191-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9209,10 +9189,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45967</v>
+        <v>45237</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9225,7 +9205,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9268,7 +9248,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 20086-2024</t>
+          <t>A 60506-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9278,14 +9258,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45434</v>
+        <v>45995</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9298,7 +9278,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9341,7 +9321,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 9510-2023</t>
+          <t>A 60508-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9355,10 +9335,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44981</v>
+        <v>45995</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9371,7 +9351,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9414,7 +9394,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 10404-2022</t>
+          <t>A 60503-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9428,10 +9408,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44623</v>
+        <v>45995</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9444,7 +9424,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9487,7 +9467,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 54680-2021</t>
+          <t>A 59025-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9501,10 +9481,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44473</v>
+        <v>45636</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9516,8 +9496,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I105" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9560,7 +9545,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 30102-2025</t>
+          <t>A 3227-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9574,10 +9559,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45826</v>
+        <v>45679</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9590,7 +9575,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9633,7 +9618,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 18955-2025</t>
+          <t>A 61788-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9647,10 +9632,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45764</v>
+        <v>46002</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9662,8 +9647,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>8.1</v>
+        <v>0.9</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9706,7 +9696,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 59522-2025</t>
+          <t>A 17243-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9716,14 +9706,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45989</v>
+        <v>45414</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9735,13 +9725,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I108" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9784,7 +9769,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 53647-2023</t>
+          <t>A 64066-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9794,14 +9779,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45230</v>
+        <v>46013</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9814,7 +9799,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9857,7 +9842,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 23620-2024</t>
+          <t>A 63628-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9871,10 +9856,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45454</v>
+        <v>46014</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9887,7 +9872,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2.2</v>
+        <v>3.8</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9930,7 +9915,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 59025-2024</t>
+          <t>A 35060-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9944,10 +9929,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45636</v>
+        <v>45527</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9965,7 +9950,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10008,7 +9993,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 60503-2025</t>
+          <t>A 1788-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10022,10 +10007,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45995</v>
+        <v>46034</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10038,7 +10023,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10081,7 +10066,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 22867-2022</t>
+          <t>A 52826-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10095,10 +10080,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44715</v>
+        <v>45610</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10111,7 +10096,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10154,7 +10139,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 60508-2025</t>
+          <t>A 52829-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10168,10 +10153,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45995</v>
+        <v>45610</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10184,7 +10169,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10227,7 +10212,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 60506-2025</t>
+          <t>A 45664-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10241,10 +10226,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45995</v>
+        <v>45923</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10256,8 +10241,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I115" t="n">
-        <v>0.8</v>
+        <v>9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10300,7 +10290,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 31397-2025</t>
+          <t>A 2911-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10314,10 +10304,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45833</v>
+        <v>46038</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10330,7 +10320,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10373,7 +10363,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 61788-2025</t>
+          <t>A 23754-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10387,10 +10377,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46002</v>
+        <v>46164</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10404,11 +10394,11 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.9</v>
+        <v>12.2</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10451,7 +10441,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 18978-2025</t>
+          <t>A 11974-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10465,10 +10455,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45764</v>
+        <v>45728</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10481,7 +10471,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10524,7 +10514,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 4801-2024</t>
+          <t>A 47222-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10538,10 +10528,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45328</v>
+        <v>45586</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10553,8 +10543,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I119" t="n">
-        <v>0.9</v>
+        <v>5.3</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10597,7 +10592,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 4802-2024</t>
+          <t>A 61271-2022</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10611,10 +10606,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45328</v>
+        <v>44909</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10626,8 +10621,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I120" t="n">
-        <v>0.9</v>
+        <v>14.1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10670,7 +10670,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 1788-2026</t>
+          <t>A 48168-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10684,10 +10684,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46034</v>
+        <v>45589</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10700,7 +10700,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10743,7 +10743,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 30961-2022</t>
+          <t>A 4587-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10757,10 +10757,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44768</v>
+        <v>45687</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10770,11 +10770,6 @@
       <c r="G122" t="inlineStr">
         <is>
           <t>KARLSKOGA</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
         </is>
       </c>
       <c r="I122" t="n">
@@ -10821,7 +10816,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 55191-2023</t>
+          <t>A 18955-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10835,10 +10830,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45237</v>
+        <v>45764</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10851,7 +10846,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.9</v>
+        <v>8.1</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10894,7 +10889,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 32287-2025</t>
+          <t>A 4587-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10908,10 +10903,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45835</v>
+        <v>45687</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10923,13 +10918,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I124" t="n">
-        <v>10.9</v>
+        <v>3.3</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10972,7 +10962,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 2911-2026</t>
+          <t>A 50614-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10986,10 +10976,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46038</v>
+        <v>45601</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11002,7 +10992,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11045,7 +11035,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 45664-2025</t>
+          <t>A 55182-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11059,10 +11049,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45923</v>
+        <v>45618</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11074,13 +11064,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I126" t="n">
-        <v>9</v>
+        <v>11.4</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11123,7 +11108,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 47222-2024</t>
+          <t>A 4058-2022</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11137,10 +11122,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45586</v>
+        <v>44588</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11152,13 +11137,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I127" t="n">
-        <v>5.3</v>
+        <v>1.7</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11201,7 +11181,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 64066-2025</t>
+          <t>A 24666-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11211,14 +11191,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46013</v>
+        <v>46171</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11231,7 +11211,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.9</v>
+        <v>6.1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11274,7 +11254,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 63628-2025</t>
+          <t>A 9917-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11288,10 +11268,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46014</v>
+        <v>46073</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11304,7 +11284,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11347,7 +11327,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 13496-2025</t>
+          <t>A 25092-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11361,10 +11341,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45736</v>
+        <v>46175</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11376,8 +11356,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I130" t="n">
-        <v>8.800000000000001</v>
+        <v>1.9</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11420,7 +11405,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 11974-2025</t>
+          <t>A 25098-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11430,14 +11415,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45728</v>
+        <v>46175</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11447,6 +11432,11 @@
       <c r="G131" t="inlineStr">
         <is>
           <t>KARLSKOGA</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I131" t="n">
@@ -11493,7 +11483,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 63863-2023</t>
+          <t>A 13473-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11507,10 +11497,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45278</v>
+        <v>46094</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11523,7 +11513,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11566,7 +11556,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 1309-2024</t>
+          <t>A 28100-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11580,10 +11570,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45303</v>
+        <v>45476</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11596,7 +11586,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11639,7 +11629,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 52826-2024</t>
+          <t>A 12897-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11653,10 +11643,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45610</v>
+        <v>46092</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11669,7 +11659,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11712,7 +11702,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 9917-2026</t>
+          <t>A 14580-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11726,10 +11716,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46073</v>
+        <v>46101</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11741,8 +11731,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I135" t="n">
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11785,7 +11780,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 1106-2024</t>
+          <t>A 26608-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11799,10 +11794,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45302</v>
+        <v>46184</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11814,8 +11809,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I136" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11858,7 +11858,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 48707-2024</t>
+          <t>A 27120-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11872,10 +11872,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45593</v>
+        <v>46188</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11888,7 +11888,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11931,7 +11931,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 13473-2026</t>
+          <t>A 26819-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11945,10 +11945,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46094</v>
+        <v>46185</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11960,8 +11960,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I138" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -12004,7 +12009,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 14580-2026</t>
+          <t>A 3239-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12018,10 +12023,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46101</v>
+        <v>46041</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12031,11 +12036,6 @@
       <c r="G139" t="inlineStr">
         <is>
           <t>KARLSKOGA</t>
-        </is>
-      </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I139" t="n">
@@ -12082,7 +12082,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 12897-2026</t>
+          <t>A 26820-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12096,10 +12096,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46092</v>
+        <v>46185</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12111,8 +12111,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I140" t="n">
-        <v>1.3</v>
+        <v>9.9</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12155,7 +12160,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 35470-2024</t>
+          <t>A 26821-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12169,10 +12174,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45531</v>
+        <v>46185</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12184,8 +12189,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I141" t="n">
-        <v>0.5</v>
+        <v>7.9</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12228,7 +12238,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 16782-2026</t>
+          <t>A 26822-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12242,10 +12252,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46113</v>
+        <v>46185</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12263,7 +12273,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12306,7 +12316,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 16783-2026</t>
+          <t>A 26824-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12320,10 +12330,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46113</v>
+        <v>46185</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12341,7 +12351,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.7</v>
+        <v>5</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12384,7 +12394,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 16787-2026</t>
+          <t>A 26825-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12398,10 +12408,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46113</v>
+        <v>46185</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12419,7 +12429,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12462,7 +12472,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 15058-2026</t>
+          <t>A 1106-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12476,10 +12486,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46104</v>
+        <v>45302</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12492,7 +12502,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>4.3</v>
+        <v>1.9</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12535,7 +12545,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 8990-2023</t>
+          <t>A 39030-2022</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12549,10 +12559,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>44979</v>
+        <v>44817</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12564,8 +12574,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I146" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12608,7 +12623,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 17734-2026</t>
+          <t>A 16783-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12622,10 +12637,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46122</v>
+        <v>46113</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12643,7 +12658,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12686,7 +12701,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 50614-2024</t>
+          <t>A 16787-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12700,10 +12715,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45601</v>
+        <v>46113</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12715,8 +12730,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I148" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12759,7 +12779,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 19011-2026</t>
+          <t>A 16782-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12773,10 +12793,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46130</v>
+        <v>46113</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12794,7 +12814,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12837,7 +12857,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 55182-2024</t>
+          <t>A 38382-2022</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12851,10 +12871,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45618</v>
+        <v>44812</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12866,8 +12886,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I150" t="n">
-        <v>11.4</v>
+        <v>2.2</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12910,7 +12935,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 19010-2026</t>
+          <t>A 27392-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12924,10 +12949,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46130</v>
+        <v>46189</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12945,7 +12970,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12988,7 +13013,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 19009-2026</t>
+          <t>A 15058-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13002,10 +13027,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46130</v>
+        <v>46104</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13017,13 +13042,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I152" t="n">
-        <v>6.3</v>
+        <v>4.3</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -13066,7 +13086,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 19008-2026</t>
+          <t>A 17734-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13080,10 +13100,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46130</v>
+        <v>46122</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13101,7 +13121,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -13144,7 +13164,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 52797-2021</t>
+          <t>A 16881-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13158,10 +13178,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>44467</v>
+        <v>45033</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13173,8 +13193,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I154" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13217,7 +13242,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 19663-2026</t>
+          <t>A 19009-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13231,10 +13256,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46134</v>
+        <v>46130</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13252,7 +13277,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.6</v>
+        <v>6.3</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13295,7 +13320,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 6835-2025</t>
+          <t>A 19011-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13309,10 +13334,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45700</v>
+        <v>46130</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13324,8 +13349,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I156" t="n">
-        <v>3</v>
+        <v>0.9</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13368,7 +13398,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 8259-2025</t>
+          <t>A 19010-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13382,10 +13412,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45708</v>
+        <v>46130</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13397,8 +13427,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I157" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13441,7 +13476,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 53620-2024</t>
+          <t>A 19008-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13455,10 +13490,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45614</v>
+        <v>46130</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13470,8 +13505,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I158" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13514,7 +13554,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 21210-2025</t>
+          <t>A 57422-2021</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13528,10 +13568,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45779</v>
+        <v>44483</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13543,13 +13583,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I159" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13592,7 +13627,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 35930-2023</t>
+          <t>A 8244-2025</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13606,10 +13641,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45148</v>
+        <v>45708</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13621,13 +13656,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I160" t="n">
-        <v>5.2</v>
+        <v>1.1</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13670,7 +13700,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 23717-2025</t>
+          <t>A 38190-2024</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13684,10 +13714,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45793</v>
+        <v>45545</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13743,7 +13773,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 47196-2023</t>
+          <t>A 20463-2025</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13757,10 +13787,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45196</v>
+        <v>45775</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13772,8 +13802,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I162" t="n">
-        <v>5.9</v>
+        <v>0.9</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13816,7 +13851,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 53618-2024</t>
+          <t>A 35470-2024</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13830,10 +13865,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45614</v>
+        <v>45531</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13846,7 +13881,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>10.1</v>
+        <v>0.5</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13889,7 +13924,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 917-2026</t>
+          <t>A 35445-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13903,10 +13938,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46030</v>
+        <v>45531</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13919,7 +13954,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>3.7</v>
+        <v>0.5</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13962,7 +13997,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 58388-2024</t>
+          <t>A 47094-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13976,10 +14011,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45633</v>
+        <v>45196</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13992,7 +14027,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>5.8</v>
+        <v>1.9</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -14035,7 +14070,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 47201-2023</t>
+          <t>A 38196-2024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -14049,10 +14084,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45196</v>
+        <v>45545</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14065,7 +14100,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -14108,7 +14143,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 52828-2024</t>
+          <t>A 50611-2024</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -14122,10 +14157,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45610</v>
+        <v>45601</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14138,7 +14173,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>8.300000000000001</v>
+        <v>1</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14181,7 +14216,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 17243-2024</t>
+          <t>A 20289-2024</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14195,10 +14230,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45414</v>
+        <v>45435</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14210,8 +14245,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I168" t="n">
-        <v>3.2</v>
+        <v>0.7</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14254,7 +14294,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 59938-2023</t>
+          <t>A 52797-2021</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14268,10 +14308,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45257</v>
+        <v>44467</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14284,7 +14324,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14327,7 +14367,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 21253-2026</t>
+          <t>A 31378-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14341,10 +14381,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46147</v>
+        <v>46213</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14357,7 +14397,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14400,7 +14440,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 21257-2026</t>
+          <t>A 20086-2024</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14410,14 +14450,14 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46147</v>
+        <v>45434</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14430,7 +14470,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14473,7 +14513,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 3227-2025</t>
+          <t>A 13496-2025</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14487,10 +14527,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45679</v>
+        <v>45736</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14503,7 +14543,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>4.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14546,7 +14586,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 38742-2023</t>
+          <t>A 56887-2022</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14556,14 +14596,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45161</v>
+        <v>44894</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14575,13 +14615,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I173" t="n">
-        <v>4.2</v>
+        <v>1.8</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14624,7 +14659,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 23754-2026</t>
+          <t>A 35094-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14638,10 +14673,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46164</v>
+        <v>46260</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14655,11 +14690,11 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I174" t="n">
-        <v>12.2</v>
+        <v>1.9</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14702,7 +14737,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 4587-2025</t>
+          <t>A 35699-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14712,14 +14747,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45687</v>
+        <v>46265</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14731,8 +14766,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I175" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14775,7 +14815,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 4587-2025</t>
+          <t>A 33011-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14789,10 +14829,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45687</v>
+        <v>45125</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14805,7 +14845,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>3.3</v>
+        <v>0.8</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14848,7 +14888,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 24666-2026</t>
+          <t>A 36374-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14862,10 +14902,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46171</v>
+        <v>46268</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14877,8 +14917,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I177" t="n">
-        <v>6.1</v>
+        <v>1.6</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14921,7 +14966,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 25098-2026</t>
+          <t>A 51344-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14931,14 +14976,14 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46175</v>
+        <v>45219</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14952,11 +14997,11 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1.4</v>
+        <v>4.5</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14999,7 +15044,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 25092-2026</t>
+          <t>A 37089-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -15013,10 +15058,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46175</v>
+        <v>46273</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15028,13 +15073,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I179" t="n">
-        <v>1.9</v>
+        <v>15.8</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -15077,7 +15117,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 26822-2026</t>
+          <t>A 10515-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -15091,10 +15131,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46185</v>
+        <v>44987</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15106,13 +15146,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I180" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -15155,7 +15190,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 26819-2026</t>
+          <t>A 39337-2022</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15169,10 +15204,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46185</v>
+        <v>44817</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15184,13 +15219,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I181" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15233,7 +15263,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 3239-2026</t>
+          <t>A 53620-2024</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15247,10 +15277,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46041</v>
+        <v>45614</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15263,7 +15293,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15306,7 +15336,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 26821-2026</t>
+          <t>A 38043-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15320,10 +15350,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46185</v>
+        <v>46280</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15337,11 +15367,11 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I183" t="n">
-        <v>7.9</v>
+        <v>1.1</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15384,7 +15414,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 26820-2026</t>
+          <t>A 13501-2025</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15398,10 +15428,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46185</v>
+        <v>45736</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15413,13 +15443,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I184" t="n">
-        <v>9.9</v>
+        <v>3.2</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15462,7 +15487,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 26608-2026</t>
+          <t>A 38020-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15476,10 +15501,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46184</v>
+        <v>46280</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15497,7 +15522,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>1.6</v>
+        <v>4.1</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15540,7 +15565,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 26824-2026</t>
+          <t>A 10404-2022</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15554,10 +15579,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46185</v>
+        <v>44623</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15569,13 +15594,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I186" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15618,7 +15638,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 26825-2026</t>
+          <t>A 38742-2023</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15628,14 +15648,14 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46185</v>
+        <v>45161</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15649,11 +15669,11 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I187" t="n">
-        <v>0.8</v>
+        <v>4.2</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15696,7 +15716,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 27392-2026</t>
+          <t>A 3735-2024</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15710,10 +15730,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46189</v>
+        <v>45321</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15727,11 +15747,11 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I188" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15774,7 +15794,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 27120-2026</t>
+          <t>A 23308-2025</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15788,10 +15808,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46188</v>
+        <v>45791</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15804,7 +15824,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>4.7</v>
+        <v>1.5</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15847,7 +15867,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 31378-2026</t>
+          <t>A 27498-2025</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15861,10 +15881,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46213</v>
+        <v>45813</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15877,7 +15897,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>3.7</v>
+        <v>1.2</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15920,7 +15940,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 35094-2026</t>
+          <t>A 23620-2024</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15934,10 +15954,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46260</v>
+        <v>45454</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15949,13 +15969,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I191" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15998,7 +16013,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 35699-2026</t>
+          <t>A 53647-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -16008,14 +16023,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46265</v>
+        <v>45230</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16027,13 +16042,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I192" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -16076,7 +16086,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 36374-2026</t>
+          <t>A 30102-2025</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -16090,10 +16100,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46268</v>
+        <v>45826</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16105,13 +16115,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I193" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -16154,7 +16159,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 37089-2026</t>
+          <t>A 54680-2021</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -16168,10 +16173,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46273</v>
+        <v>44473</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16184,7 +16189,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>15.8</v>
+        <v>2.9</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -16227,7 +16232,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 38043-2026</t>
+          <t>A 31397-2025</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16241,10 +16246,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46280</v>
+        <v>45833</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16256,13 +16261,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I195" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -16305,7 +16305,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 38020-2026</t>
+          <t>A 32287-2025</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16319,10 +16319,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46280</v>
+        <v>45835</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16336,11 +16336,11 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I196" t="n">
-        <v>4.1</v>
+        <v>10.9</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16400,7 +16400,7 @@
         <v>45953</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>

--- a/Översikt KARLSKOGA.xlsx
+++ b/Översikt KARLSKOGA.xlsx
@@ -601,7 +601,7 @@
         <v>45562</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>45958</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         <v>45989</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>44510</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>46100</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>45989</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>44473</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>46010</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>46010</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1719,7 +1719,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 60085-2021</t>
+          <t>A 8803-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1733,10 +1733,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44495</v>
+        <v>46066</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1758,10 +1758,10 @@
         <v>3</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1776,18 +1776,243 @@
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
       </c>
       <c r="T11" t="n">
+        <v>8</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp
+Platt fjädermossa
+Skogshakmossa
+Trubbfjädermossa</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 8803-2026 artfynd.xlsx", "A 8803-2026")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 8803-2026 karta.png", "A 8803-2026")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 8803-2026 georefererad karta.tif", "A 8803-2026")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 8803-2026 FSC-klagomål.docx", "A 8803-2026")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 8803-2026 FSC-klagomål mail.docx", "A 8803-2026")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 8803-2026 tillsynsbegäran.docx", "A 8803-2026")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 8803-2026 tillsynsbegäran mail.docx", "A 8803-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 63187-2025</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>46010</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>KARLSKOGA</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4</v>
+      </c>
+      <c r="T12" t="n">
+        <v>4</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Talltita
+Bronshjon
+Korallblylav
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 63187-2025 artfynd.xlsx", "A 63187-2025")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 63187-2025 karta.png", "A 63187-2025")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 63187-2025 georefererad karta.tif", "A 63187-2025")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 63187-2025 FSC-klagomål.docx", "A 63187-2025")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 63187-2025 FSC-klagomål mail.docx", "A 63187-2025")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 63187-2025 tillsynsbegäran.docx", "A 63187-2025")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 63187-2025 tillsynsbegäran mail.docx", "A 63187-2025")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 63187-2025 prioriterade fågelarter.docx", "A 63187-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 60085-2021</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>44495</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>KARLSKOGA</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>4</v>
+      </c>
+      <c r="T13" t="n">
         <v>5</v>
       </c>
-      <c r="U11" t="n">
+      <c r="U13" t="n">
         <v>1</v>
       </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Citronfingersvamp
 Mörk husmossa
@@ -1795,257 +2020,32 @@
 Västlig hakmossa</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 60085-2021 artfynd.xlsx", "A 60085-2021")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 60085-2021 karta.png", "A 60085-2021")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 60085-2021 georefererad karta.tif", "A 60085-2021")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 60085-2021 FSC-klagomål.docx", "A 60085-2021")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 60085-2021 FSC-klagomål mail.docx", "A 60085-2021")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 60085-2021 tillsynsbegäran.docx", "A 60085-2021")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 60085-2021 tillsynsbegäran mail.docx", "A 60085-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 8803-2026</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>46066</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>KARLSKOGA</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>4</v>
-      </c>
-      <c r="T12" t="n">
-        <v>8</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Dofttaggsvamp
-Platt fjädermossa
-Skogshakmossa
-Trubbfjädermossa</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 8803-2026 artfynd.xlsx", "A 8803-2026")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 8803-2026 karta.png", "A 8803-2026")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 8803-2026 georefererad karta.tif", "A 8803-2026")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 8803-2026 FSC-klagomål.docx", "A 8803-2026")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 8803-2026 FSC-klagomål mail.docx", "A 8803-2026")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 8803-2026 tillsynsbegäran.docx", "A 8803-2026")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 8803-2026 tillsynsbegäran mail.docx", "A 8803-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 63187-2025</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>46010</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>KARLSKOGA</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J13" t="n">
-        <v>2</v>
-      </c>
-      <c r="K13" t="n">
-        <v>2</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>4</v>
-      </c>
-      <c r="T13" t="n">
-        <v>4</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Talltita
-Bronshjon
-Korallblylav
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 63187-2025 artfynd.xlsx", "A 63187-2025")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 63187-2025 karta.png", "A 63187-2025")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 63187-2025 georefererad karta.tif", "A 63187-2025")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 63187-2025 FSC-klagomål.docx", "A 63187-2025")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 63187-2025 FSC-klagomål mail.docx", "A 63187-2025")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 63187-2025 tillsynsbegäran.docx", "A 63187-2025")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 63187-2025 tillsynsbegäran mail.docx", "A 63187-2025")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 63187-2025 prioriterade fågelarter.docx", "A 63187-2025")</f>
         <v/>
       </c>
     </row>
@@ -2069,7 +2069,7 @@
         <v>46127</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>46265</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 39025-2022</t>
+          <t>A 39936-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44817</v>
+        <v>45553</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2309,16 +2309,11 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>3.2</v>
+        <v>6.4</v>
       </c>
       <c r="J16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -2348,275 +2343,280 @@
         <v>2</v>
       </c>
       <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Storgröe
+Utter</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 39936-2024 artfynd.xlsx", "A 39936-2024")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 39936-2024 karta.png", "A 39936-2024")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 39936-2024 georefererad karta.tif", "A 39936-2024")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 39936-2024 FSC-klagomål.docx", "A 39936-2024")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 39936-2024 FSC-klagomål mail.docx", "A 39936-2024")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 39936-2024 tillsynsbegäran.docx", "A 39936-2024")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 39936-2024 tillsynsbegäran mail.docx", "A 39936-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 39025-2022</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>44817</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>KARLSKOGA</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J17" t="n">
         <v>2</v>
       </c>
-      <c r="U16" t="n">
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
         <v>2</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Talltita
 Tjäder</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 39025-2022 artfynd.xlsx", "A 39025-2022")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 39025-2022 karta.png", "A 39025-2022")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 39025-2022 georefererad karta.tif", "A 39025-2022")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 39025-2022 FSC-klagomål.docx", "A 39025-2022")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 39025-2022 FSC-klagomål mail.docx", "A 39025-2022")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 39025-2022 tillsynsbegäran.docx", "A 39025-2022")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 39025-2022 tillsynsbegäran mail.docx", "A 39025-2022")</f>
         <v/>
       </c>
-      <c r="AE16">
+      <c r="AE17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 39025-2022 prioriterade fågelarter.docx", "A 39025-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>A 38023-2026</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
         <v>46280</v>
       </c>
-      <c r="E17" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>KARLSKOGA</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
+      <c r="E18" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>KARLSKOGA</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I17" t="n">
+      <c r="I18" t="n">
         <v>7.2</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J18" t="n">
         <v>2</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
         <v>2</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T18" t="n">
         <v>2</v>
       </c>
-      <c r="U17" t="n">
+      <c r="U18" t="n">
         <v>1</v>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Tjäder
 Revlummer</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 38023-2026 artfynd.xlsx", "A 38023-2026")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 38023-2026 karta.png", "A 38023-2026")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 38023-2026 georefererad karta.tif", "A 38023-2026")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 38023-2026 FSC-klagomål.docx", "A 38023-2026")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 38023-2026 FSC-klagomål mail.docx", "A 38023-2026")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 38023-2026 tillsynsbegäran.docx", "A 38023-2026")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 38023-2026 tillsynsbegäran mail.docx", "A 38023-2026")</f>
         <v/>
       </c>
-      <c r="AE17">
+      <c r="AE18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 38023-2026 prioriterade fågelarter.docx", "A 38023-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 39936-2024</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45553</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>KARLSKOGA</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Storgröe
-Utter</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 39936-2024 artfynd.xlsx", "A 39936-2024")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 39936-2024 karta.png", "A 39936-2024")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 39936-2024 georefererad karta.tif", "A 39936-2024")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 39936-2024 FSC-klagomål.docx", "A 39936-2024")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 39936-2024 FSC-klagomål mail.docx", "A 39936-2024")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 39936-2024 tillsynsbegäran.docx", "A 39936-2024")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 39936-2024 tillsynsbegäran mail.docx", "A 39936-2024")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 52377-2025</t>
+          <t>A 58091-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2630,10 +2630,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45953</v>
+        <v>44900</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2684,49 +2684,49 @@
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Hårklomossa</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 52377-2025 artfynd.xlsx", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 58091-2022 artfynd.xlsx", "A 58091-2022")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 52377-2025 karta.png", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 58091-2022 karta.png", "A 58091-2022")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 52377-2025 georefererad karta.tif", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 58091-2022 georefererad karta.tif", "A 58091-2022")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 52377-2025 FSC-klagomål.docx", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 58091-2022 FSC-klagomål.docx", "A 58091-2022")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 52377-2025 FSC-klagomål mail.docx", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 58091-2022 FSC-klagomål mail.docx", "A 58091-2022")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 52377-2025 tillsynsbegäran.docx", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 58091-2022 tillsynsbegäran.docx", "A 58091-2022")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 52377-2025 tillsynsbegäran mail.docx", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 58091-2022 tillsynsbegäran mail.docx", "A 58091-2022")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 21019-2026</t>
+          <t>A 28566-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2740,10 +2740,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46145</v>
+        <v>45478</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2755,13 +2755,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>4.7</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2797,46 +2792,46 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 21019-2026 artfynd.xlsx", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 28566-2024 artfynd.xlsx", "A 28566-2024")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 21019-2026 karta.png", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 28566-2024 karta.png", "A 28566-2024")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 21019-2026 georefererad karta.tif", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 28566-2024 georefererad karta.tif", "A 28566-2024")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 21019-2026 FSC-klagomål.docx", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 28566-2024 FSC-klagomål.docx", "A 28566-2024")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 21019-2026 FSC-klagomål mail.docx", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 28566-2024 FSC-klagomål mail.docx", "A 28566-2024")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 21019-2026 tillsynsbegäran.docx", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 28566-2024 tillsynsbegäran.docx", "A 28566-2024")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 21019-2026 tillsynsbegäran mail.docx", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 28566-2024 tillsynsbegäran mail.docx", "A 28566-2024")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 28474-2023</t>
+          <t>A 63188-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2850,10 +2845,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45103</v>
+        <v>46010</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2865,8 +2860,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>5.1</v>
+        <v>1.1</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2899,53 +2899,53 @@
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Blåhake</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 28474-2023 artfynd.xlsx", "A 28474-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 63188-2025 artfynd.xlsx", "A 63188-2025")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 28474-2023 karta.png", "A 28474-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 63188-2025 karta.png", "A 63188-2025")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 28474-2023 georefererad karta.tif", "A 28474-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 63188-2025 georefererad karta.tif", "A 63188-2025")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 28474-2023 FSC-klagomål.docx", "A 28474-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 63188-2025 FSC-klagomål.docx", "A 63188-2025")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 28474-2023 FSC-klagomål mail.docx", "A 28474-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 63188-2025 FSC-klagomål mail.docx", "A 63188-2025")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 28474-2023 tillsynsbegäran.docx", "A 28474-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 63188-2025 tillsynsbegäran.docx", "A 63188-2025")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 28474-2023 tillsynsbegäran mail.docx", "A 28474-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 63188-2025 tillsynsbegäran mail.docx", "A 63188-2025")</f>
         <v/>
       </c>
       <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 28474-2023 prioriterade fågelarter.docx", "A 28474-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 63188-2025 prioriterade fågelarter.docx", "A 63188-2025")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 58091-2022</t>
+          <t>A 52377-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44900</v>
+        <v>45953</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -3013,49 +3013,49 @@
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Hårklomossa</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 58091-2022 artfynd.xlsx", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 52377-2025 artfynd.xlsx", "A 52377-2025")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 58091-2022 karta.png", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 52377-2025 karta.png", "A 52377-2025")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 58091-2022 georefererad karta.tif", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 52377-2025 georefererad karta.tif", "A 52377-2025")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 58091-2022 FSC-klagomål.docx", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 52377-2025 FSC-klagomål.docx", "A 52377-2025")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 58091-2022 FSC-klagomål mail.docx", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 52377-2025 FSC-klagomål mail.docx", "A 52377-2025")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 58091-2022 tillsynsbegäran.docx", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 52377-2025 tillsynsbegäran.docx", "A 52377-2025")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 58091-2022 tillsynsbegäran mail.docx", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 52377-2025 tillsynsbegäran mail.docx", "A 52377-2025")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 25093-2026</t>
+          <t>A 16784-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3069,10 +3069,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46175</v>
+        <v>46113</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3090,13 +3090,13 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -3123,49 +3123,49 @@
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Hårklomossa</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 25093-2026 artfynd.xlsx", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 16784-2026 artfynd.xlsx", "A 16784-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 25093-2026 karta.png", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 16784-2026 karta.png", "A 16784-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 25093-2026 georefererad karta.tif", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 16784-2026 georefererad karta.tif", "A 16784-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 25093-2026 FSC-klagomål.docx", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 16784-2026 FSC-klagomål.docx", "A 16784-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 25093-2026 FSC-klagomål mail.docx", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 16784-2026 FSC-klagomål mail.docx", "A 16784-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 25093-2026 tillsynsbegäran.docx", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 16784-2026 tillsynsbegäran.docx", "A 16784-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 25093-2026 tillsynsbegäran mail.docx", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 16784-2026 tillsynsbegäran mail.docx", "A 16784-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 63188-2025</t>
+          <t>A 18427-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46010</v>
+        <v>46127</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3209,7 +3209,7 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -3224,7 +3224,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3233,53 +3233,53 @@
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 63188-2025 artfynd.xlsx", "A 63188-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 18427-2026 artfynd.xlsx", "A 18427-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 63188-2025 karta.png", "A 63188-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 18427-2026 karta.png", "A 18427-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 63188-2025 georefererad karta.tif", "A 63188-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 18427-2026 georefererad karta.tif", "A 18427-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 63188-2025 FSC-klagomål.docx", "A 63188-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 18427-2026 FSC-klagomål.docx", "A 18427-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 63188-2025 FSC-klagomål mail.docx", "A 63188-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 18427-2026 FSC-klagomål mail.docx", "A 18427-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 63188-2025 tillsynsbegäran.docx", "A 63188-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 18427-2026 tillsynsbegäran.docx", "A 18427-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 63188-2025 tillsynsbegäran mail.docx", "A 63188-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 18427-2026 tillsynsbegäran mail.docx", "A 18427-2026")</f>
         <v/>
       </c>
       <c r="AE24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 63188-2025 prioriterade fågelarter.docx", "A 63188-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 18427-2026 prioriterade fågelarter.docx", "A 18427-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 28566-2024</t>
+          <t>A 19233-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3293,10 +3293,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45478</v>
+        <v>46132</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3309,13 +3309,13 @@
         </is>
       </c>
       <c r="I25" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
         <v>1</v>
-      </c>
-      <c r="J25" t="n">
-        <v>1</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -3345,46 +3345,46 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 28566-2024 artfynd.xlsx", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 19233-2026 artfynd.xlsx", "A 19233-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 28566-2024 karta.png", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 19233-2026 karta.png", "A 19233-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 28566-2024 georefererad karta.tif", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 19233-2026 georefererad karta.tif", "A 19233-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 28566-2024 FSC-klagomål.docx", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 19233-2026 FSC-klagomål.docx", "A 19233-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 28566-2024 FSC-klagomål mail.docx", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 19233-2026 FSC-klagomål mail.docx", "A 19233-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 28566-2024 tillsynsbegäran.docx", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 19233-2026 tillsynsbegäran.docx", "A 19233-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 28566-2024 tillsynsbegäran mail.docx", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 19233-2026 tillsynsbegäran mail.docx", "A 19233-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 16784-2026</t>
+          <t>A 21019-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3398,10 +3398,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46113</v>
+        <v>46145</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3452,49 +3452,49 @@
         <v>1</v>
       </c>
       <c r="T26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Hårklomossa</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 16784-2026 artfynd.xlsx", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 21019-2026 artfynd.xlsx", "A 21019-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 16784-2026 karta.png", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 21019-2026 karta.png", "A 21019-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 16784-2026 georefererad karta.tif", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 21019-2026 georefererad karta.tif", "A 21019-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 16784-2026 FSC-klagomål.docx", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 21019-2026 FSC-klagomål.docx", "A 21019-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 16784-2026 FSC-klagomål mail.docx", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 21019-2026 FSC-klagomål mail.docx", "A 21019-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 16784-2026 tillsynsbegäran.docx", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 21019-2026 tillsynsbegäran.docx", "A 21019-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 16784-2026 tillsynsbegäran mail.docx", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 21019-2026 tillsynsbegäran mail.docx", "A 21019-2026")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 18427-2026</t>
+          <t>A 25093-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3508,10 +3508,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46127</v>
+        <v>46175</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3529,13 +3529,13 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
         <v>1</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3569,46 +3569,42 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 18427-2026 artfynd.xlsx", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 25093-2026 artfynd.xlsx", "A 25093-2026")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 18427-2026 karta.png", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 25093-2026 karta.png", "A 25093-2026")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 18427-2026 georefererad karta.tif", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 25093-2026 georefererad karta.tif", "A 25093-2026")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 18427-2026 FSC-klagomål.docx", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 25093-2026 FSC-klagomål.docx", "A 25093-2026")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 18427-2026 FSC-klagomål mail.docx", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 25093-2026 FSC-klagomål mail.docx", "A 25093-2026")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 18427-2026 tillsynsbegäran.docx", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 25093-2026 tillsynsbegäran.docx", "A 25093-2026")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 18427-2026 tillsynsbegäran mail.docx", "A 18427-2026")</f>
-        <v/>
-      </c>
-      <c r="AE27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 18427-2026 prioriterade fågelarter.docx", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 25093-2026 tillsynsbegäran mail.docx", "A 25093-2026")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 19233-2026</t>
+          <t>A 28474-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3622,10 +3618,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46132</v>
+        <v>45103</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3638,17 +3634,17 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.6</v>
+        <v>5.1</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
         <v>1</v>
       </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
@@ -3662,7 +3658,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -3674,39 +3670,43 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåhake</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 19233-2026 artfynd.xlsx", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 28474-2023 artfynd.xlsx", "A 28474-2023")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 19233-2026 karta.png", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 28474-2023 karta.png", "A 28474-2023")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 19233-2026 georefererad karta.tif", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 28474-2023 georefererad karta.tif", "A 28474-2023")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 19233-2026 FSC-klagomål.docx", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 28474-2023 FSC-klagomål.docx", "A 28474-2023")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 19233-2026 FSC-klagomål mail.docx", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 28474-2023 FSC-klagomål mail.docx", "A 28474-2023")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 19233-2026 tillsynsbegäran.docx", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 28474-2023 tillsynsbegäran.docx", "A 28474-2023")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 19233-2026 tillsynsbegäran mail.docx", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 28474-2023 tillsynsbegäran mail.docx", "A 28474-2023")</f>
+        <v/>
+      </c>
+      <c r="AE28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 28474-2023 prioriterade fågelarter.docx", "A 28474-2023")</f>
         <v/>
       </c>
     </row>
@@ -3730,7 +3730,7 @@
         <v>46213</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>46260</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>45555</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>44546</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>44732</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>44512</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>44715</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>44508</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         <v>44480</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4486,7 +4486,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 37582-2022</t>
+          <t>A 38012-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4500,10 +4500,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44809</v>
+        <v>44811</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4516,7 +4516,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.8</v>
+        <v>3.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4559,7 +4559,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 38012-2022</t>
+          <t>A 37582-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4573,10 +4573,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44811</v>
+        <v>44809</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.7</v>
+        <v>0.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4649,7 +4649,7 @@
         <v>44628</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
         <v>44809</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         <v>44706</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4873,7 +4873,7 @@
         <v>44706</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>44817</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 35471-2024</t>
+          <t>A 8803-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5021,10 +5021,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45531</v>
+        <v>45712</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5037,7 +5037,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5080,7 +5080,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 4164-2022</t>
+          <t>A 35445-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5094,10 +5094,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44588</v>
+        <v>45531</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5109,13 +5109,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5158,7 +5153,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 9712-2024</t>
+          <t>A 39337-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5172,10 +5167,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45362</v>
+        <v>44817</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5187,13 +5182,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5236,7 +5226,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 58390-2024</t>
+          <t>A 64066-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5246,14 +5236,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45633</v>
+        <v>46013</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5266,7 +5256,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5309,7 +5299,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 42804-2023</t>
+          <t>A 63628-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5319,14 +5309,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45182</v>
+        <v>46014</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5338,13 +5328,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>0.6</v>
+        <v>3.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5387,7 +5372,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 9510-2023</t>
+          <t>A 56887-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5401,10 +5386,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44981</v>
+        <v>44894</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5417,7 +5402,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5460,7 +5445,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 1309-2024</t>
+          <t>A 38196-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5474,10 +5459,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45303</v>
+        <v>45545</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5490,7 +5475,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>4</v>
+        <v>0.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5533,7 +5518,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 35444-2024</t>
+          <t>A 1788-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5547,10 +5532,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45531</v>
+        <v>46034</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5563,7 +5548,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5606,7 +5591,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 23263-2022</t>
+          <t>A 24255-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5620,10 +5605,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44720</v>
+        <v>45457</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5636,7 +5621,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5679,7 +5664,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 47201-2023</t>
+          <t>A 20289-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5693,10 +5678,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45196</v>
+        <v>45435</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5708,8 +5693,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5752,7 +5742,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 61396-2023</t>
+          <t>A 2911-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5766,10 +5756,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45264</v>
+        <v>46038</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5782,7 +5772,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5825,7 +5815,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 8259-2025</t>
+          <t>A 17815-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5839,10 +5829,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45708</v>
+        <v>45758</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5854,8 +5844,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5898,7 +5893,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 24116-2024</t>
+          <t>A 38190-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5912,10 +5907,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45456</v>
+        <v>45545</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5928,7 +5923,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5971,7 +5966,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 35930-2023</t>
+          <t>A 45664-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5985,10 +5980,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45148</v>
+        <v>45923</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6006,7 +6001,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>5.2</v>
+        <v>9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6049,7 +6044,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 63863-2023</t>
+          <t>A 47222-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6063,10 +6058,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45278</v>
+        <v>45586</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6078,8 +6073,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>1.1</v>
+        <v>5.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6122,7 +6122,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 59938-2023</t>
+          <t>A 9712-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6136,10 +6136,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45257</v>
+        <v>45362</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6151,8 +6151,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6195,7 +6200,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 52828-2024</t>
+          <t>A 4058-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6209,10 +6214,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45610</v>
+        <v>44588</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6225,7 +6230,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>8.300000000000001</v>
+        <v>1.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6285,7 +6290,7 @@
         <v>45744</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6346,7 +6351,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 24115-2024</t>
+          <t>A 44946-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6360,10 +6365,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45456</v>
+        <v>45918</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6376,7 +6381,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>8</v>
+        <v>2.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6419,7 +6424,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 19663-2026</t>
+          <t>A 44949-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6433,10 +6438,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46134</v>
+        <v>45918</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6448,13 +6453,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6497,7 +6497,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 17815-2025</t>
+          <t>A 43075-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6511,10 +6511,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45758</v>
+        <v>45182</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6526,13 +6526,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6575,7 +6570,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 18768-2025</t>
+          <t>A 23263-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6589,10 +6584,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45764</v>
+        <v>44720</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6604,13 +6599,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6653,7 +6643,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 4801-2024</t>
+          <t>A 9917-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6667,10 +6657,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45328</v>
+        <v>46073</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6683,7 +6673,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.9</v>
+        <v>3.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6726,7 +6716,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 4802-2024</t>
+          <t>A 35444-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6740,10 +6730,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45328</v>
+        <v>45531</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6756,7 +6746,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6799,7 +6789,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 8990-2023</t>
+          <t>A 35471-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6813,10 +6803,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44979</v>
+        <v>45531</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6829,7 +6819,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6872,7 +6862,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 24255-2024</t>
+          <t>A 58390-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6886,10 +6876,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45457</v>
+        <v>45633</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6902,7 +6892,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6945,7 +6935,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 42802-2023</t>
+          <t>A 13473-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6955,14 +6945,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45182</v>
+        <v>46094</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6974,13 +6964,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7023,7 +7008,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 28471-2023</t>
+          <t>A 18768-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7037,10 +7022,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45103</v>
+        <v>45764</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7052,8 +7037,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7096,7 +7086,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 44946-2025</t>
+          <t>A 42803-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7106,14 +7096,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45918</v>
+        <v>45182</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7125,8 +7115,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7169,7 +7164,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 22867-2022</t>
+          <t>A 14580-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7183,10 +7178,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44715</v>
+        <v>46101</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7198,8 +7193,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7242,7 +7242,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 44949-2025</t>
+          <t>A 50958-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7256,10 +7256,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45918</v>
+        <v>45946</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7272,7 +7272,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7315,7 +7315,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 6835-2025</t>
+          <t>A 12897-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7329,10 +7329,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45700</v>
+        <v>46092</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7345,7 +7345,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7388,7 +7388,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 64060-2023</t>
+          <t>A 16782-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7402,10 +7402,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45279</v>
+        <v>46113</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7417,8 +7417,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7461,7 +7466,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 48707-2024</t>
+          <t>A 16783-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7475,10 +7480,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45593</v>
+        <v>46113</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7490,8 +7495,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>6</v>
+        <v>1.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7534,7 +7544,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 55832-2023</t>
+          <t>A 16787-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7548,10 +7558,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45239</v>
+        <v>46113</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7563,8 +7573,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7607,7 +7622,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 58388-2024</t>
+          <t>A 20086-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7617,14 +7632,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45633</v>
+        <v>45434</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7637,7 +7652,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>5.8</v>
+        <v>1.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7680,7 +7695,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 21210-2025</t>
+          <t>A 15058-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7694,10 +7709,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45779</v>
+        <v>46104</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7709,13 +7724,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>1.1</v>
+        <v>4.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7758,7 +7768,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 18978-2025</t>
+          <t>A 9510-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7772,10 +7782,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45764</v>
+        <v>44981</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7788,7 +7798,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7831,7 +7841,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 23717-2025</t>
+          <t>A 17734-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7845,10 +7855,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45793</v>
+        <v>46122</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7860,8 +7870,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7904,7 +7919,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 50958-2025</t>
+          <t>A 55025-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7918,10 +7933,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45946</v>
+        <v>45967</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7934,7 +7949,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7977,7 +7992,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 31921-2022</t>
+          <t>A 27498-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7991,10 +8006,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44777</v>
+        <v>45813</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8007,7 +8022,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8050,7 +8065,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 43075-2023</t>
+          <t>A 19011-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8064,10 +8079,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45182</v>
+        <v>46130</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8079,8 +8094,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>3.1</v>
+        <v>0.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8123,7 +8143,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 47196-2023</t>
+          <t>A 19010-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8137,10 +8157,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45196</v>
+        <v>46130</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8152,8 +8172,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>5.9</v>
+        <v>1.9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8196,7 +8221,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 13454-2022</t>
+          <t>A 19009-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8210,10 +8235,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44645</v>
+        <v>46130</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8225,8 +8250,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>1.7</v>
+        <v>6.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8269,7 +8299,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 53618-2024</t>
+          <t>A 19008-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8283,10 +8313,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45614</v>
+        <v>46130</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8298,8 +8328,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>10.1</v>
+        <v>1.9</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8342,7 +8377,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 30961-2022</t>
+          <t>A 19663-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8356,10 +8391,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44768</v>
+        <v>46134</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8373,11 +8408,11 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3.3</v>
+        <v>1.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8420,7 +8455,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 55025-2025</t>
+          <t>A 59025-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8434,10 +8469,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45967</v>
+        <v>45636</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8449,8 +8484,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8493,7 +8533,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 42803-2023</t>
+          <t>A 59522-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8507,10 +8547,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45182</v>
+        <v>45989</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8528,7 +8568,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8571,7 +8611,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 8803-2025</t>
+          <t>A 6835-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8585,10 +8625,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45712</v>
+        <v>45700</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8601,7 +8641,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8644,7 +8684,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 917-2026</t>
+          <t>A 13501-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8658,10 +8698,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46030</v>
+        <v>45736</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8674,7 +8714,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8717,7 +8757,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 56313-2024</t>
+          <t>A 47094-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8731,10 +8771,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45624</v>
+        <v>45196</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8746,13 +8786,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8795,7 +8830,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 59522-2025</t>
+          <t>A 60503-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8805,14 +8840,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45989</v>
+        <v>45995</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8824,13 +8859,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I96" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8873,7 +8903,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 21253-2026</t>
+          <t>A 60508-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8887,10 +8917,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46147</v>
+        <v>45995</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8903,7 +8933,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8946,7 +8976,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 21257-2026</t>
+          <t>A 60506-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8960,10 +8990,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46147</v>
+        <v>45995</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8976,7 +9006,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9019,7 +9049,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 10743-2023</t>
+          <t>A 31921-2022</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9033,10 +9063,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44988</v>
+        <v>44777</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9046,11 +9076,6 @@
       <c r="G99" t="inlineStr">
         <is>
           <t>KARLSKOGA</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I99" t="n">
@@ -9097,7 +9122,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 14215-2024</t>
+          <t>A 42804-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9107,14 +9132,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45393</v>
+        <v>45182</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9128,11 +9153,11 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I100" t="n">
-        <v>4.2</v>
+        <v>0.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9175,7 +9200,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 55191-2023</t>
+          <t>A 39030-2022</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9189,10 +9214,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45237</v>
+        <v>44817</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9204,8 +9229,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9248,7 +9278,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 60506-2025</t>
+          <t>A 61788-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9262,10 +9292,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45995</v>
+        <v>46002</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9277,8 +9307,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9321,7 +9356,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 60508-2025</t>
+          <t>A 21210-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9335,10 +9370,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45995</v>
+        <v>45779</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9350,8 +9385,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9394,7 +9434,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 60503-2025</t>
+          <t>A 8244-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9408,10 +9448,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45995</v>
+        <v>45708</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9424,7 +9464,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9467,7 +9507,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 59025-2024</t>
+          <t>A 28100-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9481,10 +9521,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45636</v>
+        <v>45476</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9496,13 +9536,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I105" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9545,7 +9580,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 3227-2025</t>
+          <t>A 23717-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9559,10 +9594,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45679</v>
+        <v>45793</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9575,7 +9610,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>4.5</v>
+        <v>2.1</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9618,7 +9653,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 61788-2025</t>
+          <t>A 51344-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9632,10 +9667,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46002</v>
+        <v>45219</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9649,11 +9684,11 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.9</v>
+        <v>4.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9696,7 +9731,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 17243-2024</t>
+          <t>A 917-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9710,10 +9745,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45414</v>
+        <v>46030</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9726,7 +9761,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9769,7 +9804,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 64066-2025</t>
+          <t>A 54680-2021</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9779,14 +9814,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46013</v>
+        <v>44473</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9799,7 +9834,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9842,7 +9877,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 63628-2025</t>
+          <t>A 30102-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9856,10 +9891,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46014</v>
+        <v>45826</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9872,7 +9907,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>3.8</v>
+        <v>1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9915,7 +9950,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 35060-2024</t>
+          <t>A 53647-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9929,10 +9964,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45527</v>
+        <v>45230</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9942,11 +9977,6 @@
       <c r="G111" t="inlineStr">
         <is>
           <t>KARLSKOGA</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I111" t="n">
@@ -9993,7 +10023,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 1788-2026</t>
+          <t>A 23620-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10007,10 +10037,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46034</v>
+        <v>45454</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10023,7 +10053,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>3.5</v>
+        <v>2.2</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10066,7 +10096,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 52826-2024</t>
+          <t>A 20463-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10080,10 +10110,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45610</v>
+        <v>45775</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10095,8 +10125,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I113" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10139,7 +10174,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 52829-2024</t>
+          <t>A 28471-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10153,10 +10188,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45610</v>
+        <v>45103</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10169,7 +10204,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10212,7 +10247,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 45664-2025</t>
+          <t>A 21253-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10226,10 +10261,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45923</v>
+        <v>46147</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10241,13 +10276,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I115" t="n">
-        <v>9</v>
+        <v>3.4</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10290,7 +10320,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 2911-2026</t>
+          <t>A 21257-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10304,10 +10334,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46038</v>
+        <v>46147</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10320,7 +10350,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10363,7 +10393,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 23754-2026</t>
+          <t>A 16881-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10377,10 +10407,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46164</v>
+        <v>45033</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10394,11 +10424,11 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I117" t="n">
-        <v>12.2</v>
+        <v>2.3</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10441,7 +10471,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 11974-2025</t>
+          <t>A 3227-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10455,10 +10485,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45728</v>
+        <v>45679</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10471,7 +10501,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.4</v>
+        <v>4.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10514,7 +10544,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 47222-2024</t>
+          <t>A 61396-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10528,10 +10558,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45586</v>
+        <v>45264</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10543,13 +10573,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I119" t="n">
-        <v>5.3</v>
+        <v>1.8</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10592,7 +10617,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 61271-2022</t>
+          <t>A 31397-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10606,10 +10631,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44909</v>
+        <v>45833</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10621,13 +10646,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I120" t="n">
-        <v>14.1</v>
+        <v>1.5</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10670,7 +10690,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 48168-2024</t>
+          <t>A 32287-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10684,10 +10704,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45589</v>
+        <v>45835</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10699,8 +10719,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I121" t="n">
-        <v>5.5</v>
+        <v>10.9</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10743,7 +10768,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 4587-2025</t>
+          <t>A 4164-2022</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10757,10 +10782,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45687</v>
+        <v>44588</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10772,8 +10797,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I122" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10816,7 +10846,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 18955-2025</t>
+          <t>A 61271-2022</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10830,10 +10860,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45764</v>
+        <v>44909</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10845,8 +10875,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I123" t="n">
-        <v>8.1</v>
+        <v>14.1</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10889,7 +10924,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 4587-2025</t>
+          <t>A 57422-2021</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10903,10 +10938,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45687</v>
+        <v>44483</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10919,7 +10954,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>3.3</v>
+        <v>1.2</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10962,7 +10997,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 50614-2024</t>
+          <t>A 23754-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10976,10 +11011,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45601</v>
+        <v>46164</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10991,8 +11026,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I125" t="n">
-        <v>0.7</v>
+        <v>12.2</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11035,7 +11075,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 55182-2024</t>
+          <t>A 4587-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11049,10 +11089,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45618</v>
+        <v>45687</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11065,7 +11105,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>11.4</v>
+        <v>3.3</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11108,7 +11148,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 4058-2022</t>
+          <t>A 4587-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11122,10 +11162,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44588</v>
+        <v>45687</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11138,7 +11178,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11181,7 +11221,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 24666-2026</t>
+          <t>A 35060-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11195,10 +11235,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46171</v>
+        <v>45527</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11210,8 +11250,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I128" t="n">
-        <v>6.1</v>
+        <v>0.6</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11254,7 +11299,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 9917-2026</t>
+          <t>A 64060-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11268,10 +11313,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46073</v>
+        <v>45279</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11284,7 +11329,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11327,7 +11372,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 25092-2026</t>
+          <t>A 24666-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11341,10 +11386,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46175</v>
+        <v>46171</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11356,13 +11401,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I130" t="n">
-        <v>1.9</v>
+        <v>6.1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11422,7 +11462,7 @@
         <v>46175</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11483,7 +11523,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 13473-2026</t>
+          <t>A 25092-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11497,10 +11537,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46094</v>
+        <v>46175</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11512,8 +11552,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I132" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11556,7 +11601,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 28100-2024</t>
+          <t>A 14215-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11570,10 +11615,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45476</v>
+        <v>45393</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11585,8 +11630,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I133" t="n">
-        <v>1.8</v>
+        <v>4.2</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11629,7 +11679,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 12897-2026</t>
+          <t>A 24116-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11643,10 +11693,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46092</v>
+        <v>45456</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11659,7 +11709,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11702,7 +11752,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 14580-2026</t>
+          <t>A 55832-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11716,10 +11766,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46101</v>
+        <v>45239</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11731,13 +11781,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I135" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11780,7 +11825,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 26608-2026</t>
+          <t>A 10515-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11794,10 +11839,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46184</v>
+        <v>44987</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11809,13 +11854,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11858,7 +11898,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 27120-2026</t>
+          <t>A 26822-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11872,10 +11912,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46188</v>
+        <v>46185</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11887,8 +11927,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I137" t="n">
-        <v>4.7</v>
+        <v>2.2</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11948,7 +11993,7 @@
         <v>46185</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12026,7 +12071,7 @@
         <v>46041</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12082,7 +12127,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 26820-2026</t>
+          <t>A 26821-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12099,7 +12144,7 @@
         <v>46185</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12117,7 +12162,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>9.9</v>
+        <v>7.9</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12160,7 +12205,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 26821-2026</t>
+          <t>A 26820-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12177,7 +12222,7 @@
         <v>46185</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12195,7 +12240,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>7.9</v>
+        <v>9.9</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12238,7 +12283,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 26822-2026</t>
+          <t>A 26608-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12252,10 +12297,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46185</v>
+        <v>46184</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12273,7 +12318,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12333,7 +12378,7 @@
         <v>46185</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12411,7 +12456,7 @@
         <v>46185</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12472,7 +12517,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 1106-2024</t>
+          <t>A 27392-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12486,10 +12531,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45302</v>
+        <v>46189</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12501,8 +12546,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I145" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12545,7 +12595,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 39030-2022</t>
+          <t>A 27120-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12559,10 +12609,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>44817</v>
+        <v>46188</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12574,13 +12624,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I146" t="n">
-        <v>1</v>
+        <v>4.7</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12623,7 +12668,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 16783-2026</t>
+          <t>A 33011-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12637,10 +12682,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46113</v>
+        <v>45125</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12652,13 +12697,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I147" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12701,7 +12741,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 16787-2026</t>
+          <t>A 48168-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12715,10 +12755,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46113</v>
+        <v>45589</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12730,13 +12770,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I148" t="n">
-        <v>2.8</v>
+        <v>5.5</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12779,7 +12814,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 16782-2026</t>
+          <t>A 13454-2022</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12793,10 +12828,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46113</v>
+        <v>44645</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12808,13 +12843,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I149" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12857,7 +12887,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 38382-2022</t>
+          <t>A 10743-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12871,10 +12901,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>44812</v>
+        <v>44988</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12892,7 +12922,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12935,7 +12965,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 27392-2026</t>
+          <t>A 50611-2024</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12949,10 +12979,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46189</v>
+        <v>45601</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12964,13 +12994,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I151" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -13013,7 +13038,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 15058-2026</t>
+          <t>A 42802-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13023,14 +13048,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46104</v>
+        <v>45182</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13042,8 +13067,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I152" t="n">
-        <v>4.3</v>
+        <v>0.6</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -13086,7 +13116,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 17734-2026</t>
+          <t>A 52829-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13100,10 +13130,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46122</v>
+        <v>45610</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13115,13 +13145,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I153" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -13164,7 +13189,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 16881-2023</t>
+          <t>A 56313-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13178,10 +13203,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45033</v>
+        <v>45624</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13199,7 +13224,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13242,7 +13267,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 19009-2026</t>
+          <t>A 38382-2022</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13256,10 +13281,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46130</v>
+        <v>44812</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13273,11 +13298,11 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I155" t="n">
-        <v>6.3</v>
+        <v>2.2</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13320,7 +13345,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 19011-2026</t>
+          <t>A 24115-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13334,10 +13359,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46130</v>
+        <v>45456</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13349,13 +13374,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I156" t="n">
-        <v>0.9</v>
+        <v>8</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13398,7 +13418,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 19010-2026</t>
+          <t>A 31378-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13412,10 +13432,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46130</v>
+        <v>46213</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13427,13 +13447,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I157" t="n">
-        <v>1.9</v>
+        <v>3.7</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13476,7 +13491,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 19008-2026</t>
+          <t>A 10404-2022</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13490,10 +13505,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46130</v>
+        <v>44623</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13505,13 +13520,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I158" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13554,7 +13564,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 57422-2021</t>
+          <t>A 35094-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13568,10 +13578,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>44483</v>
+        <v>46260</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13583,8 +13593,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I159" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13627,7 +13642,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 8244-2025</t>
+          <t>A 18955-2025</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13641,10 +13656,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45708</v>
+        <v>45764</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13657,7 +13672,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.1</v>
+        <v>8.1</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13700,7 +13715,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 38190-2024</t>
+          <t>A 22867-2022</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13714,10 +13729,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45545</v>
+        <v>44715</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13730,7 +13745,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13773,7 +13788,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 20463-2025</t>
+          <t>A 18978-2025</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13787,10 +13802,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45775</v>
+        <v>45764</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13802,13 +13817,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I162" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13851,7 +13861,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 35470-2024</t>
+          <t>A 35699-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13861,14 +13871,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45531</v>
+        <v>46265</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13880,8 +13890,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I163" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13924,7 +13939,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 35445-2024</t>
+          <t>A 4801-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13938,10 +13953,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45531</v>
+        <v>45328</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13954,7 +13969,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13997,7 +14012,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 47094-2023</t>
+          <t>A 4802-2024</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -14011,10 +14026,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45196</v>
+        <v>45328</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14027,7 +14042,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -14070,7 +14085,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 38196-2024</t>
+          <t>A 30961-2022</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -14084,10 +14099,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45545</v>
+        <v>44768</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14099,8 +14114,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I166" t="n">
-        <v>0.7</v>
+        <v>3.3</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -14143,7 +14163,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 50611-2024</t>
+          <t>A 55191-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -14157,10 +14177,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45601</v>
+        <v>45237</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14173,7 +14193,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14216,7 +14236,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 20289-2024</t>
+          <t>A 36374-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14230,10 +14250,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45435</v>
+        <v>46268</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14247,11 +14267,11 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I168" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14294,7 +14314,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 52797-2021</t>
+          <t>A 37089-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14308,10 +14328,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>44467</v>
+        <v>46273</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14324,7 +14344,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.4</v>
+        <v>15.8</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14367,7 +14387,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 31378-2026</t>
+          <t>A 13496-2025</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14381,10 +14401,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46213</v>
+        <v>45736</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14397,7 +14417,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>3.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14440,7 +14460,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 20086-2024</t>
+          <t>A 11974-2025</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14450,14 +14470,14 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45434</v>
+        <v>45728</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14470,7 +14490,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14513,7 +14533,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 13496-2025</t>
+          <t>A 63863-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14527,10 +14547,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45736</v>
+        <v>45278</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14543,7 +14563,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>8.800000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14586,7 +14606,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 56887-2022</t>
+          <t>A 38043-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14600,10 +14620,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>44894</v>
+        <v>46280</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14615,8 +14635,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I173" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14659,7 +14684,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 35094-2026</t>
+          <t>A 1309-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14673,10 +14698,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46260</v>
+        <v>45303</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14688,13 +14713,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I174" t="n">
-        <v>1.9</v>
+        <v>4</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14737,7 +14757,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 35699-2026</t>
+          <t>A 38020-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14747,14 +14767,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46265</v>
+        <v>46280</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14772,7 +14792,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14815,7 +14835,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 33011-2023</t>
+          <t>A 52826-2024</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14829,10 +14849,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45125</v>
+        <v>45610</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14845,7 +14865,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14888,7 +14908,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 36374-2026</t>
+          <t>A 1106-2024</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14902,10 +14922,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46268</v>
+        <v>45302</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14917,13 +14937,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I177" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14966,7 +14981,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 51344-2023</t>
+          <t>A 48707-2024</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14980,10 +14995,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45219</v>
+        <v>45593</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14995,13 +15010,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I178" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -15044,7 +15054,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 37089-2026</t>
+          <t>A 35470-2024</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -15058,10 +15068,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46273</v>
+        <v>45531</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15074,7 +15084,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>15.8</v>
+        <v>0.5</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -15117,7 +15127,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 10515-2023</t>
+          <t>A 8990-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -15131,10 +15141,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>44987</v>
+        <v>44979</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15147,7 +15157,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -15190,7 +15200,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 39337-2022</t>
+          <t>A 50614-2024</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15204,10 +15214,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>44817</v>
+        <v>45601</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15220,7 +15230,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15263,7 +15273,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 53620-2024</t>
+          <t>A 55182-2024</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15277,10 +15287,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45614</v>
+        <v>45618</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15293,7 +15303,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>0.7</v>
+        <v>11.4</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15336,7 +15346,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 38043-2026</t>
+          <t>A 52797-2021</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15350,10 +15360,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46280</v>
+        <v>44467</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15365,13 +15375,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I183" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15414,7 +15419,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 13501-2025</t>
+          <t>A 8259-2025</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15428,10 +15433,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45736</v>
+        <v>45708</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15444,7 +15449,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>3.2</v>
+        <v>0.7</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15487,7 +15492,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 38020-2026</t>
+          <t>A 53620-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15501,10 +15506,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46280</v>
+        <v>45614</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15516,13 +15521,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I185" t="n">
-        <v>4.1</v>
+        <v>0.7</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15565,7 +15565,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 10404-2022</t>
+          <t>A 35930-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15579,10 +15579,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>44623</v>
+        <v>45148</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15594,8 +15594,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I186" t="n">
-        <v>1</v>
+        <v>5.2</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15638,7 +15643,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 38742-2023</t>
+          <t>A 47196-2023</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15648,14 +15653,14 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45161</v>
+        <v>45196</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15667,13 +15672,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I187" t="n">
-        <v>4.2</v>
+        <v>5.9</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15716,7 +15716,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 3735-2024</t>
+          <t>A 53618-2024</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15730,10 +15730,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45321</v>
+        <v>45614</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15745,13 +15745,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I188" t="n">
-        <v>1.6</v>
+        <v>10.1</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15794,7 +15789,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 23308-2025</t>
+          <t>A 58388-2024</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15808,10 +15803,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45791</v>
+        <v>45633</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15824,7 +15819,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>1.5</v>
+        <v>5.8</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15867,7 +15862,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 27498-2025</t>
+          <t>A 47201-2023</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15881,10 +15876,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45813</v>
+        <v>45196</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15897,7 +15892,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15940,7 +15935,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 23620-2024</t>
+          <t>A 52828-2024</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15954,10 +15949,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45454</v>
+        <v>45610</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15970,7 +15965,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>2.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -16013,7 +16008,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 53647-2023</t>
+          <t>A 17243-2024</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -16027,10 +16022,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45230</v>
+        <v>45414</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16043,7 +16038,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>0.6</v>
+        <v>3.2</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -16086,7 +16081,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 30102-2025</t>
+          <t>A 59938-2023</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -16100,10 +16095,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45826</v>
+        <v>45257</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16116,7 +16111,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -16159,7 +16154,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 54680-2021</t>
+          <t>A 38742-2023</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -16169,14 +16164,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>44473</v>
+        <v>45161</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16188,8 +16183,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I194" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -16232,7 +16232,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 31397-2025</t>
+          <t>A 3735-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16246,10 +16246,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45833</v>
+        <v>45321</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16261,8 +16261,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I195" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -16305,7 +16310,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 32287-2025</t>
+          <t>A 23308-2025</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16319,10 +16324,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45835</v>
+        <v>45791</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16334,13 +16339,8 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I196" t="n">
-        <v>10.9</v>
+        <v>1.5</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16400,7 +16400,7 @@
         <v>45953</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>

--- a/Översikt KARLSKOGA.xlsx
+++ b/Översikt KARLSKOGA.xlsx
@@ -601,7 +601,7 @@
         <v>45562</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>45958</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         <v>45989</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>44510</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>46100</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>45989</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>44473</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>46010</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>46010</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>46066</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>46010</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>44495</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>46127</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>46265</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         <v>45553</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>44817</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2518,7 +2518,7 @@
         <v>46280</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>44900</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>45478</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>46010</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>45953</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>46113</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>46127</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>46132</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>46145</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>46175</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         <v>45103</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>46213</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>46260</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>45555</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>44546</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>44732</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>44512</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>44715</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>44508</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         <v>44480</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>44811</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
         <v>44809</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4649,7 +4649,7 @@
         <v>44628</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
         <v>44809</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         <v>44706</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4873,7 +4873,7 @@
         <v>44706</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>44817</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>45712</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         <v>45531</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5170,7 +5170,7 @@
         <v>44817</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         <v>46013</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5316,7 +5316,7 @@
         <v>46014</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         <v>44894</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>45545</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         <v>46034</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5608,7 +5608,7 @@
         <v>45457</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5681,7 +5681,7 @@
         <v>45435</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         <v>46038</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5832,7 +5832,7 @@
         <v>45758</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>45545</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5983,7 +5983,7 @@
         <v>45923</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6061,7 +6061,7 @@
         <v>45586</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6139,7 +6139,7 @@
         <v>45362</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v>44588</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6290,7 +6290,7 @@
         <v>45744</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6368,7 +6368,7 @@
         <v>45918</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6441,7 +6441,7 @@
         <v>45918</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6514,7 +6514,7 @@
         <v>45182</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         <v>44720</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6660,7 +6660,7 @@
         <v>46073</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6733,7 +6733,7 @@
         <v>45531</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6806,7 +6806,7 @@
         <v>45531</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
         <v>45633</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6952,7 +6952,7 @@
         <v>46094</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7025,7 +7025,7 @@
         <v>45764</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7103,7 +7103,7 @@
         <v>45182</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7181,7 +7181,7 @@
         <v>46101</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7259,7 +7259,7 @@
         <v>45946</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7332,7 +7332,7 @@
         <v>46092</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7405,7 +7405,7 @@
         <v>46113</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7483,7 +7483,7 @@
         <v>46113</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7561,7 +7561,7 @@
         <v>46113</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         <v>45434</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
         <v>46104</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7785,7 +7785,7 @@
         <v>44981</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7858,7 +7858,7 @@
         <v>46122</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7936,7 +7936,7 @@
         <v>45967</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8009,7 +8009,7 @@
         <v>45813</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8082,7 +8082,7 @@
         <v>46130</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8160,7 +8160,7 @@
         <v>46130</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8238,7 +8238,7 @@
         <v>46130</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
         <v>46130</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8394,7 +8394,7 @@
         <v>46134</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8472,7 +8472,7 @@
         <v>45636</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8550,7 +8550,7 @@
         <v>45989</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8628,7 +8628,7 @@
         <v>45700</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8701,7 +8701,7 @@
         <v>45736</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8774,7 +8774,7 @@
         <v>45196</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8847,7 +8847,7 @@
         <v>45995</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8920,7 +8920,7 @@
         <v>45995</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8993,7 +8993,7 @@
         <v>45995</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9066,7 +9066,7 @@
         <v>44777</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
         <v>45182</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9217,7 +9217,7 @@
         <v>44817</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9295,7 +9295,7 @@
         <v>46002</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9373,7 +9373,7 @@
         <v>45779</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9451,7 +9451,7 @@
         <v>45708</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9524,7 +9524,7 @@
         <v>45476</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9597,7 +9597,7 @@
         <v>45793</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         <v>45219</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9748,7 +9748,7 @@
         <v>46030</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9821,7 +9821,7 @@
         <v>44473</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9894,7 +9894,7 @@
         <v>45826</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9967,7 +9967,7 @@
         <v>45230</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10040,7 +10040,7 @@
         <v>45454</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10113,7 +10113,7 @@
         <v>45775</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10191,7 +10191,7 @@
         <v>45103</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10264,7 +10264,7 @@
         <v>46147</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10337,7 +10337,7 @@
         <v>46147</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>45033</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>45679</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10561,7 +10561,7 @@
         <v>45264</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>45833</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10707,7 +10707,7 @@
         <v>45835</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10785,7 +10785,7 @@
         <v>44588</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10863,7 +10863,7 @@
         <v>44909</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10941,7 +10941,7 @@
         <v>44483</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11014,7 +11014,7 @@
         <v>46164</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>45687</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11165,7 +11165,7 @@
         <v>45687</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11238,7 +11238,7 @@
         <v>45527</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11316,7 +11316,7 @@
         <v>45279</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11389,7 +11389,7 @@
         <v>46171</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11462,7 +11462,7 @@
         <v>46175</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11540,7 +11540,7 @@
         <v>46175</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
         <v>45393</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11696,7 +11696,7 @@
         <v>45456</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11769,7 +11769,7 @@
         <v>45239</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11842,7 +11842,7 @@
         <v>44987</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11915,7 +11915,7 @@
         <v>46185</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11993,7 +11993,7 @@
         <v>46185</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12071,7 +12071,7 @@
         <v>46041</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12144,7 +12144,7 @@
         <v>46185</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12222,7 +12222,7 @@
         <v>46185</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12300,7 +12300,7 @@
         <v>46184</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12378,7 +12378,7 @@
         <v>46185</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12456,7 +12456,7 @@
         <v>46185</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12534,7 +12534,7 @@
         <v>46189</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12612,7 +12612,7 @@
         <v>46188</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12685,7 +12685,7 @@
         <v>45125</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>45589</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12831,7 +12831,7 @@
         <v>44645</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12904,7 +12904,7 @@
         <v>44988</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12982,7 +12982,7 @@
         <v>45601</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13055,7 +13055,7 @@
         <v>45182</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13133,7 +13133,7 @@
         <v>45610</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13206,7 +13206,7 @@
         <v>45624</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13284,7 +13284,7 @@
         <v>44812</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13362,7 +13362,7 @@
         <v>45456</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13435,7 +13435,7 @@
         <v>46213</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13508,7 +13508,7 @@
         <v>44623</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13581,7 +13581,7 @@
         <v>46260</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13659,7 +13659,7 @@
         <v>45764</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13732,7 +13732,7 @@
         <v>44715</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13805,7 +13805,7 @@
         <v>45764</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13878,7 +13878,7 @@
         <v>46265</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13956,7 +13956,7 @@
         <v>45328</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
         <v>45328</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14102,7 +14102,7 @@
         <v>44768</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14180,7 +14180,7 @@
         <v>45237</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14253,7 +14253,7 @@
         <v>46268</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14331,7 +14331,7 @@
         <v>46273</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14404,7 +14404,7 @@
         <v>45736</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14477,7 +14477,7 @@
         <v>45728</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14550,7 +14550,7 @@
         <v>45278</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14623,7 +14623,7 @@
         <v>46280</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14701,7 +14701,7 @@
         <v>45303</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14774,7 +14774,7 @@
         <v>46280</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14852,7 +14852,7 @@
         <v>45610</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14925,7 +14925,7 @@
         <v>45302</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14998,7 +14998,7 @@
         <v>45593</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15071,7 +15071,7 @@
         <v>45531</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15144,7 +15144,7 @@
         <v>44979</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15217,7 +15217,7 @@
         <v>45601</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15290,7 +15290,7 @@
         <v>45618</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15363,7 +15363,7 @@
         <v>44467</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15436,7 +15436,7 @@
         <v>45708</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15509,7 +15509,7 @@
         <v>45614</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15582,7 +15582,7 @@
         <v>45148</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15660,7 +15660,7 @@
         <v>45196</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15733,7 +15733,7 @@
         <v>45614</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15806,7 +15806,7 @@
         <v>45633</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15879,7 +15879,7 @@
         <v>45196</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15952,7 +15952,7 @@
         <v>45610</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16025,7 +16025,7 @@
         <v>45414</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16098,7 +16098,7 @@
         <v>45257</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16171,7 +16171,7 @@
         <v>45161</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16249,7 +16249,7 @@
         <v>45321</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16327,7 +16327,7 @@
         <v>45791</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16400,7 +16400,7 @@
         <v>45953</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>

--- a/Översikt KARLSKOGA.xlsx
+++ b/Översikt KARLSKOGA.xlsx
@@ -601,7 +601,7 @@
         <v>45562</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>45958</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         <v>45989</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>44510</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>46100</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>45989</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>44473</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>46010</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>46010</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>46066</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>46010</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>44495</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>46127</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>46265</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         <v>45553</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>44817</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2518,7 +2518,7 @@
         <v>46280</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>44900</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>45478</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>46010</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>45953</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>46113</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>46127</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>46132</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>46145</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>46175</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         <v>45103</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>46213</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>46260</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>45555</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>44546</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>44732</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>44512</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>44715</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>44508</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         <v>44480</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>44811</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
         <v>44809</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4649,7 +4649,7 @@
         <v>44628</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
         <v>44809</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         <v>44706</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4873,7 +4873,7 @@
         <v>44706</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>44817</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>45712</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         <v>45531</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5170,7 +5170,7 @@
         <v>44817</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         <v>46013</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5316,7 +5316,7 @@
         <v>46014</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         <v>44894</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>45545</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         <v>46034</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5608,7 +5608,7 @@
         <v>45457</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5681,7 +5681,7 @@
         <v>45435</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         <v>46038</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5832,7 +5832,7 @@
         <v>45758</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>45545</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5983,7 +5983,7 @@
         <v>45923</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6061,7 +6061,7 @@
         <v>45586</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6139,7 +6139,7 @@
         <v>45362</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v>44588</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6290,7 +6290,7 @@
         <v>45744</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6368,7 +6368,7 @@
         <v>45918</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6441,7 +6441,7 @@
         <v>45918</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6514,7 +6514,7 @@
         <v>45182</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         <v>44720</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6660,7 +6660,7 @@
         <v>46073</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6733,7 +6733,7 @@
         <v>45531</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6806,7 +6806,7 @@
         <v>45531</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
         <v>45633</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6952,7 +6952,7 @@
         <v>46094</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7025,7 +7025,7 @@
         <v>45764</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7103,7 +7103,7 @@
         <v>45182</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7181,7 +7181,7 @@
         <v>46101</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7259,7 +7259,7 @@
         <v>45946</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7332,7 +7332,7 @@
         <v>46092</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7405,7 +7405,7 @@
         <v>46113</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7483,7 +7483,7 @@
         <v>46113</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7561,7 +7561,7 @@
         <v>46113</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         <v>45434</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
         <v>46104</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7785,7 +7785,7 @@
         <v>44981</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7858,7 +7858,7 @@
         <v>46122</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7936,7 +7936,7 @@
         <v>45967</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8009,7 +8009,7 @@
         <v>45813</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8082,7 +8082,7 @@
         <v>46130</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8160,7 +8160,7 @@
         <v>46130</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8238,7 +8238,7 @@
         <v>46130</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
         <v>46130</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8394,7 +8394,7 @@
         <v>46134</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8472,7 +8472,7 @@
         <v>45636</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8550,7 +8550,7 @@
         <v>45989</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8628,7 +8628,7 @@
         <v>45700</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8701,7 +8701,7 @@
         <v>45736</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8774,7 +8774,7 @@
         <v>45196</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8847,7 +8847,7 @@
         <v>45995</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8920,7 +8920,7 @@
         <v>45995</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8993,7 +8993,7 @@
         <v>45995</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9066,7 +9066,7 @@
         <v>44777</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
         <v>45182</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9217,7 +9217,7 @@
         <v>44817</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9295,7 +9295,7 @@
         <v>46002</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9373,7 +9373,7 @@
         <v>45779</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9451,7 +9451,7 @@
         <v>45708</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9524,7 +9524,7 @@
         <v>45476</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9597,7 +9597,7 @@
         <v>45793</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         <v>45219</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9748,7 +9748,7 @@
         <v>46030</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9821,7 +9821,7 @@
         <v>44473</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9894,7 +9894,7 @@
         <v>45826</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9967,7 +9967,7 @@
         <v>45230</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10040,7 +10040,7 @@
         <v>45454</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10113,7 +10113,7 @@
         <v>45775</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10191,7 +10191,7 @@
         <v>45103</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10264,7 +10264,7 @@
         <v>46147</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10337,7 +10337,7 @@
         <v>46147</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>45033</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>45679</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10561,7 +10561,7 @@
         <v>45264</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>45833</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10707,7 +10707,7 @@
         <v>45835</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10785,7 +10785,7 @@
         <v>44588</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10863,7 +10863,7 @@
         <v>44909</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10941,7 +10941,7 @@
         <v>44483</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11014,7 +11014,7 @@
         <v>46164</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>45687</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11165,7 +11165,7 @@
         <v>45687</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11238,7 +11238,7 @@
         <v>45527</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11316,7 +11316,7 @@
         <v>45279</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11389,7 +11389,7 @@
         <v>46171</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11462,7 +11462,7 @@
         <v>46175</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11540,7 +11540,7 @@
         <v>46175</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
         <v>45393</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11696,7 +11696,7 @@
         <v>45456</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11769,7 +11769,7 @@
         <v>45239</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11842,7 +11842,7 @@
         <v>44987</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11915,7 +11915,7 @@
         <v>46185</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11993,7 +11993,7 @@
         <v>46185</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12071,7 +12071,7 @@
         <v>46041</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12144,7 +12144,7 @@
         <v>46185</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12222,7 +12222,7 @@
         <v>46185</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12300,7 +12300,7 @@
         <v>46184</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12378,7 +12378,7 @@
         <v>46185</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12456,7 +12456,7 @@
         <v>46185</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12534,7 +12534,7 @@
         <v>46189</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12612,7 +12612,7 @@
         <v>46188</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12685,7 +12685,7 @@
         <v>45125</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>45589</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12831,7 +12831,7 @@
         <v>44645</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12904,7 +12904,7 @@
         <v>44988</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12982,7 +12982,7 @@
         <v>45601</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13055,7 +13055,7 @@
         <v>45182</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13133,7 +13133,7 @@
         <v>45610</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13206,7 +13206,7 @@
         <v>45624</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13284,7 +13284,7 @@
         <v>44812</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13362,7 +13362,7 @@
         <v>45456</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13435,7 +13435,7 @@
         <v>46213</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13508,7 +13508,7 @@
         <v>44623</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13581,7 +13581,7 @@
         <v>46260</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13659,7 +13659,7 @@
         <v>45764</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13732,7 +13732,7 @@
         <v>44715</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13805,7 +13805,7 @@
         <v>45764</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13878,7 +13878,7 @@
         <v>46265</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13956,7 +13956,7 @@
         <v>45328</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
         <v>45328</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14102,7 +14102,7 @@
         <v>44768</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14180,7 +14180,7 @@
         <v>45237</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14253,7 +14253,7 @@
         <v>46268</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14331,7 +14331,7 @@
         <v>46273</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14404,7 +14404,7 @@
         <v>45736</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14477,7 +14477,7 @@
         <v>45728</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14550,7 +14550,7 @@
         <v>45278</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14623,7 +14623,7 @@
         <v>46280</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14701,7 +14701,7 @@
         <v>45303</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14774,7 +14774,7 @@
         <v>46280</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14852,7 +14852,7 @@
         <v>45610</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14925,7 +14925,7 @@
         <v>45302</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14998,7 +14998,7 @@
         <v>45593</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15071,7 +15071,7 @@
         <v>45531</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15144,7 +15144,7 @@
         <v>44979</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15217,7 +15217,7 @@
         <v>45601</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15290,7 +15290,7 @@
         <v>45618</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15363,7 +15363,7 @@
         <v>44467</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15436,7 +15436,7 @@
         <v>45708</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15509,7 +15509,7 @@
         <v>45614</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15582,7 +15582,7 @@
         <v>45148</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15660,7 +15660,7 @@
         <v>45196</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15733,7 +15733,7 @@
         <v>45614</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15806,7 +15806,7 @@
         <v>45633</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15879,7 +15879,7 @@
         <v>45196</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15952,7 +15952,7 @@
         <v>45610</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16025,7 +16025,7 @@
         <v>45414</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16098,7 +16098,7 @@
         <v>45257</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16171,7 +16171,7 @@
         <v>45161</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16249,7 +16249,7 @@
         <v>45321</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16327,7 +16327,7 @@
         <v>45791</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16400,7 +16400,7 @@
         <v>45953</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>

--- a/Översikt KARLSKOGA.xlsx
+++ b/Översikt KARLSKOGA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE197"/>
+  <dimension ref="A1:AE196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45562</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>45958</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         <v>45989</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>44510</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>46100</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>45989</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>44473</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>46010</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>46010</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>46066</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>46010</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>44495</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>46127</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>46265</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 39936-2024</t>
+          <t>A 39025-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45553</v>
+        <v>44817</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2309,11 +2309,16 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>6.4</v>
+        <v>3.2</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -2343,158 +2348,153 @@
         <v>2</v>
       </c>
       <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Talltita
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 39025-2022 artfynd.xlsx", "A 39025-2022")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 39025-2022 karta.png", "A 39025-2022")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 39025-2022 georefererad karta.tif", "A 39025-2022")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 39025-2022 FSC-klagomål.docx", "A 39025-2022")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 39025-2022 FSC-klagomål mail.docx", "A 39025-2022")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 39025-2022 tillsynsbegäran.docx", "A 39025-2022")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 39025-2022 tillsynsbegäran mail.docx", "A 39025-2022")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 39025-2022 prioriterade fågelarter.docx", "A 39025-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 39936-2024</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45553</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>KARLSKOGA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
         <v>3</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U17" t="n">
         <v>1</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Storgröe
 Utter</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 39936-2024 artfynd.xlsx", "A 39936-2024")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 39936-2024 karta.png", "A 39936-2024")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 39936-2024 georefererad karta.tif", "A 39936-2024")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 39936-2024 FSC-klagomål.docx", "A 39936-2024")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 39936-2024 FSC-klagomål mail.docx", "A 39936-2024")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 39936-2024 tillsynsbegäran.docx", "A 39936-2024")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 39936-2024 tillsynsbegäran mail.docx", "A 39936-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 39025-2022</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>44817</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>KARLSKOGA</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Talltita
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 39025-2022 artfynd.xlsx", "A 39025-2022")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 39025-2022 karta.png", "A 39025-2022")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 39025-2022 georefererad karta.tif", "A 39025-2022")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 39025-2022 FSC-klagomål.docx", "A 39025-2022")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 39025-2022 FSC-klagomål mail.docx", "A 39025-2022")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 39025-2022 tillsynsbegäran.docx", "A 39025-2022")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 39025-2022 tillsynsbegäran mail.docx", "A 39025-2022")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 39025-2022 prioriterade fågelarter.docx", "A 39025-2022")</f>
         <v/>
       </c>
     </row>
@@ -2518,7 +2518,7 @@
         <v>46280</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 58091-2022</t>
+          <t>A 52377-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2630,10 +2630,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44900</v>
+        <v>45953</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2684,49 +2684,49 @@
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Hårklomossa</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 58091-2022 artfynd.xlsx", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 52377-2025 artfynd.xlsx", "A 52377-2025")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 58091-2022 karta.png", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 52377-2025 karta.png", "A 52377-2025")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 58091-2022 georefererad karta.tif", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 52377-2025 georefererad karta.tif", "A 52377-2025")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 58091-2022 FSC-klagomål.docx", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 52377-2025 FSC-klagomål.docx", "A 52377-2025")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 58091-2022 FSC-klagomål mail.docx", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 52377-2025 FSC-klagomål mail.docx", "A 52377-2025")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 58091-2022 tillsynsbegäran.docx", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 52377-2025 tillsynsbegäran.docx", "A 52377-2025")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 58091-2022 tillsynsbegäran mail.docx", "A 58091-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 52377-2025 tillsynsbegäran mail.docx", "A 52377-2025")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 28566-2024</t>
+          <t>A 63188-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2740,10 +2740,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45478</v>
+        <v>46010</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2755,8 +2755,13 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2765,7 +2770,7 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2780,7 +2785,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2789,49 +2794,53 @@
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 28566-2024 artfynd.xlsx", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 63188-2025 artfynd.xlsx", "A 63188-2025")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 28566-2024 karta.png", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 63188-2025 karta.png", "A 63188-2025")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 28566-2024 georefererad karta.tif", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 63188-2025 georefererad karta.tif", "A 63188-2025")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 28566-2024 FSC-klagomål.docx", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 63188-2025 FSC-klagomål.docx", "A 63188-2025")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 28566-2024 FSC-klagomål mail.docx", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 63188-2025 FSC-klagomål mail.docx", "A 63188-2025")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 28566-2024 tillsynsbegäran.docx", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 63188-2025 tillsynsbegäran.docx", "A 63188-2025")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 28566-2024 tillsynsbegäran mail.docx", "A 28566-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 63188-2025 tillsynsbegäran mail.docx", "A 63188-2025")</f>
+        <v/>
+      </c>
+      <c r="AE20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 63188-2025 prioriterade fågelarter.docx", "A 63188-2025")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 63188-2025</t>
+          <t>A 16784-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2845,10 +2854,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46010</v>
+        <v>46113</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2866,7 +2875,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.1</v>
+        <v>4.2</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2875,7 +2884,7 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2890,7 +2899,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2902,50 +2911,46 @@
         <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Hårklomossa</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 63188-2025 artfynd.xlsx", "A 63188-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 16784-2026 artfynd.xlsx", "A 16784-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 63188-2025 karta.png", "A 63188-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 16784-2026 karta.png", "A 16784-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 63188-2025 georefererad karta.tif", "A 63188-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 16784-2026 georefererad karta.tif", "A 16784-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 63188-2025 FSC-klagomål.docx", "A 63188-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 16784-2026 FSC-klagomål.docx", "A 16784-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 63188-2025 FSC-klagomål mail.docx", "A 63188-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 16784-2026 FSC-klagomål mail.docx", "A 16784-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 63188-2025 tillsynsbegäran.docx", "A 63188-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 16784-2026 tillsynsbegäran.docx", "A 16784-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 63188-2025 tillsynsbegäran mail.docx", "A 63188-2025")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 63188-2025 prioriterade fågelarter.docx", "A 63188-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 16784-2026 tillsynsbegäran mail.docx", "A 16784-2026")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 52377-2025</t>
+          <t>A 18427-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2959,10 +2964,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45953</v>
+        <v>46127</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2980,7 +2985,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -3020,42 +3025,46 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 52377-2025 artfynd.xlsx", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 18427-2026 artfynd.xlsx", "A 18427-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 52377-2025 karta.png", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 18427-2026 karta.png", "A 18427-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 52377-2025 georefererad karta.tif", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 18427-2026 georefererad karta.tif", "A 18427-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 52377-2025 FSC-klagomål.docx", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 18427-2026 FSC-klagomål.docx", "A 18427-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 52377-2025 FSC-klagomål mail.docx", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 18427-2026 FSC-klagomål mail.docx", "A 18427-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 52377-2025 tillsynsbegäran.docx", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 18427-2026 tillsynsbegäran.docx", "A 18427-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 52377-2025 tillsynsbegäran mail.docx", "A 52377-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 18427-2026 tillsynsbegäran mail.docx", "A 18427-2026")</f>
+        <v/>
+      </c>
+      <c r="AE22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 18427-2026 prioriterade fågelarter.docx", "A 18427-2026")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 16784-2026</t>
+          <t>A 19233-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3069,10 +3078,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46113</v>
+        <v>46132</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3084,19 +3093,14 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>4.2</v>
+        <v>1.6</v>
       </c>
       <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
         <v>1</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -3123,49 +3127,49 @@
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Hårklomossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 16784-2026 artfynd.xlsx", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 19233-2026 artfynd.xlsx", "A 19233-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 16784-2026 karta.png", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 19233-2026 karta.png", "A 19233-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 16784-2026 georefererad karta.tif", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 19233-2026 georefererad karta.tif", "A 19233-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 16784-2026 FSC-klagomål.docx", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 19233-2026 FSC-klagomål.docx", "A 19233-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 16784-2026 FSC-klagomål mail.docx", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 19233-2026 FSC-klagomål mail.docx", "A 19233-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 16784-2026 tillsynsbegäran.docx", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 19233-2026 tillsynsbegäran.docx", "A 19233-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 16784-2026 tillsynsbegäran mail.docx", "A 16784-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 19233-2026 tillsynsbegäran mail.docx", "A 19233-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 18427-2026</t>
+          <t>A 21019-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3179,10 +3183,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46127</v>
+        <v>46145</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3200,7 +3204,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3</v>
+        <v>4.7</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3236,50 +3240,46 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 18427-2026 artfynd.xlsx", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 21019-2026 artfynd.xlsx", "A 21019-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 18427-2026 karta.png", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 21019-2026 karta.png", "A 21019-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 18427-2026 georefererad karta.tif", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 21019-2026 georefererad karta.tif", "A 21019-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 18427-2026 FSC-klagomål.docx", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 21019-2026 FSC-klagomål.docx", "A 21019-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 18427-2026 FSC-klagomål mail.docx", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 21019-2026 FSC-klagomål mail.docx", "A 21019-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 18427-2026 tillsynsbegäran.docx", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 21019-2026 tillsynsbegäran.docx", "A 21019-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 18427-2026 tillsynsbegäran mail.docx", "A 18427-2026")</f>
-        <v/>
-      </c>
-      <c r="AE24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 18427-2026 prioriterade fågelarter.docx", "A 18427-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 21019-2026 tillsynsbegäran mail.docx", "A 21019-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 19233-2026</t>
+          <t>A 28474-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3293,10 +3293,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46132</v>
+        <v>45103</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3309,17 +3309,17 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.6</v>
+        <v>5.1</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
         <v>1</v>
       </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
@@ -3333,7 +3333,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3345,46 +3345,50 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåhake</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 19233-2026 artfynd.xlsx", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 28474-2023 artfynd.xlsx", "A 28474-2023")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 19233-2026 karta.png", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 28474-2023 karta.png", "A 28474-2023")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 19233-2026 georefererad karta.tif", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 28474-2023 georefererad karta.tif", "A 28474-2023")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 19233-2026 FSC-klagomål.docx", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 28474-2023 FSC-klagomål.docx", "A 28474-2023")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 19233-2026 FSC-klagomål mail.docx", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 28474-2023 FSC-klagomål mail.docx", "A 28474-2023")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 19233-2026 tillsynsbegäran.docx", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 28474-2023 tillsynsbegäran.docx", "A 28474-2023")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 19233-2026 tillsynsbegäran mail.docx", "A 19233-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 28474-2023 tillsynsbegäran mail.docx", "A 28474-2023")</f>
+        <v/>
+      </c>
+      <c r="AE25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/fåglar/A 28474-2023 prioriterade fågelarter.docx", "A 28474-2023")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 21019-2026</t>
+          <t>A 58091-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3398,10 +3402,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46145</v>
+        <v>44900</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3419,7 +3423,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>4.7</v>
+        <v>2.1</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3452,49 +3456,49 @@
         <v>1</v>
       </c>
       <c r="T26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Hårklomossa</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 21019-2026 artfynd.xlsx", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 58091-2022 artfynd.xlsx", "A 58091-2022")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 21019-2026 karta.png", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 58091-2022 karta.png", "A 58091-2022")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 21019-2026 georefererad karta.tif", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 58091-2022 georefererad karta.tif", "A 58091-2022")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 21019-2026 FSC-klagomål.docx", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 58091-2022 FSC-klagomål.docx", "A 58091-2022")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 21019-2026 FSC-klagomål mail.docx", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 58091-2022 FSC-klagomål mail.docx", "A 58091-2022")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 21019-2026 tillsynsbegäran.docx", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 58091-2022 tillsynsbegäran.docx", "A 58091-2022")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 21019-2026 tillsynsbegäran mail.docx", "A 21019-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 58091-2022 tillsynsbegäran mail.docx", "A 58091-2022")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 25093-2026</t>
+          <t>A 28566-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3508,10 +3512,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46175</v>
+        <v>45478</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3523,19 +3527,14 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3569,42 +3568,42 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 25093-2026 artfynd.xlsx", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 28566-2024 artfynd.xlsx", "A 28566-2024")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 25093-2026 karta.png", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 28566-2024 karta.png", "A 28566-2024")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 25093-2026 georefererad karta.tif", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 28566-2024 georefererad karta.tif", "A 28566-2024")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 25093-2026 FSC-klagomål.docx", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomål/A 28566-2024 FSC-klagomål.docx", "A 28566-2024")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 25093-2026 FSC-klagomål mail.docx", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/klagomålsmail/A 28566-2024 FSC-klagomål mail.docx", "A 28566-2024")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 25093-2026 tillsynsbegäran.docx", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsyn/A 28566-2024 tillsynsbegäran.docx", "A 28566-2024")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 25093-2026 tillsynsbegäran mail.docx", "A 25093-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/tillsynsmail/A 28566-2024 tillsynsbegäran mail.docx", "A 28566-2024")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 28474-2023</t>
+          <t>A 25093-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3618,10 +3617,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45103</v>
+        <v>46175</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3633,17 +3632,22 @@
           <t>KARLSKOGA</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>5.1</v>
+        <v>4</v>
       </c>
       <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
         <v>1</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
       <c r="L28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -3658,7 +3662,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -3674,39 +3678,35 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Blåhake</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 28474-2023 artfynd.xlsx", "A 28474-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/artfynd/A 25093-2026 artfynd.xlsx", "A 25093-2026")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 28474-2023 karta.png", "A 28474-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor/A 25093-2026 karta.png", "A 25093-2026")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 28474-2023 georefererad karta.tif", "A 28474-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1883/kartor_geotiff/A 25093-2026 georefererad karta.tif", "A 25093-2026")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_